--- a/Log/Magic_eraser_test_log.xlsx
+++ b/Log/Magic_eraser_test_log.xlsx
@@ -4,12 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16340" firstSheet="2" activeTab="1"/>
+    <workbookView windowHeight="16340" firstSheet="2" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Image_selector_test" sheetId="1" r:id="rId1"/>
     <sheet name="Load_memory_output_test" sheetId="2" r:id="rId2"/>
     <sheet name="Home_screen_Remove_background" sheetId="3" r:id="rId3"/>
+    <sheet name="Force_update" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="858" uniqueCount="355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="887" uniqueCount="376">
   <si>
     <t>TC</t>
   </si>
@@ -1101,6 +1102,73 @@
   </si>
   <si>
     <t>Test hiệu năng</t>
+  </si>
+  <si>
+    <t>Steps</t>
+  </si>
+  <si>
+    <t>Desire output</t>
+  </si>
+  <si>
+    <t>State</t>
+  </si>
+  <si>
+    <t>Eviroment:
+OS: Android
+version: 2.23.24,
+Test trên 2 device: redmi 14C, pixels Fold (SDK 36.0)</t>
+  </si>
+  <si>
+    <t>FU01</t>
+  </si>
+  <si>
+    <t>Ở màn hình điện thoại, App chưa mở lần nào, phiên bản hiện tại là 2.23.24, máy không có kết nối mạng</t>
+  </si>
+  <si>
+    <t>Mở app</t>
+  </si>
+  <si>
+    <t>App vào màn hình Home với phiên bản hiện tại</t>
+  </si>
+  <si>
+    <t>PASS</t>
+  </si>
+  <si>
+    <t>fetch failed</t>
+  </si>
+  <si>
+    <t>FU02</t>
+  </si>
+  <si>
+    <t>Ở màn hình điện thoại, App chưa được mở, phiên bản hiện tại là 2.23.24, chưa skip update
+server hiện đang trả về: { "latest_version": "3.0.0", "min_supported_version": "0.0.0" }</t>
+  </si>
+  <si>
+    <t>App hiện lên dialog optional update (đúng giữa màn hình)</t>
+  </si>
+  <si>
+    <t>latest_version &lt; curent_version &lt; min_supported_version</t>
+  </si>
+  <si>
+    <t>FU03</t>
+  </si>
+  <si>
+    <t>Ở màn "Home", đang có dialog optional update</t>
+  </si>
+  <si>
+    <t>Chọn Update</t>
+  </si>
+  <si>
+    <t>Chuyển vào trang của app trên store</t>
+  </si>
+  <si>
+    <t>FU04</t>
+  </si>
+  <si>
+    <t>Chọn Later</t>
+  </si>
+  <si>
+    <t>Ẩn dialog, trở về màn "Home"</t>
   </si>
 </sst>
 </file>
@@ -1864,9 +1932,21 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2473,1292 +2553,1292 @@
   <dimension ref="A1:L61"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="1" width="4" style="9" customWidth="1"/>
-    <col min="2" max="2" width="31.2890625" style="10" customWidth="1"/>
-    <col min="3" max="3" width="21.7109375" style="10" customWidth="1"/>
-    <col min="4" max="5" width="24.4296875" style="10" customWidth="1"/>
-    <col min="6" max="6" width="30.2890625" style="10" customWidth="1"/>
-    <col min="7" max="7" width="20.140625" style="10" customWidth="1"/>
-    <col min="8" max="8" width="9.140625" style="4"/>
-    <col min="9" max="9" width="17.7109375" style="4" customWidth="1"/>
-    <col min="10" max="16384" width="9.140625" style="4"/>
+    <col min="1" max="1" width="4" style="13" customWidth="1"/>
+    <col min="2" max="2" width="31.2890625" style="14" customWidth="1"/>
+    <col min="3" max="3" width="21.7109375" style="14" customWidth="1"/>
+    <col min="4" max="5" width="24.4296875" style="14" customWidth="1"/>
+    <col min="6" max="6" width="30.2890625" style="14" customWidth="1"/>
+    <col min="7" max="7" width="20.140625" style="14" customWidth="1"/>
+    <col min="8" max="8" width="9.140625" style="8"/>
+    <col min="9" max="9" width="17.7109375" style="8" customWidth="1"/>
+    <col min="10" max="16384" width="9.140625" style="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="17.75" spans="1:7">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="21" t="s">
+      <c r="B1" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="21" t="s">
+      <c r="C1" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="21" t="s">
+      <c r="D1" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="21" t="s">
+      <c r="E1" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="21" t="s">
+      <c r="F1" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="23" t="s">
+      <c r="G1" s="27" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" ht="37" customHeight="1" spans="1:12">
-      <c r="A2" s="19">
+      <c r="A2" s="23">
         <v>1</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="22" t="s">
+      <c r="C2" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="22" t="s">
+      <c r="D2" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="22" t="s">
+      <c r="E2" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="22" t="s">
+      <c r="F2" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="22"/>
-      <c r="I2" s="3" t="s">
+      <c r="G2" s="26"/>
+      <c r="I2" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="K2" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="L2" s="3"/>
+      <c r="L2" s="7"/>
     </row>
     <row r="3" ht="34" spans="1:12">
-      <c r="A3" s="9">
+      <c r="A3" s="13">
         <v>2</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="F3" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="I3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
+      <c r="I3" s="7"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="7"/>
     </row>
     <row r="4" ht="34" spans="1:12">
-      <c r="A4" s="9">
+      <c r="A4" s="13">
         <v>3</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F4" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="I4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
+      <c r="I4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="7"/>
     </row>
     <row r="5" ht="34" spans="1:12">
-      <c r="A5" s="9">
+      <c r="A5" s="13">
         <v>4</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="10" t="s">
+      <c r="E5" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="F5" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="I5" s="3"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
+      <c r="I5" s="7"/>
+      <c r="K5" s="7"/>
+      <c r="L5" s="7"/>
     </row>
     <row r="6" ht="34" spans="1:12">
-      <c r="A6" s="9">
+      <c r="A6" s="13">
         <v>5</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="D6" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="E6" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="10" t="s">
+      <c r="F6" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="7"/>
     </row>
     <row r="7" ht="17" spans="1:6">
-      <c r="A7" s="9">
+      <c r="A7" s="13">
         <v>6</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="10" t="s">
+      <c r="E7" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="F7" s="10" t="s">
+      <c r="F7" s="14" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="8" ht="50" customHeight="1" spans="1:6">
-      <c r="A8" s="9">
+      <c r="A8" s="13">
         <v>7</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="D8" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="E8" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="10" t="s">
+      <c r="F8" s="14" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="9" ht="34" spans="1:6">
-      <c r="A9" s="9">
+      <c r="A9" s="13">
         <v>8</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="D9" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="10" t="s">
+      <c r="E9" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="F9" s="10" t="s">
+      <c r="F9" s="14" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="10" ht="34" spans="1:6">
-      <c r="A10" s="9">
+      <c r="A10" s="13">
         <v>9</v>
       </c>
-      <c r="B10" s="10" t="s">
+      <c r="B10" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="D10" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E10" s="10" t="s">
+      <c r="E10" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="F10" s="10" t="s">
+      <c r="F10" s="14" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="11" ht="34" spans="1:6">
-      <c r="A11" s="9">
+      <c r="A11" s="13">
         <v>10</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="D11" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E11" s="10" t="s">
+      <c r="E11" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="F11" s="10" t="s">
+      <c r="F11" s="14" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="12" ht="34" spans="1:6">
-      <c r="A12" s="9">
+      <c r="A12" s="13">
         <v>11</v>
       </c>
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="10" t="s">
+      <c r="D12" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E12" s="10" t="s">
+      <c r="E12" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="F12" s="10" t="s">
+      <c r="F12" s="14" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="13" ht="34" spans="1:6">
-      <c r="A13" s="9">
+      <c r="A13" s="13">
         <v>12</v>
       </c>
-      <c r="B13" s="10" t="s">
+      <c r="B13" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="C13" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="D13" s="10" t="s">
+      <c r="D13" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E13" s="10" t="s">
+      <c r="E13" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="F13" s="10" t="s">
+      <c r="F13" s="14" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="14" ht="51" spans="1:6">
-      <c r="A14" s="9">
+      <c r="A14" s="13">
         <v>13</v>
       </c>
-      <c r="B14" s="10" t="s">
+      <c r="B14" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="10" t="s">
+      <c r="C14" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="D14" s="10" t="s">
+      <c r="D14" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E14" s="10" t="s">
+      <c r="E14" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="F14" s="10" t="s">
+      <c r="F14" s="14" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="15" ht="34" spans="1:6">
-      <c r="A15" s="9">
+      <c r="A15" s="13">
         <v>14</v>
       </c>
-      <c r="B15" s="10" t="s">
+      <c r="B15" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="C15" s="10" t="s">
+      <c r="C15" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="D15" s="10" t="s">
+      <c r="D15" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E15" s="10" t="s">
+      <c r="E15" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="F15" s="10" t="s">
+      <c r="F15" s="14" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="16" ht="34" spans="1:6">
-      <c r="A16" s="9">
+      <c r="A16" s="13">
         <v>15</v>
       </c>
-      <c r="B16" s="10" t="s">
+      <c r="B16" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="C16" s="10" t="s">
+      <c r="C16" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="D16" s="10" t="s">
+      <c r="D16" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E16" s="10" t="s">
+      <c r="E16" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="F16" s="10" t="s">
+      <c r="F16" s="14" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="17" ht="34" spans="1:6">
-      <c r="A17" s="9">
+      <c r="A17" s="13">
         <v>16</v>
       </c>
-      <c r="B17" s="10" t="s">
+      <c r="B17" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="C17" s="10" t="s">
+      <c r="C17" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="D17" s="10" t="s">
+      <c r="D17" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E17" s="10" t="s">
+      <c r="E17" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="F17" s="10" t="s">
+      <c r="F17" s="14" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="18" ht="34" spans="1:6">
-      <c r="A18" s="9">
+      <c r="A18" s="13">
         <v>17</v>
       </c>
-      <c r="B18" s="10" t="s">
+      <c r="B18" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="C18" s="10" t="s">
+      <c r="C18" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="D18" s="10" t="s">
+      <c r="D18" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E18" s="10" t="s">
+      <c r="E18" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="F18" s="10" t="s">
+      <c r="F18" s="14" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="19" ht="34" spans="1:6">
-      <c r="A19" s="9">
+      <c r="A19" s="13">
         <v>18</v>
       </c>
-      <c r="B19" s="10" t="s">
+      <c r="B19" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="C19" s="10" t="s">
+      <c r="C19" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="D19" s="10" t="s">
+      <c r="D19" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E19" s="10" t="s">
+      <c r="E19" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="F19" s="10" t="s">
+      <c r="F19" s="14" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="20" ht="51" spans="1:6">
-      <c r="A20" s="9">
+      <c r="A20" s="13">
         <v>19</v>
       </c>
-      <c r="B20" s="10" t="s">
+      <c r="B20" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="C20" s="10" t="s">
+      <c r="C20" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="D20" s="10" t="s">
+      <c r="D20" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E20" s="10" t="s">
+      <c r="E20" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="F20" s="10" t="s">
+      <c r="F20" s="14" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="21" ht="34" spans="1:6">
-      <c r="A21" s="9">
+      <c r="A21" s="13">
         <v>20</v>
       </c>
-      <c r="B21" s="10" t="s">
+      <c r="B21" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="C21" s="10" t="s">
+      <c r="C21" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="D21" s="10" t="s">
+      <c r="D21" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E21" s="10" t="s">
+      <c r="E21" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="F21" s="10" t="s">
+      <c r="F21" s="14" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="22" ht="34" spans="1:6">
-      <c r="A22" s="9">
+      <c r="A22" s="13">
         <v>21</v>
       </c>
-      <c r="B22" s="10" t="s">
+      <c r="B22" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="C22" s="10" t="s">
+      <c r="C22" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="D22" s="10" t="s">
+      <c r="D22" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E22" s="10" t="s">
+      <c r="E22" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="F22" s="10" t="s">
+      <c r="F22" s="14" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="23" ht="34" spans="1:6">
-      <c r="A23" s="9">
+      <c r="A23" s="13">
         <v>22</v>
       </c>
-      <c r="B23" s="10" t="s">
+      <c r="B23" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="C23" s="10" t="s">
+      <c r="C23" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="D23" s="10" t="s">
+      <c r="D23" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E23" s="10" t="s">
+      <c r="E23" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="F23" s="10" t="s">
+      <c r="F23" s="14" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="24" ht="34" spans="1:6">
-      <c r="A24" s="9">
+      <c r="A24" s="13">
         <v>23</v>
       </c>
-      <c r="B24" s="10" t="s">
+      <c r="B24" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="C24" s="10" t="s">
+      <c r="C24" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="D24" s="10" t="s">
+      <c r="D24" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E24" s="10" t="s">
+      <c r="E24" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="F24" s="10" t="s">
+      <c r="F24" s="14" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="25" ht="34" spans="1:6">
-      <c r="A25" s="9">
+      <c r="A25" s="13">
         <v>24</v>
       </c>
-      <c r="B25" s="10" t="s">
+      <c r="B25" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="C25" s="10" t="s">
+      <c r="C25" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="D25" s="10" t="s">
+      <c r="D25" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E25" s="10" t="s">
+      <c r="E25" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="F25" s="10" t="s">
+      <c r="F25" s="14" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="26" ht="34" spans="1:6">
-      <c r="A26" s="9">
+      <c r="A26" s="13">
         <v>25</v>
       </c>
-      <c r="B26" s="10" t="s">
+      <c r="B26" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="C26" s="10" t="s">
+      <c r="C26" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="D26" s="10" t="s">
+      <c r="D26" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E26" s="10" t="s">
+      <c r="E26" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="F26" s="10" t="s">
+      <c r="F26" s="14" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="27" ht="51" spans="1:6">
-      <c r="A27" s="9">
+      <c r="A27" s="13">
         <v>26</v>
       </c>
-      <c r="B27" s="10" t="s">
+      <c r="B27" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="C27" s="10" t="s">
+      <c r="C27" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="D27" s="10" t="s">
+      <c r="D27" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E27" s="10" t="s">
+      <c r="E27" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="F27" s="10" t="s">
+      <c r="F27" s="14" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="28" ht="51" spans="1:6">
-      <c r="A28" s="9">
+      <c r="A28" s="13">
         <v>27</v>
       </c>
-      <c r="B28" s="10" t="s">
+      <c r="B28" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="C28" s="10" t="s">
+      <c r="C28" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="D28" s="10" t="s">
+      <c r="D28" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E28" s="10" t="s">
+      <c r="E28" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="F28" s="10" t="s">
+      <c r="F28" s="14" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="29" ht="51" spans="1:6">
-      <c r="A29" s="9">
+      <c r="A29" s="13">
         <v>28</v>
       </c>
-      <c r="B29" s="10" t="s">
+      <c r="B29" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="C29" s="10" t="s">
+      <c r="C29" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="D29" s="10" t="s">
+      <c r="D29" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E29" s="10" t="s">
+      <c r="E29" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="F29" s="10" t="s">
+      <c r="F29" s="14" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="30" ht="51" spans="1:6">
-      <c r="A30" s="9">
+      <c r="A30" s="13">
         <v>29</v>
       </c>
-      <c r="B30" s="10" t="s">
+      <c r="B30" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="C30" s="10" t="s">
+      <c r="C30" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="D30" s="10" t="s">
+      <c r="D30" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E30" s="10" t="s">
+      <c r="E30" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="F30" s="10" t="s">
+      <c r="F30" s="14" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="31" ht="51" spans="1:6">
-      <c r="A31" s="9">
+      <c r="A31" s="13">
         <v>30</v>
       </c>
-      <c r="B31" s="10" t="s">
+      <c r="B31" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="C31" s="10" t="s">
+      <c r="C31" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="D31" s="10" t="s">
+      <c r="D31" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="E31" s="10" t="s">
+      <c r="E31" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="F31" s="10" t="s">
+      <c r="F31" s="14" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="32" ht="51" spans="1:6">
-      <c r="A32" s="9">
+      <c r="A32" s="13">
         <v>31</v>
       </c>
-      <c r="B32" s="10" t="s">
+      <c r="B32" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="C32" s="10" t="s">
+      <c r="C32" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="D32" s="10" t="s">
+      <c r="D32" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="E32" s="10" t="s">
+      <c r="E32" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="F32" s="10" t="s">
+      <c r="F32" s="14" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="33" ht="51" spans="1:6">
-      <c r="A33" s="9">
+      <c r="A33" s="13">
         <v>32</v>
       </c>
-      <c r="B33" s="10" t="s">
+      <c r="B33" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="C33" s="10" t="s">
+      <c r="C33" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="D33" s="10" t="s">
+      <c r="D33" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="E33" s="10" t="s">
+      <c r="E33" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="F33" s="10" t="s">
+      <c r="F33" s="14" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="34" ht="51" spans="1:6">
-      <c r="A34" s="9">
+      <c r="A34" s="13">
         <v>33</v>
       </c>
-      <c r="B34" s="10" t="s">
+      <c r="B34" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="C34" s="10" t="s">
+      <c r="C34" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="D34" s="10" t="s">
+      <c r="D34" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="E34" s="10" t="s">
+      <c r="E34" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="F34" s="10" t="s">
+      <c r="F34" s="14" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="35" ht="34" spans="1:6">
-      <c r="A35" s="9">
+      <c r="A35" s="13">
         <v>34</v>
       </c>
-      <c r="B35" s="10" t="s">
+      <c r="B35" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="C35" s="10" t="s">
+      <c r="C35" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="D35" s="10" t="s">
+      <c r="D35" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E35" s="10" t="s">
+      <c r="E35" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="F35" s="10" t="s">
+      <c r="F35" s="14" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="36" ht="51" spans="1:7">
-      <c r="A36" s="9">
+      <c r="A36" s="13">
         <v>35</v>
       </c>
-      <c r="B36" s="10" t="s">
+      <c r="B36" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="C36" s="10" t="s">
+      <c r="C36" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="D36" s="10" t="s">
+      <c r="D36" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E36" s="10" t="s">
+      <c r="E36" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="F36" s="10" t="s">
+      <c r="F36" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="G36" s="9" t="s">
+      <c r="G36" s="13" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="37" ht="101" spans="1:7">
-      <c r="A37" s="9">
+      <c r="A37" s="13">
         <v>36</v>
       </c>
-      <c r="B37" s="10" t="s">
+      <c r="B37" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="C37" s="10" t="s">
+      <c r="C37" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="D37" s="10" t="s">
+      <c r="D37" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E37" s="10" t="s">
+      <c r="E37" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="F37" s="10" t="s">
+      <c r="F37" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="G37" s="9"/>
+      <c r="G37" s="13"/>
     </row>
     <row r="38" ht="101" spans="1:7">
-      <c r="A38" s="9">
+      <c r="A38" s="13">
         <v>37</v>
       </c>
-      <c r="B38" s="10" t="s">
+      <c r="B38" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="C38" s="10" t="s">
+      <c r="C38" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="D38" s="10" t="s">
+      <c r="D38" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E38" s="10" t="s">
+      <c r="E38" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="F38" s="10" t="s">
+      <c r="F38" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="G38" s="9"/>
+      <c r="G38" s="13"/>
     </row>
     <row r="39" ht="118" spans="1:7">
-      <c r="A39" s="9">
+      <c r="A39" s="13">
         <v>38</v>
       </c>
-      <c r="B39" s="10" t="s">
+      <c r="B39" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="C39" s="10" t="s">
+      <c r="C39" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="D39" s="10" t="s">
+      <c r="D39" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E39" s="10" t="s">
+      <c r="E39" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="F39" s="10" t="s">
+      <c r="F39" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="G39" s="9"/>
+      <c r="G39" s="13"/>
     </row>
     <row r="40" ht="51" spans="1:7">
-      <c r="A40" s="9">
+      <c r="A40" s="13">
         <v>39</v>
       </c>
-      <c r="B40" s="10" t="s">
+      <c r="B40" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="C40" s="10" t="s">
+      <c r="C40" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="D40" s="10" t="s">
+      <c r="D40" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E40" s="10" t="s">
+      <c r="E40" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="F40" s="10" t="s">
+      <c r="F40" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="G40" s="9"/>
+      <c r="G40" s="13"/>
     </row>
     <row r="41" ht="101" spans="1:7">
-      <c r="A41" s="9">
+      <c r="A41" s="13">
         <v>40</v>
       </c>
-      <c r="B41" s="10" t="s">
+      <c r="B41" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="C41" s="10" t="s">
+      <c r="C41" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="D41" s="10" t="s">
+      <c r="D41" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E41" s="10" t="s">
+      <c r="E41" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="F41" s="10" t="s">
+      <c r="F41" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="G41" s="10" t="s">
+      <c r="G41" s="14" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="42" ht="84" spans="1:7">
-      <c r="A42" s="9">
+      <c r="A42" s="13">
         <v>41</v>
       </c>
-      <c r="B42" s="10" t="s">
+      <c r="B42" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="C42" s="10" t="s">
+      <c r="C42" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="D42" s="10" t="s">
+      <c r="D42" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E42" s="10" t="s">
+      <c r="E42" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="F42" s="10" t="s">
+      <c r="F42" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="G42" s="10" t="s">
+      <c r="G42" s="14" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="43" ht="84" spans="1:7">
-      <c r="A43" s="9">
+      <c r="A43" s="13">
         <v>42</v>
       </c>
-      <c r="B43" s="10" t="s">
+      <c r="B43" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="C43" s="10" t="s">
+      <c r="C43" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="D43" s="10" t="s">
+      <c r="D43" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E43" s="10" t="s">
+      <c r="E43" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="F43" s="10" t="s">
+      <c r="F43" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="G43" s="10" t="s">
+      <c r="G43" s="14" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="44" ht="118" spans="1:7">
-      <c r="A44" s="9">
+      <c r="A44" s="13">
         <v>43</v>
       </c>
-      <c r="B44" s="10" t="s">
+      <c r="B44" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="C44" s="10" t="s">
+      <c r="C44" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="D44" s="10" t="s">
+      <c r="D44" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E44" s="10" t="s">
+      <c r="E44" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="F44" s="10" t="s">
+      <c r="F44" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="G44" s="10" t="s">
+      <c r="G44" s="14" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="45" ht="101" spans="1:7">
-      <c r="A45" s="9">
+      <c r="A45" s="13">
         <v>44</v>
       </c>
-      <c r="B45" s="10" t="s">
+      <c r="B45" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="C45" s="10" t="s">
+      <c r="C45" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="D45" s="10" t="s">
+      <c r="D45" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E45" s="10" t="s">
+      <c r="E45" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="F45" s="10" t="s">
+      <c r="F45" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="G45" s="10" t="s">
+      <c r="G45" s="14" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="46" ht="118" spans="1:7">
-      <c r="A46" s="9">
+      <c r="A46" s="13">
         <v>45</v>
       </c>
-      <c r="B46" s="10" t="s">
+      <c r="B46" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="C46" s="10" t="s">
+      <c r="C46" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="D46" s="10" t="s">
+      <c r="D46" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E46" s="10" t="s">
+      <c r="E46" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="F46" s="10" t="s">
+      <c r="F46" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="G46" s="10" t="s">
+      <c r="G46" s="14" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="47" ht="118" spans="1:7">
-      <c r="A47" s="9">
+      <c r="A47" s="13">
         <v>46</v>
       </c>
-      <c r="B47" s="10" t="s">
+      <c r="B47" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="C47" s="10" t="s">
+      <c r="C47" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="D47" s="10" t="s">
+      <c r="D47" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E47" s="10" t="s">
+      <c r="E47" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="F47" s="10" t="s">
+      <c r="F47" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="G47" s="10" t="s">
+      <c r="G47" s="14" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="48" ht="34" spans="1:7">
-      <c r="A48" s="9">
+      <c r="A48" s="13">
         <v>47</v>
       </c>
-      <c r="B48" s="10" t="s">
+      <c r="B48" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="C48" s="10" t="s">
+      <c r="C48" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="D48" s="10" t="s">
+      <c r="D48" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E48" s="10" t="s">
+      <c r="E48" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="F48" s="10" t="s">
+      <c r="F48" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="G48" s="10" t="s">
+      <c r="G48" s="14" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="49" ht="34" spans="1:7">
-      <c r="A49" s="9">
+      <c r="A49" s="13">
         <v>48</v>
       </c>
-      <c r="B49" s="10" t="s">
+      <c r="B49" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="C49" s="10" t="s">
+      <c r="C49" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="D49" s="10" t="s">
+      <c r="D49" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E49" s="10" t="s">
+      <c r="E49" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="F49" s="10" t="s">
+      <c r="F49" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="G49" s="10" t="s">
+      <c r="G49" s="14" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="50" ht="135" spans="1:7">
-      <c r="A50" s="9">
+      <c r="A50" s="13">
         <v>49</v>
       </c>
-      <c r="B50" s="10" t="s">
+      <c r="B50" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="C50" s="10" t="s">
+      <c r="C50" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="D50" s="10" t="s">
+      <c r="D50" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E50" s="10" t="s">
+      <c r="E50" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="F50" s="10" t="s">
+      <c r="F50" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="G50" s="10" t="s">
+      <c r="G50" s="14" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="51" ht="34" spans="1:7">
-      <c r="A51" s="9">
+      <c r="A51" s="13">
         <v>50</v>
       </c>
-      <c r="B51" s="10" t="s">
+      <c r="B51" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="C51" s="10" t="s">
+      <c r="C51" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="D51" s="10" t="s">
+      <c r="D51" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E51" s="10" t="s">
+      <c r="E51" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="F51" s="10" t="s">
+      <c r="F51" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="G51" s="10" t="s">
+      <c r="G51" s="14" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="52" ht="68" spans="1:7">
-      <c r="A52" s="9">
+      <c r="A52" s="13">
         <v>51</v>
       </c>
-      <c r="B52" s="10" t="s">
+      <c r="B52" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="C52" s="10" t="s">
+      <c r="C52" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="D52" s="10" t="s">
+      <c r="D52" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E52" s="10" t="s">
+      <c r="E52" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="F52" s="9" t="s">
+      <c r="F52" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="G52" s="9" t="s">
+      <c r="G52" s="13" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="53" ht="68" spans="1:7">
-      <c r="A53" s="9">
+      <c r="A53" s="13">
         <v>52</v>
       </c>
-      <c r="B53" s="10" t="s">
+      <c r="B53" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="C53" s="10" t="s">
+      <c r="C53" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="D53" s="10" t="s">
+      <c r="D53" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E53" s="10" t="s">
+      <c r="E53" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="F53" s="9"/>
-      <c r="G53" s="9"/>
+      <c r="F53" s="13"/>
+      <c r="G53" s="13"/>
     </row>
     <row r="54" ht="68" spans="1:7">
-      <c r="A54" s="9">
+      <c r="A54" s="13">
         <v>53</v>
       </c>
-      <c r="B54" s="10" t="s">
+      <c r="B54" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="C54" s="10" t="s">
+      <c r="C54" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="D54" s="10" t="s">
+      <c r="D54" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E54" s="10" t="s">
+      <c r="E54" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="F54" s="9"/>
-      <c r="G54" s="9"/>
+      <c r="F54" s="13"/>
+      <c r="G54" s="13"/>
     </row>
     <row r="55" ht="68" spans="1:7">
-      <c r="A55" s="9">
+      <c r="A55" s="13">
         <v>54</v>
       </c>
-      <c r="B55" s="10" t="s">
+      <c r="B55" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="C55" s="10" t="s">
+      <c r="C55" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="D55" s="10" t="s">
+      <c r="D55" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E55" s="10" t="s">
+      <c r="E55" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="F55" s="9"/>
-      <c r="G55" s="9"/>
+      <c r="F55" s="13"/>
+      <c r="G55" s="13"/>
     </row>
     <row r="56" ht="68" spans="1:7">
-      <c r="A56" s="9">
+      <c r="A56" s="13">
         <v>55</v>
       </c>
-      <c r="B56" s="10" t="s">
+      <c r="B56" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="C56" s="10" t="s">
+      <c r="C56" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="D56" s="10" t="s">
+      <c r="D56" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E56" s="10" t="s">
+      <c r="E56" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="F56" s="9"/>
-      <c r="G56" s="9"/>
+      <c r="F56" s="13"/>
+      <c r="G56" s="13"/>
     </row>
     <row r="57" ht="68" spans="1:7">
-      <c r="A57" s="9">
+      <c r="A57" s="13">
         <v>56</v>
       </c>
-      <c r="B57" s="10" t="s">
+      <c r="B57" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="C57" s="10" t="s">
+      <c r="C57" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="D57" s="10" t="s">
+      <c r="D57" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E57" s="10" t="s">
+      <c r="E57" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="F57" s="9"/>
-      <c r="G57" s="9"/>
+      <c r="F57" s="13"/>
+      <c r="G57" s="13"/>
     </row>
     <row r="58" ht="68" spans="1:7">
-      <c r="A58" s="9">
+      <c r="A58" s="13">
         <v>57</v>
       </c>
-      <c r="B58" s="10" t="s">
+      <c r="B58" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="C58" s="10" t="s">
+      <c r="C58" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="D58" s="10" t="s">
+      <c r="D58" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E58" s="10" t="s">
+      <c r="E58" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="F58" s="9"/>
-      <c r="G58" s="9"/>
+      <c r="F58" s="13"/>
+      <c r="G58" s="13"/>
     </row>
     <row r="59" ht="68" spans="1:7">
-      <c r="A59" s="9">
+      <c r="A59" s="13">
         <v>58</v>
       </c>
-      <c r="B59" s="10" t="s">
+      <c r="B59" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="C59" s="10" t="s">
+      <c r="C59" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="D59" s="10" t="s">
+      <c r="D59" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E59" s="10" t="s">
+      <c r="E59" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="F59" s="9"/>
-      <c r="G59" s="9"/>
+      <c r="F59" s="13"/>
+      <c r="G59" s="13"/>
     </row>
     <row r="60" ht="68" spans="1:7">
-      <c r="A60" s="9">
+      <c r="A60" s="13">
         <v>59</v>
       </c>
-      <c r="B60" s="10" t="s">
+      <c r="B60" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="C60" s="10" t="s">
+      <c r="C60" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="D60" s="10" t="s">
+      <c r="D60" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E60" s="10" t="s">
+      <c r="E60" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="F60" s="9"/>
-      <c r="G60" s="9"/>
+      <c r="F60" s="13"/>
+      <c r="G60" s="13"/>
     </row>
     <row r="61" ht="68" spans="1:7">
-      <c r="A61" s="9">
+      <c r="A61" s="13">
         <v>60</v>
       </c>
-      <c r="B61" s="10" t="s">
+      <c r="B61" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="C61" s="10" t="s">
+      <c r="C61" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="D61" s="10" t="s">
+      <c r="D61" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E61" s="10" t="s">
+      <c r="E61" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="F61" s="9"/>
-      <c r="G61" s="9"/>
+      <c r="F61" s="13"/>
+      <c r="G61" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -3779,1566 +3859,1566 @@
   <dimension ref="A1:K84"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="1" width="5.140625" style="9" customWidth="1"/>
-    <col min="2" max="2" width="34.140625" style="10" customWidth="1"/>
-    <col min="3" max="3" width="26.859375" style="10" customWidth="1"/>
-    <col min="4" max="4" width="24.859375" style="10" customWidth="1"/>
-    <col min="5" max="5" width="26.140625" style="10" customWidth="1"/>
-    <col min="6" max="6" width="26.2890625" style="10" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="4"/>
+    <col min="1" max="1" width="5.140625" style="13" customWidth="1"/>
+    <col min="2" max="2" width="34.140625" style="14" customWidth="1"/>
+    <col min="3" max="3" width="26.859375" style="14" customWidth="1"/>
+    <col min="4" max="4" width="24.859375" style="14" customWidth="1"/>
+    <col min="5" max="5" width="26.140625" style="14" customWidth="1"/>
+    <col min="6" max="6" width="26.2890625" style="14" customWidth="1"/>
+    <col min="7" max="16384" width="9.140625" style="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:6">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="9" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" s="8" customFormat="1" ht="20" customHeight="1" spans="1:6">
-      <c r="A2" s="11" t="s">
+    <row r="2" s="12" customFormat="1" ht="20" customHeight="1" spans="1:6">
+      <c r="A2" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="16"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="20"/>
     </row>
     <row r="3" ht="118" customHeight="1" spans="1:11">
-      <c r="A3" s="9">
+      <c r="A3" s="13">
         <v>1</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="17" t="s">
         <v>112</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="E3" s="21" t="s">
         <v>112</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
+      <c r="I3" s="5"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="5"/>
     </row>
     <row r="4" ht="101" customHeight="1" spans="1:11">
-      <c r="A4" s="9">
+      <c r="A4" s="13">
         <v>2</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="17" t="s">
         <v>112</v>
       </c>
-      <c r="E4" s="18"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
+      <c r="E4" s="22"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="5"/>
     </row>
     <row r="5" ht="122" customHeight="1" spans="1:11">
-      <c r="A5" s="9">
+      <c r="A5" s="13">
         <v>3</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="17" t="s">
         <v>112</v>
       </c>
-      <c r="E5" s="18"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
+      <c r="E5" s="22"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="5"/>
     </row>
     <row r="6" ht="84" spans="1:5">
-      <c r="A6" s="9">
+      <c r="A6" s="13">
         <v>4</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="D6" s="17" t="s">
         <v>112</v>
       </c>
-      <c r="E6" s="18"/>
+      <c r="E6" s="22"/>
     </row>
     <row r="7" customFormat="1" ht="84" spans="1:6">
-      <c r="A7" s="9">
+      <c r="A7" s="13">
         <v>5</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="14" t="s">
         <v>117</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="17" t="s">
         <v>112</v>
       </c>
-      <c r="E7" s="19"/>
-      <c r="F7" s="10"/>
+      <c r="E7" s="23"/>
+      <c r="F7" s="14"/>
     </row>
     <row r="8" customFormat="1" ht="84" spans="1:6">
-      <c r="A8" s="9">
+      <c r="A8" s="13">
         <v>6</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="D8" s="13" t="s">
+      <c r="D8" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="E8" s="17" t="s">
+      <c r="E8" s="21" t="s">
         <v>119</v>
       </c>
-      <c r="F8" s="10"/>
+      <c r="F8" s="14"/>
     </row>
     <row r="9" customFormat="1" ht="84" spans="1:6">
-      <c r="A9" s="9">
+      <c r="A9" s="13">
         <v>7</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="D9" s="13" t="s">
+      <c r="D9" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="E9" s="18"/>
-      <c r="F9" s="10"/>
+      <c r="E9" s="22"/>
+      <c r="F9" s="14"/>
     </row>
     <row r="10" customFormat="1" ht="84" spans="1:6">
-      <c r="A10" s="9">
+      <c r="A10" s="13">
         <v>8</v>
       </c>
-      <c r="B10" s="10" t="s">
+      <c r="B10" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="D10" s="13" t="s">
+      <c r="D10" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="E10" s="18"/>
-      <c r="F10" s="10"/>
+      <c r="E10" s="22"/>
+      <c r="F10" s="14"/>
     </row>
     <row r="11" customFormat="1" ht="84" spans="1:6">
-      <c r="A11" s="9">
+      <c r="A11" s="13">
         <v>9</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="D11" s="13" t="s">
+      <c r="D11" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="E11" s="18"/>
-      <c r="F11" s="10"/>
+      <c r="E11" s="22"/>
+      <c r="F11" s="14"/>
     </row>
     <row r="12" customFormat="1" ht="84" spans="1:6">
-      <c r="A12" s="9">
+      <c r="A12" s="13">
         <v>10</v>
       </c>
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="14" t="s">
         <v>117</v>
       </c>
-      <c r="D12" s="13" t="s">
+      <c r="D12" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="E12" s="19"/>
-      <c r="F12" s="10"/>
+      <c r="E12" s="23"/>
+      <c r="F12" s="14"/>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="14" t="s">
+      <c r="A13" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
+      <c r="B13" s="18"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
     </row>
     <row r="14" ht="84" spans="1:6">
-      <c r="A14" s="9">
+      <c r="A14" s="13">
         <v>11</v>
       </c>
-      <c r="B14" s="10" t="s">
+      <c r="B14" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="C14" s="10" t="s">
+      <c r="C14" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="D14" s="10" t="s">
+      <c r="D14" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="E14" s="10" t="s">
+      <c r="E14" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="F14" s="10" t="s">
+      <c r="F14" s="14" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="15" ht="68" spans="1:6">
-      <c r="A15" s="9">
+      <c r="A15" s="13">
         <v>12</v>
       </c>
-      <c r="B15" s="10" t="s">
+      <c r="B15" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="C15" s="10" t="s">
+      <c r="C15" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="D15" s="10" t="s">
+      <c r="D15" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="E15" s="10" t="s">
+      <c r="E15" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="F15" s="10" t="s">
+      <c r="F15" s="14" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="16" ht="68" spans="1:6">
-      <c r="A16" s="9">
+      <c r="A16" s="13">
         <v>13</v>
       </c>
-      <c r="B16" s="10" t="s">
+      <c r="B16" s="14" t="s">
         <v>130</v>
       </c>
-      <c r="C16" s="10" t="s">
+      <c r="C16" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="D16" s="10" t="s">
+      <c r="D16" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="E16" s="10" t="s">
+      <c r="E16" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="F16" s="10" t="s">
+      <c r="F16" s="14" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="17" ht="68" spans="1:6">
-      <c r="A17" s="9">
+      <c r="A17" s="13">
         <v>14</v>
       </c>
-      <c r="B17" s="10" t="s">
+      <c r="B17" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="C17" s="10" t="s">
+      <c r="C17" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="D17" s="10" t="s">
+      <c r="D17" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="E17" s="10" t="s">
+      <c r="E17" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="F17" s="10" t="s">
+      <c r="F17" s="14" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="18" ht="90" customHeight="1" spans="1:6">
-      <c r="A18" s="9">
+      <c r="A18" s="13">
         <v>15</v>
       </c>
-      <c r="B18" s="15" t="s">
+      <c r="B18" s="19" t="s">
         <v>137</v>
       </c>
-      <c r="C18" s="15" t="s">
+      <c r="C18" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="D18" s="15" t="s">
+      <c r="D18" s="19" t="s">
         <v>139</v>
       </c>
-      <c r="E18" s="15" t="s">
+      <c r="E18" s="19" t="s">
         <v>140</v>
       </c>
-      <c r="F18" s="15" t="s">
+      <c r="F18" s="19" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="19" ht="66" customHeight="1" spans="1:6">
-      <c r="A19" s="9">
+      <c r="A19" s="13">
         <v>16</v>
       </c>
-      <c r="B19" s="15" t="s">
+      <c r="B19" s="19" t="s">
         <v>142</v>
       </c>
-      <c r="C19" s="15" t="s">
+      <c r="C19" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="D19" s="15" t="s">
+      <c r="D19" s="19" t="s">
         <v>143</v>
       </c>
-      <c r="E19" s="15" t="s">
+      <c r="E19" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="F19" s="15" t="s">
+      <c r="F19" s="19" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="20" ht="79" customHeight="1" spans="1:6">
-      <c r="A20" s="9">
+      <c r="A20" s="13">
         <v>17</v>
       </c>
-      <c r="B20" s="15" t="s">
+      <c r="B20" s="19" t="s">
         <v>145</v>
       </c>
-      <c r="C20" s="15" t="s">
+      <c r="C20" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="D20" s="15" t="s">
+      <c r="D20" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="E20" s="15" t="s">
+      <c r="E20" s="19" t="s">
         <v>147</v>
       </c>
-      <c r="F20" s="15" t="s">
+      <c r="F20" s="19" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="21" ht="80" customHeight="1" spans="1:6">
-      <c r="A21" s="9">
+      <c r="A21" s="13">
         <v>18</v>
       </c>
-      <c r="B21" s="15" t="s">
+      <c r="B21" s="19" t="s">
         <v>149</v>
       </c>
-      <c r="C21" s="15" t="s">
+      <c r="C21" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="D21" s="15" t="s">
+      <c r="D21" s="19" t="s">
         <v>150</v>
       </c>
-      <c r="E21" s="15" t="s">
+      <c r="E21" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="F21" s="15" t="s">
+      <c r="F21" s="19" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="22" ht="17" customHeight="1" spans="1:6">
-      <c r="A22" s="14" t="s">
+      <c r="A22" s="18" t="s">
         <v>152</v>
       </c>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
+      <c r="B22" s="18"/>
+      <c r="C22" s="18"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="18"/>
     </row>
     <row r="23" ht="84" spans="1:6">
-      <c r="A23" s="9">
+      <c r="A23" s="13">
         <v>19</v>
       </c>
-      <c r="B23" s="10" t="s">
+      <c r="B23" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="C23" s="10" t="s">
+      <c r="C23" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="D23" s="10" t="s">
+      <c r="D23" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="E23" s="10" t="s">
+      <c r="E23" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="F23" s="10" t="s">
+      <c r="F23" s="14" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="24" ht="68" spans="1:6">
-      <c r="A24" s="9">
+      <c r="A24" s="13">
         <v>20</v>
       </c>
-      <c r="B24" s="10" t="s">
+      <c r="B24" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="C24" s="10" t="s">
+      <c r="C24" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="D24" s="10" t="s">
+      <c r="D24" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="E24" s="10" t="s">
+      <c r="E24" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="F24" s="10" t="s">
+      <c r="F24" s="14" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="25" ht="68" spans="1:6">
-      <c r="A25" s="9">
+      <c r="A25" s="13">
         <v>21</v>
       </c>
-      <c r="B25" s="10" t="s">
+      <c r="B25" s="14" t="s">
         <v>130</v>
       </c>
-      <c r="C25" s="10" t="s">
+      <c r="C25" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="D25" s="10" t="s">
+      <c r="D25" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="E25" s="10" t="s">
+      <c r="E25" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="F25" s="10" t="s">
+      <c r="F25" s="14" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="26" ht="68" spans="1:6">
-      <c r="A26" s="9">
+      <c r="A26" s="13">
         <v>22</v>
       </c>
-      <c r="B26" s="10" t="s">
+      <c r="B26" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="C26" s="10" t="s">
+      <c r="C26" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="D26" s="10" t="s">
+      <c r="D26" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="E26" s="10" t="s">
+      <c r="E26" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="F26" s="10" t="s">
+      <c r="F26" s="14" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="27" ht="68" spans="1:6">
-      <c r="A27" s="9">
+      <c r="A27" s="13">
         <v>23</v>
       </c>
-      <c r="B27" s="15" t="s">
+      <c r="B27" s="19" t="s">
         <v>137</v>
       </c>
-      <c r="C27" s="15" t="s">
+      <c r="C27" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="D27" s="15" t="s">
+      <c r="D27" s="19" t="s">
         <v>154</v>
       </c>
-      <c r="E27" s="15" t="s">
+      <c r="E27" s="19" t="s">
         <v>155</v>
       </c>
-      <c r="F27" s="15" t="s">
+      <c r="F27" s="19" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="28" ht="51" spans="1:6">
-      <c r="A28" s="9">
+      <c r="A28" s="13">
         <v>24</v>
       </c>
-      <c r="B28" s="15" t="s">
+      <c r="B28" s="19" t="s">
         <v>142</v>
       </c>
-      <c r="C28" s="15" t="s">
+      <c r="C28" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="D28" s="15" t="s">
+      <c r="D28" s="19" t="s">
         <v>143</v>
       </c>
-      <c r="E28" s="15" t="s">
+      <c r="E28" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="F28" s="15" t="s">
+      <c r="F28" s="19" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="29" ht="68" spans="1:6">
-      <c r="A29" s="9">
+      <c r="A29" s="13">
         <v>25</v>
       </c>
-      <c r="B29" s="15" t="s">
+      <c r="B29" s="19" t="s">
         <v>145</v>
       </c>
-      <c r="C29" s="15" t="s">
+      <c r="C29" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="D29" s="15" t="s">
+      <c r="D29" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="E29" s="15" t="s">
+      <c r="E29" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="F29" s="15" t="s">
+      <c r="F29" s="19" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="30" ht="68" spans="1:6">
-      <c r="A30" s="9">
+      <c r="A30" s="13">
         <v>26</v>
       </c>
-      <c r="B30" s="15" t="s">
+      <c r="B30" s="19" t="s">
         <v>149</v>
       </c>
-      <c r="C30" s="15" t="s">
+      <c r="C30" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="D30" s="15" t="s">
+      <c r="D30" s="19" t="s">
         <v>150</v>
       </c>
-      <c r="E30" s="15" t="s">
+      <c r="E30" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="F30" s="15" t="s">
+      <c r="F30" s="19" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="31" spans="1:6">
-      <c r="A31" s="14" t="s">
+      <c r="A31" s="18" t="s">
         <v>159</v>
       </c>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
+      <c r="B31" s="18"/>
+      <c r="C31" s="18"/>
+      <c r="D31" s="18"/>
+      <c r="E31" s="18"/>
+      <c r="F31" s="18"/>
     </row>
     <row r="32" ht="68" spans="1:6">
-      <c r="A32" s="9">
+      <c r="A32" s="13">
         <v>27</v>
       </c>
-      <c r="B32" s="15" t="s">
+      <c r="B32" s="19" t="s">
         <v>137</v>
       </c>
-      <c r="C32" s="15" t="s">
+      <c r="C32" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="D32" s="15" t="s">
+      <c r="D32" s="19" t="s">
         <v>154</v>
       </c>
-      <c r="E32" s="15" t="s">
+      <c r="E32" s="19" t="s">
         <v>160</v>
       </c>
-      <c r="F32" s="15" t="s">
+      <c r="F32" s="19" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="33" ht="51" spans="1:6">
-      <c r="A33" s="9">
+      <c r="A33" s="13">
         <v>28</v>
       </c>
-      <c r="B33" s="15" t="s">
+      <c r="B33" s="19" t="s">
         <v>142</v>
       </c>
-      <c r="C33" s="15" t="s">
+      <c r="C33" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="D33" s="15" t="s">
+      <c r="D33" s="19" t="s">
         <v>143</v>
       </c>
-      <c r="E33" s="15" t="s">
+      <c r="E33" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="F33" s="15" t="s">
+      <c r="F33" s="19" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="34" ht="68" spans="1:6">
-      <c r="A34" s="9">
+      <c r="A34" s="13">
         <v>29</v>
       </c>
-      <c r="B34" s="15" t="s">
+      <c r="B34" s="19" t="s">
         <v>145</v>
       </c>
-      <c r="C34" s="15" t="s">
+      <c r="C34" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="D34" s="15" t="s">
+      <c r="D34" s="19" t="s">
         <v>161</v>
       </c>
-      <c r="E34" s="15" t="s">
+      <c r="E34" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="F34" s="15" t="s">
+      <c r="F34" s="19" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="35" ht="68" spans="1:6">
-      <c r="A35" s="9">
+      <c r="A35" s="13">
         <v>30</v>
       </c>
-      <c r="B35" s="15" t="s">
+      <c r="B35" s="19" t="s">
         <v>149</v>
       </c>
-      <c r="C35" s="15" t="s">
+      <c r="C35" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="D35" s="15" t="s">
+      <c r="D35" s="19" t="s">
         <v>162</v>
       </c>
-      <c r="E35" s="15" t="s">
+      <c r="E35" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="F35" s="15" t="s">
+      <c r="F35" s="19" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="36" spans="1:6">
-      <c r="A36" s="14" t="s">
+      <c r="A36" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
+      <c r="B36" s="18"/>
+      <c r="C36" s="18"/>
+      <c r="D36" s="18"/>
+      <c r="E36" s="18"/>
+      <c r="F36" s="18"/>
     </row>
     <row r="37" ht="84" spans="1:6">
-      <c r="A37" s="9">
+      <c r="A37" s="13">
         <v>31</v>
       </c>
-      <c r="B37" s="15" t="s">
+      <c r="B37" s="19" t="s">
         <v>137</v>
       </c>
-      <c r="C37" s="15" t="s">
+      <c r="C37" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="D37" s="15" t="s">
+      <c r="D37" s="19" t="s">
         <v>164</v>
       </c>
-      <c r="E37" s="15" t="s">
+      <c r="E37" s="19" t="s">
         <v>165</v>
       </c>
-      <c r="F37" s="15" t="s">
+      <c r="F37" s="19" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="38" ht="68" spans="1:6">
-      <c r="A38" s="9">
+      <c r="A38" s="13">
         <v>32</v>
       </c>
-      <c r="B38" s="15" t="s">
+      <c r="B38" s="19" t="s">
         <v>142</v>
       </c>
-      <c r="C38" s="15" t="s">
+      <c r="C38" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="D38" s="15" t="s">
+      <c r="D38" s="19" t="s">
         <v>166</v>
       </c>
-      <c r="E38" s="15" t="s">
+      <c r="E38" s="19" t="s">
         <v>167</v>
       </c>
-      <c r="F38" s="15" t="s">
+      <c r="F38" s="19" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="39" ht="68" spans="1:6">
-      <c r="A39" s="9">
+      <c r="A39" s="13">
         <v>33</v>
       </c>
-      <c r="B39" s="15" t="s">
+      <c r="B39" s="19" t="s">
         <v>145</v>
       </c>
-      <c r="C39" s="15" t="s">
+      <c r="C39" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="D39" s="15" t="s">
+      <c r="D39" s="19" t="s">
         <v>168</v>
       </c>
-      <c r="E39" s="15" t="s">
+      <c r="E39" s="19" t="s">
         <v>169</v>
       </c>
-      <c r="F39" s="15" t="s">
+      <c r="F39" s="19" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="40" ht="68" spans="1:6">
-      <c r="A40" s="9">
+      <c r="A40" s="13">
         <v>34</v>
       </c>
-      <c r="B40" s="15" t="s">
+      <c r="B40" s="19" t="s">
         <v>149</v>
       </c>
-      <c r="C40" s="15" t="s">
+      <c r="C40" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="D40" s="15" t="s">
+      <c r="D40" s="19" t="s">
         <v>170</v>
       </c>
-      <c r="E40" s="15" t="s">
+      <c r="E40" s="19" t="s">
         <v>169</v>
       </c>
-      <c r="F40" s="15" t="s">
+      <c r="F40" s="19" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="41" spans="1:6">
-      <c r="A41" s="14" t="s">
+      <c r="A41" s="18" t="s">
         <v>171</v>
       </c>
-      <c r="B41" s="14"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
+      <c r="B41" s="18"/>
+      <c r="C41" s="18"/>
+      <c r="D41" s="18"/>
+      <c r="E41" s="18"/>
+      <c r="F41" s="18"/>
     </row>
     <row r="42" ht="84" spans="1:6">
-      <c r="A42" s="9">
+      <c r="A42" s="13">
         <v>35</v>
       </c>
-      <c r="B42" s="10" t="s">
+      <c r="B42" s="14" t="s">
         <v>172</v>
       </c>
-      <c r="C42" s="10" t="s">
+      <c r="C42" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="D42" s="15" t="s">
+      <c r="D42" s="19" t="s">
         <v>174</v>
       </c>
-      <c r="E42" s="10" t="s">
+      <c r="E42" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="F42" s="10" t="s">
+      <c r="F42" s="14" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="43" ht="68" spans="1:6">
-      <c r="A43" s="9">
+      <c r="A43" s="13">
         <v>36</v>
       </c>
-      <c r="B43" s="10" t="s">
+      <c r="B43" s="14" t="s">
         <v>176</v>
       </c>
-      <c r="C43" s="10" t="s">
+      <c r="C43" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="D43" s="15" t="s">
+      <c r="D43" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="E43" s="10" t="s">
+      <c r="E43" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="F43" s="10" t="s">
+      <c r="F43" s="14" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="44" ht="68" spans="1:6">
-      <c r="A44" s="9">
+      <c r="A44" s="13">
         <v>37</v>
       </c>
-      <c r="B44" s="10" t="s">
+      <c r="B44" s="14" t="s">
         <v>130</v>
       </c>
-      <c r="C44" s="10" t="s">
+      <c r="C44" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="D44" s="15" t="s">
+      <c r="D44" s="19" t="s">
         <v>180</v>
       </c>
-      <c r="E44" s="10" t="s">
+      <c r="E44" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="F44" s="10" t="s">
+      <c r="F44" s="14" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="45" ht="68" spans="1:6">
-      <c r="A45" s="9">
+      <c r="A45" s="13">
         <v>38</v>
       </c>
-      <c r="B45" s="10" t="s">
+      <c r="B45" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="C45" s="10" t="s">
+      <c r="C45" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="D45" s="15" t="s">
+      <c r="D45" s="19" t="s">
         <v>182</v>
       </c>
-      <c r="E45" s="10" t="s">
+      <c r="E45" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="F45" s="10" t="s">
+      <c r="F45" s="14" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="46" ht="68" spans="1:6">
-      <c r="A46" s="9">
+      <c r="A46" s="13">
         <v>39</v>
       </c>
-      <c r="B46" s="15" t="s">
+      <c r="B46" s="19" t="s">
         <v>137</v>
       </c>
-      <c r="C46" s="15" t="s">
+      <c r="C46" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="D46" s="15" t="s">
+      <c r="D46" s="19" t="s">
         <v>184</v>
       </c>
-      <c r="E46" s="15" t="s">
+      <c r="E46" s="19" t="s">
         <v>160</v>
       </c>
-      <c r="F46" s="15" t="s">
+      <c r="F46" s="19" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="47" ht="118" spans="1:6">
-      <c r="A47" s="9">
+      <c r="A47" s="13">
         <v>40</v>
       </c>
-      <c r="B47" s="15" t="s">
+      <c r="B47" s="19" t="s">
         <v>142</v>
       </c>
-      <c r="C47" s="15" t="s">
+      <c r="C47" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="D47" s="15" t="s">
+      <c r="D47" s="19" t="s">
         <v>186</v>
       </c>
-      <c r="E47" s="15" t="s">
+      <c r="E47" s="19" t="s">
         <v>187</v>
       </c>
-      <c r="F47" s="15" t="s">
+      <c r="F47" s="19" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="48" ht="68" spans="1:6">
-      <c r="A48" s="9">
+      <c r="A48" s="13">
         <v>41</v>
       </c>
-      <c r="B48" s="15" t="s">
+      <c r="B48" s="19" t="s">
         <v>145</v>
       </c>
-      <c r="C48" s="15" t="s">
+      <c r="C48" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="D48" s="15" t="s">
+      <c r="D48" s="19" t="s">
         <v>189</v>
       </c>
-      <c r="E48" s="15" t="s">
+      <c r="E48" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="F48" s="15" t="s">
+      <c r="F48" s="19" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="49" ht="68" spans="1:6">
-      <c r="A49" s="9">
+      <c r="A49" s="13">
         <v>42</v>
       </c>
-      <c r="B49" s="15" t="s">
+      <c r="B49" s="19" t="s">
         <v>149</v>
       </c>
-      <c r="C49" s="15" t="s">
+      <c r="C49" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="D49" s="15" t="s">
+      <c r="D49" s="19" t="s">
         <v>191</v>
       </c>
-      <c r="E49" s="15" t="s">
+      <c r="E49" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="F49" s="15" t="s">
+      <c r="F49" s="19" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="A50" s="14" t="s">
+      <c r="A50" s="18" t="s">
         <v>193</v>
       </c>
-      <c r="B50" s="14"/>
-      <c r="C50" s="14"/>
-      <c r="D50" s="14"/>
-      <c r="E50" s="14"/>
-      <c r="F50" s="14"/>
+      <c r="B50" s="18"/>
+      <c r="C50" s="18"/>
+      <c r="D50" s="18"/>
+      <c r="E50" s="18"/>
+      <c r="F50" s="18"/>
     </row>
     <row r="51" ht="68" spans="1:6">
-      <c r="A51" s="9">
+      <c r="A51" s="13">
         <v>43</v>
       </c>
-      <c r="B51" s="10" t="s">
+      <c r="B51" s="14" t="s">
         <v>194</v>
       </c>
-      <c r="C51" s="10" t="s">
+      <c r="C51" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="D51" s="10" t="s">
+      <c r="D51" s="14" t="s">
         <v>195</v>
       </c>
-      <c r="E51" s="10" t="s">
+      <c r="E51" s="14" t="s">
         <v>196</v>
       </c>
-      <c r="F51" s="10" t="s">
+      <c r="F51" s="14" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="52" ht="68" spans="1:6">
-      <c r="A52" s="9">
+      <c r="A52" s="13">
         <v>44</v>
       </c>
-      <c r="B52" s="10" t="s">
+      <c r="B52" s="14" t="s">
         <v>198</v>
       </c>
-      <c r="C52" s="10" t="s">
+      <c r="C52" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="D52" s="10" t="s">
+      <c r="D52" s="14" t="s">
         <v>199</v>
       </c>
-      <c r="E52" s="10" t="s">
+      <c r="E52" s="14" t="s">
         <v>196</v>
       </c>
-      <c r="F52" s="10" t="s">
+      <c r="F52" s="14" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="53" ht="68" spans="1:6">
-      <c r="A53" s="9">
+      <c r="A53" s="13">
         <v>45</v>
       </c>
-      <c r="B53" s="10" t="s">
+      <c r="B53" s="14" t="s">
         <v>201</v>
       </c>
-      <c r="C53" s="10" t="s">
+      <c r="C53" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="D53" s="10" t="s">
+      <c r="D53" s="14" t="s">
         <v>202</v>
       </c>
-      <c r="E53" s="10" t="s">
+      <c r="E53" s="14" t="s">
         <v>196</v>
       </c>
-      <c r="F53" s="10" t="s">
+      <c r="F53" s="14" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="54" ht="68" spans="1:6">
-      <c r="A54" s="9">
+      <c r="A54" s="13">
         <v>46</v>
       </c>
-      <c r="B54" s="10" t="s">
+      <c r="B54" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="C54" s="15" t="s">
+      <c r="C54" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="D54" s="15" t="s">
+      <c r="D54" s="19" t="s">
         <v>205</v>
       </c>
-      <c r="E54" s="15" t="s">
+      <c r="E54" s="19" t="s">
         <v>160</v>
       </c>
-      <c r="F54" s="15" t="s">
+      <c r="F54" s="19" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="55" ht="68" spans="1:6">
-      <c r="A55" s="9">
+      <c r="A55" s="13">
         <v>47</v>
       </c>
-      <c r="B55" s="10" t="s">
+      <c r="B55" s="14" t="s">
         <v>206</v>
       </c>
-      <c r="C55" s="15" t="s">
+      <c r="C55" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="D55" s="15" t="s">
+      <c r="D55" s="19" t="s">
         <v>207</v>
       </c>
-      <c r="E55" s="15" t="s">
+      <c r="E55" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="F55" s="15" t="s">
+      <c r="F55" s="19" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="56" ht="68" spans="1:6">
-      <c r="A56" s="9">
+      <c r="A56" s="13">
         <v>48</v>
       </c>
-      <c r="B56" s="10" t="s">
+      <c r="B56" s="14" t="s">
         <v>208</v>
       </c>
-      <c r="C56" s="15" t="s">
+      <c r="C56" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="D56" s="15" t="s">
+      <c r="D56" s="19" t="s">
         <v>209</v>
       </c>
-      <c r="E56" s="15" t="s">
+      <c r="E56" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="F56" s="15" t="s">
+      <c r="F56" s="19" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="57" ht="68" spans="1:6">
-      <c r="A57" s="9">
+      <c r="A57" s="13">
         <v>49</v>
       </c>
-      <c r="B57" s="10" t="s">
+      <c r="B57" s="14" t="s">
         <v>210</v>
       </c>
-      <c r="C57" s="15" t="s">
+      <c r="C57" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="D57" s="15" t="s">
+      <c r="D57" s="19" t="s">
         <v>211</v>
       </c>
-      <c r="E57" s="15" t="s">
+      <c r="E57" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="F57" s="15" t="s">
+      <c r="F57" s="19" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="58" spans="1:6">
-      <c r="A58" s="14" t="s">
+      <c r="A58" s="18" t="s">
         <v>212</v>
       </c>
-      <c r="B58" s="14"/>
-      <c r="C58" s="14"/>
-      <c r="D58" s="14"/>
-      <c r="E58" s="14"/>
-      <c r="F58" s="14"/>
+      <c r="B58" s="18"/>
+      <c r="C58" s="18"/>
+      <c r="D58" s="18"/>
+      <c r="E58" s="18"/>
+      <c r="F58" s="18"/>
     </row>
     <row r="59" ht="84" spans="1:6">
-      <c r="A59" s="9">
+      <c r="A59" s="13">
         <v>50</v>
       </c>
-      <c r="B59" s="10" t="s">
+      <c r="B59" s="14" t="s">
         <v>172</v>
       </c>
-      <c r="C59" s="10" t="s">
+      <c r="C59" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="D59" s="15" t="s">
+      <c r="D59" s="19" t="s">
         <v>213</v>
       </c>
-      <c r="E59" s="10" t="s">
+      <c r="E59" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="F59" s="10" t="s">
+      <c r="F59" s="14" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="60" ht="68" spans="1:6">
-      <c r="A60" s="9">
+      <c r="A60" s="13">
         <v>51</v>
       </c>
-      <c r="B60" s="10" t="s">
+      <c r="B60" s="14" t="s">
         <v>176</v>
       </c>
-      <c r="C60" s="10" t="s">
+      <c r="C60" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="D60" s="15" t="s">
+      <c r="D60" s="19" t="s">
         <v>214</v>
       </c>
-      <c r="E60" s="10" t="s">
+      <c r="E60" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="F60" s="10" t="s">
+      <c r="F60" s="14" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="61" ht="68" spans="1:6">
-      <c r="A61" s="9">
+      <c r="A61" s="13">
         <v>52</v>
       </c>
-      <c r="B61" s="10" t="s">
+      <c r="B61" s="14" t="s">
         <v>130</v>
       </c>
-      <c r="C61" s="10" t="s">
+      <c r="C61" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="D61" s="15" t="s">
+      <c r="D61" s="19" t="s">
         <v>215</v>
       </c>
-      <c r="E61" s="10" t="s">
+      <c r="E61" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="F61" s="10" t="s">
+      <c r="F61" s="14" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="62" ht="68" spans="1:6">
-      <c r="A62" s="9">
+      <c r="A62" s="13">
         <v>53</v>
       </c>
-      <c r="B62" s="10" t="s">
+      <c r="B62" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="C62" s="10" t="s">
+      <c r="C62" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="D62" s="15" t="s">
+      <c r="D62" s="19" t="s">
         <v>216</v>
       </c>
-      <c r="E62" s="10" t="s">
+      <c r="E62" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="F62" s="10" t="s">
+      <c r="F62" s="14" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="63" ht="68" spans="1:6">
-      <c r="A63" s="9">
+      <c r="A63" s="13">
         <v>54</v>
       </c>
-      <c r="B63" s="15" t="s">
+      <c r="B63" s="19" t="s">
         <v>137</v>
       </c>
-      <c r="C63" s="15" t="s">
+      <c r="C63" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="D63" s="15" t="s">
+      <c r="D63" s="19" t="s">
         <v>217</v>
       </c>
-      <c r="E63" s="15" t="s">
+      <c r="E63" s="19" t="s">
         <v>218</v>
       </c>
-      <c r="F63" s="15" t="s">
+      <c r="F63" s="19" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="64" ht="84" spans="1:6">
-      <c r="A64" s="9">
+      <c r="A64" s="13">
         <v>55</v>
       </c>
-      <c r="B64" s="15" t="s">
+      <c r="B64" s="19" t="s">
         <v>142</v>
       </c>
-      <c r="C64" s="15" t="s">
+      <c r="C64" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="D64" s="15" t="s">
+      <c r="D64" s="19" t="s">
         <v>214</v>
       </c>
-      <c r="E64" s="15" t="s">
+      <c r="E64" s="19" t="s">
         <v>220</v>
       </c>
-      <c r="F64" s="15" t="s">
+      <c r="F64" s="19" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="65" ht="84" spans="1:6">
-      <c r="A65" s="9">
+      <c r="A65" s="13">
         <v>56</v>
       </c>
-      <c r="B65" s="15" t="s">
+      <c r="B65" s="19" t="s">
         <v>145</v>
       </c>
-      <c r="C65" s="15" t="s">
+      <c r="C65" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="D65" s="15" t="s">
+      <c r="D65" s="19" t="s">
         <v>221</v>
       </c>
-      <c r="E65" s="15" t="s">
+      <c r="E65" s="19" t="s">
         <v>220</v>
       </c>
-      <c r="F65" s="15" t="s">
+      <c r="F65" s="19" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="66" ht="68" spans="1:6">
-      <c r="A66" s="9">
+      <c r="A66" s="13">
         <v>57</v>
       </c>
-      <c r="B66" s="15" t="s">
+      <c r="B66" s="19" t="s">
         <v>149</v>
       </c>
-      <c r="C66" s="15" t="s">
+      <c r="C66" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="D66" s="15" t="s">
+      <c r="D66" s="19" t="s">
         <v>222</v>
       </c>
-      <c r="E66" s="15" t="s">
+      <c r="E66" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="F66" s="15" t="s">
+      <c r="F66" s="19" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="67" spans="1:6">
-      <c r="A67" s="14" t="s">
+      <c r="A67" s="18" t="s">
         <v>223</v>
       </c>
-      <c r="B67" s="14"/>
-      <c r="C67" s="14"/>
-      <c r="D67" s="14"/>
-      <c r="E67" s="14"/>
-      <c r="F67" s="14"/>
+      <c r="B67" s="18"/>
+      <c r="C67" s="18"/>
+      <c r="D67" s="18"/>
+      <c r="E67" s="18"/>
+      <c r="F67" s="18"/>
     </row>
     <row r="68" ht="84" spans="1:6">
-      <c r="A68" s="9">
+      <c r="A68" s="13">
         <v>58</v>
       </c>
-      <c r="B68" s="10" t="s">
+      <c r="B68" s="14" t="s">
         <v>224</v>
       </c>
-      <c r="C68" s="10" t="s">
+      <c r="C68" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="D68" s="15" t="s">
+      <c r="D68" s="19" t="s">
         <v>225</v>
       </c>
-      <c r="E68" s="10" t="s">
+      <c r="E68" s="14" t="s">
         <v>226</v>
       </c>
-      <c r="F68" s="10" t="s">
+      <c r="F68" s="14" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="69" ht="68" spans="1:6">
-      <c r="A69" s="9">
+      <c r="A69" s="13">
         <v>59</v>
       </c>
-      <c r="B69" s="10" t="s">
+      <c r="B69" s="14" t="s">
         <v>228</v>
       </c>
-      <c r="C69" s="10" t="s">
+      <c r="C69" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="D69" s="15" t="s">
+      <c r="D69" s="19" t="s">
         <v>229</v>
       </c>
-      <c r="E69" s="10" t="s">
+      <c r="E69" s="14" t="s">
         <v>230</v>
       </c>
-      <c r="F69" s="10" t="s">
+      <c r="F69" s="14" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="70" ht="68" spans="1:6">
-      <c r="A70" s="9">
+      <c r="A70" s="13">
         <v>60</v>
       </c>
-      <c r="B70" s="10" t="s">
+      <c r="B70" s="14" t="s">
         <v>232</v>
       </c>
-      <c r="C70" s="10" t="s">
+      <c r="C70" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="D70" s="15" t="s">
+      <c r="D70" s="19" t="s">
         <v>233</v>
       </c>
-      <c r="E70" s="10" t="s">
+      <c r="E70" s="14" t="s">
         <v>234</v>
       </c>
-      <c r="F70" s="10" t="s">
+      <c r="F70" s="14" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="71" ht="68" spans="1:6">
-      <c r="A71" s="9">
+      <c r="A71" s="13">
         <v>61</v>
       </c>
-      <c r="B71" s="10" t="s">
+      <c r="B71" s="14" t="s">
         <v>236</v>
       </c>
-      <c r="C71" s="10" t="s">
+      <c r="C71" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="D71" s="15" t="s">
+      <c r="D71" s="19" t="s">
         <v>237</v>
       </c>
-      <c r="E71" s="10" t="s">
+      <c r="E71" s="14" t="s">
         <v>234</v>
       </c>
-      <c r="F71" s="10" t="s">
+      <c r="F71" s="14" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="72" ht="68" spans="1:6">
-      <c r="A72" s="9">
+      <c r="A72" s="13">
         <v>62</v>
       </c>
-      <c r="B72" s="15" t="s">
+      <c r="B72" s="19" t="s">
         <v>137</v>
       </c>
-      <c r="C72" s="15" t="s">
+      <c r="C72" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="D72" s="15" t="s">
+      <c r="D72" s="19" t="s">
         <v>239</v>
       </c>
-      <c r="E72" s="15" t="s">
+      <c r="E72" s="19" t="s">
         <v>240</v>
       </c>
-      <c r="F72" s="15" t="s">
+      <c r="F72" s="19" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="73" ht="68" spans="1:6">
-      <c r="A73" s="9">
+      <c r="A73" s="13">
         <v>63</v>
       </c>
-      <c r="B73" s="15" t="s">
+      <c r="B73" s="19" t="s">
         <v>142</v>
       </c>
-      <c r="C73" s="15" t="s">
+      <c r="C73" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="D73" s="15" t="s">
+      <c r="D73" s="19" t="s">
         <v>229</v>
       </c>
-      <c r="E73" s="15" t="s">
+      <c r="E73" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="F73" s="15" t="s">
+      <c r="F73" s="19" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="74" ht="68" spans="1:6">
-      <c r="A74" s="9">
+      <c r="A74" s="13">
         <v>64</v>
       </c>
-      <c r="B74" s="15" t="s">
+      <c r="B74" s="19" t="s">
         <v>242</v>
       </c>
-      <c r="C74" s="15" t="s">
+      <c r="C74" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="D74" s="15" t="s">
+      <c r="D74" s="19" t="s">
         <v>243</v>
       </c>
-      <c r="E74" s="15" t="s">
+      <c r="E74" s="19" t="s">
         <v>244</v>
       </c>
-      <c r="F74" s="15" t="s">
+      <c r="F74" s="19" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="75" ht="68" spans="1:6">
-      <c r="A75" s="9">
+      <c r="A75" s="13">
         <v>65</v>
       </c>
-      <c r="B75" s="15" t="s">
+      <c r="B75" s="19" t="s">
         <v>245</v>
       </c>
-      <c r="C75" s="15" t="s">
+      <c r="C75" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="D75" s="15" t="s">
+      <c r="D75" s="19" t="s">
         <v>246</v>
       </c>
-      <c r="E75" s="15" t="s">
+      <c r="E75" s="19" t="s">
         <v>244</v>
       </c>
-      <c r="F75" s="15" t="s">
+      <c r="F75" s="19" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="76" spans="1:6">
-      <c r="A76" s="14" t="s">
+      <c r="A76" s="18" t="s">
         <v>247</v>
       </c>
-      <c r="B76" s="14"/>
-      <c r="C76" s="14"/>
-      <c r="D76" s="14"/>
-      <c r="E76" s="14"/>
-      <c r="F76" s="14"/>
+      <c r="B76" s="18"/>
+      <c r="C76" s="18"/>
+      <c r="D76" s="18"/>
+      <c r="E76" s="18"/>
+      <c r="F76" s="18"/>
     </row>
     <row r="77" ht="84" spans="1:6">
-      <c r="A77" s="9">
+      <c r="A77" s="13">
         <v>66</v>
       </c>
-      <c r="B77" s="10" t="s">
+      <c r="B77" s="14" t="s">
         <v>224</v>
       </c>
-      <c r="C77" s="10" t="s">
+      <c r="C77" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="D77" s="15" t="s">
+      <c r="D77" s="19" t="s">
         <v>248</v>
       </c>
-      <c r="E77" s="10" t="s">
+      <c r="E77" s="14" t="s">
         <v>226</v>
       </c>
-      <c r="F77" s="10" t="s">
+      <c r="F77" s="14" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="78" ht="68" spans="1:6">
-      <c r="A78" s="9">
+      <c r="A78" s="13">
         <v>67</v>
       </c>
-      <c r="B78" s="10" t="s">
+      <c r="B78" s="14" t="s">
         <v>249</v>
       </c>
-      <c r="C78" s="10" t="s">
+      <c r="C78" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="D78" s="15" t="s">
+      <c r="D78" s="19" t="s">
         <v>229</v>
       </c>
-      <c r="E78" s="10" t="s">
+      <c r="E78" s="14" t="s">
         <v>230</v>
       </c>
-      <c r="F78" s="10" t="s">
+      <c r="F78" s="14" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="79" ht="68" spans="1:6">
-      <c r="A79" s="9">
+      <c r="A79" s="13">
         <v>68</v>
       </c>
-      <c r="B79" s="10" t="s">
+      <c r="B79" s="14" t="s">
         <v>232</v>
       </c>
-      <c r="C79" s="10" t="s">
+      <c r="C79" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="D79" s="15" t="s">
+      <c r="D79" s="19" t="s">
         <v>233</v>
       </c>
-      <c r="E79" s="10" t="s">
+      <c r="E79" s="14" t="s">
         <v>234</v>
       </c>
-      <c r="F79" s="10" t="s">
+      <c r="F79" s="14" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="80" ht="68" spans="1:6">
-      <c r="A80" s="9">
+      <c r="A80" s="13">
         <v>69</v>
       </c>
-      <c r="B80" s="10" t="s">
+      <c r="B80" s="14" t="s">
         <v>236</v>
       </c>
-      <c r="C80" s="10" t="s">
+      <c r="C80" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="D80" s="15" t="s">
+      <c r="D80" s="19" t="s">
         <v>237</v>
       </c>
-      <c r="E80" s="10" t="s">
+      <c r="E80" s="14" t="s">
         <v>250</v>
       </c>
-      <c r="F80" s="10" t="s">
+      <c r="F80" s="14" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="81" ht="68" spans="1:6">
-      <c r="A81" s="9">
+      <c r="A81" s="13">
         <v>70</v>
       </c>
-      <c r="B81" s="15" t="s">
+      <c r="B81" s="19" t="s">
         <v>137</v>
       </c>
-      <c r="C81" s="15" t="s">
+      <c r="C81" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="D81" s="15" t="s">
+      <c r="D81" s="19" t="s">
         <v>239</v>
       </c>
-      <c r="E81" s="15" t="s">
+      <c r="E81" s="19" t="s">
         <v>160</v>
       </c>
-      <c r="F81" s="15" t="s">
+      <c r="F81" s="19" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="82" ht="68" spans="1:6">
-      <c r="A82" s="9">
+      <c r="A82" s="13">
         <v>71</v>
       </c>
-      <c r="B82" s="15" t="s">
+      <c r="B82" s="19" t="s">
         <v>142</v>
       </c>
-      <c r="C82" s="15" t="s">
+      <c r="C82" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="D82" s="15" t="s">
+      <c r="D82" s="19" t="s">
         <v>229</v>
       </c>
-      <c r="E82" s="15" t="s">
+      <c r="E82" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="F82" s="15" t="s">
+      <c r="F82" s="19" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="83" ht="68" spans="1:6">
-      <c r="A83" s="9">
+      <c r="A83" s="13">
         <v>72</v>
       </c>
-      <c r="B83" s="15" t="s">
+      <c r="B83" s="19" t="s">
         <v>242</v>
       </c>
-      <c r="C83" s="15" t="s">
+      <c r="C83" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="D83" s="15" t="s">
+      <c r="D83" s="19" t="s">
         <v>243</v>
       </c>
-      <c r="E83" s="15" t="s">
+      <c r="E83" s="19" t="s">
         <v>244</v>
       </c>
-      <c r="F83" s="15" t="s">
+      <c r="F83" s="19" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="84" ht="68" spans="1:6">
-      <c r="A84" s="9">
+      <c r="A84" s="13">
         <v>73</v>
       </c>
-      <c r="B84" s="15" t="s">
+      <c r="B84" s="19" t="s">
         <v>245</v>
       </c>
-      <c r="C84" s="15" t="s">
+      <c r="C84" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="D84" s="15" t="s">
+      <c r="D84" s="19" t="s">
         <v>246</v>
       </c>
-      <c r="E84" s="15" t="s">
+      <c r="E84" s="19" t="s">
         <v>244</v>
       </c>
-      <c r="F84" s="15" t="s">
+      <c r="F84" s="19" t="s">
         <v>192</v>
       </c>
     </row>
@@ -5369,832 +5449,832 @@
   <dimension ref="A1:F52"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="4.296875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="26.953125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="23.1796875" style="3" customWidth="1"/>
-    <col min="4" max="4" width="25.6484375" style="3" customWidth="1"/>
-    <col min="5" max="5" width="10.15625" style="3" customWidth="1"/>
-    <col min="6" max="6" width="18.875" style="3" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="4"/>
+    <col min="1" max="1" width="4.296875" style="5" customWidth="1"/>
+    <col min="2" max="2" width="26.953125" style="7" customWidth="1"/>
+    <col min="3" max="3" width="23.1796875" style="7" customWidth="1"/>
+    <col min="4" max="4" width="25.6484375" style="7" customWidth="1"/>
+    <col min="5" max="5" width="10.15625" style="7" customWidth="1"/>
+    <col min="6" max="6" width="18.875" style="7" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="20" customHeight="1" spans="1:6">
-      <c r="A1" s="5" t="s">
+    <row r="1" s="5" customFormat="1" ht="20" customHeight="1" spans="1:6">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="9" t="s">
         <v>251</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="9" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" s="2" customFormat="1" ht="20" customHeight="1" spans="1:6">
-      <c r="A2" s="6" t="s">
+    <row r="2" s="6" customFormat="1" ht="20" customHeight="1" spans="1:6">
+      <c r="A2" s="10" t="s">
         <v>252</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
     </row>
     <row r="3" ht="34" spans="1:5">
-      <c r="A3" s="1">
+      <c r="A3" s="5">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="7" t="s">
         <v>253</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="7" t="s">
         <v>255</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="7" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="4" ht="84" spans="1:5">
-      <c r="A4" s="1">
+      <c r="A4" s="5">
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="7" t="s">
         <v>257</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="7" t="s">
         <v>258</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="7" t="s">
         <v>255</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="7" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="5" s="3" customFormat="1" ht="51" spans="1:5">
-      <c r="A5" s="1">
+    <row r="5" s="7" customFormat="1" ht="51" spans="1:5">
+      <c r="A5" s="5">
         <v>3</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="7" t="s">
         <v>253</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="7" t="s">
         <v>259</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="7" t="s">
         <v>255</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="7" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" spans="1:1">
-      <c r="A6" s="1" t="s">
+    <row r="6" s="5" customFormat="1" spans="1:1">
+      <c r="A6" s="5" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="7" ht="34" spans="1:6">
-      <c r="A7" s="1">
+      <c r="A7" s="5">
         <v>3</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="7" t="s">
         <v>261</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="7" t="s">
         <v>262</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="7" t="s">
         <v>256</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="F7" s="5" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="8" ht="51" spans="1:6">
-      <c r="A8" s="1">
+      <c r="A8" s="5">
         <v>4</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="7" t="s">
         <v>264</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="7" t="s">
         <v>265</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="7" t="s">
         <v>266</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="E8" s="7" t="s">
         <v>256</v>
       </c>
-      <c r="F8" s="1"/>
+      <c r="F8" s="5"/>
     </row>
     <row r="9" ht="34" spans="1:6">
-      <c r="A9" s="1">
+      <c r="A9" s="5">
         <v>5</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="7" t="s">
         <v>267</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="7" t="s">
         <v>268</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="7" t="s">
         <v>262</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="7" t="s">
         <v>256</v>
       </c>
-      <c r="F9" s="1"/>
+      <c r="F9" s="5"/>
     </row>
     <row r="10" customFormat="1" ht="40" customHeight="1" spans="1:6">
-      <c r="A10" s="1">
+      <c r="A10" s="5">
         <v>6</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="7" t="s">
         <v>269</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" s="5" t="s">
         <v>271</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="E10" s="7" t="s">
         <v>256</v>
       </c>
-      <c r="F10" s="1"/>
+      <c r="F10" s="5"/>
     </row>
     <row r="11" customFormat="1" ht="39" customHeight="1" spans="1:6">
-      <c r="A11" s="1">
+      <c r="A11" s="5">
         <v>7</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="7" t="s">
         <v>272</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="7" t="s">
         <v>273</v>
       </c>
-      <c r="D11" s="1"/>
-      <c r="E11" s="3" t="s">
+      <c r="D11" s="5"/>
+      <c r="E11" s="7" t="s">
         <v>256</v>
       </c>
-      <c r="F11" s="1"/>
-    </row>
-    <row r="12" s="1" customFormat="1" ht="84" spans="1:5">
-      <c r="A12" s="1">
+      <c r="F11" s="5"/>
+    </row>
+    <row r="12" s="5" customFormat="1" ht="84" spans="1:5">
+      <c r="A12" s="5">
         <v>8</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="5" t="s">
         <v>274</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" s="5" t="s">
         <v>275</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="7" t="s">
         <v>262</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="E12" s="7" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" spans="1:1">
-      <c r="A13" s="1" t="s">
+    <row r="13" s="5" customFormat="1" spans="1:1">
+      <c r="A13" s="5" t="s">
         <v>276</v>
       </c>
     </row>
     <row r="14" ht="68" spans="1:5">
-      <c r="A14" s="1">
+      <c r="A14" s="5">
         <v>9</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="7" t="s">
         <v>277</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="7" t="s">
         <v>278</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="7" t="s">
         <v>279</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="E14" s="7" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="15" ht="68" spans="1:6">
-      <c r="A15" s="1">
+      <c r="A15" s="5">
         <v>10</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="7" t="s">
         <v>280</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="D15" s="7" t="s">
         <v>281</v>
       </c>
-      <c r="E15" s="3" t="s">
+      <c r="E15" s="7" t="s">
         <v>256</v>
       </c>
-      <c r="F15" s="3" t="s">
+      <c r="F15" s="7" t="s">
         <v>282</v>
       </c>
     </row>
     <row r="16" ht="68" spans="1:5">
-      <c r="A16" s="1">
+      <c r="A16" s="5">
         <v>11</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="7" t="s">
         <v>283</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D16" s="7" t="s">
         <v>281</v>
       </c>
-      <c r="E16" s="3" t="s">
+      <c r="E16" s="7" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="1" spans="1:1">
-      <c r="A17" s="1" t="s">
+    <row r="17" s="5" customFormat="1" spans="1:1">
+      <c r="A17" s="5" t="s">
         <v>284</v>
       </c>
     </row>
     <row r="18" ht="84" spans="1:5">
-      <c r="A18" s="1">
+      <c r="A18" s="5">
         <v>12</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="7" t="s">
         <v>285</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="D18" s="7" t="s">
         <v>286</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="E18" s="7" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="19" ht="34" spans="1:5">
-      <c r="A19" s="1">
+      <c r="A19" s="5">
         <v>13</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="7" t="s">
         <v>287</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="7" t="s">
         <v>288</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="D19" s="7" t="s">
         <v>289</v>
       </c>
-      <c r="E19" s="3" t="s">
+      <c r="E19" s="7" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="20" ht="34" spans="1:5">
-      <c r="A20" s="1">
+      <c r="A20" s="5">
         <v>14</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" s="5" t="s">
         <v>290</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="7" t="s">
         <v>291</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="D20" s="7" t="s">
         <v>292</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="E20" s="7" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="21" ht="41" customHeight="1" spans="1:5">
-      <c r="A21" s="1">
+      <c r="A21" s="5">
         <v>15</v>
       </c>
-      <c r="B21" s="1"/>
-      <c r="C21" s="3" t="s">
+      <c r="B21" s="5"/>
+      <c r="C21" s="7" t="s">
         <v>293</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="D21" s="7" t="s">
         <v>294</v>
       </c>
-      <c r="E21" s="3" t="s">
+      <c r="E21" s="7" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="22" ht="34" spans="1:5">
-      <c r="A22" s="1">
+      <c r="A22" s="5">
         <v>16</v>
       </c>
-      <c r="B22" s="1"/>
-      <c r="C22" s="3" t="s">
+      <c r="B22" s="5"/>
+      <c r="C22" s="7" t="s">
         <v>295</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="D22" s="7" t="s">
         <v>296</v>
       </c>
-      <c r="E22" s="3" t="s">
+      <c r="E22" s="7" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="1" t="s">
+      <c r="A23" s="5" t="s">
         <v>297</v>
       </c>
     </row>
     <row r="24" ht="85" customHeight="1" spans="1:5">
-      <c r="A24" s="1">
+      <c r="A24" s="5">
         <v>17</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="7" t="s">
         <v>298</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="C24" s="7" t="s">
         <v>299</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="D24" s="7" t="s">
         <v>300</v>
       </c>
-      <c r="E24" s="3" t="s">
+      <c r="E24" s="7" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="25" ht="51" spans="1:5">
-      <c r="A25" s="1">
+      <c r="A25" s="5">
         <v>18</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="7" t="s">
         <v>301</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="C25" s="7" t="s">
         <v>302</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="D25" s="7" t="s">
         <v>303</v>
       </c>
-      <c r="E25" s="3" t="s">
+      <c r="E25" s="7" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="26" ht="51" spans="1:5">
-      <c r="A26" s="1">
+      <c r="A26" s="5">
         <v>19</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B26" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="C26" s="7" t="s">
         <v>302</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="D26" s="7" t="s">
         <v>305</v>
       </c>
-      <c r="E26" s="3" t="s">
+      <c r="E26" s="7" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="27" ht="51" spans="1:5">
-      <c r="A27" s="1">
+      <c r="A27" s="5">
         <v>20</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B27" s="7" t="s">
         <v>306</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="C27" s="7" t="s">
         <v>307</v>
       </c>
-      <c r="D27" s="3" t="s">
+      <c r="D27" s="7" t="s">
         <v>292</v>
       </c>
-      <c r="E27" s="3" t="s">
+      <c r="E27" s="7" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="28" ht="51" spans="1:5">
-      <c r="A28" s="1">
+      <c r="A28" s="5">
         <v>21</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B28" s="7" t="s">
         <v>306</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="C28" s="7" t="s">
         <v>308</v>
       </c>
-      <c r="D28" s="3" t="s">
+      <c r="D28" s="7" t="s">
         <v>309</v>
       </c>
-      <c r="E28" s="3" t="s">
+      <c r="E28" s="7" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="29" ht="68" spans="1:5">
-      <c r="A29" s="1">
+      <c r="A29" s="5">
         <v>22</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B29" s="7" t="s">
         <v>306</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="C29" s="7" t="s">
         <v>310</v>
       </c>
-      <c r="D29" s="3" t="s">
+      <c r="D29" s="7" t="s">
         <v>311</v>
       </c>
-      <c r="E29" s="3" t="s">
+      <c r="E29" s="7" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="30" ht="84" spans="1:6">
-      <c r="A30" s="1">
+      <c r="A30" s="5">
         <v>23</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B30" s="7" t="s">
         <v>301</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="C30" s="7" t="s">
         <v>312</v>
       </c>
-      <c r="D30" s="3" t="s">
+      <c r="D30" s="7" t="s">
         <v>313</v>
       </c>
-      <c r="E30" s="3" t="s">
+      <c r="E30" s="7" t="s">
         <v>256</v>
       </c>
-      <c r="F30" s="3" t="s">
+      <c r="F30" s="7" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="31" ht="84" spans="1:5">
-      <c r="A31" s="1">
+      <c r="A31" s="5">
         <v>24</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B31" s="7" t="s">
         <v>315</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="C31" s="7" t="s">
         <v>316</v>
       </c>
-      <c r="D31" s="3" t="s">
+      <c r="D31" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="E31" s="3" t="s">
+      <c r="E31" s="7" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="32" ht="51" spans="1:5">
-      <c r="A32" s="1">
+      <c r="A32" s="5">
         <v>25</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="B32" s="7" t="s">
         <v>315</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="C32" s="7" t="s">
         <v>318</v>
       </c>
-      <c r="D32" s="3" t="s">
+      <c r="D32" s="7" t="s">
         <v>319</v>
       </c>
-      <c r="E32" s="3" t="s">
+      <c r="E32" s="7" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="33" ht="34" spans="1:5">
-      <c r="A33" s="1">
+      <c r="A33" s="5">
         <v>26</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="B33" s="7" t="s">
         <v>320</v>
       </c>
-      <c r="C33" s="3" t="s">
+      <c r="C33" s="7" t="s">
         <v>321</v>
       </c>
-      <c r="D33" s="3" t="s">
+      <c r="D33" s="7" t="s">
         <v>292</v>
       </c>
-      <c r="E33" s="3" t="s">
+      <c r="E33" s="7" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="34" ht="84" spans="1:5">
-      <c r="A34" s="1">
+      <c r="A34" s="5">
         <v>27</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="B34" s="7" t="s">
         <v>320</v>
       </c>
-      <c r="C34" s="7" t="s">
+      <c r="C34" s="11" t="s">
         <v>322</v>
       </c>
-      <c r="D34" s="3" t="s">
+      <c r="D34" s="7" t="s">
         <v>323</v>
       </c>
-      <c r="E34" s="3" t="s">
+      <c r="E34" s="7" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="35" ht="51" spans="1:5">
-      <c r="A35" s="1">
+      <c r="A35" s="5">
         <v>28</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B35" s="7" t="s">
         <v>320</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="C35" s="7" t="s">
         <v>324</v>
       </c>
-      <c r="D35" s="3" t="s">
+      <c r="D35" s="7" t="s">
         <v>325</v>
       </c>
-      <c r="E35" s="3" t="s">
+      <c r="E35" s="7" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="36" ht="51" spans="1:5">
-      <c r="A36" s="1">
+      <c r="A36" s="5">
         <v>29</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="B36" s="7" t="s">
         <v>320</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="C36" s="7" t="s">
         <v>326</v>
       </c>
-      <c r="D36" s="3" t="s">
+      <c r="D36" s="7" t="s">
         <v>327</v>
       </c>
-      <c r="E36" s="3" t="s">
+      <c r="E36" s="7" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="37" ht="34" spans="1:5">
-      <c r="A37" s="1">
+      <c r="A37" s="5">
         <v>30</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="B37" s="7" t="s">
         <v>320</v>
       </c>
-      <c r="C37" s="3" t="s">
+      <c r="C37" s="7" t="s">
         <v>328</v>
       </c>
-      <c r="D37" s="3" t="s">
+      <c r="D37" s="7" t="s">
         <v>329</v>
       </c>
-      <c r="E37" s="3" t="s">
+      <c r="E37" s="7" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="38" ht="51" spans="1:5">
-      <c r="A38" s="1">
+      <c r="A38" s="5">
         <v>31</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="B38" s="7" t="s">
         <v>320</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="C38" s="7" t="s">
         <v>330</v>
       </c>
-      <c r="D38" s="3" t="s">
+      <c r="D38" s="7" t="s">
         <v>331</v>
       </c>
-      <c r="E38" s="3" t="s">
+      <c r="E38" s="7" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="39" ht="17" spans="1:5">
-      <c r="A39" s="1">
+      <c r="A39" s="5">
         <v>32</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="B39" s="7" t="s">
         <v>315</v>
       </c>
-      <c r="C39" s="3" t="s">
+      <c r="C39" s="7" t="s">
         <v>332</v>
       </c>
-      <c r="D39" s="3" t="s">
+      <c r="D39" s="7" t="s">
         <v>333</v>
       </c>
-      <c r="E39" s="3" t="s">
+      <c r="E39" s="7" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="40" ht="84" spans="1:5">
-      <c r="A40" s="1">
+      <c r="A40" s="5">
         <v>33</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="B40" s="7" t="s">
         <v>334</v>
       </c>
-      <c r="C40" s="3" t="s">
+      <c r="C40" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="D40" s="3" t="s">
+      <c r="D40" s="7" t="s">
         <v>335</v>
       </c>
-      <c r="E40" s="3" t="s">
+      <c r="E40" s="7" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="41" ht="68" spans="1:6">
-      <c r="A41" s="1">
+      <c r="A41" s="5">
         <v>34</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="B41" s="7" t="s">
         <v>315</v>
       </c>
-      <c r="C41" s="3" t="s">
+      <c r="C41" s="7" t="s">
         <v>336</v>
       </c>
-      <c r="D41" s="3" t="s">
+      <c r="D41" s="7" t="s">
         <v>337</v>
       </c>
-      <c r="E41" s="3" t="s">
+      <c r="E41" s="7" t="s">
         <v>256</v>
       </c>
-      <c r="F41" s="3" t="s">
+      <c r="F41" s="7" t="s">
         <v>338</v>
       </c>
     </row>
     <row r="42" ht="84" spans="1:5">
-      <c r="A42" s="1">
+      <c r="A42" s="5">
         <v>35</v>
       </c>
-      <c r="B42" s="3" t="s">
+      <c r="B42" s="7" t="s">
         <v>339</v>
       </c>
-      <c r="C42" s="3" t="s">
+      <c r="C42" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="D42" s="3" t="s">
+      <c r="D42" s="7" t="s">
         <v>335</v>
       </c>
-      <c r="E42" s="3" t="s">
+      <c r="E42" s="7" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="43" spans="1:6">
-      <c r="A43" s="1" t="s">
+      <c r="A43" s="5" t="s">
         <v>340</v>
       </c>
-      <c r="B43" s="1"/>
-      <c r="C43" s="1"/>
-      <c r="D43" s="1"/>
-      <c r="E43" s="1"/>
-      <c r="F43" s="1"/>
+      <c r="B43" s="5"/>
+      <c r="C43" s="5"/>
+      <c r="D43" s="5"/>
+      <c r="E43" s="5"/>
+      <c r="F43" s="5"/>
     </row>
     <row r="44" ht="37" customHeight="1" spans="1:6">
-      <c r="A44" s="1">
+      <c r="A44" s="5">
         <v>36</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="B44" s="7" t="s">
         <v>341</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="C44" s="5" t="s">
         <v>342</v>
       </c>
-      <c r="D44" s="1" t="s">
+      <c r="D44" s="5" t="s">
         <v>343</v>
       </c>
-      <c r="E44" s="3" t="s">
+      <c r="E44" s="7" t="s">
         <v>256</v>
       </c>
-      <c r="F44" s="1" t="s">
+      <c r="F44" s="5" t="s">
         <v>344</v>
       </c>
     </row>
     <row r="45" ht="37" customHeight="1" spans="1:6">
-      <c r="A45" s="1">
+      <c r="A45" s="5">
         <v>37</v>
       </c>
-      <c r="B45" s="3" t="s">
+      <c r="B45" s="7" t="s">
         <v>345</v>
       </c>
-      <c r="C45" s="1"/>
-      <c r="D45" s="1"/>
-      <c r="E45" s="3" t="s">
+      <c r="C45" s="5"/>
+      <c r="D45" s="5"/>
+      <c r="E45" s="7" t="s">
         <v>256</v>
       </c>
-      <c r="F45" s="1"/>
+      <c r="F45" s="5"/>
     </row>
     <row r="46" ht="34" customHeight="1" spans="1:6">
-      <c r="A46" s="1">
+      <c r="A46" s="5">
         <v>38</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="B46" s="7" t="s">
         <v>346</v>
       </c>
-      <c r="C46" s="1"/>
-      <c r="D46" s="1"/>
-      <c r="E46" s="3" t="s">
+      <c r="C46" s="5"/>
+      <c r="D46" s="5"/>
+      <c r="E46" s="7" t="s">
         <v>256</v>
       </c>
-      <c r="F46" s="1"/>
+      <c r="F46" s="5"/>
     </row>
     <row r="47" ht="33" customHeight="1" spans="1:6">
-      <c r="A47" s="1">
+      <c r="A47" s="5">
         <v>39</v>
       </c>
-      <c r="B47" s="3" t="s">
+      <c r="B47" s="7" t="s">
         <v>347</v>
       </c>
-      <c r="C47" s="1"/>
-      <c r="D47" s="1"/>
-      <c r="E47" s="3" t="s">
+      <c r="C47" s="5"/>
+      <c r="D47" s="5"/>
+      <c r="E47" s="7" t="s">
         <v>256</v>
       </c>
-      <c r="F47" s="1"/>
+      <c r="F47" s="5"/>
     </row>
     <row r="48" ht="34" spans="1:6">
-      <c r="A48" s="1">
+      <c r="A48" s="5">
         <v>40</v>
       </c>
-      <c r="B48" s="3" t="s">
+      <c r="B48" s="7" t="s">
         <v>348</v>
       </c>
-      <c r="C48" s="1"/>
-      <c r="D48" s="1"/>
-      <c r="E48" s="3" t="s">
+      <c r="C48" s="5"/>
+      <c r="D48" s="5"/>
+      <c r="E48" s="7" t="s">
         <v>256</v>
       </c>
-      <c r="F48" s="1"/>
+      <c r="F48" s="5"/>
     </row>
     <row r="49" ht="34" spans="1:6">
-      <c r="A49" s="1">
+      <c r="A49" s="5">
         <v>41</v>
       </c>
-      <c r="B49" s="3" t="s">
+      <c r="B49" s="7" t="s">
         <v>349</v>
       </c>
-      <c r="C49" s="1"/>
-      <c r="D49" s="1"/>
-      <c r="E49" s="3" t="s">
+      <c r="C49" s="5"/>
+      <c r="D49" s="5"/>
+      <c r="E49" s="7" t="s">
         <v>256</v>
       </c>
-      <c r="F49" s="1"/>
+      <c r="F49" s="5"/>
     </row>
     <row r="50" ht="34" spans="1:6">
-      <c r="A50" s="1">
+      <c r="A50" s="5">
         <v>42</v>
       </c>
-      <c r="B50" s="3" t="s">
+      <c r="B50" s="7" t="s">
         <v>350</v>
       </c>
-      <c r="C50" s="1"/>
-      <c r="D50" s="1"/>
-      <c r="E50" s="3" t="s">
+      <c r="C50" s="5"/>
+      <c r="D50" s="5"/>
+      <c r="E50" s="7" t="s">
         <v>256</v>
       </c>
-      <c r="F50" s="1"/>
+      <c r="F50" s="5"/>
     </row>
     <row r="51" ht="34" spans="1:6">
-      <c r="A51" s="1">
+      <c r="A51" s="5">
         <v>43</v>
       </c>
-      <c r="B51" s="3" t="s">
+      <c r="B51" s="7" t="s">
         <v>351</v>
       </c>
-      <c r="C51" s="1"/>
-      <c r="D51" s="1"/>
-      <c r="E51" s="3" t="s">
+      <c r="C51" s="5"/>
+      <c r="D51" s="5"/>
+      <c r="E51" s="7" t="s">
         <v>256</v>
       </c>
-      <c r="F51" s="1"/>
+      <c r="F51" s="5"/>
     </row>
     <row r="52" ht="68" spans="1:6">
-      <c r="A52" s="1">
+      <c r="A52" s="5">
         <v>44</v>
       </c>
-      <c r="B52" s="3" t="s">
+      <c r="B52" s="7" t="s">
         <v>352</v>
       </c>
-      <c r="C52" s="3" t="s">
+      <c r="C52" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D52" s="3" t="s">
+      <c r="D52" s="7" t="s">
         <v>353</v>
       </c>
-      <c r="E52" s="3" t="s">
+      <c r="E52" s="7" t="s">
         <v>256</v>
       </c>
-      <c r="F52" s="3" t="s">
+      <c r="F52" s="7" t="s">
         <v>354</v>
       </c>
     </row>
@@ -6216,4 +6296,146 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:I8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="7"/>
+  <cols>
+    <col min="1" max="1" width="4.953125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="27.6015625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="16.40625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="25.2578125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="9.2421875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="19.65625" style="2" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="17" spans="1:9">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="I1" s="4"/>
+    </row>
+    <row r="2" ht="70" customHeight="1" spans="1:9">
+      <c r="A2" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+    </row>
+    <row r="3" ht="118" spans="1:9">
+      <c r="A3" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+    </row>
+    <row r="4" ht="34" spans="1:9">
+      <c r="A4" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+    </row>
+    <row r="5" ht="34" spans="1:9">
+      <c r="A5" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+    </row>
+    <row r="6" spans="8:9">
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+    </row>
+    <row r="7" spans="8:9">
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+    </row>
+    <row r="8" spans="8:9">
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="H1:I8"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/Log/Magic_eraser_test_log.xlsx
+++ b/Log/Magic_eraser_test_log.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16340" firstSheet="2" activeTab="3"/>
+    <workbookView windowWidth="23040" windowHeight="8400" firstSheet="2" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Image_selector_test" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="887" uniqueCount="376">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="899" uniqueCount="385">
   <si>
     <t>TC</t>
   </si>
@@ -1169,6 +1169,35 @@
   </si>
   <si>
     <t>Ẩn dialog, trở về màn "Home"</t>
+  </si>
+  <si>
+    <t>FU05</t>
+  </si>
+  <si>
+    <t>Ở màn hình điện thoại, App chưa được mở, phiên bản hiện tại là 2.23.24,
+server hiện đang trả về: { "latest_version": "3.0.0", "min_supported_version": "2.23.25" }</t>
+  </si>
+  <si>
+    <t>HIện lên message "force update"</t>
+  </si>
+  <si>
+    <t>PENDING</t>
+  </si>
+  <si>
+    <t>latest_version &lt; min_supported_version &lt; curent_version</t>
+  </si>
+  <si>
+    <t>FU06</t>
+  </si>
+  <si>
+    <t>Ở màn hình điện thoại, App chưa được mở, phiên bản hiện tại là 2.23.24, đã skip update
+server hiện đang trả về: { "latest_version": "3.0.0", "min_supported_version": "0.0.0" }</t>
+  </si>
+  <si>
+    <t>Vào màn hình "Home"</t>
+  </si>
+  <si>
+    <t>skip_update_version == 2.23.24</t>
   </si>
 </sst>
 </file>
@@ -1590,6 +1619,19 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color auto="1"/>
       </left>
@@ -1600,19 +1642,6 @@
         <color auto="1"/>
       </top>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1932,7 +1961,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1957,9 +1986,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1984,8 +2010,20 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1993,29 +2031,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2551,44 +2577,44 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:L61"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="16.8"/>
+  <sheetFormatPr defaultColWidth="9.13888888888889" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="4" style="13" customWidth="1"/>
-    <col min="2" max="2" width="31.2890625" style="14" customWidth="1"/>
-    <col min="3" max="3" width="21.7109375" style="14" customWidth="1"/>
-    <col min="4" max="5" width="24.4296875" style="14" customWidth="1"/>
-    <col min="6" max="6" width="30.2890625" style="14" customWidth="1"/>
-    <col min="7" max="7" width="20.140625" style="14" customWidth="1"/>
-    <col min="8" max="8" width="9.140625" style="8"/>
-    <col min="9" max="9" width="17.7109375" style="8" customWidth="1"/>
-    <col min="10" max="16384" width="9.140625" style="8"/>
+    <col min="1" max="1" width="4" style="12" customWidth="1"/>
+    <col min="2" max="2" width="31.287037037037" style="13" customWidth="1"/>
+    <col min="3" max="3" width="21.712962962963" style="13" customWidth="1"/>
+    <col min="4" max="5" width="24.4259259259259" style="13" customWidth="1"/>
+    <col min="6" max="6" width="30.287037037037" style="13" customWidth="1"/>
+    <col min="7" max="7" width="20.1388888888889" style="13" customWidth="1"/>
+    <col min="8" max="8" width="9.13888888888889" style="2"/>
+    <col min="9" max="9" width="17.712962962963" style="2" customWidth="1"/>
+    <col min="10" max="16384" width="9.13888888888889" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.75" spans="1:7">
-      <c r="A1" s="24" t="s">
+    <row r="1" ht="15.15" spans="1:7">
+      <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="25" t="s">
+      <c r="B1" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="25" t="s">
+      <c r="C1" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="25" t="s">
+      <c r="D1" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="25" t="s">
+      <c r="E1" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="25" t="s">
+      <c r="F1" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="27" t="s">
+      <c r="G1" s="25" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" ht="37" customHeight="1" spans="1:12">
-      <c r="A2" s="23">
+      <c r="A2" s="20">
         <v>1</v>
       </c>
       <c r="B2" s="26" t="s">
@@ -2615,1230 +2641,1230 @@
       </c>
       <c r="L2" s="7"/>
     </row>
-    <row r="3" ht="34" spans="1:12">
-      <c r="A3" s="13">
+    <row r="3" ht="28.8" spans="1:12">
+      <c r="A3" s="12">
         <v>2</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="D3" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="E3" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="14" t="s">
+      <c r="F3" s="13" t="s">
         <v>10</v>
       </c>
       <c r="I3" s="7"/>
       <c r="K3" s="7"/>
       <c r="L3" s="7"/>
     </row>
-    <row r="4" ht="34" spans="1:12">
-      <c r="A4" s="13">
+    <row r="4" ht="28.8" spans="1:12">
+      <c r="A4" s="12">
         <v>3</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="14" t="s">
+      <c r="D4" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="14" t="s">
+      <c r="E4" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="14" t="s">
+      <c r="F4" s="13" t="s">
         <v>16</v>
       </c>
       <c r="I4" s="7"/>
       <c r="K4" s="7"/>
       <c r="L4" s="7"/>
     </row>
-    <row r="5" ht="34" spans="1:12">
-      <c r="A5" s="13">
+    <row r="5" ht="28.8" spans="1:12">
+      <c r="A5" s="12">
         <v>4</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="D5" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="E5" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="F5" s="13" t="s">
         <v>18</v>
       </c>
       <c r="I5" s="7"/>
       <c r="K5" s="7"/>
       <c r="L5" s="7"/>
     </row>
-    <row r="6" ht="34" spans="1:12">
-      <c r="A6" s="13">
+    <row r="6" ht="28.8" spans="1:12">
+      <c r="A6" s="12">
         <v>5</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="14" t="s">
+      <c r="D6" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="14" t="s">
+      <c r="E6" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="14" t="s">
+      <c r="F6" s="13" t="s">
         <v>10</v>
       </c>
       <c r="K6" s="7"/>
       <c r="L6" s="7"/>
     </row>
-    <row r="7" ht="17" spans="1:6">
-      <c r="A7" s="13">
+    <row r="7" spans="1:6">
+      <c r="A7" s="12">
         <v>6</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="B7" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="C7" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="14" t="s">
+      <c r="D7" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="14" t="s">
+      <c r="E7" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F7" s="14" t="s">
+      <c r="F7" s="13" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="8" ht="50" customHeight="1" spans="1:6">
-      <c r="A8" s="13">
+      <c r="A8" s="12">
         <v>7</v>
       </c>
-      <c r="B8" s="14" t="s">
+      <c r="B8" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="14" t="s">
+      <c r="C8" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="14" t="s">
+      <c r="D8" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="14" t="s">
+      <c r="E8" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="14" t="s">
+      <c r="F8" s="13" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="9" ht="34" spans="1:6">
-      <c r="A9" s="13">
+    <row r="9" ht="28.8" spans="1:6">
+      <c r="A9" s="12">
         <v>8</v>
       </c>
-      <c r="B9" s="14" t="s">
+      <c r="B9" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="C9" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="14" t="s">
+      <c r="D9" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="14" t="s">
+      <c r="E9" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="F9" s="14" t="s">
+      <c r="F9" s="13" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="10" ht="34" spans="1:6">
-      <c r="A10" s="13">
+    <row r="10" ht="28.8" spans="1:6">
+      <c r="A10" s="12">
         <v>9</v>
       </c>
-      <c r="B10" s="14" t="s">
+      <c r="B10" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="14" t="s">
+      <c r="C10" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="14" t="s">
+      <c r="D10" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E10" s="14" t="s">
+      <c r="E10" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="F10" s="14" t="s">
+      <c r="F10" s="13" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="11" ht="34" spans="1:6">
-      <c r="A11" s="13">
+    <row r="11" ht="28.8" spans="1:6">
+      <c r="A11" s="12">
         <v>10</v>
       </c>
-      <c r="B11" s="14" t="s">
+      <c r="B11" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="C11" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="14" t="s">
+      <c r="D11" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E11" s="14" t="s">
+      <c r="E11" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="F11" s="14" t="s">
+      <c r="F11" s="13" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" ht="34" spans="1:6">
-      <c r="A12" s="13">
+    <row r="12" ht="28.8" spans="1:6">
+      <c r="A12" s="12">
         <v>11</v>
       </c>
-      <c r="B12" s="14" t="s">
+      <c r="B12" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="14" t="s">
+      <c r="C12" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="14" t="s">
+      <c r="D12" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E12" s="14" t="s">
+      <c r="E12" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="F12" s="14" t="s">
+      <c r="F12" s="13" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="13" ht="34" spans="1:6">
-      <c r="A13" s="13">
+    <row r="13" ht="28.8" spans="1:6">
+      <c r="A13" s="12">
         <v>12</v>
       </c>
-      <c r="B13" s="14" t="s">
+      <c r="B13" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="14" t="s">
+      <c r="C13" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D13" s="14" t="s">
+      <c r="D13" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E13" s="14" t="s">
+      <c r="E13" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F13" s="14" t="s">
+      <c r="F13" s="13" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="14" ht="51" spans="1:6">
-      <c r="A14" s="13">
+    <row r="14" ht="43.2" spans="1:6">
+      <c r="A14" s="12">
         <v>13</v>
       </c>
-      <c r="B14" s="14" t="s">
+      <c r="B14" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="14" t="s">
+      <c r="C14" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="D14" s="14" t="s">
+      <c r="D14" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E14" s="14" t="s">
+      <c r="E14" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="F14" s="14" t="s">
+      <c r="F14" s="13" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="15" ht="34" spans="1:6">
-      <c r="A15" s="13">
+    <row r="15" ht="28.8" spans="1:6">
+      <c r="A15" s="12">
         <v>14</v>
       </c>
-      <c r="B15" s="14" t="s">
+      <c r="B15" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="C15" s="14" t="s">
+      <c r="C15" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="D15" s="14" t="s">
+      <c r="D15" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E15" s="14" t="s">
+      <c r="E15" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="F15" s="14" t="s">
+      <c r="F15" s="13" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="16" ht="34" spans="1:6">
-      <c r="A16" s="13">
+    <row r="16" ht="28.8" spans="1:6">
+      <c r="A16" s="12">
         <v>15</v>
       </c>
-      <c r="B16" s="14" t="s">
+      <c r="B16" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="C16" s="14" t="s">
+      <c r="C16" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="D16" s="14" t="s">
+      <c r="D16" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E16" s="14" t="s">
+      <c r="E16" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="F16" s="14" t="s">
+      <c r="F16" s="13" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="17" ht="34" spans="1:6">
-      <c r="A17" s="13">
+    <row r="17" ht="28.8" spans="1:6">
+      <c r="A17" s="12">
         <v>16</v>
       </c>
-      <c r="B17" s="14" t="s">
+      <c r="B17" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="C17" s="14" t="s">
+      <c r="C17" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="D17" s="14" t="s">
+      <c r="D17" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E17" s="14" t="s">
+      <c r="E17" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F17" s="14" t="s">
+      <c r="F17" s="13" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="18" ht="34" spans="1:6">
-      <c r="A18" s="13">
+    <row r="18" ht="28.8" spans="1:6">
+      <c r="A18" s="12">
         <v>17</v>
       </c>
-      <c r="B18" s="14" t="s">
+      <c r="B18" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="C18" s="14" t="s">
+      <c r="C18" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="D18" s="14" t="s">
+      <c r="D18" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E18" s="14" t="s">
+      <c r="E18" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="F18" s="14" t="s">
+      <c r="F18" s="13" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="19" ht="34" spans="1:6">
-      <c r="A19" s="13">
+    <row r="19" ht="28.8" spans="1:6">
+      <c r="A19" s="12">
         <v>18</v>
       </c>
-      <c r="B19" s="14" t="s">
+      <c r="B19" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="C19" s="14" t="s">
+      <c r="C19" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D19" s="14" t="s">
+      <c r="D19" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E19" s="14" t="s">
+      <c r="E19" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F19" s="14" t="s">
+      <c r="F19" s="13" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="20" ht="51" spans="1:6">
-      <c r="A20" s="13">
+    <row r="20" ht="43.2" spans="1:6">
+      <c r="A20" s="12">
         <v>19</v>
       </c>
-      <c r="B20" s="14" t="s">
+      <c r="B20" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="C20" s="14" t="s">
+      <c r="C20" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="D20" s="14" t="s">
+      <c r="D20" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E20" s="14" t="s">
+      <c r="E20" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="F20" s="14" t="s">
+      <c r="F20" s="13" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="21" ht="34" spans="1:6">
-      <c r="A21" s="13">
+    <row r="21" ht="28.8" spans="1:6">
+      <c r="A21" s="12">
         <v>20</v>
       </c>
-      <c r="B21" s="14" t="s">
+      <c r="B21" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="C21" s="14" t="s">
+      <c r="C21" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="D21" s="14" t="s">
+      <c r="D21" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E21" s="14" t="s">
+      <c r="E21" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="F21" s="14" t="s">
+      <c r="F21" s="13" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="22" ht="34" spans="1:6">
-      <c r="A22" s="13">
+    <row r="22" ht="28.8" spans="1:6">
+      <c r="A22" s="12">
         <v>21</v>
       </c>
-      <c r="B22" s="14" t="s">
+      <c r="B22" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="C22" s="14" t="s">
+      <c r="C22" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="D22" s="14" t="s">
+      <c r="D22" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E22" s="14" t="s">
+      <c r="E22" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="F22" s="14" t="s">
+      <c r="F22" s="13" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="23" ht="34" spans="1:6">
-      <c r="A23" s="13">
+    <row r="23" ht="28.8" spans="1:6">
+      <c r="A23" s="12">
         <v>22</v>
       </c>
-      <c r="B23" s="14" t="s">
+      <c r="B23" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="C23" s="14" t="s">
+      <c r="C23" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="D23" s="14" t="s">
+      <c r="D23" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E23" s="14" t="s">
+      <c r="E23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F23" s="14" t="s">
+      <c r="F23" s="13" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="24" ht="34" spans="1:6">
-      <c r="A24" s="13">
+    <row r="24" ht="28.8" spans="1:6">
+      <c r="A24" s="12">
         <v>23</v>
       </c>
-      <c r="B24" s="14" t="s">
+      <c r="B24" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="C24" s="14" t="s">
+      <c r="C24" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="D24" s="14" t="s">
+      <c r="D24" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E24" s="14" t="s">
+      <c r="E24" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="F24" s="14" t="s">
+      <c r="F24" s="13" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="25" ht="34" spans="1:6">
-      <c r="A25" s="13">
+    <row r="25" ht="28.8" spans="1:6">
+      <c r="A25" s="12">
         <v>24</v>
       </c>
-      <c r="B25" s="14" t="s">
+      <c r="B25" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C25" s="14" t="s">
+      <c r="C25" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="D25" s="14" t="s">
+      <c r="D25" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E25" s="14" t="s">
+      <c r="E25" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="F25" s="14" t="s">
+      <c r="F25" s="13" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="26" ht="34" spans="1:6">
-      <c r="A26" s="13">
+    <row r="26" ht="28.8" spans="1:6">
+      <c r="A26" s="12">
         <v>25</v>
       </c>
-      <c r="B26" s="14" t="s">
+      <c r="B26" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="C26" s="14" t="s">
+      <c r="C26" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="D26" s="14" t="s">
+      <c r="D26" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E26" s="14" t="s">
+      <c r="E26" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="F26" s="14" t="s">
+      <c r="F26" s="13" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="27" ht="51" spans="1:6">
-      <c r="A27" s="13">
+    <row r="27" ht="43.2" spans="1:6">
+      <c r="A27" s="12">
         <v>26</v>
       </c>
-      <c r="B27" s="14" t="s">
+      <c r="B27" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="C27" s="14" t="s">
+      <c r="C27" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="D27" s="14" t="s">
+      <c r="D27" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E27" s="14" t="s">
+      <c r="E27" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="F27" s="14" t="s">
+      <c r="F27" s="13" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="28" ht="51" spans="1:6">
-      <c r="A28" s="13">
+    <row r="28" ht="43.2" spans="1:6">
+      <c r="A28" s="12">
         <v>27</v>
       </c>
-      <c r="B28" s="14" t="s">
+      <c r="B28" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="C28" s="14" t="s">
+      <c r="C28" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="D28" s="14" t="s">
+      <c r="D28" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E28" s="14" t="s">
+      <c r="E28" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="F28" s="14" t="s">
+      <c r="F28" s="13" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="29" ht="51" spans="1:6">
-      <c r="A29" s="13">
+    <row r="29" ht="43.2" spans="1:6">
+      <c r="A29" s="12">
         <v>28</v>
       </c>
-      <c r="B29" s="14" t="s">
+      <c r="B29" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="C29" s="14" t="s">
+      <c r="C29" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="D29" s="14" t="s">
+      <c r="D29" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E29" s="14" t="s">
+      <c r="E29" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="F29" s="14" t="s">
+      <c r="F29" s="13" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="30" ht="51" spans="1:6">
-      <c r="A30" s="13">
+    <row r="30" ht="43.2" spans="1:6">
+      <c r="A30" s="12">
         <v>29</v>
       </c>
-      <c r="B30" s="14" t="s">
+      <c r="B30" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="C30" s="14" t="s">
+      <c r="C30" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="D30" s="14" t="s">
+      <c r="D30" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E30" s="14" t="s">
+      <c r="E30" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="F30" s="14" t="s">
+      <c r="F30" s="13" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="31" ht="51" spans="1:6">
-      <c r="A31" s="13">
+    <row r="31" ht="43.2" spans="1:6">
+      <c r="A31" s="12">
         <v>30</v>
       </c>
-      <c r="B31" s="14" t="s">
+      <c r="B31" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="C31" s="14" t="s">
+      <c r="C31" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="D31" s="14" t="s">
+      <c r="D31" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="E31" s="14" t="s">
+      <c r="E31" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="F31" s="14" t="s">
+      <c r="F31" s="13" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="32" ht="51" spans="1:6">
-      <c r="A32" s="13">
+    <row r="32" ht="43.2" spans="1:6">
+      <c r="A32" s="12">
         <v>31</v>
       </c>
-      <c r="B32" s="14" t="s">
+      <c r="B32" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="C32" s="14" t="s">
+      <c r="C32" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="D32" s="14" t="s">
+      <c r="D32" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="E32" s="14" t="s">
+      <c r="E32" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="F32" s="14" t="s">
+      <c r="F32" s="13" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="33" ht="51" spans="1:6">
-      <c r="A33" s="13">
+    <row r="33" ht="43.2" spans="1:6">
+      <c r="A33" s="12">
         <v>32</v>
       </c>
-      <c r="B33" s="14" t="s">
+      <c r="B33" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="C33" s="14" t="s">
+      <c r="C33" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="D33" s="14" t="s">
+      <c r="D33" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="E33" s="14" t="s">
+      <c r="E33" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="F33" s="14" t="s">
+      <c r="F33" s="13" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="34" ht="51" spans="1:6">
-      <c r="A34" s="13">
+    <row r="34" ht="43.2" spans="1:6">
+      <c r="A34" s="12">
         <v>33</v>
       </c>
-      <c r="B34" s="14" t="s">
+      <c r="B34" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="C34" s="14" t="s">
+      <c r="C34" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="D34" s="14" t="s">
+      <c r="D34" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="E34" s="14" t="s">
+      <c r="E34" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="F34" s="14" t="s">
+      <c r="F34" s="13" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="35" ht="34" spans="1:6">
-      <c r="A35" s="13">
+    <row r="35" ht="28.8" spans="1:6">
+      <c r="A35" s="12">
         <v>34</v>
       </c>
-      <c r="B35" s="14" t="s">
+      <c r="B35" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="C35" s="14" t="s">
+      <c r="C35" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="D35" s="14" t="s">
+      <c r="D35" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E35" s="14" t="s">
+      <c r="E35" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="F35" s="14" t="s">
+      <c r="F35" s="13" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="36" ht="51" spans="1:7">
-      <c r="A36" s="13">
+    <row r="36" ht="43.2" spans="1:7">
+      <c r="A36" s="12">
         <v>35</v>
       </c>
-      <c r="B36" s="14" t="s">
+      <c r="B36" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="C36" s="14" t="s">
+      <c r="C36" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="D36" s="14" t="s">
+      <c r="D36" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E36" s="14" t="s">
+      <c r="E36" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="F36" s="14" t="s">
+      <c r="F36" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="G36" s="13" t="s">
+      <c r="G36" s="12" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="37" ht="101" spans="1:7">
-      <c r="A37" s="13">
+    <row r="37" ht="72" spans="1:7">
+      <c r="A37" s="12">
         <v>36</v>
       </c>
-      <c r="B37" s="14" t="s">
+      <c r="B37" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="C37" s="14" t="s">
+      <c r="C37" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="D37" s="14" t="s">
+      <c r="D37" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E37" s="14" t="s">
+      <c r="E37" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="F37" s="14" t="s">
+      <c r="F37" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="G37" s="13"/>
-    </row>
-    <row r="38" ht="101" spans="1:7">
-      <c r="A38" s="13">
+      <c r="G37" s="12"/>
+    </row>
+    <row r="38" ht="72" spans="1:7">
+      <c r="A38" s="12">
         <v>37</v>
       </c>
-      <c r="B38" s="14" t="s">
+      <c r="B38" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="C38" s="14" t="s">
+      <c r="C38" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="D38" s="14" t="s">
+      <c r="D38" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E38" s="14" t="s">
+      <c r="E38" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="F38" s="14" t="s">
+      <c r="F38" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="G38" s="13"/>
-    </row>
-    <row r="39" ht="118" spans="1:7">
-      <c r="A39" s="13">
+      <c r="G38" s="12"/>
+    </row>
+    <row r="39" ht="100.8" spans="1:7">
+      <c r="A39" s="12">
         <v>38</v>
       </c>
-      <c r="B39" s="14" t="s">
+      <c r="B39" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="C39" s="14" t="s">
+      <c r="C39" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="D39" s="14" t="s">
+      <c r="D39" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E39" s="14" t="s">
+      <c r="E39" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="F39" s="14" t="s">
+      <c r="F39" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="G39" s="13"/>
-    </row>
-    <row r="40" ht="51" spans="1:7">
-      <c r="A40" s="13">
+      <c r="G39" s="12"/>
+    </row>
+    <row r="40" ht="43.2" spans="1:7">
+      <c r="A40" s="12">
         <v>39</v>
       </c>
-      <c r="B40" s="14" t="s">
+      <c r="B40" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="C40" s="14" t="s">
+      <c r="C40" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="D40" s="14" t="s">
+      <c r="D40" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E40" s="14" t="s">
+      <c r="E40" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="F40" s="14" t="s">
+      <c r="F40" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="G40" s="13"/>
-    </row>
-    <row r="41" ht="101" spans="1:7">
-      <c r="A41" s="13">
+      <c r="G40" s="12"/>
+    </row>
+    <row r="41" ht="86.4" spans="1:7">
+      <c r="A41" s="12">
         <v>40</v>
       </c>
-      <c r="B41" s="14" t="s">
+      <c r="B41" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="C41" s="14" t="s">
+      <c r="C41" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="D41" s="14" t="s">
+      <c r="D41" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E41" s="14" t="s">
+      <c r="E41" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="F41" s="14" t="s">
+      <c r="F41" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="G41" s="14" t="s">
+      <c r="G41" s="13" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="42" ht="84" spans="1:7">
-      <c r="A42" s="13">
+    <row r="42" ht="72" spans="1:7">
+      <c r="A42" s="12">
         <v>41</v>
       </c>
-      <c r="B42" s="14" t="s">
+      <c r="B42" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="C42" s="14" t="s">
+      <c r="C42" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="D42" s="14" t="s">
+      <c r="D42" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E42" s="14" t="s">
+      <c r="E42" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="F42" s="14" t="s">
+      <c r="F42" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="G42" s="14" t="s">
+      <c r="G42" s="13" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="43" ht="84" spans="1:7">
-      <c r="A43" s="13">
+    <row r="43" ht="72" spans="1:7">
+      <c r="A43" s="12">
         <v>42</v>
       </c>
-      <c r="B43" s="14" t="s">
+      <c r="B43" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="C43" s="14" t="s">
+      <c r="C43" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="D43" s="14" t="s">
+      <c r="D43" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E43" s="14" t="s">
+      <c r="E43" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="F43" s="14" t="s">
+      <c r="F43" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="G43" s="14" t="s">
+      <c r="G43" s="13" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="44" ht="118" spans="1:7">
-      <c r="A44" s="13">
+    <row r="44" ht="100.8" spans="1:7">
+      <c r="A44" s="12">
         <v>43</v>
       </c>
-      <c r="B44" s="14" t="s">
+      <c r="B44" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="C44" s="14" t="s">
+      <c r="C44" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="D44" s="14" t="s">
+      <c r="D44" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E44" s="14" t="s">
+      <c r="E44" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="F44" s="14" t="s">
+      <c r="F44" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="G44" s="14" t="s">
+      <c r="G44" s="13" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="45" ht="101" spans="1:7">
-      <c r="A45" s="13">
+    <row r="45" ht="86.4" spans="1:7">
+      <c r="A45" s="12">
         <v>44</v>
       </c>
-      <c r="B45" s="14" t="s">
+      <c r="B45" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="C45" s="14" t="s">
+      <c r="C45" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="D45" s="14" t="s">
+      <c r="D45" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E45" s="14" t="s">
+      <c r="E45" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="F45" s="14" t="s">
+      <c r="F45" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="G45" s="14" t="s">
+      <c r="G45" s="13" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="46" ht="118" spans="1:7">
-      <c r="A46" s="13">
+    <row r="46" ht="100.8" spans="1:7">
+      <c r="A46" s="12">
         <v>45</v>
       </c>
-      <c r="B46" s="14" t="s">
+      <c r="B46" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="C46" s="14" t="s">
+      <c r="C46" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="D46" s="14" t="s">
+      <c r="D46" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E46" s="14" t="s">
+      <c r="E46" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="F46" s="14" t="s">
+      <c r="F46" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="G46" s="14" t="s">
+      <c r="G46" s="13" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="47" ht="118" spans="1:7">
-      <c r="A47" s="13">
+    <row r="47" ht="100.8" spans="1:7">
+      <c r="A47" s="12">
         <v>46</v>
       </c>
-      <c r="B47" s="14" t="s">
+      <c r="B47" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="C47" s="14" t="s">
+      <c r="C47" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="D47" s="14" t="s">
+      <c r="D47" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E47" s="14" t="s">
+      <c r="E47" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="F47" s="14" t="s">
+      <c r="F47" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="G47" s="14" t="s">
+      <c r="G47" s="13" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="48" ht="34" spans="1:7">
-      <c r="A48" s="13">
+    <row r="48" ht="28.8" spans="1:7">
+      <c r="A48" s="12">
         <v>47</v>
       </c>
-      <c r="B48" s="14" t="s">
+      <c r="B48" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="C48" s="14" t="s">
+      <c r="C48" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="D48" s="14" t="s">
+      <c r="D48" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E48" s="14" t="s">
+      <c r="E48" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="F48" s="14" t="s">
+      <c r="F48" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="G48" s="14" t="s">
+      <c r="G48" s="13" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="49" ht="34" spans="1:7">
-      <c r="A49" s="13">
+    <row r="49" ht="28.8" spans="1:7">
+      <c r="A49" s="12">
         <v>48</v>
       </c>
-      <c r="B49" s="14" t="s">
+      <c r="B49" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="C49" s="14" t="s">
+      <c r="C49" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="D49" s="14" t="s">
+      <c r="D49" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E49" s="14" t="s">
+      <c r="E49" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="F49" s="14" t="s">
+      <c r="F49" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="G49" s="14" t="s">
+      <c r="G49" s="13" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="50" ht="135" spans="1:7">
-      <c r="A50" s="13">
+    <row r="50" ht="115.2" spans="1:7">
+      <c r="A50" s="12">
         <v>49</v>
       </c>
-      <c r="B50" s="14" t="s">
+      <c r="B50" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="C50" s="14" t="s">
+      <c r="C50" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="D50" s="14" t="s">
+      <c r="D50" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E50" s="14" t="s">
+      <c r="E50" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="F50" s="14" t="s">
+      <c r="F50" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="G50" s="14" t="s">
+      <c r="G50" s="13" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="51" ht="34" spans="1:7">
-      <c r="A51" s="13">
+    <row r="51" ht="28.8" spans="1:7">
+      <c r="A51" s="12">
         <v>50</v>
       </c>
-      <c r="B51" s="14" t="s">
+      <c r="B51" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="C51" s="14" t="s">
+      <c r="C51" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="D51" s="14" t="s">
+      <c r="D51" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E51" s="14" t="s">
+      <c r="E51" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="F51" s="14" t="s">
+      <c r="F51" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="G51" s="14" t="s">
+      <c r="G51" s="13" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="52" ht="68" spans="1:7">
-      <c r="A52" s="13">
+    <row r="52" ht="57.6" spans="1:7">
+      <c r="A52" s="12">
         <v>51</v>
       </c>
-      <c r="B52" s="14" t="s">
+      <c r="B52" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="C52" s="14" t="s">
+      <c r="C52" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="D52" s="14" t="s">
+      <c r="D52" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E52" s="14" t="s">
+      <c r="E52" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="F52" s="13" t="s">
+      <c r="F52" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="G52" s="13" t="s">
+      <c r="G52" s="12" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="53" ht="68" spans="1:7">
-      <c r="A53" s="13">
+    <row r="53" ht="57.6" spans="1:7">
+      <c r="A53" s="12">
         <v>52</v>
       </c>
-      <c r="B53" s="14" t="s">
+      <c r="B53" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="C53" s="14" t="s">
+      <c r="C53" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="D53" s="14" t="s">
+      <c r="D53" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E53" s="14" t="s">
+      <c r="E53" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="F53" s="13"/>
-      <c r="G53" s="13"/>
-    </row>
-    <row r="54" ht="68" spans="1:7">
-      <c r="A54" s="13">
+      <c r="F53" s="12"/>
+      <c r="G53" s="12"/>
+    </row>
+    <row r="54" ht="57.6" spans="1:7">
+      <c r="A54" s="12">
         <v>53</v>
       </c>
-      <c r="B54" s="14" t="s">
+      <c r="B54" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="C54" s="14" t="s">
+      <c r="C54" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="D54" s="14" t="s">
+      <c r="D54" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E54" s="14" t="s">
+      <c r="E54" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="F54" s="13"/>
-      <c r="G54" s="13"/>
-    </row>
-    <row r="55" ht="68" spans="1:7">
-      <c r="A55" s="13">
+      <c r="F54" s="12"/>
+      <c r="G54" s="12"/>
+    </row>
+    <row r="55" ht="57.6" spans="1:7">
+      <c r="A55" s="12">
         <v>54</v>
       </c>
-      <c r="B55" s="14" t="s">
+      <c r="B55" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="C55" s="14" t="s">
+      <c r="C55" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="D55" s="14" t="s">
+      <c r="D55" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E55" s="14" t="s">
+      <c r="E55" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="F55" s="13"/>
-      <c r="G55" s="13"/>
-    </row>
-    <row r="56" ht="68" spans="1:7">
-      <c r="A56" s="13">
+      <c r="F55" s="12"/>
+      <c r="G55" s="12"/>
+    </row>
+    <row r="56" ht="57.6" spans="1:7">
+      <c r="A56" s="12">
         <v>55</v>
       </c>
-      <c r="B56" s="14" t="s">
+      <c r="B56" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="C56" s="14" t="s">
+      <c r="C56" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="D56" s="14" t="s">
+      <c r="D56" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E56" s="14" t="s">
+      <c r="E56" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="F56" s="13"/>
-      <c r="G56" s="13"/>
-    </row>
-    <row r="57" ht="68" spans="1:7">
-      <c r="A57" s="13">
+      <c r="F56" s="12"/>
+      <c r="G56" s="12"/>
+    </row>
+    <row r="57" ht="57.6" spans="1:7">
+      <c r="A57" s="12">
         <v>56</v>
       </c>
-      <c r="B57" s="14" t="s">
+      <c r="B57" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="C57" s="14" t="s">
+      <c r="C57" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="D57" s="14" t="s">
+      <c r="D57" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E57" s="14" t="s">
+      <c r="E57" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="F57" s="13"/>
-      <c r="G57" s="13"/>
-    </row>
-    <row r="58" ht="68" spans="1:7">
-      <c r="A58" s="13">
+      <c r="F57" s="12"/>
+      <c r="G57" s="12"/>
+    </row>
+    <row r="58" ht="57.6" spans="1:7">
+      <c r="A58" s="12">
         <v>57</v>
       </c>
-      <c r="B58" s="14" t="s">
+      <c r="B58" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="C58" s="14" t="s">
+      <c r="C58" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="D58" s="14" t="s">
+      <c r="D58" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E58" s="14" t="s">
+      <c r="E58" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="F58" s="13"/>
-      <c r="G58" s="13"/>
-    </row>
-    <row r="59" ht="68" spans="1:7">
-      <c r="A59" s="13">
+      <c r="F58" s="12"/>
+      <c r="G58" s="12"/>
+    </row>
+    <row r="59" ht="57.6" spans="1:7">
+      <c r="A59" s="12">
         <v>58</v>
       </c>
-      <c r="B59" s="14" t="s">
+      <c r="B59" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="C59" s="14" t="s">
+      <c r="C59" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="D59" s="14" t="s">
+      <c r="D59" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E59" s="14" t="s">
+      <c r="E59" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="F59" s="13"/>
-      <c r="G59" s="13"/>
-    </row>
-    <row r="60" ht="68" spans="1:7">
-      <c r="A60" s="13">
+      <c r="F59" s="12"/>
+      <c r="G59" s="12"/>
+    </row>
+    <row r="60" ht="57.6" spans="1:7">
+      <c r="A60" s="12">
         <v>59</v>
       </c>
-      <c r="B60" s="14" t="s">
+      <c r="B60" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="C60" s="14" t="s">
+      <c r="C60" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="D60" s="14" t="s">
+      <c r="D60" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E60" s="14" t="s">
+      <c r="E60" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="F60" s="13"/>
-      <c r="G60" s="13"/>
-    </row>
-    <row r="61" ht="68" spans="1:7">
-      <c r="A61" s="13">
+      <c r="F60" s="12"/>
+      <c r="G60" s="12"/>
+    </row>
+    <row r="61" ht="57.6" spans="1:7">
+      <c r="A61" s="12">
         <v>60</v>
       </c>
-      <c r="B61" s="14" t="s">
+      <c r="B61" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="C61" s="14" t="s">
+      <c r="C61" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="D61" s="14" t="s">
+      <c r="D61" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E61" s="14" t="s">
+      <c r="E61" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="F61" s="13"/>
-      <c r="G61" s="13"/>
+      <c r="F61" s="12"/>
+      <c r="G61" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -3857,61 +3883,61 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:K84"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="16.8"/>
+  <sheetFormatPr defaultColWidth="9.13888888888889" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="5.140625" style="13" customWidth="1"/>
-    <col min="2" max="2" width="34.140625" style="14" customWidth="1"/>
-    <col min="3" max="3" width="26.859375" style="14" customWidth="1"/>
-    <col min="4" max="4" width="24.859375" style="14" customWidth="1"/>
-    <col min="5" max="5" width="26.140625" style="14" customWidth="1"/>
-    <col min="6" max="6" width="26.2890625" style="14" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="8"/>
+    <col min="1" max="1" width="5.13888888888889" style="12" customWidth="1"/>
+    <col min="2" max="2" width="34.1388888888889" style="13" customWidth="1"/>
+    <col min="3" max="3" width="26.8611111111111" style="13" customWidth="1"/>
+    <col min="4" max="4" width="24.8611111111111" style="13" customWidth="1"/>
+    <col min="5" max="5" width="26.1388888888889" style="13" customWidth="1"/>
+    <col min="6" max="6" width="26.287037037037" style="13" customWidth="1"/>
+    <col min="7" max="16384" width="9.13888888888889" style="2"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:6">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="8" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" s="12" customFormat="1" ht="20" customHeight="1" spans="1:6">
-      <c r="A2" s="15" t="s">
+    <row r="2" s="11" customFormat="1" ht="20" customHeight="1" spans="1:6">
+      <c r="A2" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="20"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="16"/>
     </row>
     <row r="3" ht="118" customHeight="1" spans="1:11">
-      <c r="A3" s="13">
+      <c r="A3" s="12">
         <v>1</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="13" t="s">
         <v>111</v>
       </c>
       <c r="D3" s="17" t="s">
         <v>112</v>
       </c>
-      <c r="E3" s="21" t="s">
+      <c r="E3" s="18" t="s">
         <v>112</v>
       </c>
       <c r="H3" s="5" t="s">
@@ -3922,1503 +3948,1503 @@
       <c r="K3" s="5"/>
     </row>
     <row r="4" ht="101" customHeight="1" spans="1:11">
-      <c r="A4" s="13">
+      <c r="A4" s="12">
         <v>2</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="13" t="s">
         <v>114</v>
       </c>
       <c r="D4" s="17" t="s">
         <v>112</v>
       </c>
-      <c r="E4" s="22"/>
+      <c r="E4" s="19"/>
       <c r="H4" s="5"/>
       <c r="I4" s="5"/>
       <c r="J4" s="5"/>
       <c r="K4" s="5"/>
     </row>
     <row r="5" ht="122" customHeight="1" spans="1:11">
-      <c r="A5" s="13">
+      <c r="A5" s="12">
         <v>3</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="13" t="s">
         <v>115</v>
       </c>
       <c r="D5" s="17" t="s">
         <v>112</v>
       </c>
-      <c r="E5" s="22"/>
+      <c r="E5" s="19"/>
       <c r="H5" s="5"/>
       <c r="I5" s="5"/>
       <c r="J5" s="5"/>
       <c r="K5" s="5"/>
     </row>
-    <row r="6" ht="84" spans="1:5">
-      <c r="A6" s="13">
+    <row r="6" ht="86.4" spans="1:5">
+      <c r="A6" s="12">
         <v>4</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="13" t="s">
         <v>116</v>
       </c>
       <c r="D6" s="17" t="s">
         <v>112</v>
       </c>
-      <c r="E6" s="22"/>
-    </row>
-    <row r="7" customFormat="1" ht="84" spans="1:6">
-      <c r="A7" s="13">
+      <c r="E6" s="19"/>
+    </row>
+    <row r="7" customFormat="1" ht="86.4" spans="1:6">
+      <c r="A7" s="12">
         <v>5</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="B7" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="C7" s="13" t="s">
         <v>117</v>
       </c>
       <c r="D7" s="17" t="s">
         <v>112</v>
       </c>
-      <c r="E7" s="23"/>
-      <c r="F7" s="14"/>
-    </row>
-    <row r="8" customFormat="1" ht="84" spans="1:6">
-      <c r="A8" s="13">
+      <c r="E7" s="20"/>
+      <c r="F7" s="13"/>
+    </row>
+    <row r="8" customFormat="1" ht="86.4" spans="1:6">
+      <c r="A8" s="12">
         <v>6</v>
       </c>
-      <c r="B8" s="14" t="s">
+      <c r="B8" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="C8" s="14" t="s">
+      <c r="C8" s="13" t="s">
         <v>111</v>
       </c>
       <c r="D8" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="E8" s="21" t="s">
+      <c r="E8" s="18" t="s">
         <v>119</v>
       </c>
-      <c r="F8" s="14"/>
-    </row>
-    <row r="9" customFormat="1" ht="84" spans="1:6">
-      <c r="A9" s="13">
+      <c r="F8" s="13"/>
+    </row>
+    <row r="9" customFormat="1" ht="86.4" spans="1:6">
+      <c r="A9" s="12">
         <v>7</v>
       </c>
-      <c r="B9" s="14" t="s">
+      <c r="B9" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="C9" s="13" t="s">
         <v>114</v>
       </c>
       <c r="D9" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="E9" s="22"/>
-      <c r="F9" s="14"/>
-    </row>
-    <row r="10" customFormat="1" ht="84" spans="1:6">
-      <c r="A10" s="13">
+      <c r="E9" s="19"/>
+      <c r="F9" s="13"/>
+    </row>
+    <row r="10" customFormat="1" ht="86.4" spans="1:6">
+      <c r="A10" s="12">
         <v>8</v>
       </c>
-      <c r="B10" s="14" t="s">
+      <c r="B10" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="C10" s="14" t="s">
+      <c r="C10" s="13" t="s">
         <v>115</v>
       </c>
       <c r="D10" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="E10" s="22"/>
-      <c r="F10" s="14"/>
-    </row>
-    <row r="11" customFormat="1" ht="84" spans="1:6">
-      <c r="A11" s="13">
+      <c r="E10" s="19"/>
+      <c r="F10" s="13"/>
+    </row>
+    <row r="11" customFormat="1" ht="86.4" spans="1:6">
+      <c r="A11" s="12">
         <v>9</v>
       </c>
-      <c r="B11" s="14" t="s">
+      <c r="B11" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="C11" s="13" t="s">
         <v>116</v>
       </c>
       <c r="D11" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="E11" s="22"/>
-      <c r="F11" s="14"/>
-    </row>
-    <row r="12" customFormat="1" ht="84" spans="1:6">
-      <c r="A12" s="13">
+      <c r="E11" s="19"/>
+      <c r="F11" s="13"/>
+    </row>
+    <row r="12" customFormat="1" ht="86.4" spans="1:6">
+      <c r="A12" s="12">
         <v>10</v>
       </c>
-      <c r="B12" s="14" t="s">
+      <c r="B12" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="C12" s="14" t="s">
+      <c r="C12" s="13" t="s">
         <v>117</v>
       </c>
       <c r="D12" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="E12" s="23"/>
-      <c r="F12" s="14"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="13"/>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="18" t="s">
+      <c r="A13" s="21" t="s">
         <v>120</v>
       </c>
-      <c r="B13" s="18"/>
-      <c r="C13" s="18"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
-    </row>
-    <row r="14" ht="84" spans="1:6">
-      <c r="A14" s="13">
+      <c r="B13" s="21"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="21"/>
+    </row>
+    <row r="14" ht="72" spans="1:6">
+      <c r="A14" s="12">
         <v>11</v>
       </c>
-      <c r="B14" s="14" t="s">
+      <c r="B14" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="C14" s="14" t="s">
+      <c r="C14" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="D14" s="14" t="s">
+      <c r="D14" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="E14" s="14" t="s">
+      <c r="E14" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="F14" s="14" t="s">
+      <c r="F14" s="13" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="15" ht="68" spans="1:6">
-      <c r="A15" s="13">
+    <row r="15" ht="57.6" spans="1:6">
+      <c r="A15" s="12">
         <v>12</v>
       </c>
-      <c r="B15" s="14" t="s">
+      <c r="B15" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="C15" s="14" t="s">
+      <c r="C15" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="D15" s="14" t="s">
+      <c r="D15" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="E15" s="14" t="s">
+      <c r="E15" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="F15" s="14" t="s">
+      <c r="F15" s="13" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="16" ht="68" spans="1:6">
-      <c r="A16" s="13">
+    <row r="16" ht="57.6" spans="1:6">
+      <c r="A16" s="12">
         <v>13</v>
       </c>
-      <c r="B16" s="14" t="s">
+      <c r="B16" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="C16" s="14" t="s">
+      <c r="C16" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="D16" s="14" t="s">
+      <c r="D16" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="E16" s="14" t="s">
+      <c r="E16" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="F16" s="14" t="s">
+      <c r="F16" s="13" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="17" ht="68" spans="1:6">
-      <c r="A17" s="13">
+    <row r="17" ht="57.6" spans="1:6">
+      <c r="A17" s="12">
         <v>14</v>
       </c>
-      <c r="B17" s="14" t="s">
+      <c r="B17" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="C17" s="14" t="s">
+      <c r="C17" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="D17" s="14" t="s">
+      <c r="D17" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="E17" s="14" t="s">
+      <c r="E17" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="F17" s="14" t="s">
+      <c r="F17" s="13" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="18" ht="90" customHeight="1" spans="1:6">
-      <c r="A18" s="13">
+      <c r="A18" s="12">
         <v>15</v>
       </c>
-      <c r="B18" s="19" t="s">
+      <c r="B18" s="22" t="s">
         <v>137</v>
       </c>
-      <c r="C18" s="19" t="s">
+      <c r="C18" s="22" t="s">
         <v>138</v>
       </c>
-      <c r="D18" s="19" t="s">
+      <c r="D18" s="22" t="s">
         <v>139</v>
       </c>
-      <c r="E18" s="19" t="s">
+      <c r="E18" s="22" t="s">
         <v>140</v>
       </c>
-      <c r="F18" s="19" t="s">
+      <c r="F18" s="22" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="19" ht="66" customHeight="1" spans="1:6">
-      <c r="A19" s="13">
+      <c r="A19" s="12">
         <v>16</v>
       </c>
-      <c r="B19" s="19" t="s">
+      <c r="B19" s="22" t="s">
         <v>142</v>
       </c>
-      <c r="C19" s="19" t="s">
+      <c r="C19" s="22" t="s">
         <v>138</v>
       </c>
-      <c r="D19" s="19" t="s">
+      <c r="D19" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="E19" s="19" t="s">
+      <c r="E19" s="22" t="s">
         <v>128</v>
       </c>
-      <c r="F19" s="19" t="s">
+      <c r="F19" s="22" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="20" ht="79" customHeight="1" spans="1:6">
-      <c r="A20" s="13">
+      <c r="A20" s="12">
         <v>17</v>
       </c>
-      <c r="B20" s="19" t="s">
+      <c r="B20" s="22" t="s">
         <v>145</v>
       </c>
-      <c r="C20" s="19" t="s">
+      <c r="C20" s="22" t="s">
         <v>138</v>
       </c>
-      <c r="D20" s="19" t="s">
+      <c r="D20" s="22" t="s">
         <v>146</v>
       </c>
-      <c r="E20" s="19" t="s">
+      <c r="E20" s="22" t="s">
         <v>147</v>
       </c>
-      <c r="F20" s="19" t="s">
+      <c r="F20" s="22" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="21" ht="80" customHeight="1" spans="1:6">
-      <c r="A21" s="13">
+      <c r="A21" s="12">
         <v>18</v>
       </c>
-      <c r="B21" s="19" t="s">
+      <c r="B21" s="22" t="s">
         <v>149</v>
       </c>
-      <c r="C21" s="19" t="s">
+      <c r="C21" s="22" t="s">
         <v>138</v>
       </c>
-      <c r="D21" s="19" t="s">
+      <c r="D21" s="22" t="s">
         <v>150</v>
       </c>
-      <c r="E21" s="19" t="s">
+      <c r="E21" s="22" t="s">
         <v>132</v>
       </c>
-      <c r="F21" s="19" t="s">
+      <c r="F21" s="22" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="22" ht="17" customHeight="1" spans="1:6">
-      <c r="A22" s="18" t="s">
+      <c r="A22" s="21" t="s">
         <v>152</v>
       </c>
-      <c r="B22" s="18"/>
-      <c r="C22" s="18"/>
-      <c r="D22" s="18"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="18"/>
-    </row>
-    <row r="23" ht="84" spans="1:6">
-      <c r="A23" s="13">
+      <c r="B22" s="21"/>
+      <c r="C22" s="21"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="21"/>
+      <c r="F22" s="21"/>
+    </row>
+    <row r="23" ht="72" spans="1:6">
+      <c r="A23" s="12">
         <v>19</v>
       </c>
-      <c r="B23" s="14" t="s">
+      <c r="B23" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="C23" s="14" t="s">
+      <c r="C23" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="D23" s="14" t="s">
+      <c r="D23" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="E23" s="14" t="s">
+      <c r="E23" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="F23" s="14" t="s">
+      <c r="F23" s="13" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="24" ht="68" spans="1:6">
-      <c r="A24" s="13">
+    <row r="24" ht="57.6" spans="1:6">
+      <c r="A24" s="12">
         <v>20</v>
       </c>
-      <c r="B24" s="14" t="s">
+      <c r="B24" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="C24" s="14" t="s">
+      <c r="C24" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="D24" s="14" t="s">
+      <c r="D24" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="E24" s="14" t="s">
+      <c r="E24" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="F24" s="14" t="s">
+      <c r="F24" s="13" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="25" ht="68" spans="1:6">
-      <c r="A25" s="13">
+    <row r="25" ht="57.6" spans="1:6">
+      <c r="A25" s="12">
         <v>21</v>
       </c>
-      <c r="B25" s="14" t="s">
+      <c r="B25" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="C25" s="14" t="s">
+      <c r="C25" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="D25" s="14" t="s">
+      <c r="D25" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="E25" s="14" t="s">
+      <c r="E25" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="F25" s="14" t="s">
+      <c r="F25" s="13" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="26" ht="68" spans="1:6">
-      <c r="A26" s="13">
+    <row r="26" ht="57.6" spans="1:6">
+      <c r="A26" s="12">
         <v>22</v>
       </c>
-      <c r="B26" s="14" t="s">
+      <c r="B26" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="C26" s="14" t="s">
+      <c r="C26" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="D26" s="14" t="s">
+      <c r="D26" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="E26" s="14" t="s">
+      <c r="E26" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="F26" s="14" t="s">
+      <c r="F26" s="13" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="27" ht="68" spans="1:6">
-      <c r="A27" s="13">
+    <row r="27" ht="57.6" spans="1:6">
+      <c r="A27" s="12">
         <v>23</v>
       </c>
-      <c r="B27" s="19" t="s">
+      <c r="B27" s="22" t="s">
         <v>137</v>
       </c>
-      <c r="C27" s="19" t="s">
+      <c r="C27" s="22" t="s">
         <v>138</v>
       </c>
-      <c r="D27" s="19" t="s">
+      <c r="D27" s="22" t="s">
         <v>154</v>
       </c>
-      <c r="E27" s="19" t="s">
+      <c r="E27" s="22" t="s">
         <v>155</v>
       </c>
-      <c r="F27" s="19" t="s">
+      <c r="F27" s="22" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="28" ht="51" spans="1:6">
-      <c r="A28" s="13">
+    <row r="28" ht="43.2" spans="1:6">
+      <c r="A28" s="12">
         <v>24</v>
       </c>
-      <c r="B28" s="19" t="s">
+      <c r="B28" s="22" t="s">
         <v>142</v>
       </c>
-      <c r="C28" s="19" t="s">
+      <c r="C28" s="22" t="s">
         <v>138</v>
       </c>
-      <c r="D28" s="19" t="s">
+      <c r="D28" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="E28" s="19" t="s">
+      <c r="E28" s="22" t="s">
         <v>128</v>
       </c>
-      <c r="F28" s="19" t="s">
+      <c r="F28" s="22" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="29" ht="68" spans="1:6">
-      <c r="A29" s="13">
+    <row r="29" ht="57.6" spans="1:6">
+      <c r="A29" s="12">
         <v>25</v>
       </c>
-      <c r="B29" s="19" t="s">
+      <c r="B29" s="22" t="s">
         <v>145</v>
       </c>
-      <c r="C29" s="19" t="s">
+      <c r="C29" s="22" t="s">
         <v>138</v>
       </c>
-      <c r="D29" s="19" t="s">
+      <c r="D29" s="22" t="s">
         <v>146</v>
       </c>
-      <c r="E29" s="19" t="s">
+      <c r="E29" s="22" t="s">
         <v>132</v>
       </c>
-      <c r="F29" s="19" t="s">
+      <c r="F29" s="22" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="30" ht="68" spans="1:6">
-      <c r="A30" s="13">
+    <row r="30" ht="57.6" spans="1:6">
+      <c r="A30" s="12">
         <v>26</v>
       </c>
-      <c r="B30" s="19" t="s">
+      <c r="B30" s="22" t="s">
         <v>149</v>
       </c>
-      <c r="C30" s="19" t="s">
+      <c r="C30" s="22" t="s">
         <v>138</v>
       </c>
-      <c r="D30" s="19" t="s">
+      <c r="D30" s="22" t="s">
         <v>150</v>
       </c>
-      <c r="E30" s="19" t="s">
+      <c r="E30" s="22" t="s">
         <v>132</v>
       </c>
-      <c r="F30" s="19" t="s">
+      <c r="F30" s="22" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="31" spans="1:6">
-      <c r="A31" s="18" t="s">
+      <c r="A31" s="21" t="s">
         <v>159</v>
       </c>
-      <c r="B31" s="18"/>
-      <c r="C31" s="18"/>
-      <c r="D31" s="18"/>
-      <c r="E31" s="18"/>
-      <c r="F31" s="18"/>
-    </row>
-    <row r="32" ht="68" spans="1:6">
-      <c r="A32" s="13">
+      <c r="B31" s="21"/>
+      <c r="C31" s="21"/>
+      <c r="D31" s="21"/>
+      <c r="E31" s="21"/>
+      <c r="F31" s="21"/>
+    </row>
+    <row r="32" ht="57.6" spans="1:6">
+      <c r="A32" s="12">
         <v>27</v>
       </c>
-      <c r="B32" s="19" t="s">
+      <c r="B32" s="22" t="s">
         <v>137</v>
       </c>
-      <c r="C32" s="19" t="s">
+      <c r="C32" s="22" t="s">
         <v>138</v>
       </c>
-      <c r="D32" s="19" t="s">
+      <c r="D32" s="22" t="s">
         <v>154</v>
       </c>
-      <c r="E32" s="19" t="s">
+      <c r="E32" s="22" t="s">
         <v>160</v>
       </c>
-      <c r="F32" s="19" t="s">
+      <c r="F32" s="22" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="33" ht="51" spans="1:6">
-      <c r="A33" s="13">
+    <row r="33" ht="43.2" spans="1:6">
+      <c r="A33" s="12">
         <v>28</v>
       </c>
-      <c r="B33" s="19" t="s">
+      <c r="B33" s="22" t="s">
         <v>142</v>
       </c>
-      <c r="C33" s="19" t="s">
+      <c r="C33" s="22" t="s">
         <v>138</v>
       </c>
-      <c r="D33" s="19" t="s">
+      <c r="D33" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="E33" s="19" t="s">
+      <c r="E33" s="22" t="s">
         <v>128</v>
       </c>
-      <c r="F33" s="19" t="s">
+      <c r="F33" s="22" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="34" ht="68" spans="1:6">
-      <c r="A34" s="13">
+    <row r="34" ht="57.6" spans="1:6">
+      <c r="A34" s="12">
         <v>29</v>
       </c>
-      <c r="B34" s="19" t="s">
+      <c r="B34" s="22" t="s">
         <v>145</v>
       </c>
-      <c r="C34" s="19" t="s">
+      <c r="C34" s="22" t="s">
         <v>138</v>
       </c>
-      <c r="D34" s="19" t="s">
+      <c r="D34" s="22" t="s">
         <v>161</v>
       </c>
-      <c r="E34" s="19" t="s">
+      <c r="E34" s="22" t="s">
         <v>132</v>
       </c>
-      <c r="F34" s="19" t="s">
+      <c r="F34" s="22" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="35" ht="68" spans="1:6">
-      <c r="A35" s="13">
+    <row r="35" ht="57.6" spans="1:6">
+      <c r="A35" s="12">
         <v>30</v>
       </c>
-      <c r="B35" s="19" t="s">
+      <c r="B35" s="22" t="s">
         <v>149</v>
       </c>
-      <c r="C35" s="19" t="s">
+      <c r="C35" s="22" t="s">
         <v>138</v>
       </c>
-      <c r="D35" s="19" t="s">
+      <c r="D35" s="22" t="s">
         <v>162</v>
       </c>
-      <c r="E35" s="19" t="s">
+      <c r="E35" s="22" t="s">
         <v>132</v>
       </c>
-      <c r="F35" s="19" t="s">
+      <c r="F35" s="22" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="36" spans="1:6">
-      <c r="A36" s="18" t="s">
+      <c r="A36" s="21" t="s">
         <v>163</v>
       </c>
-      <c r="B36" s="18"/>
-      <c r="C36" s="18"/>
-      <c r="D36" s="18"/>
-      <c r="E36" s="18"/>
-      <c r="F36" s="18"/>
-    </row>
-    <row r="37" ht="84" spans="1:6">
-      <c r="A37" s="13">
+      <c r="B36" s="21"/>
+      <c r="C36" s="21"/>
+      <c r="D36" s="21"/>
+      <c r="E36" s="21"/>
+      <c r="F36" s="21"/>
+    </row>
+    <row r="37" ht="72" spans="1:6">
+      <c r="A37" s="12">
         <v>31</v>
       </c>
-      <c r="B37" s="19" t="s">
+      <c r="B37" s="22" t="s">
         <v>137</v>
       </c>
-      <c r="C37" s="19" t="s">
+      <c r="C37" s="22" t="s">
         <v>138</v>
       </c>
-      <c r="D37" s="19" t="s">
+      <c r="D37" s="22" t="s">
         <v>164</v>
       </c>
-      <c r="E37" s="19" t="s">
+      <c r="E37" s="22" t="s">
         <v>165</v>
       </c>
-      <c r="F37" s="19" t="s">
+      <c r="F37" s="22" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="38" ht="68" spans="1:6">
-      <c r="A38" s="13">
+    <row r="38" ht="57.6" spans="1:6">
+      <c r="A38" s="12">
         <v>32</v>
       </c>
-      <c r="B38" s="19" t="s">
+      <c r="B38" s="22" t="s">
         <v>142</v>
       </c>
-      <c r="C38" s="19" t="s">
+      <c r="C38" s="22" t="s">
         <v>138</v>
       </c>
-      <c r="D38" s="19" t="s">
+      <c r="D38" s="22" t="s">
         <v>166</v>
       </c>
-      <c r="E38" s="19" t="s">
+      <c r="E38" s="22" t="s">
         <v>167</v>
       </c>
-      <c r="F38" s="19" t="s">
+      <c r="F38" s="22" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="39" ht="68" spans="1:6">
-      <c r="A39" s="13">
+    <row r="39" ht="57.6" spans="1:6">
+      <c r="A39" s="12">
         <v>33</v>
       </c>
-      <c r="B39" s="19" t="s">
+      <c r="B39" s="22" t="s">
         <v>145</v>
       </c>
-      <c r="C39" s="19" t="s">
+      <c r="C39" s="22" t="s">
         <v>138</v>
       </c>
-      <c r="D39" s="19" t="s">
+      <c r="D39" s="22" t="s">
         <v>168</v>
       </c>
-      <c r="E39" s="19" t="s">
+      <c r="E39" s="22" t="s">
         <v>169</v>
       </c>
-      <c r="F39" s="19" t="s">
+      <c r="F39" s="22" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="40" ht="68" spans="1:6">
-      <c r="A40" s="13">
+    <row r="40" ht="57.6" spans="1:6">
+      <c r="A40" s="12">
         <v>34</v>
       </c>
-      <c r="B40" s="19" t="s">
+      <c r="B40" s="22" t="s">
         <v>149</v>
       </c>
-      <c r="C40" s="19" t="s">
+      <c r="C40" s="22" t="s">
         <v>138</v>
       </c>
-      <c r="D40" s="19" t="s">
+      <c r="D40" s="22" t="s">
         <v>170</v>
       </c>
-      <c r="E40" s="19" t="s">
+      <c r="E40" s="22" t="s">
         <v>169</v>
       </c>
-      <c r="F40" s="19" t="s">
+      <c r="F40" s="22" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="41" spans="1:6">
-      <c r="A41" s="18" t="s">
+      <c r="A41" s="21" t="s">
         <v>171</v>
       </c>
-      <c r="B41" s="18"/>
-      <c r="C41" s="18"/>
-      <c r="D41" s="18"/>
-      <c r="E41" s="18"/>
-      <c r="F41" s="18"/>
-    </row>
-    <row r="42" ht="84" spans="1:6">
-      <c r="A42" s="13">
+      <c r="B41" s="21"/>
+      <c r="C41" s="21"/>
+      <c r="D41" s="21"/>
+      <c r="E41" s="21"/>
+      <c r="F41" s="21"/>
+    </row>
+    <row r="42" ht="72" spans="1:6">
+      <c r="A42" s="12">
         <v>35</v>
       </c>
-      <c r="B42" s="14" t="s">
+      <c r="B42" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="C42" s="14" t="s">
+      <c r="C42" s="13" t="s">
         <v>173</v>
       </c>
-      <c r="D42" s="19" t="s">
+      <c r="D42" s="22" t="s">
         <v>174</v>
       </c>
-      <c r="E42" s="14" t="s">
+      <c r="E42" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="F42" s="14" t="s">
+      <c r="F42" s="13" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="43" ht="68" spans="1:6">
-      <c r="A43" s="13">
+    <row r="43" ht="57.6" spans="1:6">
+      <c r="A43" s="12">
         <v>36</v>
       </c>
-      <c r="B43" s="14" t="s">
+      <c r="B43" s="13" t="s">
         <v>176</v>
       </c>
-      <c r="C43" s="14" t="s">
+      <c r="C43" s="13" t="s">
         <v>173</v>
       </c>
-      <c r="D43" s="19" t="s">
+      <c r="D43" s="22" t="s">
         <v>177</v>
       </c>
-      <c r="E43" s="14" t="s">
+      <c r="E43" s="13" t="s">
         <v>178</v>
       </c>
-      <c r="F43" s="14" t="s">
+      <c r="F43" s="13" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="44" ht="68" spans="1:6">
-      <c r="A44" s="13">
+    <row r="44" ht="57.6" spans="1:6">
+      <c r="A44" s="12">
         <v>37</v>
       </c>
-      <c r="B44" s="14" t="s">
+      <c r="B44" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="C44" s="14" t="s">
+      <c r="C44" s="13" t="s">
         <v>173</v>
       </c>
-      <c r="D44" s="19" t="s">
+      <c r="D44" s="22" t="s">
         <v>180</v>
       </c>
-      <c r="E44" s="14" t="s">
+      <c r="E44" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="F44" s="14" t="s">
+      <c r="F44" s="13" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="45" ht="68" spans="1:6">
-      <c r="A45" s="13">
+    <row r="45" ht="57.6" spans="1:6">
+      <c r="A45" s="12">
         <v>38</v>
       </c>
-      <c r="B45" s="14" t="s">
+      <c r="B45" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="C45" s="14" t="s">
+      <c r="C45" s="13" t="s">
         <v>173</v>
       </c>
-      <c r="D45" s="19" t="s">
+      <c r="D45" s="22" t="s">
         <v>182</v>
       </c>
-      <c r="E45" s="14" t="s">
+      <c r="E45" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="F45" s="14" t="s">
+      <c r="F45" s="13" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="46" ht="68" spans="1:6">
-      <c r="A46" s="13">
+    <row r="46" ht="57.6" spans="1:6">
+      <c r="A46" s="12">
         <v>39</v>
       </c>
-      <c r="B46" s="19" t="s">
+      <c r="B46" s="22" t="s">
         <v>137</v>
       </c>
-      <c r="C46" s="19" t="s">
+      <c r="C46" s="22" t="s">
         <v>138</v>
       </c>
-      <c r="D46" s="19" t="s">
+      <c r="D46" s="22" t="s">
         <v>184</v>
       </c>
-      <c r="E46" s="19" t="s">
+      <c r="E46" s="22" t="s">
         <v>160</v>
       </c>
-      <c r="F46" s="19" t="s">
+      <c r="F46" s="22" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="47" ht="118" spans="1:6">
-      <c r="A47" s="13">
+    <row r="47" ht="100.8" spans="1:6">
+      <c r="A47" s="12">
         <v>40</v>
       </c>
-      <c r="B47" s="19" t="s">
+      <c r="B47" s="22" t="s">
         <v>142</v>
       </c>
-      <c r="C47" s="19" t="s">
+      <c r="C47" s="22" t="s">
         <v>138</v>
       </c>
-      <c r="D47" s="19" t="s">
+      <c r="D47" s="22" t="s">
         <v>186</v>
       </c>
-      <c r="E47" s="19" t="s">
+      <c r="E47" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="F47" s="19" t="s">
+      <c r="F47" s="22" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="48" ht="68" spans="1:6">
-      <c r="A48" s="13">
+    <row r="48" ht="57.6" spans="1:6">
+      <c r="A48" s="12">
         <v>41</v>
       </c>
-      <c r="B48" s="19" t="s">
+      <c r="B48" s="22" t="s">
         <v>145</v>
       </c>
-      <c r="C48" s="19" t="s">
+      <c r="C48" s="22" t="s">
         <v>138</v>
       </c>
-      <c r="D48" s="19" t="s">
+      <c r="D48" s="22" t="s">
         <v>189</v>
       </c>
-      <c r="E48" s="19" t="s">
+      <c r="E48" s="22" t="s">
         <v>132</v>
       </c>
-      <c r="F48" s="19" t="s">
+      <c r="F48" s="22" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="49" ht="68" spans="1:6">
-      <c r="A49" s="13">
+    <row r="49" ht="57.6" spans="1:6">
+      <c r="A49" s="12">
         <v>42</v>
       </c>
-      <c r="B49" s="19" t="s">
+      <c r="B49" s="22" t="s">
         <v>149</v>
       </c>
-      <c r="C49" s="19" t="s">
+      <c r="C49" s="22" t="s">
         <v>138</v>
       </c>
-      <c r="D49" s="19" t="s">
+      <c r="D49" s="22" t="s">
         <v>191</v>
       </c>
-      <c r="E49" s="19" t="s">
+      <c r="E49" s="22" t="s">
         <v>132</v>
       </c>
-      <c r="F49" s="19" t="s">
+      <c r="F49" s="22" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="A50" s="18" t="s">
+      <c r="A50" s="21" t="s">
         <v>193</v>
       </c>
-      <c r="B50" s="18"/>
-      <c r="C50" s="18"/>
-      <c r="D50" s="18"/>
-      <c r="E50" s="18"/>
-      <c r="F50" s="18"/>
-    </row>
-    <row r="51" ht="68" spans="1:6">
-      <c r="A51" s="13">
+      <c r="B50" s="21"/>
+      <c r="C50" s="21"/>
+      <c r="D50" s="21"/>
+      <c r="E50" s="21"/>
+      <c r="F50" s="21"/>
+    </row>
+    <row r="51" ht="57.6" spans="1:6">
+      <c r="A51" s="12">
         <v>43</v>
       </c>
-      <c r="B51" s="14" t="s">
+      <c r="B51" s="13" t="s">
         <v>194</v>
       </c>
-      <c r="C51" s="14" t="s">
+      <c r="C51" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="D51" s="14" t="s">
+      <c r="D51" s="13" t="s">
         <v>195</v>
       </c>
-      <c r="E51" s="14" t="s">
+      <c r="E51" s="13" t="s">
         <v>196</v>
       </c>
-      <c r="F51" s="14" t="s">
+      <c r="F51" s="13" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="52" ht="68" spans="1:6">
-      <c r="A52" s="13">
+    <row r="52" ht="57.6" spans="1:6">
+      <c r="A52" s="12">
         <v>44</v>
       </c>
-      <c r="B52" s="14" t="s">
+      <c r="B52" s="13" t="s">
         <v>198</v>
       </c>
-      <c r="C52" s="14" t="s">
+      <c r="C52" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="D52" s="14" t="s">
+      <c r="D52" s="13" t="s">
         <v>199</v>
       </c>
-      <c r="E52" s="14" t="s">
+      <c r="E52" s="13" t="s">
         <v>196</v>
       </c>
-      <c r="F52" s="14" t="s">
+      <c r="F52" s="13" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="53" ht="68" spans="1:6">
-      <c r="A53" s="13">
+    <row r="53" ht="57.6" spans="1:6">
+      <c r="A53" s="12">
         <v>45</v>
       </c>
-      <c r="B53" s="14" t="s">
+      <c r="B53" s="13" t="s">
         <v>201</v>
       </c>
-      <c r="C53" s="14" t="s">
+      <c r="C53" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="D53" s="14" t="s">
+      <c r="D53" s="13" t="s">
         <v>202</v>
       </c>
-      <c r="E53" s="14" t="s">
+      <c r="E53" s="13" t="s">
         <v>196</v>
       </c>
-      <c r="F53" s="14" t="s">
+      <c r="F53" s="13" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="54" ht="68" spans="1:6">
-      <c r="A54" s="13">
+    <row r="54" ht="57.6" spans="1:6">
+      <c r="A54" s="12">
         <v>46</v>
       </c>
-      <c r="B54" s="14" t="s">
+      <c r="B54" s="13" t="s">
         <v>204</v>
       </c>
-      <c r="C54" s="19" t="s">
+      <c r="C54" s="22" t="s">
         <v>138</v>
       </c>
-      <c r="D54" s="19" t="s">
+      <c r="D54" s="22" t="s">
         <v>205</v>
       </c>
-      <c r="E54" s="19" t="s">
+      <c r="E54" s="22" t="s">
         <v>160</v>
       </c>
-      <c r="F54" s="19" t="s">
+      <c r="F54" s="22" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="55" ht="68" spans="1:6">
-      <c r="A55" s="13">
+    <row r="55" ht="57.6" spans="1:6">
+      <c r="A55" s="12">
         <v>47</v>
       </c>
-      <c r="B55" s="14" t="s">
+      <c r="B55" s="13" t="s">
         <v>206</v>
       </c>
-      <c r="C55" s="19" t="s">
+      <c r="C55" s="22" t="s">
         <v>138</v>
       </c>
-      <c r="D55" s="19" t="s">
+      <c r="D55" s="22" t="s">
         <v>207</v>
       </c>
-      <c r="E55" s="19" t="s">
+      <c r="E55" s="22" t="s">
         <v>128</v>
       </c>
-      <c r="F55" s="19" t="s">
+      <c r="F55" s="22" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="56" ht="68" spans="1:6">
-      <c r="A56" s="13">
+    <row r="56" ht="57.6" spans="1:6">
+      <c r="A56" s="12">
         <v>48</v>
       </c>
-      <c r="B56" s="14" t="s">
+      <c r="B56" s="13" t="s">
         <v>208</v>
       </c>
-      <c r="C56" s="19" t="s">
+      <c r="C56" s="22" t="s">
         <v>138</v>
       </c>
-      <c r="D56" s="19" t="s">
+      <c r="D56" s="22" t="s">
         <v>209</v>
       </c>
-      <c r="E56" s="19" t="s">
+      <c r="E56" s="22" t="s">
         <v>132</v>
       </c>
-      <c r="F56" s="19" t="s">
+      <c r="F56" s="22" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="57" ht="68" spans="1:6">
-      <c r="A57" s="13">
+    <row r="57" ht="57.6" spans="1:6">
+      <c r="A57" s="12">
         <v>49</v>
       </c>
-      <c r="B57" s="14" t="s">
+      <c r="B57" s="13" t="s">
         <v>210</v>
       </c>
-      <c r="C57" s="19" t="s">
+      <c r="C57" s="22" t="s">
         <v>138</v>
       </c>
-      <c r="D57" s="19" t="s">
+      <c r="D57" s="22" t="s">
         <v>211</v>
       </c>
-      <c r="E57" s="19" t="s">
+      <c r="E57" s="22" t="s">
         <v>132</v>
       </c>
-      <c r="F57" s="19" t="s">
+      <c r="F57" s="22" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="58" spans="1:6">
-      <c r="A58" s="18" t="s">
+      <c r="A58" s="21" t="s">
         <v>212</v>
       </c>
-      <c r="B58" s="18"/>
-      <c r="C58" s="18"/>
-      <c r="D58" s="18"/>
-      <c r="E58" s="18"/>
-      <c r="F58" s="18"/>
-    </row>
-    <row r="59" ht="84" spans="1:6">
-      <c r="A59" s="13">
+      <c r="B58" s="21"/>
+      <c r="C58" s="21"/>
+      <c r="D58" s="21"/>
+      <c r="E58" s="21"/>
+      <c r="F58" s="21"/>
+    </row>
+    <row r="59" ht="72" spans="1:6">
+      <c r="A59" s="12">
         <v>50</v>
       </c>
-      <c r="B59" s="14" t="s">
+      <c r="B59" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="C59" s="14" t="s">
+      <c r="C59" s="13" t="s">
         <v>173</v>
       </c>
-      <c r="D59" s="19" t="s">
+      <c r="D59" s="22" t="s">
         <v>213</v>
       </c>
-      <c r="E59" s="14" t="s">
+      <c r="E59" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="F59" s="14" t="s">
+      <c r="F59" s="13" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="60" ht="68" spans="1:6">
-      <c r="A60" s="13">
+    <row r="60" ht="57.6" spans="1:6">
+      <c r="A60" s="12">
         <v>51</v>
       </c>
-      <c r="B60" s="14" t="s">
+      <c r="B60" s="13" t="s">
         <v>176</v>
       </c>
-      <c r="C60" s="14" t="s">
+      <c r="C60" s="13" t="s">
         <v>173</v>
       </c>
-      <c r="D60" s="19" t="s">
+      <c r="D60" s="22" t="s">
         <v>214</v>
       </c>
-      <c r="E60" s="14" t="s">
+      <c r="E60" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="F60" s="14" t="s">
+      <c r="F60" s="13" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="61" ht="68" spans="1:6">
-      <c r="A61" s="13">
+    <row r="61" ht="57.6" spans="1:6">
+      <c r="A61" s="12">
         <v>52</v>
       </c>
-      <c r="B61" s="14" t="s">
+      <c r="B61" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="C61" s="14" t="s">
+      <c r="C61" s="13" t="s">
         <v>173</v>
       </c>
-      <c r="D61" s="19" t="s">
+      <c r="D61" s="22" t="s">
         <v>215</v>
       </c>
-      <c r="E61" s="14" t="s">
+      <c r="E61" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="F61" s="14" t="s">
+      <c r="F61" s="13" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="62" ht="68" spans="1:6">
-      <c r="A62" s="13">
+    <row r="62" ht="57.6" spans="1:6">
+      <c r="A62" s="12">
         <v>53</v>
       </c>
-      <c r="B62" s="14" t="s">
+      <c r="B62" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="C62" s="14" t="s">
+      <c r="C62" s="13" t="s">
         <v>173</v>
       </c>
-      <c r="D62" s="19" t="s">
+      <c r="D62" s="22" t="s">
         <v>216</v>
       </c>
-      <c r="E62" s="14" t="s">
+      <c r="E62" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="F62" s="14" t="s">
+      <c r="F62" s="13" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="63" ht="68" spans="1:6">
-      <c r="A63" s="13">
+    <row r="63" ht="57.6" spans="1:6">
+      <c r="A63" s="12">
         <v>54</v>
       </c>
-      <c r="B63" s="19" t="s">
+      <c r="B63" s="22" t="s">
         <v>137</v>
       </c>
-      <c r="C63" s="19" t="s">
+      <c r="C63" s="22" t="s">
         <v>138</v>
       </c>
-      <c r="D63" s="19" t="s">
+      <c r="D63" s="22" t="s">
         <v>217</v>
       </c>
-      <c r="E63" s="19" t="s">
+      <c r="E63" s="22" t="s">
         <v>218</v>
       </c>
-      <c r="F63" s="19" t="s">
+      <c r="F63" s="22" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="64" ht="84" spans="1:6">
-      <c r="A64" s="13">
+    <row r="64" ht="72" spans="1:6">
+      <c r="A64" s="12">
         <v>55</v>
       </c>
-      <c r="B64" s="19" t="s">
+      <c r="B64" s="22" t="s">
         <v>142</v>
       </c>
-      <c r="C64" s="19" t="s">
+      <c r="C64" s="22" t="s">
         <v>138</v>
       </c>
-      <c r="D64" s="19" t="s">
+      <c r="D64" s="22" t="s">
         <v>214</v>
       </c>
-      <c r="E64" s="19" t="s">
+      <c r="E64" s="22" t="s">
         <v>220</v>
       </c>
-      <c r="F64" s="19" t="s">
+      <c r="F64" s="22" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="65" ht="84" spans="1:6">
-      <c r="A65" s="13">
+    <row r="65" ht="72" spans="1:6">
+      <c r="A65" s="12">
         <v>56</v>
       </c>
-      <c r="B65" s="19" t="s">
+      <c r="B65" s="22" t="s">
         <v>145</v>
       </c>
-      <c r="C65" s="19" t="s">
+      <c r="C65" s="22" t="s">
         <v>138</v>
       </c>
-      <c r="D65" s="19" t="s">
+      <c r="D65" s="22" t="s">
         <v>221</v>
       </c>
-      <c r="E65" s="19" t="s">
+      <c r="E65" s="22" t="s">
         <v>220</v>
       </c>
-      <c r="F65" s="19" t="s">
+      <c r="F65" s="22" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="66" ht="68" spans="1:6">
-      <c r="A66" s="13">
+    <row r="66" ht="57.6" spans="1:6">
+      <c r="A66" s="12">
         <v>57</v>
       </c>
-      <c r="B66" s="19" t="s">
+      <c r="B66" s="22" t="s">
         <v>149</v>
       </c>
-      <c r="C66" s="19" t="s">
+      <c r="C66" s="22" t="s">
         <v>138</v>
       </c>
-      <c r="D66" s="19" t="s">
+      <c r="D66" s="22" t="s">
         <v>222</v>
       </c>
-      <c r="E66" s="19" t="s">
+      <c r="E66" s="22" t="s">
         <v>132</v>
       </c>
-      <c r="F66" s="19" t="s">
+      <c r="F66" s="22" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="67" spans="1:6">
-      <c r="A67" s="18" t="s">
+      <c r="A67" s="21" t="s">
         <v>223</v>
       </c>
-      <c r="B67" s="18"/>
-      <c r="C67" s="18"/>
-      <c r="D67" s="18"/>
-      <c r="E67" s="18"/>
-      <c r="F67" s="18"/>
-    </row>
-    <row r="68" ht="84" spans="1:6">
-      <c r="A68" s="13">
+      <c r="B67" s="21"/>
+      <c r="C67" s="21"/>
+      <c r="D67" s="21"/>
+      <c r="E67" s="21"/>
+      <c r="F67" s="21"/>
+    </row>
+    <row r="68" ht="72" spans="1:6">
+      <c r="A68" s="12">
         <v>58</v>
       </c>
-      <c r="B68" s="14" t="s">
+      <c r="B68" s="13" t="s">
         <v>224</v>
       </c>
-      <c r="C68" s="14" t="s">
+      <c r="C68" s="13" t="s">
         <v>173</v>
       </c>
-      <c r="D68" s="19" t="s">
+      <c r="D68" s="22" t="s">
         <v>225</v>
       </c>
-      <c r="E68" s="14" t="s">
+      <c r="E68" s="13" t="s">
         <v>226</v>
       </c>
-      <c r="F68" s="14" t="s">
+      <c r="F68" s="13" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="69" ht="68" spans="1:6">
-      <c r="A69" s="13">
+    <row r="69" ht="57.6" spans="1:6">
+      <c r="A69" s="12">
         <v>59</v>
       </c>
-      <c r="B69" s="14" t="s">
+      <c r="B69" s="13" t="s">
         <v>228</v>
       </c>
-      <c r="C69" s="14" t="s">
+      <c r="C69" s="13" t="s">
         <v>173</v>
       </c>
-      <c r="D69" s="19" t="s">
+      <c r="D69" s="22" t="s">
         <v>229</v>
       </c>
-      <c r="E69" s="14" t="s">
+      <c r="E69" s="13" t="s">
         <v>230</v>
       </c>
-      <c r="F69" s="14" t="s">
+      <c r="F69" s="13" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="70" ht="68" spans="1:6">
-      <c r="A70" s="13">
+    <row r="70" ht="57.6" spans="1:6">
+      <c r="A70" s="12">
         <v>60</v>
       </c>
-      <c r="B70" s="14" t="s">
+      <c r="B70" s="13" t="s">
         <v>232</v>
       </c>
-      <c r="C70" s="14" t="s">
+      <c r="C70" s="13" t="s">
         <v>173</v>
       </c>
-      <c r="D70" s="19" t="s">
+      <c r="D70" s="22" t="s">
         <v>233</v>
       </c>
-      <c r="E70" s="14" t="s">
+      <c r="E70" s="13" t="s">
         <v>234</v>
       </c>
-      <c r="F70" s="14" t="s">
+      <c r="F70" s="13" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="71" ht="68" spans="1:6">
-      <c r="A71" s="13">
+    <row r="71" ht="57.6" spans="1:6">
+      <c r="A71" s="12">
         <v>61</v>
       </c>
-      <c r="B71" s="14" t="s">
+      <c r="B71" s="13" t="s">
         <v>236</v>
       </c>
-      <c r="C71" s="14" t="s">
+      <c r="C71" s="13" t="s">
         <v>173</v>
       </c>
-      <c r="D71" s="19" t="s">
+      <c r="D71" s="22" t="s">
         <v>237</v>
       </c>
-      <c r="E71" s="14" t="s">
+      <c r="E71" s="13" t="s">
         <v>234</v>
       </c>
-      <c r="F71" s="14" t="s">
+      <c r="F71" s="13" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="72" ht="68" spans="1:6">
-      <c r="A72" s="13">
+    <row r="72" ht="57.6" spans="1:6">
+      <c r="A72" s="12">
         <v>62</v>
       </c>
-      <c r="B72" s="19" t="s">
+      <c r="B72" s="22" t="s">
         <v>137</v>
       </c>
-      <c r="C72" s="19" t="s">
+      <c r="C72" s="22" t="s">
         <v>138</v>
       </c>
-      <c r="D72" s="19" t="s">
+      <c r="D72" s="22" t="s">
         <v>239</v>
       </c>
-      <c r="E72" s="19" t="s">
+      <c r="E72" s="22" t="s">
         <v>240</v>
       </c>
-      <c r="F72" s="19" t="s">
+      <c r="F72" s="22" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="73" ht="68" spans="1:6">
-      <c r="A73" s="13">
+    <row r="73" ht="57.6" spans="1:6">
+      <c r="A73" s="12">
         <v>63</v>
       </c>
-      <c r="B73" s="19" t="s">
+      <c r="B73" s="22" t="s">
         <v>142</v>
       </c>
-      <c r="C73" s="19" t="s">
+      <c r="C73" s="22" t="s">
         <v>138</v>
       </c>
-      <c r="D73" s="19" t="s">
+      <c r="D73" s="22" t="s">
         <v>229</v>
       </c>
-      <c r="E73" s="19" t="s">
+      <c r="E73" s="22" t="s">
         <v>128</v>
       </c>
-      <c r="F73" s="19" t="s">
+      <c r="F73" s="22" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="74" ht="68" spans="1:6">
-      <c r="A74" s="13">
+    <row r="74" ht="57.6" spans="1:6">
+      <c r="A74" s="12">
         <v>64</v>
       </c>
-      <c r="B74" s="19" t="s">
+      <c r="B74" s="22" t="s">
         <v>242</v>
       </c>
-      <c r="C74" s="19" t="s">
+      <c r="C74" s="22" t="s">
         <v>138</v>
       </c>
-      <c r="D74" s="19" t="s">
+      <c r="D74" s="22" t="s">
         <v>243</v>
       </c>
-      <c r="E74" s="19" t="s">
+      <c r="E74" s="22" t="s">
         <v>244</v>
       </c>
-      <c r="F74" s="19" t="s">
+      <c r="F74" s="22" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="75" ht="68" spans="1:6">
-      <c r="A75" s="13">
+    <row r="75" ht="57.6" spans="1:6">
+      <c r="A75" s="12">
         <v>65</v>
       </c>
-      <c r="B75" s="19" t="s">
+      <c r="B75" s="22" t="s">
         <v>245</v>
       </c>
-      <c r="C75" s="19" t="s">
+      <c r="C75" s="22" t="s">
         <v>138</v>
       </c>
-      <c r="D75" s="19" t="s">
+      <c r="D75" s="22" t="s">
         <v>246</v>
       </c>
-      <c r="E75" s="19" t="s">
+      <c r="E75" s="22" t="s">
         <v>244</v>
       </c>
-      <c r="F75" s="19" t="s">
+      <c r="F75" s="22" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="76" spans="1:6">
-      <c r="A76" s="18" t="s">
+      <c r="A76" s="21" t="s">
         <v>247</v>
       </c>
-      <c r="B76" s="18"/>
-      <c r="C76" s="18"/>
-      <c r="D76" s="18"/>
-      <c r="E76" s="18"/>
-      <c r="F76" s="18"/>
-    </row>
-    <row r="77" ht="84" spans="1:6">
-      <c r="A77" s="13">
+      <c r="B76" s="21"/>
+      <c r="C76" s="21"/>
+      <c r="D76" s="21"/>
+      <c r="E76" s="21"/>
+      <c r="F76" s="21"/>
+    </row>
+    <row r="77" ht="72" spans="1:6">
+      <c r="A77" s="12">
         <v>66</v>
       </c>
-      <c r="B77" s="14" t="s">
+      <c r="B77" s="13" t="s">
         <v>224</v>
       </c>
-      <c r="C77" s="14" t="s">
+      <c r="C77" s="13" t="s">
         <v>173</v>
       </c>
-      <c r="D77" s="19" t="s">
+      <c r="D77" s="22" t="s">
         <v>248</v>
       </c>
-      <c r="E77" s="14" t="s">
+      <c r="E77" s="13" t="s">
         <v>226</v>
       </c>
-      <c r="F77" s="14" t="s">
+      <c r="F77" s="13" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="78" ht="68" spans="1:6">
-      <c r="A78" s="13">
+    <row r="78" ht="57.6" spans="1:6">
+      <c r="A78" s="12">
         <v>67</v>
       </c>
-      <c r="B78" s="14" t="s">
+      <c r="B78" s="13" t="s">
         <v>249</v>
       </c>
-      <c r="C78" s="14" t="s">
+      <c r="C78" s="13" t="s">
         <v>173</v>
       </c>
-      <c r="D78" s="19" t="s">
+      <c r="D78" s="22" t="s">
         <v>229</v>
       </c>
-      <c r="E78" s="14" t="s">
+      <c r="E78" s="13" t="s">
         <v>230</v>
       </c>
-      <c r="F78" s="14" t="s">
+      <c r="F78" s="13" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="79" ht="68" spans="1:6">
-      <c r="A79" s="13">
+    <row r="79" ht="57.6" spans="1:6">
+      <c r="A79" s="12">
         <v>68</v>
       </c>
-      <c r="B79" s="14" t="s">
+      <c r="B79" s="13" t="s">
         <v>232</v>
       </c>
-      <c r="C79" s="14" t="s">
+      <c r="C79" s="13" t="s">
         <v>173</v>
       </c>
-      <c r="D79" s="19" t="s">
+      <c r="D79" s="22" t="s">
         <v>233</v>
       </c>
-      <c r="E79" s="14" t="s">
+      <c r="E79" s="13" t="s">
         <v>234</v>
       </c>
-      <c r="F79" s="14" t="s">
+      <c r="F79" s="13" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="80" ht="68" spans="1:6">
-      <c r="A80" s="13">
+    <row r="80" ht="57.6" spans="1:6">
+      <c r="A80" s="12">
         <v>69</v>
       </c>
-      <c r="B80" s="14" t="s">
+      <c r="B80" s="13" t="s">
         <v>236</v>
       </c>
-      <c r="C80" s="14" t="s">
+      <c r="C80" s="13" t="s">
         <v>173</v>
       </c>
-      <c r="D80" s="19" t="s">
+      <c r="D80" s="22" t="s">
         <v>237</v>
       </c>
-      <c r="E80" s="14" t="s">
+      <c r="E80" s="13" t="s">
         <v>250</v>
       </c>
-      <c r="F80" s="14" t="s">
+      <c r="F80" s="13" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="81" ht="68" spans="1:6">
-      <c r="A81" s="13">
+    <row r="81" ht="57.6" spans="1:6">
+      <c r="A81" s="12">
         <v>70</v>
       </c>
-      <c r="B81" s="19" t="s">
+      <c r="B81" s="22" t="s">
         <v>137</v>
       </c>
-      <c r="C81" s="19" t="s">
+      <c r="C81" s="22" t="s">
         <v>138</v>
       </c>
-      <c r="D81" s="19" t="s">
+      <c r="D81" s="22" t="s">
         <v>239</v>
       </c>
-      <c r="E81" s="19" t="s">
+      <c r="E81" s="22" t="s">
         <v>160</v>
       </c>
-      <c r="F81" s="19" t="s">
+      <c r="F81" s="22" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="82" ht="68" spans="1:6">
-      <c r="A82" s="13">
+    <row r="82" ht="57.6" spans="1:6">
+      <c r="A82" s="12">
         <v>71</v>
       </c>
-      <c r="B82" s="19" t="s">
+      <c r="B82" s="22" t="s">
         <v>142</v>
       </c>
-      <c r="C82" s="19" t="s">
+      <c r="C82" s="22" t="s">
         <v>138</v>
       </c>
-      <c r="D82" s="19" t="s">
+      <c r="D82" s="22" t="s">
         <v>229</v>
       </c>
-      <c r="E82" s="19" t="s">
+      <c r="E82" s="22" t="s">
         <v>128</v>
       </c>
-      <c r="F82" s="19" t="s">
+      <c r="F82" s="22" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="83" ht="68" spans="1:6">
-      <c r="A83" s="13">
+    <row r="83" ht="57.6" spans="1:6">
+      <c r="A83" s="12">
         <v>72</v>
       </c>
-      <c r="B83" s="19" t="s">
+      <c r="B83" s="22" t="s">
         <v>242</v>
       </c>
-      <c r="C83" s="19" t="s">
+      <c r="C83" s="22" t="s">
         <v>138</v>
       </c>
-      <c r="D83" s="19" t="s">
+      <c r="D83" s="22" t="s">
         <v>243</v>
       </c>
-      <c r="E83" s="19" t="s">
+      <c r="E83" s="22" t="s">
         <v>244</v>
       </c>
-      <c r="F83" s="19" t="s">
+      <c r="F83" s="22" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="84" ht="68" spans="1:6">
-      <c r="A84" s="13">
+    <row r="84" ht="57.6" spans="1:6">
+      <c r="A84" s="12">
         <v>73</v>
       </c>
-      <c r="B84" s="19" t="s">
+      <c r="B84" s="22" t="s">
         <v>245</v>
       </c>
-      <c r="C84" s="19" t="s">
+      <c r="C84" s="22" t="s">
         <v>138</v>
       </c>
-      <c r="D84" s="19" t="s">
+      <c r="D84" s="22" t="s">
         <v>246</v>
       </c>
-      <c r="E84" s="19" t="s">
+      <c r="E84" s="22" t="s">
         <v>244</v>
       </c>
-      <c r="F84" s="19" t="s">
+      <c r="F84" s="22" t="s">
         <v>192</v>
       </c>
     </row>
@@ -5447,48 +5473,48 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F52"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="4.296875" style="5" customWidth="1"/>
-    <col min="2" max="2" width="26.953125" style="7" customWidth="1"/>
-    <col min="3" max="3" width="23.1796875" style="7" customWidth="1"/>
-    <col min="4" max="4" width="25.6484375" style="7" customWidth="1"/>
-    <col min="5" max="5" width="10.15625" style="7" customWidth="1"/>
-    <col min="6" max="6" width="18.875" style="7" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="8"/>
+    <col min="1" max="1" width="4.2962962962963" style="5" customWidth="1"/>
+    <col min="2" max="2" width="26.9537037037037" style="7" customWidth="1"/>
+    <col min="3" max="3" width="23.1759259259259" style="7" customWidth="1"/>
+    <col min="4" max="4" width="25.6481481481481" style="7" customWidth="1"/>
+    <col min="5" max="5" width="10.1574074074074" style="7" customWidth="1"/>
+    <col min="6" max="6" width="18.8796296296296" style="7" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" s="5" customFormat="1" ht="20" customHeight="1" spans="1:6">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="8" t="s">
         <v>251</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="8" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" s="6" customFormat="1" ht="20" customHeight="1" spans="1:6">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>252</v>
       </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-    </row>
-    <row r="3" ht="34" spans="1:5">
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+    </row>
+    <row r="3" ht="28.8" spans="1:5">
       <c r="A3" s="5">
         <v>1</v>
       </c>
@@ -5505,7 +5531,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="4" ht="84" spans="1:5">
+    <row r="4" ht="72" spans="1:5">
       <c r="A4" s="5">
         <v>2</v>
       </c>
@@ -5522,7 +5548,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="5" s="7" customFormat="1" ht="51" spans="1:5">
+    <row r="5" s="7" customFormat="1" ht="43.2" spans="1:5">
       <c r="A5" s="5">
         <v>3</v>
       </c>
@@ -5544,7 +5570,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="7" ht="34" spans="1:6">
+    <row r="7" ht="28.8" spans="1:6">
       <c r="A7" s="5">
         <v>3</v>
       </c>
@@ -5564,7 +5590,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="8" ht="51" spans="1:6">
+    <row r="8" ht="43.2" spans="1:6">
       <c r="A8" s="5">
         <v>4</v>
       </c>
@@ -5582,7 +5608,7 @@
       </c>
       <c r="F8" s="5"/>
     </row>
-    <row r="9" ht="34" spans="1:6">
+    <row r="9" ht="28.8" spans="1:6">
       <c r="A9" s="5">
         <v>5</v>
       </c>
@@ -5634,7 +5660,7 @@
       </c>
       <c r="F11" s="5"/>
     </row>
-    <row r="12" s="5" customFormat="1" ht="84" spans="1:5">
+    <row r="12" s="5" customFormat="1" ht="72" spans="1:5">
       <c r="A12" s="5">
         <v>8</v>
       </c>
@@ -5656,7 +5682,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="14" ht="68" spans="1:5">
+    <row r="14" ht="57.6" spans="1:5">
       <c r="A14" s="5">
         <v>9</v>
       </c>
@@ -5673,7 +5699,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="15" ht="68" spans="1:6">
+    <row r="15" ht="57.6" spans="1:6">
       <c r="A15" s="5">
         <v>10</v>
       </c>
@@ -5693,7 +5719,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="16" ht="68" spans="1:5">
+    <row r="16" ht="57.6" spans="1:5">
       <c r="A16" s="5">
         <v>11</v>
       </c>
@@ -5715,7 +5741,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="18" ht="84" spans="1:5">
+    <row r="18" ht="72" spans="1:5">
       <c r="A18" s="5">
         <v>12</v>
       </c>
@@ -5732,7 +5758,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="19" ht="34" spans="1:5">
+    <row r="19" ht="28.8" spans="1:5">
       <c r="A19" s="5">
         <v>13</v>
       </c>
@@ -5749,7 +5775,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="20" ht="34" spans="1:5">
+    <row r="20" ht="28.8" spans="1:5">
       <c r="A20" s="5">
         <v>14</v>
       </c>
@@ -5781,7 +5807,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="22" ht="34" spans="1:5">
+    <row r="22" ht="28.8" spans="1:5">
       <c r="A22" s="5">
         <v>16</v>
       </c>
@@ -5818,7 +5844,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="25" ht="51" spans="1:5">
+    <row r="25" ht="43.2" spans="1:5">
       <c r="A25" s="5">
         <v>18</v>
       </c>
@@ -5835,7 +5861,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="26" ht="51" spans="1:5">
+    <row r="26" ht="43.2" spans="1:5">
       <c r="A26" s="5">
         <v>19</v>
       </c>
@@ -5852,7 +5878,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="27" ht="51" spans="1:5">
+    <row r="27" ht="43.2" spans="1:5">
       <c r="A27" s="5">
         <v>20</v>
       </c>
@@ -5869,7 +5895,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="28" ht="51" spans="1:5">
+    <row r="28" ht="43.2" spans="1:5">
       <c r="A28" s="5">
         <v>21</v>
       </c>
@@ -5886,7 +5912,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="29" ht="68" spans="1:5">
+    <row r="29" ht="57.6" spans="1:5">
       <c r="A29" s="5">
         <v>22</v>
       </c>
@@ -5903,7 +5929,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="30" ht="84" spans="1:6">
+    <row r="30" ht="72" spans="1:6">
       <c r="A30" s="5">
         <v>23</v>
       </c>
@@ -5923,7 +5949,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="31" ht="84" spans="1:5">
+    <row r="31" ht="72" spans="1:5">
       <c r="A31" s="5">
         <v>24</v>
       </c>
@@ -5940,7 +5966,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="32" ht="51" spans="1:5">
+    <row r="32" ht="43.2" spans="1:5">
       <c r="A32" s="5">
         <v>25</v>
       </c>
@@ -5957,7 +5983,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="33" ht="34" spans="1:5">
+    <row r="33" ht="28.8" spans="1:5">
       <c r="A33" s="5">
         <v>26</v>
       </c>
@@ -5974,14 +6000,14 @@
         <v>256</v>
       </c>
     </row>
-    <row r="34" ht="84" spans="1:5">
+    <row r="34" ht="72" spans="1:5">
       <c r="A34" s="5">
         <v>27</v>
       </c>
       <c r="B34" s="7" t="s">
         <v>320</v>
       </c>
-      <c r="C34" s="11" t="s">
+      <c r="C34" s="10" t="s">
         <v>322</v>
       </c>
       <c r="D34" s="7" t="s">
@@ -5991,7 +6017,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="35" ht="51" spans="1:5">
+    <row r="35" ht="43.2" spans="1:5">
       <c r="A35" s="5">
         <v>28</v>
       </c>
@@ -6008,7 +6034,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="36" ht="51" spans="1:5">
+    <row r="36" ht="43.2" spans="1:5">
       <c r="A36" s="5">
         <v>29</v>
       </c>
@@ -6025,7 +6051,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="37" ht="34" spans="1:5">
+    <row r="37" ht="28.8" spans="1:5">
       <c r="A37" s="5">
         <v>30</v>
       </c>
@@ -6042,7 +6068,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="38" ht="51" spans="1:5">
+    <row r="38" ht="43.2" spans="1:5">
       <c r="A38" s="5">
         <v>31</v>
       </c>
@@ -6059,7 +6085,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="39" ht="17" spans="1:5">
+    <row r="39" spans="1:5">
       <c r="A39" s="5">
         <v>32</v>
       </c>
@@ -6076,7 +6102,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="40" ht="84" spans="1:5">
+    <row r="40" ht="72" spans="1:5">
       <c r="A40" s="5">
         <v>33</v>
       </c>
@@ -6093,7 +6119,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="41" ht="68" spans="1:6">
+    <row r="41" ht="57.6" spans="1:6">
       <c r="A41" s="5">
         <v>34</v>
       </c>
@@ -6113,7 +6139,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="42" ht="84" spans="1:5">
+    <row r="42" ht="72" spans="1:5">
       <c r="A42" s="5">
         <v>35</v>
       </c>
@@ -6202,7 +6228,7 @@
       </c>
       <c r="F47" s="5"/>
     </row>
-    <row r="48" ht="34" spans="1:6">
+    <row r="48" ht="28.8" spans="1:6">
       <c r="A48" s="5">
         <v>40</v>
       </c>
@@ -6216,7 +6242,7 @@
       </c>
       <c r="F48" s="5"/>
     </row>
-    <row r="49" ht="34" spans="1:6">
+    <row r="49" ht="28.8" spans="1:6">
       <c r="A49" s="5">
         <v>41</v>
       </c>
@@ -6230,7 +6256,7 @@
       </c>
       <c r="F49" s="5"/>
     </row>
-    <row r="50" ht="34" spans="1:6">
+    <row r="50" ht="28.8" spans="1:6">
       <c r="A50" s="5">
         <v>42</v>
       </c>
@@ -6244,7 +6270,7 @@
       </c>
       <c r="F50" s="5"/>
     </row>
-    <row r="51" ht="34" spans="1:6">
+    <row r="51" ht="28.8" spans="1:6">
       <c r="A51" s="5">
         <v>43</v>
       </c>
@@ -6258,7 +6284,7 @@
       </c>
       <c r="F51" s="5"/>
     </row>
-    <row r="52" ht="68" spans="1:6">
+    <row r="52" ht="57.6" spans="1:6">
       <c r="A52" s="5">
         <v>44</v>
       </c>
@@ -6302,18 +6328,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:I8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="7"/>
   <cols>
-    <col min="1" max="1" width="4.953125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="27.6015625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="16.40625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="25.2578125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="9.2421875" style="2" customWidth="1"/>
-    <col min="6" max="6" width="19.65625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="4.9537037037037" style="2" customWidth="1"/>
+    <col min="2" max="2" width="27.6018518518519" style="2" customWidth="1"/>
+    <col min="3" max="3" width="16.4074074074074" style="2" customWidth="1"/>
+    <col min="4" max="4" width="25.2592592592593" style="2" customWidth="1"/>
+    <col min="5" max="5" width="9.24074074074074" style="2" customWidth="1"/>
+    <col min="6" max="6" width="19.6574074074074" style="2" customWidth="1"/>
     <col min="7" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="17" spans="1:9">
+    <row r="1" s="1" customFormat="1" spans="1:9">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -6359,7 +6385,7 @@
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
     </row>
-    <row r="3" ht="118" spans="1:9">
+    <row r="3" ht="100.8" spans="1:9">
       <c r="A3" s="2" t="s">
         <v>365</v>
       </c>
@@ -6381,7 +6407,7 @@
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
     </row>
-    <row r="4" ht="34" spans="1:9">
+    <row r="4" ht="28.8" spans="1:9">
       <c r="A4" s="2" t="s">
         <v>369</v>
       </c>
@@ -6400,7 +6426,7 @@
       <c r="H4" s="4"/>
       <c r="I4" s="4"/>
     </row>
-    <row r="5" ht="34" spans="1:9">
+    <row r="5" ht="28.8" spans="1:9">
       <c r="A5" s="2" t="s">
         <v>373</v>
       </c>
@@ -6419,11 +6445,47 @@
       <c r="H5" s="4"/>
       <c r="I5" s="4"/>
     </row>
-    <row r="6" spans="8:9">
+    <row r="6" ht="100.8" spans="1:9">
+      <c r="A6" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>380</v>
+      </c>
       <c r="H6" s="4"/>
       <c r="I6" s="4"/>
     </row>
-    <row r="7" spans="8:9">
+    <row r="7" ht="100.8" spans="1:9">
+      <c r="A7" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>384</v>
+      </c>
       <c r="H7" s="4"/>
       <c r="I7" s="4"/>
     </row>

--- a/Log/Magic_eraser_test_log.xlsx
+++ b/Log/Magic_eraser_test_log.xlsx
@@ -4,13 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="8400" firstSheet="2" activeTab="3"/>
+    <workbookView windowWidth="18960" windowHeight="16340" firstSheet="2" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Image_selector_test" sheetId="1" r:id="rId1"/>
     <sheet name="Load_memory_output_test" sheetId="2" r:id="rId2"/>
     <sheet name="Home_screen_Remove_background" sheetId="3" r:id="rId3"/>
     <sheet name="Force_update" sheetId="4" r:id="rId4"/>
+    <sheet name="Test_thông_luồng" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="899" uniqueCount="385">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="994" uniqueCount="443">
   <si>
     <t>TC</t>
   </si>
@@ -1178,10 +1179,7 @@
 server hiện đang trả về: { "latest_version": "3.0.0", "min_supported_version": "2.23.25" }</t>
   </si>
   <si>
-    <t>HIện lên message "force update"</t>
-  </si>
-  <si>
-    <t>PENDING</t>
+    <t>Vào màn "force update"</t>
   </si>
   <si>
     <t>latest_version &lt; min_supported_version &lt; curent_version</t>
@@ -1198,6 +1196,261 @@
   </si>
   <si>
     <t>skip_update_version == 2.23.24</t>
+  </si>
+  <si>
+    <t>FU07</t>
+  </si>
+  <si>
+    <t>Ở màn hình điện thoại, App đã được mở, phiên bản hiện tịa là 2.23.24, chưa skip update, không có kết nối internet 
+server lần trước trả về: { "latest_version": "3.0.0", "min_supported_version": "0.0.0" }</t>
+  </si>
+  <si>
+    <t>FU08</t>
+  </si>
+  <si>
+    <t>Ở màn force update</t>
+  </si>
+  <si>
+    <t>Enviroment: 
+OS: android
+device: redmi14C, pixcel Fold (SDK 36.0)</t>
+  </si>
+  <si>
+    <t>HOME</t>
+  </si>
+  <si>
+    <t>Ở màn hình điện thoại, app chưa được mở khi tải về</t>
+  </si>
+  <si>
+    <t>1. Mở app
+2. Chuyển qua phase giới thiệu app
+3. Chọn option quan tâm
+4. Thoát màn tiếp thị 
+5. chọn button More 
+6. chọn button Less</t>
+  </si>
+  <si>
+    <t>Chuyển tiếp mượt mà giữa các màn: màn giới thiệu chức năng, màn thăm dò, màn tiếp thị, màn Home. Nhấn nút More sẽ hiển thị toàn bộ các button chức năng, nút Lesss ẩn bớt các chức năng</t>
+  </si>
+  <si>
+    <t>BE</t>
+  </si>
+  <si>
+    <t>1. Mở chức năng Basic Edit bằng 1 trong các cách sau:
+a. chọn button Basic Edit 
+b. chọn baner Basic Edit
+2. Chọn 1 ảnh bất kỳ 
+3. Thực hiện chỉnh sửa (sử dụng hết tất cả các button 1 lượt) 
+4. chọn Save
+5. Đánh giá độ hài lòng 
+6. Thoát trở về màn hình Home</t>
+  </si>
+  <si>
+    <t>Chuyển tiếp mượt giữa các màn: màn Home, màn chọn ảnh, màn Basic Edit, màn Saved, màn Home. Ở màn Basic Edit, hình ảnh được cập nhật tương ứng với từng giai đoạn chỉnh sửa, ảnh được lưu đúng với các custom đã thực hiện</t>
+  </si>
+  <si>
+    <t>mã TC của basic edit: BE</t>
+  </si>
+  <si>
+    <t>RO</t>
+  </si>
+  <si>
+    <t>1. Mở chức năng Basic Edit bằng 1 trong các cách sau: 
+a. chọn image carousel hiển thị chức năng remove objects 
+b. chọn button Remove Objects 
+c. chọn banner Remove Objects 
+2. Chọn 1 ảnh bất kỳ 
+3. Khoanh vùng vật thể muốn xoá (mỗi option sử dụng ít nhất 1 lần) 
+4. Xoá vật thể đã khoanh
+5. Lưu hình ảnh 
+6. Thoát về màn hình Home</t>
+  </si>
+  <si>
+    <t>Chuyển tiếp mượt giữa các màn: màn Home, màn chọn ảnh, màn Remove Objects, màn Basic Edit, màn Saved, màn Home. Hình ảnh được lưu đúng với các custom đã thực hiện</t>
+  </si>
+  <si>
+    <t>mã TC của Remove Objects: RO</t>
+  </si>
+  <si>
+    <t>AFL</t>
+  </si>
+  <si>
+    <t>Ở màn hình Home, tài khoản pro</t>
+  </si>
+  <si>
+    <t>1. Mở chức năng AI Fill bằng 1 trong các cách sau: 
+a. chọn image carousel hiển thị chức năng AI Fill 
+b. chọn button AI Fill 
+c. chọn banner AI Fill 
+2. Chọn 1 ảnh bất kỳ
+3. Khoanh vùng muốn vẽ vật thể 
+4. Mô tả vật thể muốn vẽ 
+5. Tiến hành Fill
+6. Xác nhận thay đổi
+7. Lưu hình ảnh
+8. Thoát về màn hình Home</t>
+  </si>
+  <si>
+    <t>Chuyển tiếp mượt giữa các màn: màn Home, màn AI Fill, màn xác nhận, màn AI Fill, màn Basic Edit, màn Saved, màn Home. Hình ảnh được lưu đúng với các custom đã thực hiện</t>
+  </si>
+  <si>
+    <t>mã TC của AI Fill: AFL</t>
+  </si>
+  <si>
+    <t>AFT</t>
+  </si>
+  <si>
+    <t>1. Mở chức năng AI Filter bằng 1 trong các cách sau:
+a. chọn image carousel hiển thị chức năng AI FIlter 
+b. chọn button AI Filter 
+c. chọn banner AI Filter 
+d. chọn option AI Filters trên thanh task bar
+2. Chọn 1 Style bất kỳ
+3. Chọn 1 ảnh bất kỳ 
+4. Lưu hình ảnh 
+5. Thoát về màn chọn AI Filter</t>
+  </si>
+  <si>
+    <t>Chuyển tiếp mượt giữa các màn: Home, AI Filters, chọn ảnh, edit AI Filter, saved, AI FIlters. Hình ảnh được lưu đúng với các custom đã thực hiện</t>
+  </si>
+  <si>
+    <t>mã TC của AI Filter: AFT</t>
+  </si>
+  <si>
+    <t>RB</t>
+  </si>
+  <si>
+    <t>1. Mở chức năng Remove Background bằng 1 trong các cách sau: 
+a. chọn image carousel hiển thị chức năng Remove Background 
+b. chọn button Remove Backgronnd 
+c. chọn baner Remove Background 
+2. Chọn 1 ảnh bất kỳ 
+3. chỉnh sửa phần cut của ảnh 
+4. chọn 1 style ảnh bất kỳ 
+5. Lưu hình ảnh
+6. Trở về màn hình Home</t>
+  </si>
+  <si>
+    <t>Chuyển tiếp mượt mà giữa các màn: Home, chọn ảnh, Home Edit, Cut editor, Home Edit, Basic Edit, Saved, Home. Hình ảnh được lưu đúng với các custom đã thực hiện</t>
+  </si>
+  <si>
+    <t>mã TC của Remove background: RB</t>
+  </si>
+  <si>
+    <t>EI</t>
+  </si>
+  <si>
+    <t>1. Mở chức năng Expand Image bằng 1 trong các cách sau: 
+a. chọn button Expand Image 
+b. chọn baner Expand Image 
+2. chụp 1 ảnh 
+3. custom kích thước ảnh mong muốn (kéo ra to hơn) 
+4. Lưu hình ảnh 
+5. Thoát về màn Home</t>
+  </si>
+  <si>
+    <t>Chuyển tiếp mượt giữa các màn: Home, chọn ảnh, chụp ảnh, expand edit, Basic Edit, Saved, Home. Hình ảnh được lưu đúng với các custom đã thực hiện</t>
+  </si>
+  <si>
+    <t>mã TC của Expand Image: EI</t>
+  </si>
+  <si>
+    <t>EQ</t>
+  </si>
+  <si>
+    <t>1. Mở chức năng Enhance Quality bằng 1 trong các cách sau: 
+a. chọn image carousel hiển thị chức năng Enhance Quality 
+b. chọn button Enhance Quality 
+c. chọn baner Enhance Quality 
+2. Chọn 1 ảnh bất kỳ 
+3. Custom Enhance 
+4. Lưu hình ảnh 
+5. Thoát về màn Home</t>
+  </si>
+  <si>
+    <t>Chuyển tiếp mượt giữa các màn: Home, chọn ảnh, edit Enhance, Basic Edit, Saved, Home. Hình ảnh được lưu đúng với các custom đã thực hiện</t>
+  </si>
+  <si>
+    <t>mã TC của Enhance Quality: EQ</t>
+  </si>
+  <si>
+    <t>AG</t>
+  </si>
+  <si>
+    <t>1. Mở chức năng AI Generate  bằng 1 trong các cách sau: 
+a. chọn button AI Generate 
+b. chọn baner AI Generate 
+c. chọn option AI Generate trên task bar 
+2. Cung cấp thông tin (Describe, version, Resolutions, Advanced, Options, Style) và tạo ảnh 
+3. Tạo lại ảnh 
+4. Lưu về máy 
+5. Thoát về màn AI Generate</t>
+  </si>
+  <si>
+    <t>Chuyển tiếp mượt giữa các màn: Home, AI Generate, Edit AI-Gen, AI Generate. HÌnh được lưu đúng với ảnh được Generate với các thông số đã được custom</t>
+  </si>
+  <si>
+    <t>mã TC của AI Generate: AG</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>1. Chọn button Stiker 
+2. Chọn Sticker 
+3. Chỉnh sửa thêm 
+4. Lưu hình ảnh 
+5. Thoát về màn Home</t>
+  </si>
+  <si>
+    <t>Chuyển tiếp mượt giữa các màn: Home, chọn ảnh, Basic Edit, Saved, Home. Hình ảnh được lưu đúng với các custom đã thực hiện</t>
+  </si>
+  <si>
+    <t>Mã TC của Sticker: S</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t>1. Chọn button Text 
+2. Nhập text 
+3. Nhập thêm text mới 
+4. Thực hiện thêm 1 số chỉnh sửa. 
+5. Lưu hình ảnh 
+6. Thoát về màn Home</t>
+  </si>
+  <si>
+    <t>Chuyển tiếp mượt giữa các màn: Home, chonj ảnh, Basic Edit, Saved, Home. Hình ảnh được thực hiện đúng với các custom đã thực hiện</t>
+  </si>
+  <si>
+    <t>Mã TC của Text: T</t>
+  </si>
+  <si>
+    <t>EV</t>
+  </si>
+  <si>
+    <t>Ở màn hình Home, đã install app "Video Eraser"</t>
+  </si>
+  <si>
+    <t>chọn Video Object Remover</t>
+  </si>
+  <si>
+    <t>Mở App "Video Eraser"</t>
+  </si>
+  <si>
+    <t>Mã TC của Edit Videos: ED</t>
+  </si>
+  <si>
+    <t>CWU</t>
+  </si>
+  <si>
+    <t>Chọn 1 trong các option connect</t>
+  </si>
+  <si>
+    <t>Mở đường link tương ứng với các option</t>
+  </si>
+  <si>
+    <t>Mã TC của Connect with us: CWU</t>
   </si>
 </sst>
 </file>
@@ -1619,6 +1872,19 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right style="thin">
         <color auto="1"/>
@@ -1629,19 +1895,6 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -1961,22 +2214,25 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2010,13 +2266,19 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2025,23 +2287,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2577,44 +2833,44 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:L61"/>
-  <sheetFormatPr defaultColWidth="9.13888888888889" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="1" width="4" style="12" customWidth="1"/>
-    <col min="2" max="2" width="31.287037037037" style="13" customWidth="1"/>
-    <col min="3" max="3" width="21.712962962963" style="13" customWidth="1"/>
-    <col min="4" max="5" width="24.4259259259259" style="13" customWidth="1"/>
-    <col min="6" max="6" width="30.287037037037" style="13" customWidth="1"/>
-    <col min="7" max="7" width="20.1388888888889" style="13" customWidth="1"/>
-    <col min="8" max="8" width="9.13888888888889" style="2"/>
-    <col min="9" max="9" width="17.712962962963" style="2" customWidth="1"/>
-    <col min="10" max="16384" width="9.13888888888889" style="2"/>
+    <col min="1" max="1" width="4" style="13" customWidth="1"/>
+    <col min="2" max="2" width="31.2890625" style="14" customWidth="1"/>
+    <col min="3" max="3" width="21.7109375" style="14" customWidth="1"/>
+    <col min="4" max="5" width="24.4296875" style="14" customWidth="1"/>
+    <col min="6" max="6" width="30.2890625" style="14" customWidth="1"/>
+    <col min="7" max="7" width="20.140625" style="14" customWidth="1"/>
+    <col min="8" max="8" width="9.140625" style="5"/>
+    <col min="9" max="9" width="17.7109375" style="5" customWidth="1"/>
+    <col min="10" max="16384" width="9.140625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.15" spans="1:7">
-      <c r="A1" s="23" t="s">
+    <row r="1" ht="17.75" spans="1:7">
+      <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="24" t="s">
+      <c r="B1" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="24" t="s">
+      <c r="C1" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="24" t="s">
+      <c r="D1" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="24" t="s">
+      <c r="E1" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="24" t="s">
+      <c r="F1" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="25" t="s">
+      <c r="G1" s="27" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" ht="37" customHeight="1" spans="1:12">
-      <c r="A2" s="20">
+      <c r="A2" s="23">
         <v>1</v>
       </c>
       <c r="B2" s="26" t="s">
@@ -2633,1238 +2889,1238 @@
         <v>10</v>
       </c>
       <c r="G2" s="26"/>
-      <c r="I2" s="7" t="s">
+      <c r="I2" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="K2" s="7" t="s">
+      <c r="K2" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="L2" s="7"/>
-    </row>
-    <row r="3" ht="28.8" spans="1:12">
-      <c r="A3" s="12">
+      <c r="L2" s="8"/>
+    </row>
+    <row r="3" ht="34" spans="1:12">
+      <c r="A3" s="13">
         <v>2</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="F3" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="I3" s="7"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="7"/>
-    </row>
-    <row r="4" ht="28.8" spans="1:12">
-      <c r="A4" s="12">
+      <c r="I3" s="8"/>
+      <c r="K3" s="8"/>
+      <c r="L3" s="8"/>
+    </row>
+    <row r="4" ht="34" spans="1:12">
+      <c r="A4" s="13">
         <v>3</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="E4" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="13" t="s">
+      <c r="F4" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="I4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="7"/>
-    </row>
-    <row r="5" ht="28.8" spans="1:12">
-      <c r="A5" s="12">
+      <c r="I4" s="8"/>
+      <c r="K4" s="8"/>
+      <c r="L4" s="8"/>
+    </row>
+    <row r="5" ht="34" spans="1:12">
+      <c r="A5" s="13">
         <v>4</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="E5" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="13" t="s">
+      <c r="F5" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="I5" s="7"/>
-      <c r="K5" s="7"/>
-      <c r="L5" s="7"/>
-    </row>
-    <row r="6" ht="28.8" spans="1:12">
-      <c r="A6" s="12">
+      <c r="I5" s="8"/>
+      <c r="K5" s="8"/>
+      <c r="L5" s="8"/>
+    </row>
+    <row r="6" ht="34" spans="1:12">
+      <c r="A6" s="13">
         <v>5</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="D6" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="13" t="s">
+      <c r="E6" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="13" t="s">
+      <c r="F6" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="K6" s="7"/>
-      <c r="L6" s="7"/>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="12">
+      <c r="K6" s="8"/>
+      <c r="L6" s="8"/>
+    </row>
+    <row r="7" ht="17" spans="1:6">
+      <c r="A7" s="13">
         <v>6</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="13" t="s">
+      <c r="E7" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="F7" s="13" t="s">
+      <c r="F7" s="14" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="8" ht="50" customHeight="1" spans="1:6">
-      <c r="A8" s="12">
+      <c r="A8" s="13">
         <v>7</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="C8" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="13" t="s">
+      <c r="D8" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="13" t="s">
+      <c r="E8" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="13" t="s">
+      <c r="F8" s="14" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="9" ht="28.8" spans="1:6">
-      <c r="A9" s="12">
+    <row r="9" ht="34" spans="1:6">
+      <c r="A9" s="13">
         <v>8</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="13" t="s">
+      <c r="D9" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="13" t="s">
+      <c r="E9" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="F9" s="13" t="s">
+      <c r="F9" s="14" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="10" ht="28.8" spans="1:6">
-      <c r="A10" s="12">
+    <row r="10" ht="34" spans="1:6">
+      <c r="A10" s="13">
         <v>9</v>
       </c>
-      <c r="B10" s="13" t="s">
+      <c r="B10" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="13" t="s">
+      <c r="D10" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E10" s="13" t="s">
+      <c r="E10" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="F10" s="13" t="s">
+      <c r="F10" s="14" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="11" ht="28.8" spans="1:6">
-      <c r="A11" s="12">
+    <row r="11" ht="34" spans="1:6">
+      <c r="A11" s="13">
         <v>10</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="13" t="s">
+      <c r="D11" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E11" s="13" t="s">
+      <c r="E11" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="F11" s="13" t="s">
+      <c r="F11" s="14" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" ht="28.8" spans="1:6">
-      <c r="A12" s="12">
+    <row r="12" ht="34" spans="1:6">
+      <c r="A12" s="13">
         <v>11</v>
       </c>
-      <c r="B12" s="13" t="s">
+      <c r="B12" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="C12" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="13" t="s">
+      <c r="D12" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E12" s="13" t="s">
+      <c r="E12" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="F12" s="13" t="s">
+      <c r="F12" s="14" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="13" ht="28.8" spans="1:6">
-      <c r="A13" s="12">
+    <row r="13" ht="34" spans="1:6">
+      <c r="A13" s="13">
         <v>12</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C13" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="D13" s="13" t="s">
+      <c r="D13" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E13" s="13" t="s">
+      <c r="E13" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="F13" s="13" t="s">
+      <c r="F13" s="14" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="14" ht="43.2" spans="1:6">
-      <c r="A14" s="12">
+    <row r="14" ht="51" spans="1:6">
+      <c r="A14" s="13">
         <v>13</v>
       </c>
-      <c r="B14" s="13" t="s">
+      <c r="B14" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="C14" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="D14" s="13" t="s">
+      <c r="D14" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E14" s="13" t="s">
+      <c r="E14" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="F14" s="13" t="s">
+      <c r="F14" s="14" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="15" ht="28.8" spans="1:6">
-      <c r="A15" s="12">
+    <row r="15" ht="34" spans="1:6">
+      <c r="A15" s="13">
         <v>14</v>
       </c>
-      <c r="B15" s="13" t="s">
+      <c r="B15" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="C15" s="13" t="s">
+      <c r="C15" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="D15" s="13" t="s">
+      <c r="D15" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E15" s="13" t="s">
+      <c r="E15" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="F15" s="13" t="s">
+      <c r="F15" s="14" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="16" ht="28.8" spans="1:6">
-      <c r="A16" s="12">
+    <row r="16" ht="34" spans="1:6">
+      <c r="A16" s="13">
         <v>15</v>
       </c>
-      <c r="B16" s="13" t="s">
+      <c r="B16" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="C16" s="13" t="s">
+      <c r="C16" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="D16" s="13" t="s">
+      <c r="D16" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E16" s="13" t="s">
+      <c r="E16" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="F16" s="13" t="s">
+      <c r="F16" s="14" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="17" ht="28.8" spans="1:6">
-      <c r="A17" s="12">
+    <row r="17" ht="34" spans="1:6">
+      <c r="A17" s="13">
         <v>16</v>
       </c>
-      <c r="B17" s="13" t="s">
+      <c r="B17" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="C17" s="13" t="s">
+      <c r="C17" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="D17" s="13" t="s">
+      <c r="D17" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E17" s="13" t="s">
+      <c r="E17" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="F17" s="13" t="s">
+      <c r="F17" s="14" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="18" ht="28.8" spans="1:6">
-      <c r="A18" s="12">
+    <row r="18" ht="34" spans="1:6">
+      <c r="A18" s="13">
         <v>17</v>
       </c>
-      <c r="B18" s="13" t="s">
+      <c r="B18" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="C18" s="13" t="s">
+      <c r="C18" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="D18" s="13" t="s">
+      <c r="D18" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E18" s="13" t="s">
+      <c r="E18" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="F18" s="13" t="s">
+      <c r="F18" s="14" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="19" ht="28.8" spans="1:6">
-      <c r="A19" s="12">
+    <row r="19" ht="34" spans="1:6">
+      <c r="A19" s="13">
         <v>18</v>
       </c>
-      <c r="B19" s="13" t="s">
+      <c r="B19" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="C19" s="13" t="s">
+      <c r="C19" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="D19" s="13" t="s">
+      <c r="D19" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E19" s="13" t="s">
+      <c r="E19" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="F19" s="13" t="s">
+      <c r="F19" s="14" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="20" ht="43.2" spans="1:6">
-      <c r="A20" s="12">
+    <row r="20" ht="51" spans="1:6">
+      <c r="A20" s="13">
         <v>19</v>
       </c>
-      <c r="B20" s="13" t="s">
+      <c r="B20" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="C20" s="13" t="s">
+      <c r="C20" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="D20" s="13" t="s">
+      <c r="D20" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E20" s="13" t="s">
+      <c r="E20" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="F20" s="13" t="s">
+      <c r="F20" s="14" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="21" ht="28.8" spans="1:6">
-      <c r="A21" s="12">
+    <row r="21" ht="34" spans="1:6">
+      <c r="A21" s="13">
         <v>20</v>
       </c>
-      <c r="B21" s="13" t="s">
+      <c r="B21" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="C21" s="13" t="s">
+      <c r="C21" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="D21" s="13" t="s">
+      <c r="D21" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E21" s="13" t="s">
+      <c r="E21" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="F21" s="13" t="s">
+      <c r="F21" s="14" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="22" ht="28.8" spans="1:6">
-      <c r="A22" s="12">
+    <row r="22" ht="34" spans="1:6">
+      <c r="A22" s="13">
         <v>21</v>
       </c>
-      <c r="B22" s="13" t="s">
+      <c r="B22" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="C22" s="13" t="s">
+      <c r="C22" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="D22" s="13" t="s">
+      <c r="D22" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E22" s="13" t="s">
+      <c r="E22" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="F22" s="13" t="s">
+      <c r="F22" s="14" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="23" ht="28.8" spans="1:6">
-      <c r="A23" s="12">
+    <row r="23" ht="34" spans="1:6">
+      <c r="A23" s="13">
         <v>22</v>
       </c>
-      <c r="B23" s="13" t="s">
+      <c r="B23" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="C23" s="13" t="s">
+      <c r="C23" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="D23" s="13" t="s">
+      <c r="D23" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E23" s="13" t="s">
+      <c r="E23" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="F23" s="13" t="s">
+      <c r="F23" s="14" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="24" ht="28.8" spans="1:6">
-      <c r="A24" s="12">
+    <row r="24" ht="34" spans="1:6">
+      <c r="A24" s="13">
         <v>23</v>
       </c>
-      <c r="B24" s="13" t="s">
+      <c r="B24" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="C24" s="13" t="s">
+      <c r="C24" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="D24" s="13" t="s">
+      <c r="D24" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E24" s="13" t="s">
+      <c r="E24" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="F24" s="13" t="s">
+      <c r="F24" s="14" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="25" ht="28.8" spans="1:6">
-      <c r="A25" s="12">
+    <row r="25" ht="34" spans="1:6">
+      <c r="A25" s="13">
         <v>24</v>
       </c>
-      <c r="B25" s="13" t="s">
+      <c r="B25" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="C25" s="13" t="s">
+      <c r="C25" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="D25" s="13" t="s">
+      <c r="D25" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E25" s="13" t="s">
+      <c r="E25" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="F25" s="13" t="s">
+      <c r="F25" s="14" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="26" ht="28.8" spans="1:6">
-      <c r="A26" s="12">
+    <row r="26" ht="34" spans="1:6">
+      <c r="A26" s="13">
         <v>25</v>
       </c>
-      <c r="B26" s="13" t="s">
+      <c r="B26" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="C26" s="13" t="s">
+      <c r="C26" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="D26" s="13" t="s">
+      <c r="D26" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E26" s="13" t="s">
+      <c r="E26" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="F26" s="13" t="s">
+      <c r="F26" s="14" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="27" ht="43.2" spans="1:6">
-      <c r="A27" s="12">
+    <row r="27" ht="51" spans="1:6">
+      <c r="A27" s="13">
         <v>26</v>
       </c>
-      <c r="B27" s="13" t="s">
+      <c r="B27" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="C27" s="13" t="s">
+      <c r="C27" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="D27" s="13" t="s">
+      <c r="D27" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E27" s="13" t="s">
+      <c r="E27" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="F27" s="13" t="s">
+      <c r="F27" s="14" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="28" ht="43.2" spans="1:6">
-      <c r="A28" s="12">
+    <row r="28" ht="51" spans="1:6">
+      <c r="A28" s="13">
         <v>27</v>
       </c>
-      <c r="B28" s="13" t="s">
+      <c r="B28" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="C28" s="13" t="s">
+      <c r="C28" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="D28" s="13" t="s">
+      <c r="D28" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E28" s="13" t="s">
+      <c r="E28" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="F28" s="13" t="s">
+      <c r="F28" s="14" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="29" ht="43.2" spans="1:6">
-      <c r="A29" s="12">
+    <row r="29" ht="51" spans="1:6">
+      <c r="A29" s="13">
         <v>28</v>
       </c>
-      <c r="B29" s="13" t="s">
+      <c r="B29" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="C29" s="13" t="s">
+      <c r="C29" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="D29" s="13" t="s">
+      <c r="D29" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E29" s="13" t="s">
+      <c r="E29" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="F29" s="13" t="s">
+      <c r="F29" s="14" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="30" ht="43.2" spans="1:6">
-      <c r="A30" s="12">
+    <row r="30" ht="51" spans="1:6">
+      <c r="A30" s="13">
         <v>29</v>
       </c>
-      <c r="B30" s="13" t="s">
+      <c r="B30" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="C30" s="13" t="s">
+      <c r="C30" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="D30" s="13" t="s">
+      <c r="D30" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E30" s="13" t="s">
+      <c r="E30" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="F30" s="13" t="s">
+      <c r="F30" s="14" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="31" ht="43.2" spans="1:6">
-      <c r="A31" s="12">
+    <row r="31" ht="51" spans="1:6">
+      <c r="A31" s="13">
         <v>30</v>
       </c>
-      <c r="B31" s="13" t="s">
+      <c r="B31" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="C31" s="13" t="s">
+      <c r="C31" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="D31" s="13" t="s">
+      <c r="D31" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="E31" s="13" t="s">
+      <c r="E31" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="F31" s="13" t="s">
+      <c r="F31" s="14" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="32" ht="43.2" spans="1:6">
-      <c r="A32" s="12">
+    <row r="32" ht="51" spans="1:6">
+      <c r="A32" s="13">
         <v>31</v>
       </c>
-      <c r="B32" s="13" t="s">
+      <c r="B32" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="C32" s="13" t="s">
+      <c r="C32" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="D32" s="13" t="s">
+      <c r="D32" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="E32" s="13" t="s">
+      <c r="E32" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="F32" s="13" t="s">
+      <c r="F32" s="14" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="33" ht="43.2" spans="1:6">
-      <c r="A33" s="12">
+    <row r="33" ht="51" spans="1:6">
+      <c r="A33" s="13">
         <v>32</v>
       </c>
-      <c r="B33" s="13" t="s">
+      <c r="B33" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="C33" s="13" t="s">
+      <c r="C33" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="D33" s="13" t="s">
+      <c r="D33" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="E33" s="13" t="s">
+      <c r="E33" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="F33" s="13" t="s">
+      <c r="F33" s="14" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="34" ht="43.2" spans="1:6">
-      <c r="A34" s="12">
+    <row r="34" ht="51" spans="1:6">
+      <c r="A34" s="13">
         <v>33</v>
       </c>
-      <c r="B34" s="13" t="s">
+      <c r="B34" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="C34" s="13" t="s">
+      <c r="C34" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="D34" s="13" t="s">
+      <c r="D34" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="E34" s="13" t="s">
+      <c r="E34" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="F34" s="13" t="s">
+      <c r="F34" s="14" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="35" ht="28.8" spans="1:6">
-      <c r="A35" s="12">
+    <row r="35" ht="34" spans="1:6">
+      <c r="A35" s="13">
         <v>34</v>
       </c>
-      <c r="B35" s="13" t="s">
+      <c r="B35" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="C35" s="13" t="s">
+      <c r="C35" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="D35" s="13" t="s">
+      <c r="D35" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E35" s="13" t="s">
+      <c r="E35" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="F35" s="13" t="s">
+      <c r="F35" s="14" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="36" ht="43.2" spans="1:7">
-      <c r="A36" s="12">
+    <row r="36" ht="51" spans="1:7">
+      <c r="A36" s="13">
         <v>35</v>
       </c>
-      <c r="B36" s="13" t="s">
+      <c r="B36" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="C36" s="13" t="s">
+      <c r="C36" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="D36" s="13" t="s">
+      <c r="D36" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E36" s="13" t="s">
+      <c r="E36" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="F36" s="13" t="s">
+      <c r="F36" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="G36" s="12" t="s">
+      <c r="G36" s="13" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="37" ht="72" spans="1:7">
-      <c r="A37" s="12">
+    <row r="37" ht="101" spans="1:7">
+      <c r="A37" s="13">
         <v>36</v>
       </c>
-      <c r="B37" s="13" t="s">
+      <c r="B37" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="C37" s="13" t="s">
+      <c r="C37" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="D37" s="13" t="s">
+      <c r="D37" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E37" s="13" t="s">
+      <c r="E37" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="F37" s="13" t="s">
+      <c r="F37" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="G37" s="12"/>
-    </row>
-    <row r="38" ht="72" spans="1:7">
-      <c r="A38" s="12">
+      <c r="G37" s="13"/>
+    </row>
+    <row r="38" ht="101" spans="1:7">
+      <c r="A38" s="13">
         <v>37</v>
       </c>
-      <c r="B38" s="13" t="s">
+      <c r="B38" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="C38" s="13" t="s">
+      <c r="C38" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="D38" s="13" t="s">
+      <c r="D38" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E38" s="13" t="s">
+      <c r="E38" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="F38" s="13" t="s">
+      <c r="F38" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="G38" s="12"/>
-    </row>
-    <row r="39" ht="100.8" spans="1:7">
-      <c r="A39" s="12">
+      <c r="G38" s="13"/>
+    </row>
+    <row r="39" ht="118" spans="1:7">
+      <c r="A39" s="13">
         <v>38</v>
       </c>
-      <c r="B39" s="13" t="s">
+      <c r="B39" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="C39" s="13" t="s">
+      <c r="C39" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="D39" s="13" t="s">
+      <c r="D39" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E39" s="13" t="s">
+      <c r="E39" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="F39" s="13" t="s">
+      <c r="F39" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="G39" s="12"/>
-    </row>
-    <row r="40" ht="43.2" spans="1:7">
-      <c r="A40" s="12">
+      <c r="G39" s="13"/>
+    </row>
+    <row r="40" ht="51" spans="1:7">
+      <c r="A40" s="13">
         <v>39</v>
       </c>
-      <c r="B40" s="13" t="s">
+      <c r="B40" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="C40" s="13" t="s">
+      <c r="C40" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="D40" s="13" t="s">
+      <c r="D40" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E40" s="13" t="s">
+      <c r="E40" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="F40" s="13" t="s">
+      <c r="F40" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="G40" s="12"/>
-    </row>
-    <row r="41" ht="86.4" spans="1:7">
-      <c r="A41" s="12">
+      <c r="G40" s="13"/>
+    </row>
+    <row r="41" ht="101" spans="1:7">
+      <c r="A41" s="13">
         <v>40</v>
       </c>
-      <c r="B41" s="13" t="s">
+      <c r="B41" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="C41" s="13" t="s">
+      <c r="C41" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="D41" s="13" t="s">
+      <c r="D41" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E41" s="13" t="s">
+      <c r="E41" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="F41" s="13" t="s">
+      <c r="F41" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="G41" s="13" t="s">
+      <c r="G41" s="14" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="42" ht="72" spans="1:7">
-      <c r="A42" s="12">
+    <row r="42" ht="84" spans="1:7">
+      <c r="A42" s="13">
         <v>41</v>
       </c>
-      <c r="B42" s="13" t="s">
+      <c r="B42" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="C42" s="13" t="s">
+      <c r="C42" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="D42" s="13" t="s">
+      <c r="D42" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E42" s="13" t="s">
+      <c r="E42" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="F42" s="13" t="s">
+      <c r="F42" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="G42" s="13" t="s">
+      <c r="G42" s="14" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="43" ht="72" spans="1:7">
-      <c r="A43" s="12">
+    <row r="43" ht="84" spans="1:7">
+      <c r="A43" s="13">
         <v>42</v>
       </c>
-      <c r="B43" s="13" t="s">
+      <c r="B43" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="C43" s="13" t="s">
+      <c r="C43" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="D43" s="13" t="s">
+      <c r="D43" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E43" s="13" t="s">
+      <c r="E43" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="F43" s="13" t="s">
+      <c r="F43" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="G43" s="13" t="s">
+      <c r="G43" s="14" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="44" ht="100.8" spans="1:7">
-      <c r="A44" s="12">
+    <row r="44" ht="118" spans="1:7">
+      <c r="A44" s="13">
         <v>43</v>
       </c>
-      <c r="B44" s="13" t="s">
+      <c r="B44" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="C44" s="13" t="s">
+      <c r="C44" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="D44" s="13" t="s">
+      <c r="D44" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E44" s="13" t="s">
+      <c r="E44" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="F44" s="13" t="s">
+      <c r="F44" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="G44" s="13" t="s">
+      <c r="G44" s="14" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="45" ht="86.4" spans="1:7">
-      <c r="A45" s="12">
+    <row r="45" ht="101" spans="1:7">
+      <c r="A45" s="13">
         <v>44</v>
       </c>
-      <c r="B45" s="13" t="s">
+      <c r="B45" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="C45" s="13" t="s">
+      <c r="C45" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="D45" s="13" t="s">
+      <c r="D45" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E45" s="13" t="s">
+      <c r="E45" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="F45" s="13" t="s">
+      <c r="F45" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="G45" s="13" t="s">
+      <c r="G45" s="14" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="46" ht="100.8" spans="1:7">
-      <c r="A46" s="12">
+    <row r="46" ht="118" spans="1:7">
+      <c r="A46" s="13">
         <v>45</v>
       </c>
-      <c r="B46" s="13" t="s">
+      <c r="B46" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="C46" s="13" t="s">
+      <c r="C46" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="D46" s="13" t="s">
+      <c r="D46" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E46" s="13" t="s">
+      <c r="E46" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="F46" s="13" t="s">
+      <c r="F46" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="G46" s="13" t="s">
+      <c r="G46" s="14" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="47" ht="100.8" spans="1:7">
-      <c r="A47" s="12">
+    <row r="47" ht="118" spans="1:7">
+      <c r="A47" s="13">
         <v>46</v>
       </c>
-      <c r="B47" s="13" t="s">
+      <c r="B47" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="C47" s="13" t="s">
+      <c r="C47" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="D47" s="13" t="s">
+      <c r="D47" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E47" s="13" t="s">
+      <c r="E47" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="F47" s="13" t="s">
+      <c r="F47" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="G47" s="13" t="s">
+      <c r="G47" s="14" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="48" ht="28.8" spans="1:7">
-      <c r="A48" s="12">
+    <row r="48" ht="34" spans="1:7">
+      <c r="A48" s="13">
         <v>47</v>
       </c>
-      <c r="B48" s="13" t="s">
+      <c r="B48" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="C48" s="13" t="s">
+      <c r="C48" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="D48" s="13" t="s">
+      <c r="D48" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E48" s="13" t="s">
+      <c r="E48" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="F48" s="13" t="s">
+      <c r="F48" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="G48" s="13" t="s">
+      <c r="G48" s="14" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="49" ht="28.8" spans="1:7">
-      <c r="A49" s="12">
+    <row r="49" ht="34" spans="1:7">
+      <c r="A49" s="13">
         <v>48</v>
       </c>
-      <c r="B49" s="13" t="s">
+      <c r="B49" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="C49" s="13" t="s">
+      <c r="C49" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="D49" s="13" t="s">
+      <c r="D49" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E49" s="13" t="s">
+      <c r="E49" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="F49" s="13" t="s">
+      <c r="F49" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="G49" s="13" t="s">
+      <c r="G49" s="14" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="50" ht="115.2" spans="1:7">
-      <c r="A50" s="12">
+    <row r="50" ht="135" spans="1:7">
+      <c r="A50" s="13">
         <v>49</v>
       </c>
-      <c r="B50" s="13" t="s">
+      <c r="B50" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="C50" s="13" t="s">
+      <c r="C50" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="D50" s="13" t="s">
+      <c r="D50" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E50" s="13" t="s">
+      <c r="E50" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="F50" s="13" t="s">
+      <c r="F50" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="G50" s="13" t="s">
+      <c r="G50" s="14" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="51" ht="28.8" spans="1:7">
-      <c r="A51" s="12">
+    <row r="51" ht="34" spans="1:7">
+      <c r="A51" s="13">
         <v>50</v>
       </c>
-      <c r="B51" s="13" t="s">
+      <c r="B51" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="C51" s="13" t="s">
+      <c r="C51" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="D51" s="13" t="s">
+      <c r="D51" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E51" s="13" t="s">
+      <c r="E51" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="F51" s="13" t="s">
+      <c r="F51" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="G51" s="13" t="s">
+      <c r="G51" s="14" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="52" ht="57.6" spans="1:7">
-      <c r="A52" s="12">
+    <row r="52" ht="68" spans="1:7">
+      <c r="A52" s="13">
         <v>51</v>
       </c>
-      <c r="B52" s="13" t="s">
+      <c r="B52" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="C52" s="13" t="s">
+      <c r="C52" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="D52" s="13" t="s">
+      <c r="D52" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E52" s="13" t="s">
+      <c r="E52" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="F52" s="12" t="s">
+      <c r="F52" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="G52" s="12" t="s">
+      <c r="G52" s="13" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="53" ht="57.6" spans="1:7">
-      <c r="A53" s="12">
+    <row r="53" ht="68" spans="1:7">
+      <c r="A53" s="13">
         <v>52</v>
       </c>
-      <c r="B53" s="13" t="s">
+      <c r="B53" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="C53" s="13" t="s">
+      <c r="C53" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="D53" s="13" t="s">
+      <c r="D53" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E53" s="13" t="s">
+      <c r="E53" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="F53" s="12"/>
-      <c r="G53" s="12"/>
-    </row>
-    <row r="54" ht="57.6" spans="1:7">
-      <c r="A54" s="12">
+      <c r="F53" s="13"/>
+      <c r="G53" s="13"/>
+    </row>
+    <row r="54" ht="68" spans="1:7">
+      <c r="A54" s="13">
         <v>53</v>
       </c>
-      <c r="B54" s="13" t="s">
+      <c r="B54" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="C54" s="13" t="s">
+      <c r="C54" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="D54" s="13" t="s">
+      <c r="D54" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E54" s="13" t="s">
+      <c r="E54" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="F54" s="12"/>
-      <c r="G54" s="12"/>
-    </row>
-    <row r="55" ht="57.6" spans="1:7">
-      <c r="A55" s="12">
+      <c r="F54" s="13"/>
+      <c r="G54" s="13"/>
+    </row>
+    <row r="55" ht="68" spans="1:7">
+      <c r="A55" s="13">
         <v>54</v>
       </c>
-      <c r="B55" s="13" t="s">
+      <c r="B55" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="C55" s="13" t="s">
+      <c r="C55" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="D55" s="13" t="s">
+      <c r="D55" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E55" s="13" t="s">
+      <c r="E55" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="F55" s="12"/>
-      <c r="G55" s="12"/>
-    </row>
-    <row r="56" ht="57.6" spans="1:7">
-      <c r="A56" s="12">
+      <c r="F55" s="13"/>
+      <c r="G55" s="13"/>
+    </row>
+    <row r="56" ht="68" spans="1:7">
+      <c r="A56" s="13">
         <v>55</v>
       </c>
-      <c r="B56" s="13" t="s">
+      <c r="B56" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="C56" s="13" t="s">
+      <c r="C56" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="D56" s="13" t="s">
+      <c r="D56" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E56" s="13" t="s">
+      <c r="E56" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="F56" s="12"/>
-      <c r="G56" s="12"/>
-    </row>
-    <row r="57" ht="57.6" spans="1:7">
-      <c r="A57" s="12">
+      <c r="F56" s="13"/>
+      <c r="G56" s="13"/>
+    </row>
+    <row r="57" ht="68" spans="1:7">
+      <c r="A57" s="13">
         <v>56</v>
       </c>
-      <c r="B57" s="13" t="s">
+      <c r="B57" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="C57" s="13" t="s">
+      <c r="C57" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="D57" s="13" t="s">
+      <c r="D57" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E57" s="13" t="s">
+      <c r="E57" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="F57" s="12"/>
-      <c r="G57" s="12"/>
-    </row>
-    <row r="58" ht="57.6" spans="1:7">
-      <c r="A58" s="12">
+      <c r="F57" s="13"/>
+      <c r="G57" s="13"/>
+    </row>
+    <row r="58" ht="68" spans="1:7">
+      <c r="A58" s="13">
         <v>57</v>
       </c>
-      <c r="B58" s="13" t="s">
+      <c r="B58" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="C58" s="13" t="s">
+      <c r="C58" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="D58" s="13" t="s">
+      <c r="D58" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E58" s="13" t="s">
+      <c r="E58" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="F58" s="12"/>
-      <c r="G58" s="12"/>
-    </row>
-    <row r="59" ht="57.6" spans="1:7">
-      <c r="A59" s="12">
+      <c r="F58" s="13"/>
+      <c r="G58" s="13"/>
+    </row>
+    <row r="59" ht="68" spans="1:7">
+      <c r="A59" s="13">
         <v>58</v>
       </c>
-      <c r="B59" s="13" t="s">
+      <c r="B59" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="C59" s="13" t="s">
+      <c r="C59" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="D59" s="13" t="s">
+      <c r="D59" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E59" s="13" t="s">
+      <c r="E59" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="F59" s="12"/>
-      <c r="G59" s="12"/>
-    </row>
-    <row r="60" ht="57.6" spans="1:7">
-      <c r="A60" s="12">
+      <c r="F59" s="13"/>
+      <c r="G59" s="13"/>
+    </row>
+    <row r="60" ht="68" spans="1:7">
+      <c r="A60" s="13">
         <v>59</v>
       </c>
-      <c r="B60" s="13" t="s">
+      <c r="B60" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="C60" s="13" t="s">
+      <c r="C60" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="D60" s="13" t="s">
+      <c r="D60" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E60" s="13" t="s">
+      <c r="E60" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="F60" s="12"/>
-      <c r="G60" s="12"/>
-    </row>
-    <row r="61" ht="57.6" spans="1:7">
-      <c r="A61" s="12">
+      <c r="F60" s="13"/>
+      <c r="G60" s="13"/>
+    </row>
+    <row r="61" ht="68" spans="1:7">
+      <c r="A61" s="13">
         <v>60</v>
       </c>
-      <c r="B61" s="13" t="s">
+      <c r="B61" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="C61" s="13" t="s">
+      <c r="C61" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="D61" s="13" t="s">
+      <c r="D61" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E61" s="13" t="s">
+      <c r="E61" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="F61" s="12"/>
-      <c r="G61" s="12"/>
+      <c r="F61" s="13"/>
+      <c r="G61" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -3883,1568 +4139,1568 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:K84"/>
-  <sheetFormatPr defaultColWidth="9.13888888888889" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="1" width="5.13888888888889" style="12" customWidth="1"/>
-    <col min="2" max="2" width="34.1388888888889" style="13" customWidth="1"/>
-    <col min="3" max="3" width="26.8611111111111" style="13" customWidth="1"/>
-    <col min="4" max="4" width="24.8611111111111" style="13" customWidth="1"/>
-    <col min="5" max="5" width="26.1388888888889" style="13" customWidth="1"/>
-    <col min="6" max="6" width="26.287037037037" style="13" customWidth="1"/>
-    <col min="7" max="16384" width="9.13888888888889" style="2"/>
+    <col min="1" max="1" width="5.140625" style="13" customWidth="1"/>
+    <col min="2" max="2" width="34.140625" style="14" customWidth="1"/>
+    <col min="3" max="3" width="26.859375" style="14" customWidth="1"/>
+    <col min="4" max="4" width="24.859375" style="14" customWidth="1"/>
+    <col min="5" max="5" width="26.140625" style="14" customWidth="1"/>
+    <col min="6" max="6" width="26.2890625" style="14" customWidth="1"/>
+    <col min="7" max="16384" width="9.140625" style="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:6">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="9" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" s="11" customFormat="1" ht="20" customHeight="1" spans="1:6">
-      <c r="A2" s="14" t="s">
+    <row r="2" s="12" customFormat="1" ht="20" customHeight="1" spans="1:6">
+      <c r="A2" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="16"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="20"/>
     </row>
     <row r="3" ht="118" customHeight="1" spans="1:11">
-      <c r="A3" s="12">
+      <c r="A3" s="13">
         <v>1</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="14" t="s">
         <v>111</v>
       </c>
       <c r="D3" s="17" t="s">
         <v>112</v>
       </c>
-      <c r="E3" s="18" t="s">
+      <c r="E3" s="21" t="s">
         <v>112</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
     </row>
     <row r="4" ht="101" customHeight="1" spans="1:11">
-      <c r="A4" s="12">
+      <c r="A4" s="13">
         <v>2</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="14" t="s">
         <v>114</v>
       </c>
       <c r="D4" s="17" t="s">
         <v>112</v>
       </c>
-      <c r="E4" s="19"/>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="5"/>
-      <c r="K4" s="5"/>
+      <c r="E4" s="22"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
     </row>
     <row r="5" ht="122" customHeight="1" spans="1:11">
-      <c r="A5" s="12">
+      <c r="A5" s="13">
         <v>3</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="14" t="s">
         <v>115</v>
       </c>
       <c r="D5" s="17" t="s">
         <v>112</v>
       </c>
-      <c r="E5" s="19"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-    </row>
-    <row r="6" ht="86.4" spans="1:5">
-      <c r="A6" s="12">
+      <c r="E5" s="22"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6"/>
+    </row>
+    <row r="6" ht="84" spans="1:5">
+      <c r="A6" s="13">
         <v>4</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="14" t="s">
         <v>116</v>
       </c>
       <c r="D6" s="17" t="s">
         <v>112</v>
       </c>
-      <c r="E6" s="19"/>
-    </row>
-    <row r="7" customFormat="1" ht="86.4" spans="1:6">
-      <c r="A7" s="12">
+      <c r="E6" s="22"/>
+    </row>
+    <row r="7" customFormat="1" ht="84" spans="1:6">
+      <c r="A7" s="13">
         <v>5</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="14" t="s">
         <v>117</v>
       </c>
       <c r="D7" s="17" t="s">
         <v>112</v>
       </c>
-      <c r="E7" s="20"/>
-      <c r="F7" s="13"/>
-    </row>
-    <row r="8" customFormat="1" ht="86.4" spans="1:6">
-      <c r="A8" s="12">
+      <c r="E7" s="23"/>
+      <c r="F7" s="14"/>
+    </row>
+    <row r="8" customFormat="1" ht="84" spans="1:6">
+      <c r="A8" s="13">
         <v>6</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="C8" s="14" t="s">
         <v>111</v>
       </c>
       <c r="D8" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="E8" s="18" t="s">
+      <c r="E8" s="21" t="s">
         <v>119</v>
       </c>
-      <c r="F8" s="13"/>
-    </row>
-    <row r="9" customFormat="1" ht="86.4" spans="1:6">
-      <c r="A9" s="12">
+      <c r="F8" s="14"/>
+    </row>
+    <row r="9" customFormat="1" ht="84" spans="1:6">
+      <c r="A9" s="13">
         <v>7</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" s="14" t="s">
         <v>114</v>
       </c>
       <c r="D9" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="E9" s="19"/>
-      <c r="F9" s="13"/>
-    </row>
-    <row r="10" customFormat="1" ht="86.4" spans="1:6">
-      <c r="A10" s="12">
+      <c r="E9" s="22"/>
+      <c r="F9" s="14"/>
+    </row>
+    <row r="10" customFormat="1" ht="84" spans="1:6">
+      <c r="A10" s="13">
         <v>8</v>
       </c>
-      <c r="B10" s="13" t="s">
+      <c r="B10" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="14" t="s">
         <v>115</v>
       </c>
       <c r="D10" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="E10" s="19"/>
-      <c r="F10" s="13"/>
-    </row>
-    <row r="11" customFormat="1" ht="86.4" spans="1:6">
-      <c r="A11" s="12">
+      <c r="E10" s="22"/>
+      <c r="F10" s="14"/>
+    </row>
+    <row r="11" customFormat="1" ht="84" spans="1:6">
+      <c r="A11" s="13">
         <v>9</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="14" t="s">
         <v>116</v>
       </c>
       <c r="D11" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="E11" s="19"/>
-      <c r="F11" s="13"/>
-    </row>
-    <row r="12" customFormat="1" ht="86.4" spans="1:6">
-      <c r="A12" s="12">
+      <c r="E11" s="22"/>
+      <c r="F11" s="14"/>
+    </row>
+    <row r="12" customFormat="1" ht="84" spans="1:6">
+      <c r="A12" s="13">
         <v>10</v>
       </c>
-      <c r="B12" s="13" t="s">
+      <c r="B12" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="C12" s="14" t="s">
         <v>117</v>
       </c>
       <c r="D12" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="E12" s="20"/>
-      <c r="F12" s="13"/>
+      <c r="E12" s="23"/>
+      <c r="F12" s="14"/>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="21" t="s">
+      <c r="A13" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="B13" s="21"/>
-      <c r="C13" s="21"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="21"/>
-    </row>
-    <row r="14" ht="72" spans="1:6">
-      <c r="A14" s="12">
+      <c r="B13" s="18"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
+    </row>
+    <row r="14" ht="84" spans="1:6">
+      <c r="A14" s="13">
         <v>11</v>
       </c>
-      <c r="B14" s="13" t="s">
+      <c r="B14" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="C14" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="D14" s="13" t="s">
+      <c r="D14" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="E14" s="13" t="s">
+      <c r="E14" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="F14" s="13" t="s">
+      <c r="F14" s="14" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="15" ht="57.6" spans="1:6">
-      <c r="A15" s="12">
+    <row r="15" ht="68" spans="1:6">
+      <c r="A15" s="13">
         <v>12</v>
       </c>
-      <c r="B15" s="13" t="s">
+      <c r="B15" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="C15" s="13" t="s">
+      <c r="C15" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="D15" s="13" t="s">
+      <c r="D15" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="E15" s="13" t="s">
+      <c r="E15" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="F15" s="13" t="s">
+      <c r="F15" s="14" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="16" ht="57.6" spans="1:6">
-      <c r="A16" s="12">
+    <row r="16" ht="68" spans="1:6">
+      <c r="A16" s="13">
         <v>13</v>
       </c>
-      <c r="B16" s="13" t="s">
+      <c r="B16" s="14" t="s">
         <v>130</v>
       </c>
-      <c r="C16" s="13" t="s">
+      <c r="C16" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="D16" s="13" t="s">
+      <c r="D16" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="E16" s="13" t="s">
+      <c r="E16" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="F16" s="13" t="s">
+      <c r="F16" s="14" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="17" ht="57.6" spans="1:6">
-      <c r="A17" s="12">
+    <row r="17" ht="68" spans="1:6">
+      <c r="A17" s="13">
         <v>14</v>
       </c>
-      <c r="B17" s="13" t="s">
+      <c r="B17" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="C17" s="13" t="s">
+      <c r="C17" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="D17" s="13" t="s">
+      <c r="D17" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="E17" s="13" t="s">
+      <c r="E17" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="F17" s="13" t="s">
+      <c r="F17" s="14" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="18" ht="90" customHeight="1" spans="1:6">
-      <c r="A18" s="12">
+      <c r="A18" s="13">
         <v>15</v>
       </c>
-      <c r="B18" s="22" t="s">
+      <c r="B18" s="19" t="s">
         <v>137</v>
       </c>
-      <c r="C18" s="22" t="s">
+      <c r="C18" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="D18" s="22" t="s">
+      <c r="D18" s="19" t="s">
         <v>139</v>
       </c>
-      <c r="E18" s="22" t="s">
+      <c r="E18" s="19" t="s">
         <v>140</v>
       </c>
-      <c r="F18" s="22" t="s">
+      <c r="F18" s="19" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="19" ht="66" customHeight="1" spans="1:6">
-      <c r="A19" s="12">
+      <c r="A19" s="13">
         <v>16</v>
       </c>
-      <c r="B19" s="22" t="s">
+      <c r="B19" s="19" t="s">
         <v>142</v>
       </c>
-      <c r="C19" s="22" t="s">
+      <c r="C19" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="D19" s="22" t="s">
+      <c r="D19" s="19" t="s">
         <v>143</v>
       </c>
-      <c r="E19" s="22" t="s">
+      <c r="E19" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="F19" s="22" t="s">
+      <c r="F19" s="19" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="20" ht="79" customHeight="1" spans="1:6">
-      <c r="A20" s="12">
+      <c r="A20" s="13">
         <v>17</v>
       </c>
-      <c r="B20" s="22" t="s">
+      <c r="B20" s="19" t="s">
         <v>145</v>
       </c>
-      <c r="C20" s="22" t="s">
+      <c r="C20" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="D20" s="22" t="s">
+      <c r="D20" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="E20" s="22" t="s">
+      <c r="E20" s="19" t="s">
         <v>147</v>
       </c>
-      <c r="F20" s="22" t="s">
+      <c r="F20" s="19" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="21" ht="80" customHeight="1" spans="1:6">
-      <c r="A21" s="12">
+      <c r="A21" s="13">
         <v>18</v>
       </c>
-      <c r="B21" s="22" t="s">
+      <c r="B21" s="19" t="s">
         <v>149</v>
       </c>
-      <c r="C21" s="22" t="s">
+      <c r="C21" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="D21" s="22" t="s">
+      <c r="D21" s="19" t="s">
         <v>150</v>
       </c>
-      <c r="E21" s="22" t="s">
+      <c r="E21" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="F21" s="22" t="s">
+      <c r="F21" s="19" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="22" ht="17" customHeight="1" spans="1:6">
-      <c r="A22" s="21" t="s">
+      <c r="A22" s="18" t="s">
         <v>152</v>
       </c>
-      <c r="B22" s="21"/>
-      <c r="C22" s="21"/>
-      <c r="D22" s="21"/>
-      <c r="E22" s="21"/>
-      <c r="F22" s="21"/>
-    </row>
-    <row r="23" ht="72" spans="1:6">
-      <c r="A23" s="12">
+      <c r="B22" s="18"/>
+      <c r="C22" s="18"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="18"/>
+    </row>
+    <row r="23" ht="84" spans="1:6">
+      <c r="A23" s="13">
         <v>19</v>
       </c>
-      <c r="B23" s="13" t="s">
+      <c r="B23" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="C23" s="13" t="s">
+      <c r="C23" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="D23" s="13" t="s">
+      <c r="D23" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="E23" s="13" t="s">
+      <c r="E23" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="F23" s="13" t="s">
+      <c r="F23" s="14" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="24" ht="57.6" spans="1:6">
-      <c r="A24" s="12">
+    <row r="24" ht="68" spans="1:6">
+      <c r="A24" s="13">
         <v>20</v>
       </c>
-      <c r="B24" s="13" t="s">
+      <c r="B24" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="C24" s="13" t="s">
+      <c r="C24" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="D24" s="13" t="s">
+      <c r="D24" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="E24" s="13" t="s">
+      <c r="E24" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="F24" s="13" t="s">
+      <c r="F24" s="14" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="25" ht="57.6" spans="1:6">
-      <c r="A25" s="12">
+    <row r="25" ht="68" spans="1:6">
+      <c r="A25" s="13">
         <v>21</v>
       </c>
-      <c r="B25" s="13" t="s">
+      <c r="B25" s="14" t="s">
         <v>130</v>
       </c>
-      <c r="C25" s="13" t="s">
+      <c r="C25" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="D25" s="13" t="s">
+      <c r="D25" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="E25" s="13" t="s">
+      <c r="E25" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="F25" s="13" t="s">
+      <c r="F25" s="14" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="26" ht="57.6" spans="1:6">
-      <c r="A26" s="12">
+    <row r="26" ht="68" spans="1:6">
+      <c r="A26" s="13">
         <v>22</v>
       </c>
-      <c r="B26" s="13" t="s">
+      <c r="B26" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="C26" s="13" t="s">
+      <c r="C26" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="D26" s="13" t="s">
+      <c r="D26" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="E26" s="13" t="s">
+      <c r="E26" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="F26" s="13" t="s">
+      <c r="F26" s="14" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="27" ht="57.6" spans="1:6">
-      <c r="A27" s="12">
+    <row r="27" ht="68" spans="1:6">
+      <c r="A27" s="13">
         <v>23</v>
       </c>
-      <c r="B27" s="22" t="s">
+      <c r="B27" s="19" t="s">
         <v>137</v>
       </c>
-      <c r="C27" s="22" t="s">
+      <c r="C27" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="D27" s="22" t="s">
+      <c r="D27" s="19" t="s">
         <v>154</v>
       </c>
-      <c r="E27" s="22" t="s">
+      <c r="E27" s="19" t="s">
         <v>155</v>
       </c>
-      <c r="F27" s="22" t="s">
+      <c r="F27" s="19" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="28" ht="43.2" spans="1:6">
-      <c r="A28" s="12">
+    <row r="28" ht="51" spans="1:6">
+      <c r="A28" s="13">
         <v>24</v>
       </c>
-      <c r="B28" s="22" t="s">
+      <c r="B28" s="19" t="s">
         <v>142</v>
       </c>
-      <c r="C28" s="22" t="s">
+      <c r="C28" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="D28" s="22" t="s">
+      <c r="D28" s="19" t="s">
         <v>143</v>
       </c>
-      <c r="E28" s="22" t="s">
+      <c r="E28" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="F28" s="22" t="s">
+      <c r="F28" s="19" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="29" ht="57.6" spans="1:6">
-      <c r="A29" s="12">
+    <row r="29" ht="68" spans="1:6">
+      <c r="A29" s="13">
         <v>25</v>
       </c>
-      <c r="B29" s="22" t="s">
+      <c r="B29" s="19" t="s">
         <v>145</v>
       </c>
-      <c r="C29" s="22" t="s">
+      <c r="C29" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="D29" s="22" t="s">
+      <c r="D29" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="E29" s="22" t="s">
+      <c r="E29" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="F29" s="22" t="s">
+      <c r="F29" s="19" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="30" ht="57.6" spans="1:6">
-      <c r="A30" s="12">
+    <row r="30" ht="68" spans="1:6">
+      <c r="A30" s="13">
         <v>26</v>
       </c>
-      <c r="B30" s="22" t="s">
+      <c r="B30" s="19" t="s">
         <v>149</v>
       </c>
-      <c r="C30" s="22" t="s">
+      <c r="C30" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="D30" s="22" t="s">
+      <c r="D30" s="19" t="s">
         <v>150</v>
       </c>
-      <c r="E30" s="22" t="s">
+      <c r="E30" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="F30" s="22" t="s">
+      <c r="F30" s="19" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="31" spans="1:6">
-      <c r="A31" s="21" t="s">
+      <c r="A31" s="18" t="s">
         <v>159</v>
       </c>
-      <c r="B31" s="21"/>
-      <c r="C31" s="21"/>
-      <c r="D31" s="21"/>
-      <c r="E31" s="21"/>
-      <c r="F31" s="21"/>
-    </row>
-    <row r="32" ht="57.6" spans="1:6">
-      <c r="A32" s="12">
+      <c r="B31" s="18"/>
+      <c r="C31" s="18"/>
+      <c r="D31" s="18"/>
+      <c r="E31" s="18"/>
+      <c r="F31" s="18"/>
+    </row>
+    <row r="32" ht="68" spans="1:6">
+      <c r="A32" s="13">
         <v>27</v>
       </c>
-      <c r="B32" s="22" t="s">
+      <c r="B32" s="19" t="s">
         <v>137</v>
       </c>
-      <c r="C32" s="22" t="s">
+      <c r="C32" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="D32" s="22" t="s">
+      <c r="D32" s="19" t="s">
         <v>154</v>
       </c>
-      <c r="E32" s="22" t="s">
+      <c r="E32" s="19" t="s">
         <v>160</v>
       </c>
-      <c r="F32" s="22" t="s">
+      <c r="F32" s="19" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="33" ht="43.2" spans="1:6">
-      <c r="A33" s="12">
+    <row r="33" ht="51" spans="1:6">
+      <c r="A33" s="13">
         <v>28</v>
       </c>
-      <c r="B33" s="22" t="s">
+      <c r="B33" s="19" t="s">
         <v>142</v>
       </c>
-      <c r="C33" s="22" t="s">
+      <c r="C33" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="D33" s="22" t="s">
+      <c r="D33" s="19" t="s">
         <v>143</v>
       </c>
-      <c r="E33" s="22" t="s">
+      <c r="E33" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="F33" s="22" t="s">
+      <c r="F33" s="19" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="34" ht="57.6" spans="1:6">
-      <c r="A34" s="12">
+    <row r="34" ht="68" spans="1:6">
+      <c r="A34" s="13">
         <v>29</v>
       </c>
-      <c r="B34" s="22" t="s">
+      <c r="B34" s="19" t="s">
         <v>145</v>
       </c>
-      <c r="C34" s="22" t="s">
+      <c r="C34" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="D34" s="22" t="s">
+      <c r="D34" s="19" t="s">
         <v>161</v>
       </c>
-      <c r="E34" s="22" t="s">
+      <c r="E34" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="F34" s="22" t="s">
+      <c r="F34" s="19" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="35" ht="57.6" spans="1:6">
-      <c r="A35" s="12">
+    <row r="35" ht="68" spans="1:6">
+      <c r="A35" s="13">
         <v>30</v>
       </c>
-      <c r="B35" s="22" t="s">
+      <c r="B35" s="19" t="s">
         <v>149</v>
       </c>
-      <c r="C35" s="22" t="s">
+      <c r="C35" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="D35" s="22" t="s">
+      <c r="D35" s="19" t="s">
         <v>162</v>
       </c>
-      <c r="E35" s="22" t="s">
+      <c r="E35" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="F35" s="22" t="s">
+      <c r="F35" s="19" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="36" spans="1:6">
-      <c r="A36" s="21" t="s">
+      <c r="A36" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="B36" s="21"/>
-      <c r="C36" s="21"/>
-      <c r="D36" s="21"/>
-      <c r="E36" s="21"/>
-      <c r="F36" s="21"/>
-    </row>
-    <row r="37" ht="72" spans="1:6">
-      <c r="A37" s="12">
+      <c r="B36" s="18"/>
+      <c r="C36" s="18"/>
+      <c r="D36" s="18"/>
+      <c r="E36" s="18"/>
+      <c r="F36" s="18"/>
+    </row>
+    <row r="37" ht="84" spans="1:6">
+      <c r="A37" s="13">
         <v>31</v>
       </c>
-      <c r="B37" s="22" t="s">
+      <c r="B37" s="19" t="s">
         <v>137</v>
       </c>
-      <c r="C37" s="22" t="s">
+      <c r="C37" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="D37" s="22" t="s">
+      <c r="D37" s="19" t="s">
         <v>164</v>
       </c>
-      <c r="E37" s="22" t="s">
+      <c r="E37" s="19" t="s">
         <v>165</v>
       </c>
-      <c r="F37" s="22" t="s">
+      <c r="F37" s="19" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="38" ht="57.6" spans="1:6">
-      <c r="A38" s="12">
+    <row r="38" ht="68" spans="1:6">
+      <c r="A38" s="13">
         <v>32</v>
       </c>
-      <c r="B38" s="22" t="s">
+      <c r="B38" s="19" t="s">
         <v>142</v>
       </c>
-      <c r="C38" s="22" t="s">
+      <c r="C38" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="D38" s="22" t="s">
+      <c r="D38" s="19" t="s">
         <v>166</v>
       </c>
-      <c r="E38" s="22" t="s">
+      <c r="E38" s="19" t="s">
         <v>167</v>
       </c>
-      <c r="F38" s="22" t="s">
+      <c r="F38" s="19" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="39" ht="57.6" spans="1:6">
-      <c r="A39" s="12">
+    <row r="39" ht="68" spans="1:6">
+      <c r="A39" s="13">
         <v>33</v>
       </c>
-      <c r="B39" s="22" t="s">
+      <c r="B39" s="19" t="s">
         <v>145</v>
       </c>
-      <c r="C39" s="22" t="s">
+      <c r="C39" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="D39" s="22" t="s">
+      <c r="D39" s="19" t="s">
         <v>168</v>
       </c>
-      <c r="E39" s="22" t="s">
+      <c r="E39" s="19" t="s">
         <v>169</v>
       </c>
-      <c r="F39" s="22" t="s">
+      <c r="F39" s="19" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="40" ht="57.6" spans="1:6">
-      <c r="A40" s="12">
+    <row r="40" ht="68" spans="1:6">
+      <c r="A40" s="13">
         <v>34</v>
       </c>
-      <c r="B40" s="22" t="s">
+      <c r="B40" s="19" t="s">
         <v>149</v>
       </c>
-      <c r="C40" s="22" t="s">
+      <c r="C40" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="D40" s="22" t="s">
+      <c r="D40" s="19" t="s">
         <v>170</v>
       </c>
-      <c r="E40" s="22" t="s">
+      <c r="E40" s="19" t="s">
         <v>169</v>
       </c>
-      <c r="F40" s="22" t="s">
+      <c r="F40" s="19" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="41" spans="1:6">
-      <c r="A41" s="21" t="s">
+      <c r="A41" s="18" t="s">
         <v>171</v>
       </c>
-      <c r="B41" s="21"/>
-      <c r="C41" s="21"/>
-      <c r="D41" s="21"/>
-      <c r="E41" s="21"/>
-      <c r="F41" s="21"/>
-    </row>
-    <row r="42" ht="72" spans="1:6">
-      <c r="A42" s="12">
+      <c r="B41" s="18"/>
+      <c r="C41" s="18"/>
+      <c r="D41" s="18"/>
+      <c r="E41" s="18"/>
+      <c r="F41" s="18"/>
+    </row>
+    <row r="42" ht="84" spans="1:6">
+      <c r="A42" s="13">
         <v>35</v>
       </c>
-      <c r="B42" s="13" t="s">
+      <c r="B42" s="14" t="s">
         <v>172</v>
       </c>
-      <c r="C42" s="13" t="s">
+      <c r="C42" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="D42" s="22" t="s">
+      <c r="D42" s="19" t="s">
         <v>174</v>
       </c>
-      <c r="E42" s="13" t="s">
+      <c r="E42" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="F42" s="13" t="s">
+      <c r="F42" s="14" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="43" ht="57.6" spans="1:6">
-      <c r="A43" s="12">
+    <row r="43" ht="68" spans="1:6">
+      <c r="A43" s="13">
         <v>36</v>
       </c>
-      <c r="B43" s="13" t="s">
+      <c r="B43" s="14" t="s">
         <v>176</v>
       </c>
-      <c r="C43" s="13" t="s">
+      <c r="C43" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="D43" s="22" t="s">
+      <c r="D43" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="E43" s="13" t="s">
+      <c r="E43" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="F43" s="13" t="s">
+      <c r="F43" s="14" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="44" ht="57.6" spans="1:6">
-      <c r="A44" s="12">
+    <row r="44" ht="68" spans="1:6">
+      <c r="A44" s="13">
         <v>37</v>
       </c>
-      <c r="B44" s="13" t="s">
+      <c r="B44" s="14" t="s">
         <v>130</v>
       </c>
-      <c r="C44" s="13" t="s">
+      <c r="C44" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="D44" s="22" t="s">
+      <c r="D44" s="19" t="s">
         <v>180</v>
       </c>
-      <c r="E44" s="13" t="s">
+      <c r="E44" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="F44" s="13" t="s">
+      <c r="F44" s="14" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="45" ht="57.6" spans="1:6">
-      <c r="A45" s="12">
+    <row r="45" ht="68" spans="1:6">
+      <c r="A45" s="13">
         <v>38</v>
       </c>
-      <c r="B45" s="13" t="s">
+      <c r="B45" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="C45" s="13" t="s">
+      <c r="C45" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="D45" s="22" t="s">
+      <c r="D45" s="19" t="s">
         <v>182</v>
       </c>
-      <c r="E45" s="13" t="s">
+      <c r="E45" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="F45" s="13" t="s">
+      <c r="F45" s="14" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="46" ht="57.6" spans="1:6">
-      <c r="A46" s="12">
+    <row r="46" ht="68" spans="1:6">
+      <c r="A46" s="13">
         <v>39</v>
       </c>
-      <c r="B46" s="22" t="s">
+      <c r="B46" s="19" t="s">
         <v>137</v>
       </c>
-      <c r="C46" s="22" t="s">
+      <c r="C46" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="D46" s="22" t="s">
+      <c r="D46" s="19" t="s">
         <v>184</v>
       </c>
-      <c r="E46" s="22" t="s">
+      <c r="E46" s="19" t="s">
         <v>160</v>
       </c>
-      <c r="F46" s="22" t="s">
+      <c r="F46" s="19" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="47" ht="100.8" spans="1:6">
-      <c r="A47" s="12">
+    <row r="47" ht="118" spans="1:6">
+      <c r="A47" s="13">
         <v>40</v>
       </c>
-      <c r="B47" s="22" t="s">
+      <c r="B47" s="19" t="s">
         <v>142</v>
       </c>
-      <c r="C47" s="22" t="s">
+      <c r="C47" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="D47" s="22" t="s">
+      <c r="D47" s="19" t="s">
         <v>186</v>
       </c>
-      <c r="E47" s="22" t="s">
+      <c r="E47" s="19" t="s">
         <v>187</v>
       </c>
-      <c r="F47" s="22" t="s">
+      <c r="F47" s="19" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="48" ht="57.6" spans="1:6">
-      <c r="A48" s="12">
+    <row r="48" ht="68" spans="1:6">
+      <c r="A48" s="13">
         <v>41</v>
       </c>
-      <c r="B48" s="22" t="s">
+      <c r="B48" s="19" t="s">
         <v>145</v>
       </c>
-      <c r="C48" s="22" t="s">
+      <c r="C48" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="D48" s="22" t="s">
+      <c r="D48" s="19" t="s">
         <v>189</v>
       </c>
-      <c r="E48" s="22" t="s">
+      <c r="E48" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="F48" s="22" t="s">
+      <c r="F48" s="19" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="49" ht="57.6" spans="1:6">
-      <c r="A49" s="12">
+    <row r="49" ht="68" spans="1:6">
+      <c r="A49" s="13">
         <v>42</v>
       </c>
-      <c r="B49" s="22" t="s">
+      <c r="B49" s="19" t="s">
         <v>149</v>
       </c>
-      <c r="C49" s="22" t="s">
+      <c r="C49" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="D49" s="22" t="s">
+      <c r="D49" s="19" t="s">
         <v>191</v>
       </c>
-      <c r="E49" s="22" t="s">
+      <c r="E49" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="F49" s="22" t="s">
+      <c r="F49" s="19" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="A50" s="21" t="s">
+      <c r="A50" s="18" t="s">
         <v>193</v>
       </c>
-      <c r="B50" s="21"/>
-      <c r="C50" s="21"/>
-      <c r="D50" s="21"/>
-      <c r="E50" s="21"/>
-      <c r="F50" s="21"/>
-    </row>
-    <row r="51" ht="57.6" spans="1:6">
-      <c r="A51" s="12">
+      <c r="B50" s="18"/>
+      <c r="C50" s="18"/>
+      <c r="D50" s="18"/>
+      <c r="E50" s="18"/>
+      <c r="F50" s="18"/>
+    </row>
+    <row r="51" ht="68" spans="1:6">
+      <c r="A51" s="13">
         <v>43</v>
       </c>
-      <c r="B51" s="13" t="s">
+      <c r="B51" s="14" t="s">
         <v>194</v>
       </c>
-      <c r="C51" s="13" t="s">
+      <c r="C51" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="D51" s="13" t="s">
+      <c r="D51" s="14" t="s">
         <v>195</v>
       </c>
-      <c r="E51" s="13" t="s">
+      <c r="E51" s="14" t="s">
         <v>196</v>
       </c>
-      <c r="F51" s="13" t="s">
+      <c r="F51" s="14" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="52" ht="57.6" spans="1:6">
-      <c r="A52" s="12">
+    <row r="52" ht="68" spans="1:6">
+      <c r="A52" s="13">
         <v>44</v>
       </c>
-      <c r="B52" s="13" t="s">
+      <c r="B52" s="14" t="s">
         <v>198</v>
       </c>
-      <c r="C52" s="13" t="s">
+      <c r="C52" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="D52" s="13" t="s">
+      <c r="D52" s="14" t="s">
         <v>199</v>
       </c>
-      <c r="E52" s="13" t="s">
+      <c r="E52" s="14" t="s">
         <v>196</v>
       </c>
-      <c r="F52" s="13" t="s">
+      <c r="F52" s="14" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="53" ht="57.6" spans="1:6">
-      <c r="A53" s="12">
+    <row r="53" ht="68" spans="1:6">
+      <c r="A53" s="13">
         <v>45</v>
       </c>
-      <c r="B53" s="13" t="s">
+      <c r="B53" s="14" t="s">
         <v>201</v>
       </c>
-      <c r="C53" s="13" t="s">
+      <c r="C53" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="D53" s="13" t="s">
+      <c r="D53" s="14" t="s">
         <v>202</v>
       </c>
-      <c r="E53" s="13" t="s">
+      <c r="E53" s="14" t="s">
         <v>196</v>
       </c>
-      <c r="F53" s="13" t="s">
+      <c r="F53" s="14" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="54" ht="57.6" spans="1:6">
-      <c r="A54" s="12">
+    <row r="54" ht="68" spans="1:6">
+      <c r="A54" s="13">
         <v>46</v>
       </c>
-      <c r="B54" s="13" t="s">
+      <c r="B54" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="C54" s="22" t="s">
+      <c r="C54" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="D54" s="22" t="s">
+      <c r="D54" s="19" t="s">
         <v>205</v>
       </c>
-      <c r="E54" s="22" t="s">
+      <c r="E54" s="19" t="s">
         <v>160</v>
       </c>
-      <c r="F54" s="22" t="s">
+      <c r="F54" s="19" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="55" ht="57.6" spans="1:6">
-      <c r="A55" s="12">
+    <row r="55" ht="68" spans="1:6">
+      <c r="A55" s="13">
         <v>47</v>
       </c>
-      <c r="B55" s="13" t="s">
+      <c r="B55" s="14" t="s">
         <v>206</v>
       </c>
-      <c r="C55" s="22" t="s">
+      <c r="C55" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="D55" s="22" t="s">
+      <c r="D55" s="19" t="s">
         <v>207</v>
       </c>
-      <c r="E55" s="22" t="s">
+      <c r="E55" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="F55" s="22" t="s">
+      <c r="F55" s="19" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="56" ht="57.6" spans="1:6">
-      <c r="A56" s="12">
+    <row r="56" ht="68" spans="1:6">
+      <c r="A56" s="13">
         <v>48</v>
       </c>
-      <c r="B56" s="13" t="s">
+      <c r="B56" s="14" t="s">
         <v>208</v>
       </c>
-      <c r="C56" s="22" t="s">
+      <c r="C56" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="D56" s="22" t="s">
+      <c r="D56" s="19" t="s">
         <v>209</v>
       </c>
-      <c r="E56" s="22" t="s">
+      <c r="E56" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="F56" s="22" t="s">
+      <c r="F56" s="19" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="57" ht="57.6" spans="1:6">
-      <c r="A57" s="12">
+    <row r="57" ht="68" spans="1:6">
+      <c r="A57" s="13">
         <v>49</v>
       </c>
-      <c r="B57" s="13" t="s">
+      <c r="B57" s="14" t="s">
         <v>210</v>
       </c>
-      <c r="C57" s="22" t="s">
+      <c r="C57" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="D57" s="22" t="s">
+      <c r="D57" s="19" t="s">
         <v>211</v>
       </c>
-      <c r="E57" s="22" t="s">
+      <c r="E57" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="F57" s="22" t="s">
+      <c r="F57" s="19" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="58" spans="1:6">
-      <c r="A58" s="21" t="s">
+      <c r="A58" s="18" t="s">
         <v>212</v>
       </c>
-      <c r="B58" s="21"/>
-      <c r="C58" s="21"/>
-      <c r="D58" s="21"/>
-      <c r="E58" s="21"/>
-      <c r="F58" s="21"/>
-    </row>
-    <row r="59" ht="72" spans="1:6">
-      <c r="A59" s="12">
+      <c r="B58" s="18"/>
+      <c r="C58" s="18"/>
+      <c r="D58" s="18"/>
+      <c r="E58" s="18"/>
+      <c r="F58" s="18"/>
+    </row>
+    <row r="59" ht="84" spans="1:6">
+      <c r="A59" s="13">
         <v>50</v>
       </c>
-      <c r="B59" s="13" t="s">
+      <c r="B59" s="14" t="s">
         <v>172</v>
       </c>
-      <c r="C59" s="13" t="s">
+      <c r="C59" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="D59" s="22" t="s">
+      <c r="D59" s="19" t="s">
         <v>213</v>
       </c>
-      <c r="E59" s="13" t="s">
+      <c r="E59" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="F59" s="13" t="s">
+      <c r="F59" s="14" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="60" ht="57.6" spans="1:6">
-      <c r="A60" s="12">
+    <row r="60" ht="68" spans="1:6">
+      <c r="A60" s="13">
         <v>51</v>
       </c>
-      <c r="B60" s="13" t="s">
+      <c r="B60" s="14" t="s">
         <v>176</v>
       </c>
-      <c r="C60" s="13" t="s">
+      <c r="C60" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="D60" s="22" t="s">
+      <c r="D60" s="19" t="s">
         <v>214</v>
       </c>
-      <c r="E60" s="13" t="s">
+      <c r="E60" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="F60" s="13" t="s">
+      <c r="F60" s="14" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="61" ht="57.6" spans="1:6">
-      <c r="A61" s="12">
+    <row r="61" ht="68" spans="1:6">
+      <c r="A61" s="13">
         <v>52</v>
       </c>
-      <c r="B61" s="13" t="s">
+      <c r="B61" s="14" t="s">
         <v>130</v>
       </c>
-      <c r="C61" s="13" t="s">
+      <c r="C61" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="D61" s="22" t="s">
+      <c r="D61" s="19" t="s">
         <v>215</v>
       </c>
-      <c r="E61" s="13" t="s">
+      <c r="E61" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="F61" s="13" t="s">
+      <c r="F61" s="14" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="62" ht="57.6" spans="1:6">
-      <c r="A62" s="12">
+    <row r="62" ht="68" spans="1:6">
+      <c r="A62" s="13">
         <v>53</v>
       </c>
-      <c r="B62" s="13" t="s">
+      <c r="B62" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="C62" s="13" t="s">
+      <c r="C62" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="D62" s="22" t="s">
+      <c r="D62" s="19" t="s">
         <v>216</v>
       </c>
-      <c r="E62" s="13" t="s">
+      <c r="E62" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="F62" s="13" t="s">
+      <c r="F62" s="14" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="63" ht="57.6" spans="1:6">
-      <c r="A63" s="12">
+    <row r="63" ht="68" spans="1:6">
+      <c r="A63" s="13">
         <v>54</v>
       </c>
-      <c r="B63" s="22" t="s">
+      <c r="B63" s="19" t="s">
         <v>137</v>
       </c>
-      <c r="C63" s="22" t="s">
+      <c r="C63" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="D63" s="22" t="s">
+      <c r="D63" s="19" t="s">
         <v>217</v>
       </c>
-      <c r="E63" s="22" t="s">
+      <c r="E63" s="19" t="s">
         <v>218</v>
       </c>
-      <c r="F63" s="22" t="s">
+      <c r="F63" s="19" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="64" ht="72" spans="1:6">
-      <c r="A64" s="12">
+    <row r="64" ht="84" spans="1:6">
+      <c r="A64" s="13">
         <v>55</v>
       </c>
-      <c r="B64" s="22" t="s">
+      <c r="B64" s="19" t="s">
         <v>142</v>
       </c>
-      <c r="C64" s="22" t="s">
+      <c r="C64" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="D64" s="22" t="s">
+      <c r="D64" s="19" t="s">
         <v>214</v>
       </c>
-      <c r="E64" s="22" t="s">
+      <c r="E64" s="19" t="s">
         <v>220</v>
       </c>
-      <c r="F64" s="22" t="s">
+      <c r="F64" s="19" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="65" ht="72" spans="1:6">
-      <c r="A65" s="12">
+    <row r="65" ht="84" spans="1:6">
+      <c r="A65" s="13">
         <v>56</v>
       </c>
-      <c r="B65" s="22" t="s">
+      <c r="B65" s="19" t="s">
         <v>145</v>
       </c>
-      <c r="C65" s="22" t="s">
+      <c r="C65" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="D65" s="22" t="s">
+      <c r="D65" s="19" t="s">
         <v>221</v>
       </c>
-      <c r="E65" s="22" t="s">
+      <c r="E65" s="19" t="s">
         <v>220</v>
       </c>
-      <c r="F65" s="22" t="s">
+      <c r="F65" s="19" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="66" ht="57.6" spans="1:6">
-      <c r="A66" s="12">
+    <row r="66" ht="68" spans="1:6">
+      <c r="A66" s="13">
         <v>57</v>
       </c>
-      <c r="B66" s="22" t="s">
+      <c r="B66" s="19" t="s">
         <v>149</v>
       </c>
-      <c r="C66" s="22" t="s">
+      <c r="C66" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="D66" s="22" t="s">
+      <c r="D66" s="19" t="s">
         <v>222</v>
       </c>
-      <c r="E66" s="22" t="s">
+      <c r="E66" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="F66" s="22" t="s">
+      <c r="F66" s="19" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="67" spans="1:6">
-      <c r="A67" s="21" t="s">
+      <c r="A67" s="18" t="s">
         <v>223</v>
       </c>
-      <c r="B67" s="21"/>
-      <c r="C67" s="21"/>
-      <c r="D67" s="21"/>
-      <c r="E67" s="21"/>
-      <c r="F67" s="21"/>
-    </row>
-    <row r="68" ht="72" spans="1:6">
-      <c r="A68" s="12">
+      <c r="B67" s="18"/>
+      <c r="C67" s="18"/>
+      <c r="D67" s="18"/>
+      <c r="E67" s="18"/>
+      <c r="F67" s="18"/>
+    </row>
+    <row r="68" ht="84" spans="1:6">
+      <c r="A68" s="13">
         <v>58</v>
       </c>
-      <c r="B68" s="13" t="s">
+      <c r="B68" s="14" t="s">
         <v>224</v>
       </c>
-      <c r="C68" s="13" t="s">
+      <c r="C68" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="D68" s="22" t="s">
+      <c r="D68" s="19" t="s">
         <v>225</v>
       </c>
-      <c r="E68" s="13" t="s">
+      <c r="E68" s="14" t="s">
         <v>226</v>
       </c>
-      <c r="F68" s="13" t="s">
+      <c r="F68" s="14" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="69" ht="57.6" spans="1:6">
-      <c r="A69" s="12">
+    <row r="69" ht="68" spans="1:6">
+      <c r="A69" s="13">
         <v>59</v>
       </c>
-      <c r="B69" s="13" t="s">
+      <c r="B69" s="14" t="s">
         <v>228</v>
       </c>
-      <c r="C69" s="13" t="s">
+      <c r="C69" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="D69" s="22" t="s">
+      <c r="D69" s="19" t="s">
         <v>229</v>
       </c>
-      <c r="E69" s="13" t="s">
+      <c r="E69" s="14" t="s">
         <v>230</v>
       </c>
-      <c r="F69" s="13" t="s">
+      <c r="F69" s="14" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="70" ht="57.6" spans="1:6">
-      <c r="A70" s="12">
+    <row r="70" ht="68" spans="1:6">
+      <c r="A70" s="13">
         <v>60</v>
       </c>
-      <c r="B70" s="13" t="s">
+      <c r="B70" s="14" t="s">
         <v>232</v>
       </c>
-      <c r="C70" s="13" t="s">
+      <c r="C70" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="D70" s="22" t="s">
+      <c r="D70" s="19" t="s">
         <v>233</v>
       </c>
-      <c r="E70" s="13" t="s">
+      <c r="E70" s="14" t="s">
         <v>234</v>
       </c>
-      <c r="F70" s="13" t="s">
+      <c r="F70" s="14" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="71" ht="57.6" spans="1:6">
-      <c r="A71" s="12">
+    <row r="71" ht="68" spans="1:6">
+      <c r="A71" s="13">
         <v>61</v>
       </c>
-      <c r="B71" s="13" t="s">
+      <c r="B71" s="14" t="s">
         <v>236</v>
       </c>
-      <c r="C71" s="13" t="s">
+      <c r="C71" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="D71" s="22" t="s">
+      <c r="D71" s="19" t="s">
         <v>237</v>
       </c>
-      <c r="E71" s="13" t="s">
+      <c r="E71" s="14" t="s">
         <v>234</v>
       </c>
-      <c r="F71" s="13" t="s">
+      <c r="F71" s="14" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="72" ht="57.6" spans="1:6">
-      <c r="A72" s="12">
+    <row r="72" ht="68" spans="1:6">
+      <c r="A72" s="13">
         <v>62</v>
       </c>
-      <c r="B72" s="22" t="s">
+      <c r="B72" s="19" t="s">
         <v>137</v>
       </c>
-      <c r="C72" s="22" t="s">
+      <c r="C72" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="D72" s="22" t="s">
+      <c r="D72" s="19" t="s">
         <v>239</v>
       </c>
-      <c r="E72" s="22" t="s">
+      <c r="E72" s="19" t="s">
         <v>240</v>
       </c>
-      <c r="F72" s="22" t="s">
+      <c r="F72" s="19" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="73" ht="57.6" spans="1:6">
-      <c r="A73" s="12">
+    <row r="73" ht="68" spans="1:6">
+      <c r="A73" s="13">
         <v>63</v>
       </c>
-      <c r="B73" s="22" t="s">
+      <c r="B73" s="19" t="s">
         <v>142</v>
       </c>
-      <c r="C73" s="22" t="s">
+      <c r="C73" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="D73" s="22" t="s">
+      <c r="D73" s="19" t="s">
         <v>229</v>
       </c>
-      <c r="E73" s="22" t="s">
+      <c r="E73" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="F73" s="22" t="s">
+      <c r="F73" s="19" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="74" ht="57.6" spans="1:6">
-      <c r="A74" s="12">
+    <row r="74" ht="68" spans="1:6">
+      <c r="A74" s="13">
         <v>64</v>
       </c>
-      <c r="B74" s="22" t="s">
+      <c r="B74" s="19" t="s">
         <v>242</v>
       </c>
-      <c r="C74" s="22" t="s">
+      <c r="C74" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="D74" s="22" t="s">
+      <c r="D74" s="19" t="s">
         <v>243</v>
       </c>
-      <c r="E74" s="22" t="s">
+      <c r="E74" s="19" t="s">
         <v>244</v>
       </c>
-      <c r="F74" s="22" t="s">
+      <c r="F74" s="19" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="75" ht="57.6" spans="1:6">
-      <c r="A75" s="12">
+    <row r="75" ht="68" spans="1:6">
+      <c r="A75" s="13">
         <v>65</v>
       </c>
-      <c r="B75" s="22" t="s">
+      <c r="B75" s="19" t="s">
         <v>245</v>
       </c>
-      <c r="C75" s="22" t="s">
+      <c r="C75" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="D75" s="22" t="s">
+      <c r="D75" s="19" t="s">
         <v>246</v>
       </c>
-      <c r="E75" s="22" t="s">
+      <c r="E75" s="19" t="s">
         <v>244</v>
       </c>
-      <c r="F75" s="22" t="s">
+      <c r="F75" s="19" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="76" spans="1:6">
-      <c r="A76" s="21" t="s">
+      <c r="A76" s="18" t="s">
         <v>247</v>
       </c>
-      <c r="B76" s="21"/>
-      <c r="C76" s="21"/>
-      <c r="D76" s="21"/>
-      <c r="E76" s="21"/>
-      <c r="F76" s="21"/>
-    </row>
-    <row r="77" ht="72" spans="1:6">
-      <c r="A77" s="12">
+      <c r="B76" s="18"/>
+      <c r="C76" s="18"/>
+      <c r="D76" s="18"/>
+      <c r="E76" s="18"/>
+      <c r="F76" s="18"/>
+    </row>
+    <row r="77" ht="84" spans="1:6">
+      <c r="A77" s="13">
         <v>66</v>
       </c>
-      <c r="B77" s="13" t="s">
+      <c r="B77" s="14" t="s">
         <v>224</v>
       </c>
-      <c r="C77" s="13" t="s">
+      <c r="C77" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="D77" s="22" t="s">
+      <c r="D77" s="19" t="s">
         <v>248</v>
       </c>
-      <c r="E77" s="13" t="s">
+      <c r="E77" s="14" t="s">
         <v>226</v>
       </c>
-      <c r="F77" s="13" t="s">
+      <c r="F77" s="14" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="78" ht="57.6" spans="1:6">
-      <c r="A78" s="12">
+    <row r="78" ht="68" spans="1:6">
+      <c r="A78" s="13">
         <v>67</v>
       </c>
-      <c r="B78" s="13" t="s">
+      <c r="B78" s="14" t="s">
         <v>249</v>
       </c>
-      <c r="C78" s="13" t="s">
+      <c r="C78" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="D78" s="22" t="s">
+      <c r="D78" s="19" t="s">
         <v>229</v>
       </c>
-      <c r="E78" s="13" t="s">
+      <c r="E78" s="14" t="s">
         <v>230</v>
       </c>
-      <c r="F78" s="13" t="s">
+      <c r="F78" s="14" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="79" ht="57.6" spans="1:6">
-      <c r="A79" s="12">
+    <row r="79" ht="68" spans="1:6">
+      <c r="A79" s="13">
         <v>68</v>
       </c>
-      <c r="B79" s="13" t="s">
+      <c r="B79" s="14" t="s">
         <v>232</v>
       </c>
-      <c r="C79" s="13" t="s">
+      <c r="C79" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="D79" s="22" t="s">
+      <c r="D79" s="19" t="s">
         <v>233</v>
       </c>
-      <c r="E79" s="13" t="s">
+      <c r="E79" s="14" t="s">
         <v>234</v>
       </c>
-      <c r="F79" s="13" t="s">
+      <c r="F79" s="14" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="80" ht="57.6" spans="1:6">
-      <c r="A80" s="12">
+    <row r="80" ht="68" spans="1:6">
+      <c r="A80" s="13">
         <v>69</v>
       </c>
-      <c r="B80" s="13" t="s">
+      <c r="B80" s="14" t="s">
         <v>236</v>
       </c>
-      <c r="C80" s="13" t="s">
+      <c r="C80" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="D80" s="22" t="s">
+      <c r="D80" s="19" t="s">
         <v>237</v>
       </c>
-      <c r="E80" s="13" t="s">
+      <c r="E80" s="14" t="s">
         <v>250</v>
       </c>
-      <c r="F80" s="13" t="s">
+      <c r="F80" s="14" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="81" ht="57.6" spans="1:6">
-      <c r="A81" s="12">
+    <row r="81" ht="68" spans="1:6">
+      <c r="A81" s="13">
         <v>70</v>
       </c>
-      <c r="B81" s="22" t="s">
+      <c r="B81" s="19" t="s">
         <v>137</v>
       </c>
-      <c r="C81" s="22" t="s">
+      <c r="C81" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="D81" s="22" t="s">
+      <c r="D81" s="19" t="s">
         <v>239</v>
       </c>
-      <c r="E81" s="22" t="s">
+      <c r="E81" s="19" t="s">
         <v>160</v>
       </c>
-      <c r="F81" s="22" t="s">
+      <c r="F81" s="19" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="82" ht="57.6" spans="1:6">
-      <c r="A82" s="12">
+    <row r="82" ht="68" spans="1:6">
+      <c r="A82" s="13">
         <v>71</v>
       </c>
-      <c r="B82" s="22" t="s">
+      <c r="B82" s="19" t="s">
         <v>142</v>
       </c>
-      <c r="C82" s="22" t="s">
+      <c r="C82" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="D82" s="22" t="s">
+      <c r="D82" s="19" t="s">
         <v>229</v>
       </c>
-      <c r="E82" s="22" t="s">
+      <c r="E82" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="F82" s="22" t="s">
+      <c r="F82" s="19" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="83" ht="57.6" spans="1:6">
-      <c r="A83" s="12">
+    <row r="83" ht="68" spans="1:6">
+      <c r="A83" s="13">
         <v>72</v>
       </c>
-      <c r="B83" s="22" t="s">
+      <c r="B83" s="19" t="s">
         <v>242</v>
       </c>
-      <c r="C83" s="22" t="s">
+      <c r="C83" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="D83" s="22" t="s">
+      <c r="D83" s="19" t="s">
         <v>243</v>
       </c>
-      <c r="E83" s="22" t="s">
+      <c r="E83" s="19" t="s">
         <v>244</v>
       </c>
-      <c r="F83" s="22" t="s">
+      <c r="F83" s="19" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="84" ht="57.6" spans="1:6">
-      <c r="A84" s="12">
+    <row r="84" ht="68" spans="1:6">
+      <c r="A84" s="13">
         <v>73</v>
       </c>
-      <c r="B84" s="22" t="s">
+      <c r="B84" s="19" t="s">
         <v>245</v>
       </c>
-      <c r="C84" s="22" t="s">
+      <c r="C84" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="D84" s="22" t="s">
+      <c r="D84" s="19" t="s">
         <v>246</v>
       </c>
-      <c r="E84" s="22" t="s">
+      <c r="E84" s="19" t="s">
         <v>244</v>
       </c>
-      <c r="F84" s="22" t="s">
+      <c r="F84" s="19" t="s">
         <v>192</v>
       </c>
     </row>
@@ -5473,834 +5729,834 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F52"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="4.2962962962963" style="5" customWidth="1"/>
-    <col min="2" max="2" width="26.9537037037037" style="7" customWidth="1"/>
-    <col min="3" max="3" width="23.1759259259259" style="7" customWidth="1"/>
-    <col min="4" max="4" width="25.6481481481481" style="7" customWidth="1"/>
-    <col min="5" max="5" width="10.1574074074074" style="7" customWidth="1"/>
-    <col min="6" max="6" width="18.8796296296296" style="7" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="2"/>
+    <col min="1" max="1" width="4.296875" style="6" customWidth="1"/>
+    <col min="2" max="2" width="26.953125" style="8" customWidth="1"/>
+    <col min="3" max="3" width="23.1796875" style="8" customWidth="1"/>
+    <col min="4" max="4" width="25.6484375" style="8" customWidth="1"/>
+    <col min="5" max="5" width="10.15625" style="8" customWidth="1"/>
+    <col min="6" max="6" width="18.8828125" style="8" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" s="5" customFormat="1" ht="20" customHeight="1" spans="1:6">
-      <c r="A1" s="8" t="s">
+    <row r="1" s="6" customFormat="1" ht="20" customHeight="1" spans="1:6">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="9" t="s">
         <v>251</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="9" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" s="6" customFormat="1" ht="20" customHeight="1" spans="1:6">
-      <c r="A2" s="9" t="s">
+    <row r="2" s="7" customFormat="1" ht="20" customHeight="1" spans="1:6">
+      <c r="A2" s="10" t="s">
         <v>252</v>
       </c>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-    </row>
-    <row r="3" ht="28.8" spans="1:5">
-      <c r="A3" s="5">
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+    </row>
+    <row r="3" ht="34" spans="1:5">
+      <c r="A3" s="6">
         <v>1</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="8" t="s">
         <v>253</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="8" t="s">
         <v>254</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="8" t="s">
         <v>255</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="8" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="4" ht="72" spans="1:5">
-      <c r="A4" s="5">
+    <row r="4" ht="84" spans="1:5">
+      <c r="A4" s="6">
         <v>2</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="8" t="s">
         <v>257</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="8" t="s">
         <v>258</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="8" t="s">
         <v>255</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="8" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="5" s="7" customFormat="1" ht="43.2" spans="1:5">
-      <c r="A5" s="5">
+    <row r="5" s="8" customFormat="1" ht="51" spans="1:5">
+      <c r="A5" s="6">
         <v>3</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="8" t="s">
         <v>253</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="8" t="s">
         <v>259</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="8" t="s">
         <v>255</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="8" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="6" s="5" customFormat="1" spans="1:1">
-      <c r="A6" s="5" t="s">
+    <row r="6" s="6" customFormat="1" spans="1:1">
+      <c r="A6" s="6" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="7" ht="28.8" spans="1:6">
-      <c r="A7" s="5">
+    <row r="7" ht="34" spans="1:6">
+      <c r="A7" s="6">
         <v>3</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="8" t="s">
         <v>261</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="8" t="s">
         <v>262</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="8" t="s">
         <v>256</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="F7" s="6" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="8" ht="43.2" spans="1:6">
-      <c r="A8" s="5">
+    <row r="8" ht="51" spans="1:6">
+      <c r="A8" s="6">
         <v>4</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="8" t="s">
         <v>264</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="8" t="s">
         <v>265</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="8" t="s">
         <v>266</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="8" t="s">
         <v>256</v>
       </c>
-      <c r="F8" s="5"/>
-    </row>
-    <row r="9" ht="28.8" spans="1:6">
-      <c r="A9" s="5">
+      <c r="F8" s="6"/>
+    </row>
+    <row r="9" ht="34" spans="1:6">
+      <c r="A9" s="6">
         <v>5</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="8" t="s">
         <v>267</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="8" t="s">
         <v>268</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="8" t="s">
         <v>262</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="8" t="s">
         <v>256</v>
       </c>
-      <c r="F9" s="5"/>
+      <c r="F9" s="6"/>
     </row>
     <row r="10" customFormat="1" ht="40" customHeight="1" spans="1:6">
-      <c r="A10" s="5">
+      <c r="A10" s="6">
         <v>6</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="8" t="s">
         <v>269</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="8" t="s">
         <v>270</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="6" t="s">
         <v>271</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="8" t="s">
         <v>256</v>
       </c>
-      <c r="F10" s="5"/>
+      <c r="F10" s="6"/>
     </row>
     <row r="11" customFormat="1" ht="39" customHeight="1" spans="1:6">
-      <c r="A11" s="5">
+      <c r="A11" s="6">
         <v>7</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="8" t="s">
         <v>272</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="8" t="s">
         <v>273</v>
       </c>
-      <c r="D11" s="5"/>
-      <c r="E11" s="7" t="s">
+      <c r="D11" s="6"/>
+      <c r="E11" s="8" t="s">
         <v>256</v>
       </c>
-      <c r="F11" s="5"/>
-    </row>
-    <row r="12" s="5" customFormat="1" ht="72" spans="1:5">
-      <c r="A12" s="5">
+      <c r="F11" s="6"/>
+    </row>
+    <row r="12" s="6" customFormat="1" ht="84" spans="1:5">
+      <c r="A12" s="6">
         <v>8</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="6" t="s">
         <v>275</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="8" t="s">
         <v>262</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="E12" s="8" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="13" s="5" customFormat="1" spans="1:1">
-      <c r="A13" s="5" t="s">
+    <row r="13" s="6" customFormat="1" spans="1:1">
+      <c r="A13" s="6" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="14" ht="57.6" spans="1:5">
-      <c r="A14" s="5">
+    <row r="14" ht="68" spans="1:5">
+      <c r="A14" s="6">
         <v>9</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="8" t="s">
         <v>277</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="8" t="s">
         <v>278</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D14" s="8" t="s">
         <v>279</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="E14" s="8" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="15" ht="57.6" spans="1:6">
-      <c r="A15" s="5">
+    <row r="15" ht="68" spans="1:6">
+      <c r="A15" s="6">
         <v>10</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="8" t="s">
         <v>280</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D15" s="8" t="s">
         <v>281</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="E15" s="8" t="s">
         <v>256</v>
       </c>
-      <c r="F15" s="7" t="s">
+      <c r="F15" s="8" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="16" ht="57.6" spans="1:5">
-      <c r="A16" s="5">
+    <row r="16" ht="68" spans="1:5">
+      <c r="A16" s="6">
         <v>11</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="8" t="s">
         <v>283</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D16" s="8" t="s">
         <v>281</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="E16" s="8" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="17" s="5" customFormat="1" spans="1:1">
-      <c r="A17" s="5" t="s">
+    <row r="17" s="6" customFormat="1" spans="1:1">
+      <c r="A17" s="6" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="18" ht="72" spans="1:5">
-      <c r="A18" s="5">
+    <row r="18" ht="84" spans="1:5">
+      <c r="A18" s="6">
         <v>12</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="B18" s="8" t="s">
         <v>285</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="D18" s="8" t="s">
         <v>286</v>
       </c>
-      <c r="E18" s="7" t="s">
+      <c r="E18" s="8" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="19" ht="28.8" spans="1:5">
-      <c r="A19" s="5">
+    <row r="19" ht="34" spans="1:5">
+      <c r="A19" s="6">
         <v>13</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="B19" s="8" t="s">
         <v>287</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="C19" s="8" t="s">
         <v>288</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="D19" s="8" t="s">
         <v>289</v>
       </c>
-      <c r="E19" s="7" t="s">
+      <c r="E19" s="8" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="20" ht="28.8" spans="1:5">
-      <c r="A20" s="5">
+    <row r="20" ht="34" spans="1:5">
+      <c r="A20" s="6">
         <v>14</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="6" t="s">
         <v>290</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="C20" s="8" t="s">
         <v>291</v>
       </c>
-      <c r="D20" s="7" t="s">
+      <c r="D20" s="8" t="s">
         <v>292</v>
       </c>
-      <c r="E20" s="7" t="s">
+      <c r="E20" s="8" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="21" ht="41" customHeight="1" spans="1:5">
-      <c r="A21" s="5">
+      <c r="A21" s="6">
         <v>15</v>
       </c>
-      <c r="B21" s="5"/>
-      <c r="C21" s="7" t="s">
+      <c r="B21" s="6"/>
+      <c r="C21" s="8" t="s">
         <v>293</v>
       </c>
-      <c r="D21" s="7" t="s">
+      <c r="D21" s="8" t="s">
         <v>294</v>
       </c>
-      <c r="E21" s="7" t="s">
+      <c r="E21" s="8" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="22" ht="28.8" spans="1:5">
-      <c r="A22" s="5">
+    <row r="22" ht="34" spans="1:5">
+      <c r="A22" s="6">
         <v>16</v>
       </c>
-      <c r="B22" s="5"/>
-      <c r="C22" s="7" t="s">
+      <c r="B22" s="6"/>
+      <c r="C22" s="8" t="s">
         <v>295</v>
       </c>
-      <c r="D22" s="7" t="s">
+      <c r="D22" s="8" t="s">
         <v>296</v>
       </c>
-      <c r="E22" s="7" t="s">
+      <c r="E22" s="8" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="6" t="s">
         <v>297</v>
       </c>
     </row>
     <row r="24" ht="85" customHeight="1" spans="1:5">
-      <c r="A24" s="5">
+      <c r="A24" s="6">
         <v>17</v>
       </c>
-      <c r="B24" s="7" t="s">
+      <c r="B24" s="8" t="s">
         <v>298</v>
       </c>
-      <c r="C24" s="7" t="s">
+      <c r="C24" s="8" t="s">
         <v>299</v>
       </c>
-      <c r="D24" s="7" t="s">
+      <c r="D24" s="8" t="s">
         <v>300</v>
       </c>
-      <c r="E24" s="7" t="s">
+      <c r="E24" s="8" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="25" ht="43.2" spans="1:5">
-      <c r="A25" s="5">
+    <row r="25" ht="51" spans="1:5">
+      <c r="A25" s="6">
         <v>18</v>
       </c>
-      <c r="B25" s="7" t="s">
+      <c r="B25" s="8" t="s">
         <v>301</v>
       </c>
-      <c r="C25" s="7" t="s">
+      <c r="C25" s="8" t="s">
         <v>302</v>
       </c>
-      <c r="D25" s="7" t="s">
+      <c r="D25" s="8" t="s">
         <v>303</v>
       </c>
-      <c r="E25" s="7" t="s">
+      <c r="E25" s="8" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="26" ht="43.2" spans="1:5">
-      <c r="A26" s="5">
+    <row r="26" ht="51" spans="1:5">
+      <c r="A26" s="6">
         <v>19</v>
       </c>
-      <c r="B26" s="7" t="s">
+      <c r="B26" s="8" t="s">
         <v>304</v>
       </c>
-      <c r="C26" s="7" t="s">
+      <c r="C26" s="8" t="s">
         <v>302</v>
       </c>
-      <c r="D26" s="7" t="s">
+      <c r="D26" s="8" t="s">
         <v>305</v>
       </c>
-      <c r="E26" s="7" t="s">
+      <c r="E26" s="8" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="27" ht="43.2" spans="1:5">
-      <c r="A27" s="5">
+    <row r="27" ht="51" spans="1:5">
+      <c r="A27" s="6">
         <v>20</v>
       </c>
-      <c r="B27" s="7" t="s">
+      <c r="B27" s="8" t="s">
         <v>306</v>
       </c>
-      <c r="C27" s="7" t="s">
+      <c r="C27" s="8" t="s">
         <v>307</v>
       </c>
-      <c r="D27" s="7" t="s">
+      <c r="D27" s="8" t="s">
         <v>292</v>
       </c>
-      <c r="E27" s="7" t="s">
+      <c r="E27" s="8" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="28" ht="43.2" spans="1:5">
-      <c r="A28" s="5">
+    <row r="28" ht="51" spans="1:5">
+      <c r="A28" s="6">
         <v>21</v>
       </c>
-      <c r="B28" s="7" t="s">
+      <c r="B28" s="8" t="s">
         <v>306</v>
       </c>
-      <c r="C28" s="7" t="s">
+      <c r="C28" s="8" t="s">
         <v>308</v>
       </c>
-      <c r="D28" s="7" t="s">
+      <c r="D28" s="8" t="s">
         <v>309</v>
       </c>
-      <c r="E28" s="7" t="s">
+      <c r="E28" s="8" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="29" ht="57.6" spans="1:5">
-      <c r="A29" s="5">
+    <row r="29" ht="68" spans="1:5">
+      <c r="A29" s="6">
         <v>22</v>
       </c>
-      <c r="B29" s="7" t="s">
+      <c r="B29" s="8" t="s">
         <v>306</v>
       </c>
-      <c r="C29" s="7" t="s">
+      <c r="C29" s="8" t="s">
         <v>310</v>
       </c>
-      <c r="D29" s="7" t="s">
+      <c r="D29" s="8" t="s">
         <v>311</v>
       </c>
-      <c r="E29" s="7" t="s">
+      <c r="E29" s="8" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="30" ht="72" spans="1:6">
-      <c r="A30" s="5">
+    <row r="30" ht="84" spans="1:6">
+      <c r="A30" s="6">
         <v>23</v>
       </c>
-      <c r="B30" s="7" t="s">
+      <c r="B30" s="8" t="s">
         <v>301</v>
       </c>
-      <c r="C30" s="7" t="s">
+      <c r="C30" s="8" t="s">
         <v>312</v>
       </c>
-      <c r="D30" s="7" t="s">
+      <c r="D30" s="8" t="s">
         <v>313</v>
       </c>
-      <c r="E30" s="7" t="s">
+      <c r="E30" s="8" t="s">
         <v>256</v>
       </c>
-      <c r="F30" s="7" t="s">
+      <c r="F30" s="8" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="31" ht="72" spans="1:5">
-      <c r="A31" s="5">
+    <row r="31" ht="84" spans="1:5">
+      <c r="A31" s="6">
         <v>24</v>
       </c>
-      <c r="B31" s="7" t="s">
+      <c r="B31" s="8" t="s">
         <v>315</v>
       </c>
-      <c r="C31" s="7" t="s">
+      <c r="C31" s="8" t="s">
         <v>316</v>
       </c>
-      <c r="D31" s="7" t="s">
+      <c r="D31" s="8" t="s">
         <v>317</v>
       </c>
-      <c r="E31" s="7" t="s">
+      <c r="E31" s="8" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="32" ht="43.2" spans="1:5">
-      <c r="A32" s="5">
+    <row r="32" ht="51" spans="1:5">
+      <c r="A32" s="6">
         <v>25</v>
       </c>
-      <c r="B32" s="7" t="s">
+      <c r="B32" s="8" t="s">
         <v>315</v>
       </c>
-      <c r="C32" s="7" t="s">
+      <c r="C32" s="8" t="s">
         <v>318</v>
       </c>
-      <c r="D32" s="7" t="s">
+      <c r="D32" s="8" t="s">
         <v>319</v>
       </c>
-      <c r="E32" s="7" t="s">
+      <c r="E32" s="8" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="33" ht="28.8" spans="1:5">
-      <c r="A33" s="5">
+    <row r="33" ht="34" spans="1:5">
+      <c r="A33" s="6">
         <v>26</v>
       </c>
-      <c r="B33" s="7" t="s">
+      <c r="B33" s="8" t="s">
         <v>320</v>
       </c>
-      <c r="C33" s="7" t="s">
+      <c r="C33" s="8" t="s">
         <v>321</v>
       </c>
-      <c r="D33" s="7" t="s">
+      <c r="D33" s="8" t="s">
         <v>292</v>
       </c>
-      <c r="E33" s="7" t="s">
+      <c r="E33" s="8" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="34" ht="72" spans="1:5">
-      <c r="A34" s="5">
+    <row r="34" ht="84" spans="1:5">
+      <c r="A34" s="6">
         <v>27</v>
       </c>
-      <c r="B34" s="7" t="s">
+      <c r="B34" s="8" t="s">
         <v>320</v>
       </c>
-      <c r="C34" s="10" t="s">
+      <c r="C34" s="11" t="s">
         <v>322</v>
       </c>
-      <c r="D34" s="7" t="s">
+      <c r="D34" s="8" t="s">
         <v>323</v>
       </c>
-      <c r="E34" s="7" t="s">
+      <c r="E34" s="8" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="35" ht="43.2" spans="1:5">
-      <c r="A35" s="5">
+    <row r="35" ht="51" spans="1:5">
+      <c r="A35" s="6">
         <v>28</v>
       </c>
-      <c r="B35" s="7" t="s">
+      <c r="B35" s="8" t="s">
         <v>320</v>
       </c>
-      <c r="C35" s="7" t="s">
+      <c r="C35" s="8" t="s">
         <v>324</v>
       </c>
-      <c r="D35" s="7" t="s">
+      <c r="D35" s="8" t="s">
         <v>325</v>
       </c>
-      <c r="E35" s="7" t="s">
+      <c r="E35" s="8" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="36" ht="43.2" spans="1:5">
-      <c r="A36" s="5">
+    <row r="36" ht="51" spans="1:5">
+      <c r="A36" s="6">
         <v>29</v>
       </c>
-      <c r="B36" s="7" t="s">
+      <c r="B36" s="8" t="s">
         <v>320</v>
       </c>
-      <c r="C36" s="7" t="s">
+      <c r="C36" s="8" t="s">
         <v>326</v>
       </c>
-      <c r="D36" s="7" t="s">
+      <c r="D36" s="8" t="s">
         <v>327</v>
       </c>
-      <c r="E36" s="7" t="s">
+      <c r="E36" s="8" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="37" ht="28.8" spans="1:5">
-      <c r="A37" s="5">
+    <row r="37" ht="34" spans="1:5">
+      <c r="A37" s="6">
         <v>30</v>
       </c>
-      <c r="B37" s="7" t="s">
+      <c r="B37" s="8" t="s">
         <v>320</v>
       </c>
-      <c r="C37" s="7" t="s">
+      <c r="C37" s="8" t="s">
         <v>328</v>
       </c>
-      <c r="D37" s="7" t="s">
+      <c r="D37" s="8" t="s">
         <v>329</v>
       </c>
-      <c r="E37" s="7" t="s">
+      <c r="E37" s="8" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="38" ht="43.2" spans="1:5">
-      <c r="A38" s="5">
+    <row r="38" ht="51" spans="1:5">
+      <c r="A38" s="6">
         <v>31</v>
       </c>
-      <c r="B38" s="7" t="s">
+      <c r="B38" s="8" t="s">
         <v>320</v>
       </c>
-      <c r="C38" s="7" t="s">
+      <c r="C38" s="8" t="s">
         <v>330</v>
       </c>
-      <c r="D38" s="7" t="s">
+      <c r="D38" s="8" t="s">
         <v>331</v>
       </c>
-      <c r="E38" s="7" t="s">
+      <c r="E38" s="8" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5">
+    <row r="39" ht="17" spans="1:5">
+      <c r="A39" s="6">
         <v>32</v>
       </c>
-      <c r="B39" s="7" t="s">
+      <c r="B39" s="8" t="s">
         <v>315</v>
       </c>
-      <c r="C39" s="7" t="s">
+      <c r="C39" s="8" t="s">
         <v>332</v>
       </c>
-      <c r="D39" s="7" t="s">
+      <c r="D39" s="8" t="s">
         <v>333</v>
       </c>
-      <c r="E39" s="7" t="s">
+      <c r="E39" s="8" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="40" ht="72" spans="1:5">
-      <c r="A40" s="5">
+    <row r="40" ht="84" spans="1:5">
+      <c r="A40" s="6">
         <v>33</v>
       </c>
-      <c r="B40" s="7" t="s">
+      <c r="B40" s="8" t="s">
         <v>334</v>
       </c>
-      <c r="C40" s="7" t="s">
+      <c r="C40" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="D40" s="7" t="s">
+      <c r="D40" s="8" t="s">
         <v>335</v>
       </c>
-      <c r="E40" s="7" t="s">
+      <c r="E40" s="8" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="41" ht="57.6" spans="1:6">
-      <c r="A41" s="5">
+    <row r="41" ht="68" spans="1:6">
+      <c r="A41" s="6">
         <v>34</v>
       </c>
-      <c r="B41" s="7" t="s">
+      <c r="B41" s="8" t="s">
         <v>315</v>
       </c>
-      <c r="C41" s="7" t="s">
+      <c r="C41" s="8" t="s">
         <v>336</v>
       </c>
-      <c r="D41" s="7" t="s">
+      <c r="D41" s="8" t="s">
         <v>337</v>
       </c>
-      <c r="E41" s="7" t="s">
+      <c r="E41" s="8" t="s">
         <v>256</v>
       </c>
-      <c r="F41" s="7" t="s">
+      <c r="F41" s="8" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="42" ht="72" spans="1:5">
-      <c r="A42" s="5">
+    <row r="42" ht="84" spans="1:5">
+      <c r="A42" s="6">
         <v>35</v>
       </c>
-      <c r="B42" s="7" t="s">
+      <c r="B42" s="8" t="s">
         <v>339</v>
       </c>
-      <c r="C42" s="7" t="s">
+      <c r="C42" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="D42" s="7" t="s">
+      <c r="D42" s="8" t="s">
         <v>335</v>
       </c>
-      <c r="E42" s="7" t="s">
+      <c r="E42" s="8" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="43" spans="1:6">
-      <c r="A43" s="5" t="s">
+      <c r="A43" s="6" t="s">
         <v>340</v>
       </c>
-      <c r="B43" s="5"/>
-      <c r="C43" s="5"/>
-      <c r="D43" s="5"/>
-      <c r="E43" s="5"/>
-      <c r="F43" s="5"/>
+      <c r="B43" s="6"/>
+      <c r="C43" s="6"/>
+      <c r="D43" s="6"/>
+      <c r="E43" s="6"/>
+      <c r="F43" s="6"/>
     </row>
     <row r="44" ht="37" customHeight="1" spans="1:6">
-      <c r="A44" s="5">
+      <c r="A44" s="6">
         <v>36</v>
       </c>
-      <c r="B44" s="7" t="s">
+      <c r="B44" s="8" t="s">
         <v>341</v>
       </c>
-      <c r="C44" s="5" t="s">
+      <c r="C44" s="6" t="s">
         <v>342</v>
       </c>
-      <c r="D44" s="5" t="s">
+      <c r="D44" s="6" t="s">
         <v>343</v>
       </c>
-      <c r="E44" s="7" t="s">
+      <c r="E44" s="8" t="s">
         <v>256</v>
       </c>
-      <c r="F44" s="5" t="s">
+      <c r="F44" s="6" t="s">
         <v>344</v>
       </c>
     </row>
     <row r="45" ht="37" customHeight="1" spans="1:6">
-      <c r="A45" s="5">
+      <c r="A45" s="6">
         <v>37</v>
       </c>
-      <c r="B45" s="7" t="s">
+      <c r="B45" s="8" t="s">
         <v>345</v>
       </c>
-      <c r="C45" s="5"/>
-      <c r="D45" s="5"/>
-      <c r="E45" s="7" t="s">
+      <c r="C45" s="6"/>
+      <c r="D45" s="6"/>
+      <c r="E45" s="8" t="s">
         <v>256</v>
       </c>
-      <c r="F45" s="5"/>
+      <c r="F45" s="6"/>
     </row>
     <row r="46" ht="34" customHeight="1" spans="1:6">
-      <c r="A46" s="5">
+      <c r="A46" s="6">
         <v>38</v>
       </c>
-      <c r="B46" s="7" t="s">
+      <c r="B46" s="8" t="s">
         <v>346</v>
       </c>
-      <c r="C46" s="5"/>
-      <c r="D46" s="5"/>
-      <c r="E46" s="7" t="s">
+      <c r="C46" s="6"/>
+      <c r="D46" s="6"/>
+      <c r="E46" s="8" t="s">
         <v>256</v>
       </c>
-      <c r="F46" s="5"/>
+      <c r="F46" s="6"/>
     </row>
     <row r="47" ht="33" customHeight="1" spans="1:6">
-      <c r="A47" s="5">
+      <c r="A47" s="6">
         <v>39</v>
       </c>
-      <c r="B47" s="7" t="s">
+      <c r="B47" s="8" t="s">
         <v>347</v>
       </c>
-      <c r="C47" s="5"/>
-      <c r="D47" s="5"/>
-      <c r="E47" s="7" t="s">
+      <c r="C47" s="6"/>
+      <c r="D47" s="6"/>
+      <c r="E47" s="8" t="s">
         <v>256</v>
       </c>
-      <c r="F47" s="5"/>
-    </row>
-    <row r="48" ht="28.8" spans="1:6">
-      <c r="A48" s="5">
+      <c r="F47" s="6"/>
+    </row>
+    <row r="48" ht="34" spans="1:6">
+      <c r="A48" s="6">
         <v>40</v>
       </c>
-      <c r="B48" s="7" t="s">
+      <c r="B48" s="8" t="s">
         <v>348</v>
       </c>
-      <c r="C48" s="5"/>
-      <c r="D48" s="5"/>
-      <c r="E48" s="7" t="s">
+      <c r="C48" s="6"/>
+      <c r="D48" s="6"/>
+      <c r="E48" s="8" t="s">
         <v>256</v>
       </c>
-      <c r="F48" s="5"/>
-    </row>
-    <row r="49" ht="28.8" spans="1:6">
-      <c r="A49" s="5">
+      <c r="F48" s="6"/>
+    </row>
+    <row r="49" ht="34" spans="1:6">
+      <c r="A49" s="6">
         <v>41</v>
       </c>
-      <c r="B49" s="7" t="s">
+      <c r="B49" s="8" t="s">
         <v>349</v>
       </c>
-      <c r="C49" s="5"/>
-      <c r="D49" s="5"/>
-      <c r="E49" s="7" t="s">
+      <c r="C49" s="6"/>
+      <c r="D49" s="6"/>
+      <c r="E49" s="8" t="s">
         <v>256</v>
       </c>
-      <c r="F49" s="5"/>
-    </row>
-    <row r="50" ht="28.8" spans="1:6">
-      <c r="A50" s="5">
+      <c r="F49" s="6"/>
+    </row>
+    <row r="50" ht="34" spans="1:6">
+      <c r="A50" s="6">
         <v>42</v>
       </c>
-      <c r="B50" s="7" t="s">
+      <c r="B50" s="8" t="s">
         <v>350</v>
       </c>
-      <c r="C50" s="5"/>
-      <c r="D50" s="5"/>
-      <c r="E50" s="7" t="s">
+      <c r="C50" s="6"/>
+      <c r="D50" s="6"/>
+      <c r="E50" s="8" t="s">
         <v>256</v>
       </c>
-      <c r="F50" s="5"/>
-    </row>
-    <row r="51" ht="28.8" spans="1:6">
-      <c r="A51" s="5">
+      <c r="F50" s="6"/>
+    </row>
+    <row r="51" ht="34" spans="1:6">
+      <c r="A51" s="6">
         <v>43</v>
       </c>
-      <c r="B51" s="7" t="s">
+      <c r="B51" s="8" t="s">
         <v>351</v>
       </c>
-      <c r="C51" s="5"/>
-      <c r="D51" s="5"/>
-      <c r="E51" s="7" t="s">
+      <c r="C51" s="6"/>
+      <c r="D51" s="6"/>
+      <c r="E51" s="8" t="s">
         <v>256</v>
       </c>
-      <c r="F51" s="5"/>
-    </row>
-    <row r="52" ht="57.6" spans="1:6">
-      <c r="A52" s="5">
+      <c r="F51" s="6"/>
+    </row>
+    <row r="52" ht="68" spans="1:6">
+      <c r="A52" s="6">
         <v>44</v>
       </c>
-      <c r="B52" s="7" t="s">
+      <c r="B52" s="8" t="s">
         <v>352</v>
       </c>
-      <c r="C52" s="7" t="s">
+      <c r="C52" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D52" s="7" t="s">
+      <c r="D52" s="8" t="s">
         <v>353</v>
       </c>
-      <c r="E52" s="7" t="s">
+      <c r="E52" s="8" t="s">
         <v>256</v>
       </c>
-      <c r="F52" s="7" t="s">
+      <c r="F52" s="8" t="s">
         <v>354</v>
       </c>
     </row>
@@ -6327,19 +6583,233 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="7"/>
+  <dimension ref="A1:I9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="1" width="4.9537037037037" style="2" customWidth="1"/>
-    <col min="2" max="2" width="27.6018518518519" style="2" customWidth="1"/>
-    <col min="3" max="3" width="16.4074074074074" style="2" customWidth="1"/>
-    <col min="4" max="4" width="25.2592592592593" style="2" customWidth="1"/>
-    <col min="5" max="5" width="9.24074074074074" style="2" customWidth="1"/>
-    <col min="6" max="6" width="19.6574074074074" style="2" customWidth="1"/>
+    <col min="1" max="1" width="4.953125" style="5" customWidth="1"/>
+    <col min="2" max="2" width="27.6015625" style="5" customWidth="1"/>
+    <col min="3" max="3" width="16.40625" style="5" customWidth="1"/>
+    <col min="4" max="4" width="25.2578125" style="5" customWidth="1"/>
+    <col min="5" max="5" width="9.2421875" style="5" customWidth="1"/>
+    <col min="6" max="6" width="19.65625" style="5" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="4" customFormat="1" ht="17" spans="1:8">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="2" ht="70" customHeight="1" spans="1:9">
+      <c r="A2" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>362</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>364</v>
+      </c>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+    </row>
+    <row r="3" ht="118" spans="1:9">
+      <c r="A3" s="5" t="s">
+        <v>365</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>366</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+    </row>
+    <row r="4" ht="34" spans="1:9">
+      <c r="A4" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>370</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>371</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+    </row>
+    <row r="5" ht="34" spans="1:9">
+      <c r="A5" s="5" t="s">
+        <v>373</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>370</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+    </row>
+    <row r="6" ht="118" spans="1:9">
+      <c r="A6" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>377</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+    </row>
+    <row r="7" ht="118" spans="1:9">
+      <c r="A7" s="5" t="s">
+        <v>380</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>383</v>
+      </c>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+    </row>
+    <row r="8" ht="135" spans="1:9">
+      <c r="A8" s="5" t="s">
+        <v>384</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>385</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+    </row>
+    <row r="9" ht="34" spans="1:9">
+      <c r="A9" s="5" t="s">
+        <v>386</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>387</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>371</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="H1:I9"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:I14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+  <cols>
+    <col min="1" max="1" width="7.546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="18.75" style="2" customWidth="1"/>
+    <col min="3" max="3" width="26.4296875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="19.78125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="8.84375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="18.359375" style="2" customWidth="1"/>
     <col min="7" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:9">
+    <row r="1" ht="21" customHeight="1" spans="1:9">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -6358,144 +6828,289 @@
       <c r="F1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
-        <v>358</v>
-      </c>
-      <c r="I1" s="4"/>
-    </row>
-    <row r="2" ht="70" customHeight="1" spans="1:9">
-      <c r="A2" s="2" t="s">
-        <v>359</v>
+      <c r="H1" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="I1" s="1"/>
+    </row>
+    <row r="2" ht="159" customHeight="1" spans="1:9">
+      <c r="A2" s="1" t="s">
+        <v>389</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>360</v>
+        <v>390</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>361</v>
+        <v>391</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="E2" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-    </row>
-    <row r="3" ht="100.8" spans="1:9">
-      <c r="A3" s="2" t="s">
-        <v>365</v>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" ht="210" customHeight="1" spans="1:9">
+      <c r="A3" s="1" t="s">
+        <v>393</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>366</v>
+        <v>253</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>361</v>
+        <v>394</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="E3" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>363</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
-    </row>
-    <row r="4" ht="28.8" spans="1:9">
-      <c r="A4" s="2" t="s">
-        <v>369</v>
+        <v>396</v>
+      </c>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+    </row>
+    <row r="4" ht="226" customHeight="1" spans="1:9">
+      <c r="A4" s="1" t="s">
+        <v>397</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>370</v>
+        <v>253</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>371</v>
+        <v>398</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="E4" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-    </row>
-    <row r="5" ht="28.8" spans="1:9">
-      <c r="A5" s="2" t="s">
-        <v>373</v>
+      <c r="F4" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+    </row>
+    <row r="5" ht="236" spans="1:9">
+      <c r="A5" s="1" t="s">
+        <v>401</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>370</v>
+        <v>402</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>374</v>
+        <v>403</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E5" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
-    </row>
-    <row r="6" ht="100.8" spans="1:9">
-      <c r="A6" s="2" t="s">
-        <v>376</v>
+      <c r="F5" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+    </row>
+    <row r="6" ht="202" spans="1:9">
+      <c r="A6" s="1" t="s">
+        <v>406</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>377</v>
+        <v>253</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>361</v>
+        <v>407</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>379</v>
+        <v>408</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>363</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-    </row>
-    <row r="7" ht="100.8" spans="1:9">
-      <c r="A7" s="2" t="s">
-        <v>381</v>
+        <v>409</v>
+      </c>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+    </row>
+    <row r="7" ht="236" spans="1:9">
+      <c r="A7" s="1" t="s">
+        <v>410</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>382</v>
+        <v>253</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>361</v>
+        <v>411</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="E7" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>363</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
-    </row>
-    <row r="8" spans="8:9">
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
+        <v>413</v>
+      </c>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+    </row>
+    <row r="8" ht="152" spans="1:9">
+      <c r="A8" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+    </row>
+    <row r="9" ht="185" spans="1:9">
+      <c r="A9" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+    </row>
+    <row r="10" ht="202" spans="1:9">
+      <c r="A10" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+    </row>
+    <row r="11" ht="101" spans="1:6">
+      <c r="A11" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="12" ht="118" spans="1:6">
+      <c r="A12" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="13" ht="51" spans="1:6">
+      <c r="A13" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="14" ht="34" spans="1:6">
+      <c r="A14" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>442</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="H1:I8"/>
+    <mergeCell ref="H1:I10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/Log/Magic_eraser_test_log.xlsx
+++ b/Log/Magic_eraser_test_log.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18960" windowHeight="16340" firstSheet="2" activeTab="4"/>
+    <workbookView windowWidth="23620" windowHeight="9380" firstSheet="2" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Image_selector_test" sheetId="1" r:id="rId1"/>
@@ -2214,7 +2214,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2228,12 +2228,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2835,1292 +2829,1292 @@
   <dimension ref="A1:L61"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="1" width="4" style="13" customWidth="1"/>
-    <col min="2" max="2" width="31.2890625" style="14" customWidth="1"/>
-    <col min="3" max="3" width="21.7109375" style="14" customWidth="1"/>
-    <col min="4" max="5" width="24.4296875" style="14" customWidth="1"/>
-    <col min="6" max="6" width="30.2890625" style="14" customWidth="1"/>
-    <col min="7" max="7" width="20.140625" style="14" customWidth="1"/>
-    <col min="8" max="8" width="9.140625" style="5"/>
-    <col min="9" max="9" width="17.7109375" style="5" customWidth="1"/>
-    <col min="10" max="16384" width="9.140625" style="5"/>
+    <col min="1" max="1" width="4" style="11" customWidth="1"/>
+    <col min="2" max="2" width="31.2890625" style="12" customWidth="1"/>
+    <col min="3" max="3" width="21.7109375" style="12" customWidth="1"/>
+    <col min="4" max="5" width="24.4296875" style="12" customWidth="1"/>
+    <col min="6" max="6" width="30.2890625" style="12" customWidth="1"/>
+    <col min="7" max="7" width="20.140625" style="12" customWidth="1"/>
+    <col min="8" max="8" width="9.140625" style="2"/>
+    <col min="9" max="9" width="17.7109375" style="2" customWidth="1"/>
+    <col min="10" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" ht="17.75" spans="1:7">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="25" t="s">
+      <c r="B1" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="25" t="s">
+      <c r="C1" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="25" t="s">
+      <c r="D1" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="25" t="s">
+      <c r="E1" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="25" t="s">
+      <c r="F1" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="27" t="s">
+      <c r="G1" s="25" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" ht="37" customHeight="1" spans="1:12">
-      <c r="A2" s="23">
+      <c r="A2" s="21">
         <v>1</v>
       </c>
-      <c r="B2" s="26" t="s">
+      <c r="B2" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="26" t="s">
+      <c r="C2" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="26" t="s">
+      <c r="D2" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="26" t="s">
+      <c r="E2" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="26" t="s">
+      <c r="F2" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="26"/>
-      <c r="I2" s="8" t="s">
+      <c r="G2" s="24"/>
+      <c r="I2" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="K2" s="8" t="s">
+      <c r="K2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="L2" s="8"/>
+      <c r="L2" s="6"/>
     </row>
     <row r="3" ht="34" spans="1:12">
-      <c r="A3" s="13">
+      <c r="A3" s="11">
         <v>2</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="D3" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="E3" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="14" t="s">
+      <c r="F3" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="I3" s="8"/>
-      <c r="K3" s="8"/>
-      <c r="L3" s="8"/>
+      <c r="I3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
     </row>
     <row r="4" ht="34" spans="1:12">
-      <c r="A4" s="13">
+      <c r="A4" s="11">
         <v>3</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="14" t="s">
+      <c r="D4" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="14" t="s">
+      <c r="E4" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="14" t="s">
+      <c r="F4" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="I4" s="8"/>
-      <c r="K4" s="8"/>
-      <c r="L4" s="8"/>
+      <c r="I4" s="6"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
     </row>
     <row r="5" ht="34" spans="1:12">
-      <c r="A5" s="13">
+      <c r="A5" s="11">
         <v>4</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="D5" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="E5" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="F5" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="I5" s="8"/>
-      <c r="K5" s="8"/>
-      <c r="L5" s="8"/>
+      <c r="I5" s="6"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="6"/>
     </row>
     <row r="6" ht="34" spans="1:12">
-      <c r="A6" s="13">
+      <c r="A6" s="11">
         <v>5</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="14" t="s">
+      <c r="D6" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="14" t="s">
+      <c r="E6" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="14" t="s">
+      <c r="F6" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="K6" s="8"/>
-      <c r="L6" s="8"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="6"/>
     </row>
     <row r="7" ht="17" spans="1:6">
-      <c r="A7" s="13">
+      <c r="A7" s="11">
         <v>6</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="B7" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="C7" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="14" t="s">
+      <c r="D7" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="14" t="s">
+      <c r="E7" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="F7" s="14" t="s">
+      <c r="F7" s="12" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="8" ht="50" customHeight="1" spans="1:6">
-      <c r="A8" s="13">
+      <c r="A8" s="11">
         <v>7</v>
       </c>
-      <c r="B8" s="14" t="s">
+      <c r="B8" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="14" t="s">
+      <c r="C8" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="14" t="s">
+      <c r="D8" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="14" t="s">
+      <c r="E8" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="14" t="s">
+      <c r="F8" s="12" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="9" ht="34" spans="1:6">
-      <c r="A9" s="13">
+      <c r="A9" s="11">
         <v>8</v>
       </c>
-      <c r="B9" s="14" t="s">
+      <c r="B9" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="C9" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="14" t="s">
+      <c r="D9" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="14" t="s">
+      <c r="E9" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F9" s="14" t="s">
+      <c r="F9" s="12" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="10" ht="34" spans="1:6">
-      <c r="A10" s="13">
+      <c r="A10" s="11">
         <v>9</v>
       </c>
-      <c r="B10" s="14" t="s">
+      <c r="B10" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="14" t="s">
+      <c r="C10" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="14" t="s">
+      <c r="D10" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E10" s="14" t="s">
+      <c r="E10" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F10" s="14" t="s">
+      <c r="F10" s="12" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="11" ht="34" spans="1:6">
-      <c r="A11" s="13">
+      <c r="A11" s="11">
         <v>10</v>
       </c>
-      <c r="B11" s="14" t="s">
+      <c r="B11" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="C11" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="14" t="s">
+      <c r="D11" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E11" s="14" t="s">
+      <c r="E11" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F11" s="14" t="s">
+      <c r="F11" s="12" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="12" ht="34" spans="1:6">
-      <c r="A12" s="13">
+      <c r="A12" s="11">
         <v>11</v>
       </c>
-      <c r="B12" s="14" t="s">
+      <c r="B12" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="14" t="s">
+      <c r="C12" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="14" t="s">
+      <c r="D12" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E12" s="14" t="s">
+      <c r="E12" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F12" s="14" t="s">
+      <c r="F12" s="12" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="13" ht="34" spans="1:6">
-      <c r="A13" s="13">
+      <c r="A13" s="11">
         <v>12</v>
       </c>
-      <c r="B13" s="14" t="s">
+      <c r="B13" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="14" t="s">
+      <c r="C13" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="D13" s="14" t="s">
+      <c r="D13" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E13" s="14" t="s">
+      <c r="E13" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="F13" s="14" t="s">
+      <c r="F13" s="12" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="14" ht="51" spans="1:6">
-      <c r="A14" s="13">
+      <c r="A14" s="11">
         <v>13</v>
       </c>
-      <c r="B14" s="14" t="s">
+      <c r="B14" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="14" t="s">
+      <c r="C14" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="D14" s="14" t="s">
+      <c r="D14" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E14" s="14" t="s">
+      <c r="E14" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="F14" s="14" t="s">
+      <c r="F14" s="12" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="15" ht="34" spans="1:6">
-      <c r="A15" s="13">
+      <c r="A15" s="11">
         <v>14</v>
       </c>
-      <c r="B15" s="14" t="s">
+      <c r="B15" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="C15" s="14" t="s">
+      <c r="C15" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="D15" s="14" t="s">
+      <c r="D15" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E15" s="14" t="s">
+      <c r="E15" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="F15" s="14" t="s">
+      <c r="F15" s="12" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="16" ht="34" spans="1:6">
-      <c r="A16" s="13">
+      <c r="A16" s="11">
         <v>15</v>
       </c>
-      <c r="B16" s="14" t="s">
+      <c r="B16" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="C16" s="14" t="s">
+      <c r="C16" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="D16" s="14" t="s">
+      <c r="D16" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E16" s="14" t="s">
+      <c r="E16" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="F16" s="14" t="s">
+      <c r="F16" s="12" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="17" ht="34" spans="1:6">
-      <c r="A17" s="13">
+      <c r="A17" s="11">
         <v>16</v>
       </c>
-      <c r="B17" s="14" t="s">
+      <c r="B17" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="C17" s="14" t="s">
+      <c r="C17" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="D17" s="14" t="s">
+      <c r="D17" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E17" s="14" t="s">
+      <c r="E17" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="F17" s="14" t="s">
+      <c r="F17" s="12" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="18" ht="34" spans="1:6">
-      <c r="A18" s="13">
+      <c r="A18" s="11">
         <v>17</v>
       </c>
-      <c r="B18" s="14" t="s">
+      <c r="B18" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="C18" s="14" t="s">
+      <c r="C18" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="D18" s="14" t="s">
+      <c r="D18" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E18" s="14" t="s">
+      <c r="E18" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F18" s="14" t="s">
+      <c r="F18" s="12" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="19" ht="34" spans="1:6">
-      <c r="A19" s="13">
+      <c r="A19" s="11">
         <v>18</v>
       </c>
-      <c r="B19" s="14" t="s">
+      <c r="B19" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="C19" s="14" t="s">
+      <c r="C19" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="D19" s="14" t="s">
+      <c r="D19" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E19" s="14" t="s">
+      <c r="E19" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="F19" s="14" t="s">
+      <c r="F19" s="12" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="20" ht="51" spans="1:6">
-      <c r="A20" s="13">
+      <c r="A20" s="11">
         <v>19</v>
       </c>
-      <c r="B20" s="14" t="s">
+      <c r="B20" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="C20" s="14" t="s">
+      <c r="C20" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="D20" s="14" t="s">
+      <c r="D20" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E20" s="14" t="s">
+      <c r="E20" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="F20" s="14" t="s">
+      <c r="F20" s="12" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="21" ht="34" spans="1:6">
-      <c r="A21" s="13">
+      <c r="A21" s="11">
         <v>20</v>
       </c>
-      <c r="B21" s="14" t="s">
+      <c r="B21" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="C21" s="14" t="s">
+      <c r="C21" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="D21" s="14" t="s">
+      <c r="D21" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E21" s="14" t="s">
+      <c r="E21" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="F21" s="14" t="s">
+      <c r="F21" s="12" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="22" ht="34" spans="1:6">
-      <c r="A22" s="13">
+      <c r="A22" s="11">
         <v>21</v>
       </c>
-      <c r="B22" s="14" t="s">
+      <c r="B22" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="C22" s="14" t="s">
+      <c r="C22" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="D22" s="14" t="s">
+      <c r="D22" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E22" s="14" t="s">
+      <c r="E22" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="F22" s="14" t="s">
+      <c r="F22" s="12" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="23" ht="34" spans="1:6">
-      <c r="A23" s="13">
+      <c r="A23" s="11">
         <v>22</v>
       </c>
-      <c r="B23" s="14" t="s">
+      <c r="B23" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="C23" s="14" t="s">
+      <c r="C23" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="D23" s="14" t="s">
+      <c r="D23" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E23" s="14" t="s">
+      <c r="E23" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="F23" s="14" t="s">
+      <c r="F23" s="12" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="24" ht="34" spans="1:6">
-      <c r="A24" s="13">
+      <c r="A24" s="11">
         <v>23</v>
       </c>
-      <c r="B24" s="14" t="s">
+      <c r="B24" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="C24" s="14" t="s">
+      <c r="C24" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="D24" s="14" t="s">
+      <c r="D24" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E24" s="14" t="s">
+      <c r="E24" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F24" s="14" t="s">
+      <c r="F24" s="12" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="25" ht="34" spans="1:6">
-      <c r="A25" s="13">
+      <c r="A25" s="11">
         <v>24</v>
       </c>
-      <c r="B25" s="14" t="s">
+      <c r="B25" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="C25" s="14" t="s">
+      <c r="C25" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="D25" s="14" t="s">
+      <c r="D25" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E25" s="14" t="s">
+      <c r="E25" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F25" s="14" t="s">
+      <c r="F25" s="12" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="26" ht="34" spans="1:6">
-      <c r="A26" s="13">
+      <c r="A26" s="11">
         <v>25</v>
       </c>
-      <c r="B26" s="14" t="s">
+      <c r="B26" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="C26" s="14" t="s">
+      <c r="C26" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="D26" s="14" t="s">
+      <c r="D26" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E26" s="14" t="s">
+      <c r="E26" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="F26" s="14" t="s">
+      <c r="F26" s="12" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="27" ht="51" spans="1:6">
-      <c r="A27" s="13">
+      <c r="A27" s="11">
         <v>26</v>
       </c>
-      <c r="B27" s="14" t="s">
+      <c r="B27" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="C27" s="14" t="s">
+      <c r="C27" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="D27" s="14" t="s">
+      <c r="D27" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E27" s="14" t="s">
+      <c r="E27" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="F27" s="14" t="s">
+      <c r="F27" s="12" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="28" ht="51" spans="1:6">
-      <c r="A28" s="13">
+      <c r="A28" s="11">
         <v>27</v>
       </c>
-      <c r="B28" s="14" t="s">
+      <c r="B28" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="C28" s="14" t="s">
+      <c r="C28" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="D28" s="14" t="s">
+      <c r="D28" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E28" s="14" t="s">
+      <c r="E28" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="F28" s="14" t="s">
+      <c r="F28" s="12" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="29" ht="51" spans="1:6">
-      <c r="A29" s="13">
+      <c r="A29" s="11">
         <v>28</v>
       </c>
-      <c r="B29" s="14" t="s">
+      <c r="B29" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="C29" s="14" t="s">
+      <c r="C29" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="D29" s="14" t="s">
+      <c r="D29" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E29" s="14" t="s">
+      <c r="E29" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="F29" s="14" t="s">
+      <c r="F29" s="12" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="30" ht="51" spans="1:6">
-      <c r="A30" s="13">
+      <c r="A30" s="11">
         <v>29</v>
       </c>
-      <c r="B30" s="14" t="s">
+      <c r="B30" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="C30" s="14" t="s">
+      <c r="C30" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="D30" s="14" t="s">
+      <c r="D30" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E30" s="14" t="s">
+      <c r="E30" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="F30" s="14" t="s">
+      <c r="F30" s="12" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="31" ht="51" spans="1:6">
-      <c r="A31" s="13">
+      <c r="A31" s="11">
         <v>30</v>
       </c>
-      <c r="B31" s="14" t="s">
+      <c r="B31" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="C31" s="14" t="s">
+      <c r="C31" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="D31" s="14" t="s">
+      <c r="D31" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="E31" s="14" t="s">
+      <c r="E31" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="F31" s="14" t="s">
+      <c r="F31" s="12" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="32" ht="51" spans="1:6">
-      <c r="A32" s="13">
+      <c r="A32" s="11">
         <v>31</v>
       </c>
-      <c r="B32" s="14" t="s">
+      <c r="B32" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="C32" s="14" t="s">
+      <c r="C32" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="D32" s="14" t="s">
+      <c r="D32" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="E32" s="14" t="s">
+      <c r="E32" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="F32" s="14" t="s">
+      <c r="F32" s="12" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="33" ht="51" spans="1:6">
-      <c r="A33" s="13">
+      <c r="A33" s="11">
         <v>32</v>
       </c>
-      <c r="B33" s="14" t="s">
+      <c r="B33" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="C33" s="14" t="s">
+      <c r="C33" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="D33" s="14" t="s">
+      <c r="D33" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="E33" s="14" t="s">
+      <c r="E33" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="F33" s="14" t="s">
+      <c r="F33" s="12" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="34" ht="51" spans="1:6">
-      <c r="A34" s="13">
+      <c r="A34" s="11">
         <v>33</v>
       </c>
-      <c r="B34" s="14" t="s">
+      <c r="B34" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="C34" s="14" t="s">
+      <c r="C34" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="D34" s="14" t="s">
+      <c r="D34" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="E34" s="14" t="s">
+      <c r="E34" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="F34" s="14" t="s">
+      <c r="F34" s="12" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="35" ht="34" spans="1:6">
-      <c r="A35" s="13">
+      <c r="A35" s="11">
         <v>34</v>
       </c>
-      <c r="B35" s="14" t="s">
+      <c r="B35" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="C35" s="14" t="s">
+      <c r="C35" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="D35" s="14" t="s">
+      <c r="D35" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E35" s="14" t="s">
+      <c r="E35" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="F35" s="14" t="s">
+      <c r="F35" s="12" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="36" ht="51" spans="1:7">
-      <c r="A36" s="13">
+      <c r="A36" s="11">
         <v>35</v>
       </c>
-      <c r="B36" s="14" t="s">
+      <c r="B36" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="C36" s="14" t="s">
+      <c r="C36" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="D36" s="14" t="s">
+      <c r="D36" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E36" s="14" t="s">
+      <c r="E36" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="F36" s="14" t="s">
+      <c r="F36" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="G36" s="13" t="s">
+      <c r="G36" s="11" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="37" ht="101" spans="1:7">
-      <c r="A37" s="13">
+      <c r="A37" s="11">
         <v>36</v>
       </c>
-      <c r="B37" s="14" t="s">
+      <c r="B37" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="C37" s="14" t="s">
+      <c r="C37" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="D37" s="14" t="s">
+      <c r="D37" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E37" s="14" t="s">
+      <c r="E37" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="F37" s="14" t="s">
+      <c r="F37" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="G37" s="13"/>
+      <c r="G37" s="11"/>
     </row>
     <row r="38" ht="101" spans="1:7">
-      <c r="A38" s="13">
+      <c r="A38" s="11">
         <v>37</v>
       </c>
-      <c r="B38" s="14" t="s">
+      <c r="B38" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="C38" s="14" t="s">
+      <c r="C38" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="D38" s="14" t="s">
+      <c r="D38" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E38" s="14" t="s">
+      <c r="E38" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="F38" s="14" t="s">
+      <c r="F38" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="G38" s="13"/>
+      <c r="G38" s="11"/>
     </row>
     <row r="39" ht="118" spans="1:7">
-      <c r="A39" s="13">
+      <c r="A39" s="11">
         <v>38</v>
       </c>
-      <c r="B39" s="14" t="s">
+      <c r="B39" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="C39" s="14" t="s">
+      <c r="C39" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="D39" s="14" t="s">
+      <c r="D39" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E39" s="14" t="s">
+      <c r="E39" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="F39" s="14" t="s">
+      <c r="F39" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="G39" s="13"/>
+      <c r="G39" s="11"/>
     </row>
     <row r="40" ht="51" spans="1:7">
-      <c r="A40" s="13">
+      <c r="A40" s="11">
         <v>39</v>
       </c>
-      <c r="B40" s="14" t="s">
+      <c r="B40" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="C40" s="14" t="s">
+      <c r="C40" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="D40" s="14" t="s">
+      <c r="D40" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E40" s="14" t="s">
+      <c r="E40" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="F40" s="14" t="s">
+      <c r="F40" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="G40" s="13"/>
+      <c r="G40" s="11"/>
     </row>
     <row r="41" ht="101" spans="1:7">
-      <c r="A41" s="13">
+      <c r="A41" s="11">
         <v>40</v>
       </c>
-      <c r="B41" s="14" t="s">
+      <c r="B41" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="C41" s="14" t="s">
+      <c r="C41" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="D41" s="14" t="s">
+      <c r="D41" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E41" s="14" t="s">
+      <c r="E41" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="F41" s="14" t="s">
+      <c r="F41" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="G41" s="14" t="s">
+      <c r="G41" s="12" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="42" ht="84" spans="1:7">
-      <c r="A42" s="13">
+      <c r="A42" s="11">
         <v>41</v>
       </c>
-      <c r="B42" s="14" t="s">
+      <c r="B42" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="C42" s="14" t="s">
+      <c r="C42" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="D42" s="14" t="s">
+      <c r="D42" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E42" s="14" t="s">
+      <c r="E42" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="F42" s="14" t="s">
+      <c r="F42" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="G42" s="14" t="s">
+      <c r="G42" s="12" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="43" ht="84" spans="1:7">
-      <c r="A43" s="13">
+      <c r="A43" s="11">
         <v>42</v>
       </c>
-      <c r="B43" s="14" t="s">
+      <c r="B43" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="C43" s="14" t="s">
+      <c r="C43" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="D43" s="14" t="s">
+      <c r="D43" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E43" s="14" t="s">
+      <c r="E43" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="F43" s="14" t="s">
+      <c r="F43" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="G43" s="14" t="s">
+      <c r="G43" s="12" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="44" ht="118" spans="1:7">
-      <c r="A44" s="13">
+      <c r="A44" s="11">
         <v>43</v>
       </c>
-      <c r="B44" s="14" t="s">
+      <c r="B44" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="C44" s="14" t="s">
+      <c r="C44" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="D44" s="14" t="s">
+      <c r="D44" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E44" s="14" t="s">
+      <c r="E44" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="F44" s="14" t="s">
+      <c r="F44" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="G44" s="14" t="s">
+      <c r="G44" s="12" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="45" ht="101" spans="1:7">
-      <c r="A45" s="13">
+      <c r="A45" s="11">
         <v>44</v>
       </c>
-      <c r="B45" s="14" t="s">
+      <c r="B45" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="C45" s="14" t="s">
+      <c r="C45" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="D45" s="14" t="s">
+      <c r="D45" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E45" s="14" t="s">
+      <c r="E45" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="F45" s="14" t="s">
+      <c r="F45" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="G45" s="14" t="s">
+      <c r="G45" s="12" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="46" ht="118" spans="1:7">
-      <c r="A46" s="13">
+      <c r="A46" s="11">
         <v>45</v>
       </c>
-      <c r="B46" s="14" t="s">
+      <c r="B46" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="C46" s="14" t="s">
+      <c r="C46" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="D46" s="14" t="s">
+      <c r="D46" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E46" s="14" t="s">
+      <c r="E46" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="F46" s="14" t="s">
+      <c r="F46" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="G46" s="14" t="s">
+      <c r="G46" s="12" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="47" ht="118" spans="1:7">
-      <c r="A47" s="13">
+      <c r="A47" s="11">
         <v>46</v>
       </c>
-      <c r="B47" s="14" t="s">
+      <c r="B47" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="C47" s="14" t="s">
+      <c r="C47" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="D47" s="14" t="s">
+      <c r="D47" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E47" s="14" t="s">
+      <c r="E47" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="F47" s="14" t="s">
+      <c r="F47" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="G47" s="14" t="s">
+      <c r="G47" s="12" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="48" ht="34" spans="1:7">
-      <c r="A48" s="13">
+      <c r="A48" s="11">
         <v>47</v>
       </c>
-      <c r="B48" s="14" t="s">
+      <c r="B48" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="C48" s="14" t="s">
+      <c r="C48" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="D48" s="14" t="s">
+      <c r="D48" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E48" s="14" t="s">
+      <c r="E48" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="F48" s="14" t="s">
+      <c r="F48" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="G48" s="14" t="s">
+      <c r="G48" s="12" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="49" ht="34" spans="1:7">
-      <c r="A49" s="13">
+      <c r="A49" s="11">
         <v>48</v>
       </c>
-      <c r="B49" s="14" t="s">
+      <c r="B49" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="C49" s="14" t="s">
+      <c r="C49" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="D49" s="14" t="s">
+      <c r="D49" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E49" s="14" t="s">
+      <c r="E49" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="F49" s="14" t="s">
+      <c r="F49" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="G49" s="14" t="s">
+      <c r="G49" s="12" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="50" ht="135" spans="1:7">
-      <c r="A50" s="13">
+      <c r="A50" s="11">
         <v>49</v>
       </c>
-      <c r="B50" s="14" t="s">
+      <c r="B50" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="C50" s="14" t="s">
+      <c r="C50" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="D50" s="14" t="s">
+      <c r="D50" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E50" s="14" t="s">
+      <c r="E50" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="F50" s="14" t="s">
+      <c r="F50" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="G50" s="14" t="s">
+      <c r="G50" s="12" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="51" ht="34" spans="1:7">
-      <c r="A51" s="13">
+      <c r="A51" s="11">
         <v>50</v>
       </c>
-      <c r="B51" s="14" t="s">
+      <c r="B51" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="C51" s="14" t="s">
+      <c r="C51" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="D51" s="14" t="s">
+      <c r="D51" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E51" s="14" t="s">
+      <c r="E51" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="F51" s="14" t="s">
+      <c r="F51" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="G51" s="14" t="s">
+      <c r="G51" s="12" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="52" ht="68" spans="1:7">
-      <c r="A52" s="13">
+      <c r="A52" s="11">
         <v>51</v>
       </c>
-      <c r="B52" s="14" t="s">
+      <c r="B52" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="C52" s="14" t="s">
+      <c r="C52" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="D52" s="14" t="s">
+      <c r="D52" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E52" s="14" t="s">
+      <c r="E52" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="F52" s="13" t="s">
+      <c r="F52" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="G52" s="13" t="s">
+      <c r="G52" s="11" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="53" ht="68" spans="1:7">
-      <c r="A53" s="13">
+      <c r="A53" s="11">
         <v>52</v>
       </c>
-      <c r="B53" s="14" t="s">
+      <c r="B53" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="C53" s="14" t="s">
+      <c r="C53" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="D53" s="14" t="s">
+      <c r="D53" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E53" s="14" t="s">
+      <c r="E53" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="F53" s="13"/>
-      <c r="G53" s="13"/>
+      <c r="F53" s="11"/>
+      <c r="G53" s="11"/>
     </row>
     <row r="54" ht="68" spans="1:7">
-      <c r="A54" s="13">
+      <c r="A54" s="11">
         <v>53</v>
       </c>
-      <c r="B54" s="14" t="s">
+      <c r="B54" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="C54" s="14" t="s">
+      <c r="C54" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="D54" s="14" t="s">
+      <c r="D54" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E54" s="14" t="s">
+      <c r="E54" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="F54" s="13"/>
-      <c r="G54" s="13"/>
+      <c r="F54" s="11"/>
+      <c r="G54" s="11"/>
     </row>
     <row r="55" ht="68" spans="1:7">
-      <c r="A55" s="13">
+      <c r="A55" s="11">
         <v>54</v>
       </c>
-      <c r="B55" s="14" t="s">
+      <c r="B55" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="C55" s="14" t="s">
+      <c r="C55" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="D55" s="14" t="s">
+      <c r="D55" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E55" s="14" t="s">
+      <c r="E55" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="F55" s="13"/>
-      <c r="G55" s="13"/>
+      <c r="F55" s="11"/>
+      <c r="G55" s="11"/>
     </row>
     <row r="56" ht="68" spans="1:7">
-      <c r="A56" s="13">
+      <c r="A56" s="11">
         <v>55</v>
       </c>
-      <c r="B56" s="14" t="s">
+      <c r="B56" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="C56" s="14" t="s">
+      <c r="C56" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="D56" s="14" t="s">
+      <c r="D56" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E56" s="14" t="s">
+      <c r="E56" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="F56" s="13"/>
-      <c r="G56" s="13"/>
+      <c r="F56" s="11"/>
+      <c r="G56" s="11"/>
     </row>
     <row r="57" ht="68" spans="1:7">
-      <c r="A57" s="13">
+      <c r="A57" s="11">
         <v>56</v>
       </c>
-      <c r="B57" s="14" t="s">
+      <c r="B57" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="C57" s="14" t="s">
+      <c r="C57" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="D57" s="14" t="s">
+      <c r="D57" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E57" s="14" t="s">
+      <c r="E57" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="F57" s="13"/>
-      <c r="G57" s="13"/>
+      <c r="F57" s="11"/>
+      <c r="G57" s="11"/>
     </row>
     <row r="58" ht="68" spans="1:7">
-      <c r="A58" s="13">
+      <c r="A58" s="11">
         <v>57</v>
       </c>
-      <c r="B58" s="14" t="s">
+      <c r="B58" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="C58" s="14" t="s">
+      <c r="C58" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="D58" s="14" t="s">
+      <c r="D58" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E58" s="14" t="s">
+      <c r="E58" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="F58" s="13"/>
-      <c r="G58" s="13"/>
+      <c r="F58" s="11"/>
+      <c r="G58" s="11"/>
     </row>
     <row r="59" ht="68" spans="1:7">
-      <c r="A59" s="13">
+      <c r="A59" s="11">
         <v>58</v>
       </c>
-      <c r="B59" s="14" t="s">
+      <c r="B59" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="C59" s="14" t="s">
+      <c r="C59" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="D59" s="14" t="s">
+      <c r="D59" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E59" s="14" t="s">
+      <c r="E59" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="F59" s="13"/>
-      <c r="G59" s="13"/>
+      <c r="F59" s="11"/>
+      <c r="G59" s="11"/>
     </row>
     <row r="60" ht="68" spans="1:7">
-      <c r="A60" s="13">
+      <c r="A60" s="11">
         <v>59</v>
       </c>
-      <c r="B60" s="14" t="s">
+      <c r="B60" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="C60" s="14" t="s">
+      <c r="C60" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="D60" s="14" t="s">
+      <c r="D60" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E60" s="14" t="s">
+      <c r="E60" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="F60" s="13"/>
-      <c r="G60" s="13"/>
+      <c r="F60" s="11"/>
+      <c r="G60" s="11"/>
     </row>
     <row r="61" ht="68" spans="1:7">
-      <c r="A61" s="13">
+      <c r="A61" s="11">
         <v>60</v>
       </c>
-      <c r="B61" s="14" t="s">
+      <c r="B61" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="C61" s="14" t="s">
+      <c r="C61" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="D61" s="14" t="s">
+      <c r="D61" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E61" s="14" t="s">
+      <c r="E61" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="F61" s="13"/>
-      <c r="G61" s="13"/>
+      <c r="F61" s="11"/>
+      <c r="G61" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -4141,1566 +4135,1566 @@
   <dimension ref="A1:K84"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="1" width="5.140625" style="13" customWidth="1"/>
-    <col min="2" max="2" width="34.140625" style="14" customWidth="1"/>
-    <col min="3" max="3" width="26.859375" style="14" customWidth="1"/>
-    <col min="4" max="4" width="24.859375" style="14" customWidth="1"/>
-    <col min="5" max="5" width="26.140625" style="14" customWidth="1"/>
-    <col min="6" max="6" width="26.2890625" style="14" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="5"/>
+    <col min="1" max="1" width="5.140625" style="11" customWidth="1"/>
+    <col min="2" max="2" width="34.140625" style="12" customWidth="1"/>
+    <col min="3" max="3" width="26.859375" style="12" customWidth="1"/>
+    <col min="4" max="4" width="24.859375" style="12" customWidth="1"/>
+    <col min="5" max="5" width="26.140625" style="12" customWidth="1"/>
+    <col min="6" max="6" width="26.2890625" style="12" customWidth="1"/>
+    <col min="7" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:6">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="7" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" s="12" customFormat="1" ht="20" customHeight="1" spans="1:6">
-      <c r="A2" s="15" t="s">
+    <row r="2" s="10" customFormat="1" ht="20" customHeight="1" spans="1:6">
+      <c r="A2" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="20"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="18"/>
     </row>
     <row r="3" ht="118" customHeight="1" spans="1:11">
-      <c r="A3" s="13">
+      <c r="A3" s="11">
         <v>1</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="D3" s="17" t="s">
+      <c r="D3" s="15" t="s">
         <v>112</v>
       </c>
-      <c r="E3" s="21" t="s">
+      <c r="E3" s="19" t="s">
         <v>112</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="I3" s="6"/>
-      <c r="J3" s="6"/>
-      <c r="K3" s="6"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
     </row>
     <row r="4" ht="101" customHeight="1" spans="1:11">
-      <c r="A4" s="13">
+      <c r="A4" s="11">
         <v>2</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="D4" s="17" t="s">
+      <c r="D4" s="15" t="s">
         <v>112</v>
       </c>
-      <c r="E4" s="22"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6"/>
+      <c r="E4" s="20"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
     </row>
     <row r="5" ht="122" customHeight="1" spans="1:11">
-      <c r="A5" s="13">
+      <c r="A5" s="11">
         <v>3</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="D5" s="17" t="s">
+      <c r="D5" s="15" t="s">
         <v>112</v>
       </c>
-      <c r="E5" s="22"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="6"/>
-      <c r="K5" s="6"/>
+      <c r="E5" s="20"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
     </row>
     <row r="6" ht="84" spans="1:5">
-      <c r="A6" s="13">
+      <c r="A6" s="11">
         <v>4</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="D6" s="17" t="s">
+      <c r="D6" s="15" t="s">
         <v>112</v>
       </c>
-      <c r="E6" s="22"/>
+      <c r="E6" s="20"/>
     </row>
     <row r="7" customFormat="1" ht="84" spans="1:6">
-      <c r="A7" s="13">
+      <c r="A7" s="11">
         <v>5</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="B7" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="C7" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="D7" s="17" t="s">
+      <c r="D7" s="15" t="s">
         <v>112</v>
       </c>
-      <c r="E7" s="23"/>
-      <c r="F7" s="14"/>
+      <c r="E7" s="21"/>
+      <c r="F7" s="12"/>
     </row>
     <row r="8" customFormat="1" ht="84" spans="1:6">
-      <c r="A8" s="13">
+      <c r="A8" s="11">
         <v>6</v>
       </c>
-      <c r="B8" s="14" t="s">
+      <c r="B8" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="C8" s="14" t="s">
+      <c r="C8" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="D8" s="17" t="s">
+      <c r="D8" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="E8" s="21" t="s">
+      <c r="E8" s="19" t="s">
         <v>119</v>
       </c>
-      <c r="F8" s="14"/>
+      <c r="F8" s="12"/>
     </row>
     <row r="9" customFormat="1" ht="84" spans="1:6">
-      <c r="A9" s="13">
+      <c r="A9" s="11">
         <v>7</v>
       </c>
-      <c r="B9" s="14" t="s">
+      <c r="B9" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="C9" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="D9" s="17" t="s">
+      <c r="D9" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="E9" s="22"/>
-      <c r="F9" s="14"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="12"/>
     </row>
     <row r="10" customFormat="1" ht="84" spans="1:6">
-      <c r="A10" s="13">
+      <c r="A10" s="11">
         <v>8</v>
       </c>
-      <c r="B10" s="14" t="s">
+      <c r="B10" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="C10" s="14" t="s">
+      <c r="C10" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="D10" s="17" t="s">
+      <c r="D10" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="E10" s="22"/>
-      <c r="F10" s="14"/>
+      <c r="E10" s="20"/>
+      <c r="F10" s="12"/>
     </row>
     <row r="11" customFormat="1" ht="84" spans="1:6">
-      <c r="A11" s="13">
+      <c r="A11" s="11">
         <v>9</v>
       </c>
-      <c r="B11" s="14" t="s">
+      <c r="B11" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="C11" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="D11" s="17" t="s">
+      <c r="D11" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="E11" s="22"/>
-      <c r="F11" s="14"/>
+      <c r="E11" s="20"/>
+      <c r="F11" s="12"/>
     </row>
     <row r="12" customFormat="1" ht="84" spans="1:6">
-      <c r="A12" s="13">
+      <c r="A12" s="11">
         <v>10</v>
       </c>
-      <c r="B12" s="14" t="s">
+      <c r="B12" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="C12" s="14" t="s">
+      <c r="C12" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="D12" s="17" t="s">
+      <c r="D12" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="E12" s="23"/>
-      <c r="F12" s="14"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="12"/>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="18" t="s">
+      <c r="A13" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="B13" s="18"/>
-      <c r="C13" s="18"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
+      <c r="B13" s="16"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="16"/>
     </row>
     <row r="14" ht="84" spans="1:6">
-      <c r="A14" s="13">
+      <c r="A14" s="11">
         <v>11</v>
       </c>
-      <c r="B14" s="14" t="s">
+      <c r="B14" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="C14" s="14" t="s">
+      <c r="C14" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="D14" s="14" t="s">
+      <c r="D14" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="E14" s="14" t="s">
+      <c r="E14" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="F14" s="14" t="s">
+      <c r="F14" s="12" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="15" ht="68" spans="1:6">
-      <c r="A15" s="13">
+      <c r="A15" s="11">
         <v>12</v>
       </c>
-      <c r="B15" s="14" t="s">
+      <c r="B15" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="C15" s="14" t="s">
+      <c r="C15" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="D15" s="14" t="s">
+      <c r="D15" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="E15" s="14" t="s">
+      <c r="E15" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="F15" s="14" t="s">
+      <c r="F15" s="12" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="16" ht="68" spans="1:6">
-      <c r="A16" s="13">
+      <c r="A16" s="11">
         <v>13</v>
       </c>
-      <c r="B16" s="14" t="s">
+      <c r="B16" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="C16" s="14" t="s">
+      <c r="C16" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="D16" s="14" t="s">
+      <c r="D16" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="E16" s="14" t="s">
+      <c r="E16" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="F16" s="14" t="s">
+      <c r="F16" s="12" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="17" ht="68" spans="1:6">
-      <c r="A17" s="13">
+      <c r="A17" s="11">
         <v>14</v>
       </c>
-      <c r="B17" s="14" t="s">
+      <c r="B17" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="C17" s="14" t="s">
+      <c r="C17" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="D17" s="14" t="s">
+      <c r="D17" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="E17" s="14" t="s">
+      <c r="E17" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="F17" s="14" t="s">
+      <c r="F17" s="12" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="18" ht="90" customHeight="1" spans="1:6">
-      <c r="A18" s="13">
+      <c r="A18" s="11">
         <v>15</v>
       </c>
-      <c r="B18" s="19" t="s">
+      <c r="B18" s="17" t="s">
         <v>137</v>
       </c>
-      <c r="C18" s="19" t="s">
+      <c r="C18" s="17" t="s">
         <v>138</v>
       </c>
-      <c r="D18" s="19" t="s">
+      <c r="D18" s="17" t="s">
         <v>139</v>
       </c>
-      <c r="E18" s="19" t="s">
+      <c r="E18" s="17" t="s">
         <v>140</v>
       </c>
-      <c r="F18" s="19" t="s">
+      <c r="F18" s="17" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="19" ht="66" customHeight="1" spans="1:6">
-      <c r="A19" s="13">
+      <c r="A19" s="11">
         <v>16</v>
       </c>
-      <c r="B19" s="19" t="s">
+      <c r="B19" s="17" t="s">
         <v>142</v>
       </c>
-      <c r="C19" s="19" t="s">
+      <c r="C19" s="17" t="s">
         <v>138</v>
       </c>
-      <c r="D19" s="19" t="s">
+      <c r="D19" s="17" t="s">
         <v>143</v>
       </c>
-      <c r="E19" s="19" t="s">
+      <c r="E19" s="17" t="s">
         <v>128</v>
       </c>
-      <c r="F19" s="19" t="s">
+      <c r="F19" s="17" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="20" ht="79" customHeight="1" spans="1:6">
-      <c r="A20" s="13">
+      <c r="A20" s="11">
         <v>17</v>
       </c>
-      <c r="B20" s="19" t="s">
+      <c r="B20" s="17" t="s">
         <v>145</v>
       </c>
-      <c r="C20" s="19" t="s">
+      <c r="C20" s="17" t="s">
         <v>138</v>
       </c>
-      <c r="D20" s="19" t="s">
+      <c r="D20" s="17" t="s">
         <v>146</v>
       </c>
-      <c r="E20" s="19" t="s">
+      <c r="E20" s="17" t="s">
         <v>147</v>
       </c>
-      <c r="F20" s="19" t="s">
+      <c r="F20" s="17" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="21" ht="80" customHeight="1" spans="1:6">
-      <c r="A21" s="13">
+      <c r="A21" s="11">
         <v>18</v>
       </c>
-      <c r="B21" s="19" t="s">
+      <c r="B21" s="17" t="s">
         <v>149</v>
       </c>
-      <c r="C21" s="19" t="s">
+      <c r="C21" s="17" t="s">
         <v>138</v>
       </c>
-      <c r="D21" s="19" t="s">
+      <c r="D21" s="17" t="s">
         <v>150</v>
       </c>
-      <c r="E21" s="19" t="s">
+      <c r="E21" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="F21" s="19" t="s">
+      <c r="F21" s="17" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="22" ht="17" customHeight="1" spans="1:6">
-      <c r="A22" s="18" t="s">
+      <c r="A22" s="16" t="s">
         <v>152</v>
       </c>
-      <c r="B22" s="18"/>
-      <c r="C22" s="18"/>
-      <c r="D22" s="18"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="18"/>
+      <c r="B22" s="16"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="16"/>
+      <c r="F22" s="16"/>
     </row>
     <row r="23" ht="84" spans="1:6">
-      <c r="A23" s="13">
+      <c r="A23" s="11">
         <v>19</v>
       </c>
-      <c r="B23" s="14" t="s">
+      <c r="B23" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="C23" s="14" t="s">
+      <c r="C23" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="D23" s="14" t="s">
+      <c r="D23" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="E23" s="14" t="s">
+      <c r="E23" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="F23" s="14" t="s">
+      <c r="F23" s="12" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="24" ht="68" spans="1:6">
-      <c r="A24" s="13">
+      <c r="A24" s="11">
         <v>20</v>
       </c>
-      <c r="B24" s="14" t="s">
+      <c r="B24" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="C24" s="14" t="s">
+      <c r="C24" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="D24" s="14" t="s">
+      <c r="D24" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="E24" s="14" t="s">
+      <c r="E24" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="F24" s="14" t="s">
+      <c r="F24" s="12" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="25" ht="68" spans="1:6">
-      <c r="A25" s="13">
+      <c r="A25" s="11">
         <v>21</v>
       </c>
-      <c r="B25" s="14" t="s">
+      <c r="B25" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="C25" s="14" t="s">
+      <c r="C25" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="D25" s="14" t="s">
+      <c r="D25" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="E25" s="14" t="s">
+      <c r="E25" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="F25" s="14" t="s">
+      <c r="F25" s="12" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="26" ht="68" spans="1:6">
-      <c r="A26" s="13">
+      <c r="A26" s="11">
         <v>22</v>
       </c>
-      <c r="B26" s="14" t="s">
+      <c r="B26" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="C26" s="14" t="s">
+      <c r="C26" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="D26" s="14" t="s">
+      <c r="D26" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="E26" s="14" t="s">
+      <c r="E26" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="F26" s="14" t="s">
+      <c r="F26" s="12" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="27" ht="68" spans="1:6">
-      <c r="A27" s="13">
+      <c r="A27" s="11">
         <v>23</v>
       </c>
-      <c r="B27" s="19" t="s">
+      <c r="B27" s="17" t="s">
         <v>137</v>
       </c>
-      <c r="C27" s="19" t="s">
+      <c r="C27" s="17" t="s">
         <v>138</v>
       </c>
-      <c r="D27" s="19" t="s">
+      <c r="D27" s="17" t="s">
         <v>154</v>
       </c>
-      <c r="E27" s="19" t="s">
+      <c r="E27" s="17" t="s">
         <v>155</v>
       </c>
-      <c r="F27" s="19" t="s">
+      <c r="F27" s="17" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="28" ht="51" spans="1:6">
-      <c r="A28" s="13">
+      <c r="A28" s="11">
         <v>24</v>
       </c>
-      <c r="B28" s="19" t="s">
+      <c r="B28" s="17" t="s">
         <v>142</v>
       </c>
-      <c r="C28" s="19" t="s">
+      <c r="C28" s="17" t="s">
         <v>138</v>
       </c>
-      <c r="D28" s="19" t="s">
+      <c r="D28" s="17" t="s">
         <v>143</v>
       </c>
-      <c r="E28" s="19" t="s">
+      <c r="E28" s="17" t="s">
         <v>128</v>
       </c>
-      <c r="F28" s="19" t="s">
+      <c r="F28" s="17" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="29" ht="68" spans="1:6">
-      <c r="A29" s="13">
+      <c r="A29" s="11">
         <v>25</v>
       </c>
-      <c r="B29" s="19" t="s">
+      <c r="B29" s="17" t="s">
         <v>145</v>
       </c>
-      <c r="C29" s="19" t="s">
+      <c r="C29" s="17" t="s">
         <v>138</v>
       </c>
-      <c r="D29" s="19" t="s">
+      <c r="D29" s="17" t="s">
         <v>146</v>
       </c>
-      <c r="E29" s="19" t="s">
+      <c r="E29" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="F29" s="19" t="s">
+      <c r="F29" s="17" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="30" ht="68" spans="1:6">
-      <c r="A30" s="13">
+      <c r="A30" s="11">
         <v>26</v>
       </c>
-      <c r="B30" s="19" t="s">
+      <c r="B30" s="17" t="s">
         <v>149</v>
       </c>
-      <c r="C30" s="19" t="s">
+      <c r="C30" s="17" t="s">
         <v>138</v>
       </c>
-      <c r="D30" s="19" t="s">
+      <c r="D30" s="17" t="s">
         <v>150</v>
       </c>
-      <c r="E30" s="19" t="s">
+      <c r="E30" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="F30" s="19" t="s">
+      <c r="F30" s="17" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="31" spans="1:6">
-      <c r="A31" s="18" t="s">
+      <c r="A31" s="16" t="s">
         <v>159</v>
       </c>
-      <c r="B31" s="18"/>
-      <c r="C31" s="18"/>
-      <c r="D31" s="18"/>
-      <c r="E31" s="18"/>
-      <c r="F31" s="18"/>
+      <c r="B31" s="16"/>
+      <c r="C31" s="16"/>
+      <c r="D31" s="16"/>
+      <c r="E31" s="16"/>
+      <c r="F31" s="16"/>
     </row>
     <row r="32" ht="68" spans="1:6">
-      <c r="A32" s="13">
+      <c r="A32" s="11">
         <v>27</v>
       </c>
-      <c r="B32" s="19" t="s">
+      <c r="B32" s="17" t="s">
         <v>137</v>
       </c>
-      <c r="C32" s="19" t="s">
+      <c r="C32" s="17" t="s">
         <v>138</v>
       </c>
-      <c r="D32" s="19" t="s">
+      <c r="D32" s="17" t="s">
         <v>154</v>
       </c>
-      <c r="E32" s="19" t="s">
+      <c r="E32" s="17" t="s">
         <v>160</v>
       </c>
-      <c r="F32" s="19" t="s">
+      <c r="F32" s="17" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="33" ht="51" spans="1:6">
-      <c r="A33" s="13">
+      <c r="A33" s="11">
         <v>28</v>
       </c>
-      <c r="B33" s="19" t="s">
+      <c r="B33" s="17" t="s">
         <v>142</v>
       </c>
-      <c r="C33" s="19" t="s">
+      <c r="C33" s="17" t="s">
         <v>138</v>
       </c>
-      <c r="D33" s="19" t="s">
+      <c r="D33" s="17" t="s">
         <v>143</v>
       </c>
-      <c r="E33" s="19" t="s">
+      <c r="E33" s="17" t="s">
         <v>128</v>
       </c>
-      <c r="F33" s="19" t="s">
+      <c r="F33" s="17" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="34" ht="68" spans="1:6">
-      <c r="A34" s="13">
+      <c r="A34" s="11">
         <v>29</v>
       </c>
-      <c r="B34" s="19" t="s">
+      <c r="B34" s="17" t="s">
         <v>145</v>
       </c>
-      <c r="C34" s="19" t="s">
+      <c r="C34" s="17" t="s">
         <v>138</v>
       </c>
-      <c r="D34" s="19" t="s">
+      <c r="D34" s="17" t="s">
         <v>161</v>
       </c>
-      <c r="E34" s="19" t="s">
+      <c r="E34" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="F34" s="19" t="s">
+      <c r="F34" s="17" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="35" ht="68" spans="1:6">
-      <c r="A35" s="13">
+      <c r="A35" s="11">
         <v>30</v>
       </c>
-      <c r="B35" s="19" t="s">
+      <c r="B35" s="17" t="s">
         <v>149</v>
       </c>
-      <c r="C35" s="19" t="s">
+      <c r="C35" s="17" t="s">
         <v>138</v>
       </c>
-      <c r="D35" s="19" t="s">
+      <c r="D35" s="17" t="s">
         <v>162</v>
       </c>
-      <c r="E35" s="19" t="s">
+      <c r="E35" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="F35" s="19" t="s">
+      <c r="F35" s="17" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="36" spans="1:6">
-      <c r="A36" s="18" t="s">
+      <c r="A36" s="16" t="s">
         <v>163</v>
       </c>
-      <c r="B36" s="18"/>
-      <c r="C36" s="18"/>
-      <c r="D36" s="18"/>
-      <c r="E36" s="18"/>
-      <c r="F36" s="18"/>
+      <c r="B36" s="16"/>
+      <c r="C36" s="16"/>
+      <c r="D36" s="16"/>
+      <c r="E36" s="16"/>
+      <c r="F36" s="16"/>
     </row>
     <row r="37" ht="84" spans="1:6">
-      <c r="A37" s="13">
+      <c r="A37" s="11">
         <v>31</v>
       </c>
-      <c r="B37" s="19" t="s">
+      <c r="B37" s="17" t="s">
         <v>137</v>
       </c>
-      <c r="C37" s="19" t="s">
+      <c r="C37" s="17" t="s">
         <v>138</v>
       </c>
-      <c r="D37" s="19" t="s">
+      <c r="D37" s="17" t="s">
         <v>164</v>
       </c>
-      <c r="E37" s="19" t="s">
+      <c r="E37" s="17" t="s">
         <v>165</v>
       </c>
-      <c r="F37" s="19" t="s">
+      <c r="F37" s="17" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="38" ht="68" spans="1:6">
-      <c r="A38" s="13">
+      <c r="A38" s="11">
         <v>32</v>
       </c>
-      <c r="B38" s="19" t="s">
+      <c r="B38" s="17" t="s">
         <v>142</v>
       </c>
-      <c r="C38" s="19" t="s">
+      <c r="C38" s="17" t="s">
         <v>138</v>
       </c>
-      <c r="D38" s="19" t="s">
+      <c r="D38" s="17" t="s">
         <v>166</v>
       </c>
-      <c r="E38" s="19" t="s">
+      <c r="E38" s="17" t="s">
         <v>167</v>
       </c>
-      <c r="F38" s="19" t="s">
+      <c r="F38" s="17" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="39" ht="68" spans="1:6">
-      <c r="A39" s="13">
+      <c r="A39" s="11">
         <v>33</v>
       </c>
-      <c r="B39" s="19" t="s">
+      <c r="B39" s="17" t="s">
         <v>145</v>
       </c>
-      <c r="C39" s="19" t="s">
+      <c r="C39" s="17" t="s">
         <v>138</v>
       </c>
-      <c r="D39" s="19" t="s">
+      <c r="D39" s="17" t="s">
         <v>168</v>
       </c>
-      <c r="E39" s="19" t="s">
+      <c r="E39" s="17" t="s">
         <v>169</v>
       </c>
-      <c r="F39" s="19" t="s">
+      <c r="F39" s="17" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="40" ht="68" spans="1:6">
-      <c r="A40" s="13">
+      <c r="A40" s="11">
         <v>34</v>
       </c>
-      <c r="B40" s="19" t="s">
+      <c r="B40" s="17" t="s">
         <v>149</v>
       </c>
-      <c r="C40" s="19" t="s">
+      <c r="C40" s="17" t="s">
         <v>138</v>
       </c>
-      <c r="D40" s="19" t="s">
+      <c r="D40" s="17" t="s">
         <v>170</v>
       </c>
-      <c r="E40" s="19" t="s">
+      <c r="E40" s="17" t="s">
         <v>169</v>
       </c>
-      <c r="F40" s="19" t="s">
+      <c r="F40" s="17" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="41" spans="1:6">
-      <c r="A41" s="18" t="s">
+      <c r="A41" s="16" t="s">
         <v>171</v>
       </c>
-      <c r="B41" s="18"/>
-      <c r="C41" s="18"/>
-      <c r="D41" s="18"/>
-      <c r="E41" s="18"/>
-      <c r="F41" s="18"/>
+      <c r="B41" s="16"/>
+      <c r="C41" s="16"/>
+      <c r="D41" s="16"/>
+      <c r="E41" s="16"/>
+      <c r="F41" s="16"/>
     </row>
     <row r="42" ht="84" spans="1:6">
-      <c r="A42" s="13">
+      <c r="A42" s="11">
         <v>35</v>
       </c>
-      <c r="B42" s="14" t="s">
+      <c r="B42" s="12" t="s">
         <v>172</v>
       </c>
-      <c r="C42" s="14" t="s">
+      <c r="C42" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="D42" s="19" t="s">
+      <c r="D42" s="17" t="s">
         <v>174</v>
       </c>
-      <c r="E42" s="14" t="s">
+      <c r="E42" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="F42" s="14" t="s">
+      <c r="F42" s="12" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="43" ht="68" spans="1:6">
-      <c r="A43" s="13">
+      <c r="A43" s="11">
         <v>36</v>
       </c>
-      <c r="B43" s="14" t="s">
+      <c r="B43" s="12" t="s">
         <v>176</v>
       </c>
-      <c r="C43" s="14" t="s">
+      <c r="C43" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="D43" s="19" t="s">
+      <c r="D43" s="17" t="s">
         <v>177</v>
       </c>
-      <c r="E43" s="14" t="s">
+      <c r="E43" s="12" t="s">
         <v>178</v>
       </c>
-      <c r="F43" s="14" t="s">
+      <c r="F43" s="12" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="44" ht="68" spans="1:6">
-      <c r="A44" s="13">
+      <c r="A44" s="11">
         <v>37</v>
       </c>
-      <c r="B44" s="14" t="s">
+      <c r="B44" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="C44" s="14" t="s">
+      <c r="C44" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="D44" s="19" t="s">
+      <c r="D44" s="17" t="s">
         <v>180</v>
       </c>
-      <c r="E44" s="14" t="s">
+      <c r="E44" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="F44" s="14" t="s">
+      <c r="F44" s="12" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="45" ht="68" spans="1:6">
-      <c r="A45" s="13">
+      <c r="A45" s="11">
         <v>38</v>
       </c>
-      <c r="B45" s="14" t="s">
+      <c r="B45" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="C45" s="14" t="s">
+      <c r="C45" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="D45" s="19" t="s">
+      <c r="D45" s="17" t="s">
         <v>182</v>
       </c>
-      <c r="E45" s="14" t="s">
+      <c r="E45" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="F45" s="14" t="s">
+      <c r="F45" s="12" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="46" ht="68" spans="1:6">
-      <c r="A46" s="13">
+      <c r="A46" s="11">
         <v>39</v>
       </c>
-      <c r="B46" s="19" t="s">
+      <c r="B46" s="17" t="s">
         <v>137</v>
       </c>
-      <c r="C46" s="19" t="s">
+      <c r="C46" s="17" t="s">
         <v>138</v>
       </c>
-      <c r="D46" s="19" t="s">
+      <c r="D46" s="17" t="s">
         <v>184</v>
       </c>
-      <c r="E46" s="19" t="s">
+      <c r="E46" s="17" t="s">
         <v>160</v>
       </c>
-      <c r="F46" s="19" t="s">
+      <c r="F46" s="17" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="47" ht="118" spans="1:6">
-      <c r="A47" s="13">
+      <c r="A47" s="11">
         <v>40</v>
       </c>
-      <c r="B47" s="19" t="s">
+      <c r="B47" s="17" t="s">
         <v>142</v>
       </c>
-      <c r="C47" s="19" t="s">
+      <c r="C47" s="17" t="s">
         <v>138</v>
       </c>
-      <c r="D47" s="19" t="s">
+      <c r="D47" s="17" t="s">
         <v>186</v>
       </c>
-      <c r="E47" s="19" t="s">
+      <c r="E47" s="17" t="s">
         <v>187</v>
       </c>
-      <c r="F47" s="19" t="s">
+      <c r="F47" s="17" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="48" ht="68" spans="1:6">
-      <c r="A48" s="13">
+      <c r="A48" s="11">
         <v>41</v>
       </c>
-      <c r="B48" s="19" t="s">
+      <c r="B48" s="17" t="s">
         <v>145</v>
       </c>
-      <c r="C48" s="19" t="s">
+      <c r="C48" s="17" t="s">
         <v>138</v>
       </c>
-      <c r="D48" s="19" t="s">
+      <c r="D48" s="17" t="s">
         <v>189</v>
       </c>
-      <c r="E48" s="19" t="s">
+      <c r="E48" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="F48" s="19" t="s">
+      <c r="F48" s="17" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="49" ht="68" spans="1:6">
-      <c r="A49" s="13">
+      <c r="A49" s="11">
         <v>42</v>
       </c>
-      <c r="B49" s="19" t="s">
+      <c r="B49" s="17" t="s">
         <v>149</v>
       </c>
-      <c r="C49" s="19" t="s">
+      <c r="C49" s="17" t="s">
         <v>138</v>
       </c>
-      <c r="D49" s="19" t="s">
+      <c r="D49" s="17" t="s">
         <v>191</v>
       </c>
-      <c r="E49" s="19" t="s">
+      <c r="E49" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="F49" s="19" t="s">
+      <c r="F49" s="17" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="A50" s="18" t="s">
+      <c r="A50" s="16" t="s">
         <v>193</v>
       </c>
-      <c r="B50" s="18"/>
-      <c r="C50" s="18"/>
-      <c r="D50" s="18"/>
-      <c r="E50" s="18"/>
-      <c r="F50" s="18"/>
+      <c r="B50" s="16"/>
+      <c r="C50" s="16"/>
+      <c r="D50" s="16"/>
+      <c r="E50" s="16"/>
+      <c r="F50" s="16"/>
     </row>
     <row r="51" ht="68" spans="1:6">
-      <c r="A51" s="13">
+      <c r="A51" s="11">
         <v>43</v>
       </c>
-      <c r="B51" s="14" t="s">
+      <c r="B51" s="12" t="s">
         <v>194</v>
       </c>
-      <c r="C51" s="14" t="s">
+      <c r="C51" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="D51" s="14" t="s">
+      <c r="D51" s="12" t="s">
         <v>195</v>
       </c>
-      <c r="E51" s="14" t="s">
+      <c r="E51" s="12" t="s">
         <v>196</v>
       </c>
-      <c r="F51" s="14" t="s">
+      <c r="F51" s="12" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="52" ht="68" spans="1:6">
-      <c r="A52" s="13">
+      <c r="A52" s="11">
         <v>44</v>
       </c>
-      <c r="B52" s="14" t="s">
+      <c r="B52" s="12" t="s">
         <v>198</v>
       </c>
-      <c r="C52" s="14" t="s">
+      <c r="C52" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="D52" s="14" t="s">
+      <c r="D52" s="12" t="s">
         <v>199</v>
       </c>
-      <c r="E52" s="14" t="s">
+      <c r="E52" s="12" t="s">
         <v>196</v>
       </c>
-      <c r="F52" s="14" t="s">
+      <c r="F52" s="12" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="53" ht="68" spans="1:6">
-      <c r="A53" s="13">
+      <c r="A53" s="11">
         <v>45</v>
       </c>
-      <c r="B53" s="14" t="s">
+      <c r="B53" s="12" t="s">
         <v>201</v>
       </c>
-      <c r="C53" s="14" t="s">
+      <c r="C53" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="D53" s="14" t="s">
+      <c r="D53" s="12" t="s">
         <v>202</v>
       </c>
-      <c r="E53" s="14" t="s">
+      <c r="E53" s="12" t="s">
         <v>196</v>
       </c>
-      <c r="F53" s="14" t="s">
+      <c r="F53" s="12" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="54" ht="68" spans="1:6">
-      <c r="A54" s="13">
+      <c r="A54" s="11">
         <v>46</v>
       </c>
-      <c r="B54" s="14" t="s">
+      <c r="B54" s="12" t="s">
         <v>204</v>
       </c>
-      <c r="C54" s="19" t="s">
+      <c r="C54" s="17" t="s">
         <v>138</v>
       </c>
-      <c r="D54" s="19" t="s">
+      <c r="D54" s="17" t="s">
         <v>205</v>
       </c>
-      <c r="E54" s="19" t="s">
+      <c r="E54" s="17" t="s">
         <v>160</v>
       </c>
-      <c r="F54" s="19" t="s">
+      <c r="F54" s="17" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="55" ht="68" spans="1:6">
-      <c r="A55" s="13">
+      <c r="A55" s="11">
         <v>47</v>
       </c>
-      <c r="B55" s="14" t="s">
+      <c r="B55" s="12" t="s">
         <v>206</v>
       </c>
-      <c r="C55" s="19" t="s">
+      <c r="C55" s="17" t="s">
         <v>138</v>
       </c>
-      <c r="D55" s="19" t="s">
+      <c r="D55" s="17" t="s">
         <v>207</v>
       </c>
-      <c r="E55" s="19" t="s">
+      <c r="E55" s="17" t="s">
         <v>128</v>
       </c>
-      <c r="F55" s="19" t="s">
+      <c r="F55" s="17" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="56" ht="68" spans="1:6">
-      <c r="A56" s="13">
+      <c r="A56" s="11">
         <v>48</v>
       </c>
-      <c r="B56" s="14" t="s">
+      <c r="B56" s="12" t="s">
         <v>208</v>
       </c>
-      <c r="C56" s="19" t="s">
+      <c r="C56" s="17" t="s">
         <v>138</v>
       </c>
-      <c r="D56" s="19" t="s">
+      <c r="D56" s="17" t="s">
         <v>209</v>
       </c>
-      <c r="E56" s="19" t="s">
+      <c r="E56" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="F56" s="19" t="s">
+      <c r="F56" s="17" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="57" ht="68" spans="1:6">
-      <c r="A57" s="13">
+      <c r="A57" s="11">
         <v>49</v>
       </c>
-      <c r="B57" s="14" t="s">
+      <c r="B57" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="C57" s="19" t="s">
+      <c r="C57" s="17" t="s">
         <v>138</v>
       </c>
-      <c r="D57" s="19" t="s">
+      <c r="D57" s="17" t="s">
         <v>211</v>
       </c>
-      <c r="E57" s="19" t="s">
+      <c r="E57" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="F57" s="19" t="s">
+      <c r="F57" s="17" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="58" spans="1:6">
-      <c r="A58" s="18" t="s">
+      <c r="A58" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="B58" s="18"/>
-      <c r="C58" s="18"/>
-      <c r="D58" s="18"/>
-      <c r="E58" s="18"/>
-      <c r="F58" s="18"/>
+      <c r="B58" s="16"/>
+      <c r="C58" s="16"/>
+      <c r="D58" s="16"/>
+      <c r="E58" s="16"/>
+      <c r="F58" s="16"/>
     </row>
     <row r="59" ht="84" spans="1:6">
-      <c r="A59" s="13">
+      <c r="A59" s="11">
         <v>50</v>
       </c>
-      <c r="B59" s="14" t="s">
+      <c r="B59" s="12" t="s">
         <v>172</v>
       </c>
-      <c r="C59" s="14" t="s">
+      <c r="C59" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="D59" s="19" t="s">
+      <c r="D59" s="17" t="s">
         <v>213</v>
       </c>
-      <c r="E59" s="14" t="s">
+      <c r="E59" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="F59" s="14" t="s">
+      <c r="F59" s="12" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="60" ht="68" spans="1:6">
-      <c r="A60" s="13">
+      <c r="A60" s="11">
         <v>51</v>
       </c>
-      <c r="B60" s="14" t="s">
+      <c r="B60" s="12" t="s">
         <v>176</v>
       </c>
-      <c r="C60" s="14" t="s">
+      <c r="C60" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="D60" s="19" t="s">
+      <c r="D60" s="17" t="s">
         <v>214</v>
       </c>
-      <c r="E60" s="14" t="s">
+      <c r="E60" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="F60" s="14" t="s">
+      <c r="F60" s="12" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="61" ht="68" spans="1:6">
-      <c r="A61" s="13">
+      <c r="A61" s="11">
         <v>52</v>
       </c>
-      <c r="B61" s="14" t="s">
+      <c r="B61" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="C61" s="14" t="s">
+      <c r="C61" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="D61" s="19" t="s">
+      <c r="D61" s="17" t="s">
         <v>215</v>
       </c>
-      <c r="E61" s="14" t="s">
+      <c r="E61" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="F61" s="14" t="s">
+      <c r="F61" s="12" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="62" ht="68" spans="1:6">
-      <c r="A62" s="13">
+      <c r="A62" s="11">
         <v>53</v>
       </c>
-      <c r="B62" s="14" t="s">
+      <c r="B62" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="C62" s="14" t="s">
+      <c r="C62" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="D62" s="19" t="s">
+      <c r="D62" s="17" t="s">
         <v>216</v>
       </c>
-      <c r="E62" s="14" t="s">
+      <c r="E62" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="F62" s="14" t="s">
+      <c r="F62" s="12" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="63" ht="68" spans="1:6">
-      <c r="A63" s="13">
+      <c r="A63" s="11">
         <v>54</v>
       </c>
-      <c r="B63" s="19" t="s">
+      <c r="B63" s="17" t="s">
         <v>137</v>
       </c>
-      <c r="C63" s="19" t="s">
+      <c r="C63" s="17" t="s">
         <v>138</v>
       </c>
-      <c r="D63" s="19" t="s">
+      <c r="D63" s="17" t="s">
         <v>217</v>
       </c>
-      <c r="E63" s="19" t="s">
+      <c r="E63" s="17" t="s">
         <v>218</v>
       </c>
-      <c r="F63" s="19" t="s">
+      <c r="F63" s="17" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="64" ht="84" spans="1:6">
-      <c r="A64" s="13">
+      <c r="A64" s="11">
         <v>55</v>
       </c>
-      <c r="B64" s="19" t="s">
+      <c r="B64" s="17" t="s">
         <v>142</v>
       </c>
-      <c r="C64" s="19" t="s">
+      <c r="C64" s="17" t="s">
         <v>138</v>
       </c>
-      <c r="D64" s="19" t="s">
+      <c r="D64" s="17" t="s">
         <v>214</v>
       </c>
-      <c r="E64" s="19" t="s">
+      <c r="E64" s="17" t="s">
         <v>220</v>
       </c>
-      <c r="F64" s="19" t="s">
+      <c r="F64" s="17" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="65" ht="84" spans="1:6">
-      <c r="A65" s="13">
+      <c r="A65" s="11">
         <v>56</v>
       </c>
-      <c r="B65" s="19" t="s">
+      <c r="B65" s="17" t="s">
         <v>145</v>
       </c>
-      <c r="C65" s="19" t="s">
+      <c r="C65" s="17" t="s">
         <v>138</v>
       </c>
-      <c r="D65" s="19" t="s">
+      <c r="D65" s="17" t="s">
         <v>221</v>
       </c>
-      <c r="E65" s="19" t="s">
+      <c r="E65" s="17" t="s">
         <v>220</v>
       </c>
-      <c r="F65" s="19" t="s">
+      <c r="F65" s="17" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="66" ht="68" spans="1:6">
-      <c r="A66" s="13">
+      <c r="A66" s="11">
         <v>57</v>
       </c>
-      <c r="B66" s="19" t="s">
+      <c r="B66" s="17" t="s">
         <v>149</v>
       </c>
-      <c r="C66" s="19" t="s">
+      <c r="C66" s="17" t="s">
         <v>138</v>
       </c>
-      <c r="D66" s="19" t="s">
+      <c r="D66" s="17" t="s">
         <v>222</v>
       </c>
-      <c r="E66" s="19" t="s">
+      <c r="E66" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="F66" s="19" t="s">
+      <c r="F66" s="17" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="67" spans="1:6">
-      <c r="A67" s="18" t="s">
+      <c r="A67" s="16" t="s">
         <v>223</v>
       </c>
-      <c r="B67" s="18"/>
-      <c r="C67" s="18"/>
-      <c r="D67" s="18"/>
-      <c r="E67" s="18"/>
-      <c r="F67" s="18"/>
+      <c r="B67" s="16"/>
+      <c r="C67" s="16"/>
+      <c r="D67" s="16"/>
+      <c r="E67" s="16"/>
+      <c r="F67" s="16"/>
     </row>
     <row r="68" ht="84" spans="1:6">
-      <c r="A68" s="13">
+      <c r="A68" s="11">
         <v>58</v>
       </c>
-      <c r="B68" s="14" t="s">
+      <c r="B68" s="12" t="s">
         <v>224</v>
       </c>
-      <c r="C68" s="14" t="s">
+      <c r="C68" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="D68" s="19" t="s">
+      <c r="D68" s="17" t="s">
         <v>225</v>
       </c>
-      <c r="E68" s="14" t="s">
+      <c r="E68" s="12" t="s">
         <v>226</v>
       </c>
-      <c r="F68" s="14" t="s">
+      <c r="F68" s="12" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="69" ht="68" spans="1:6">
-      <c r="A69" s="13">
+      <c r="A69" s="11">
         <v>59</v>
       </c>
-      <c r="B69" s="14" t="s">
+      <c r="B69" s="12" t="s">
         <v>228</v>
       </c>
-      <c r="C69" s="14" t="s">
+      <c r="C69" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="D69" s="19" t="s">
+      <c r="D69" s="17" t="s">
         <v>229</v>
       </c>
-      <c r="E69" s="14" t="s">
+      <c r="E69" s="12" t="s">
         <v>230</v>
       </c>
-      <c r="F69" s="14" t="s">
+      <c r="F69" s="12" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="70" ht="68" spans="1:6">
-      <c r="A70" s="13">
+      <c r="A70" s="11">
         <v>60</v>
       </c>
-      <c r="B70" s="14" t="s">
+      <c r="B70" s="12" t="s">
         <v>232</v>
       </c>
-      <c r="C70" s="14" t="s">
+      <c r="C70" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="D70" s="19" t="s">
+      <c r="D70" s="17" t="s">
         <v>233</v>
       </c>
-      <c r="E70" s="14" t="s">
+      <c r="E70" s="12" t="s">
         <v>234</v>
       </c>
-      <c r="F70" s="14" t="s">
+      <c r="F70" s="12" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="71" ht="68" spans="1:6">
-      <c r="A71" s="13">
+      <c r="A71" s="11">
         <v>61</v>
       </c>
-      <c r="B71" s="14" t="s">
+      <c r="B71" s="12" t="s">
         <v>236</v>
       </c>
-      <c r="C71" s="14" t="s">
+      <c r="C71" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="D71" s="19" t="s">
+      <c r="D71" s="17" t="s">
         <v>237</v>
       </c>
-      <c r="E71" s="14" t="s">
+      <c r="E71" s="12" t="s">
         <v>234</v>
       </c>
-      <c r="F71" s="14" t="s">
+      <c r="F71" s="12" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="72" ht="68" spans="1:6">
-      <c r="A72" s="13">
+      <c r="A72" s="11">
         <v>62</v>
       </c>
-      <c r="B72" s="19" t="s">
+      <c r="B72" s="17" t="s">
         <v>137</v>
       </c>
-      <c r="C72" s="19" t="s">
+      <c r="C72" s="17" t="s">
         <v>138</v>
       </c>
-      <c r="D72" s="19" t="s">
+      <c r="D72" s="17" t="s">
         <v>239</v>
       </c>
-      <c r="E72" s="19" t="s">
+      <c r="E72" s="17" t="s">
         <v>240</v>
       </c>
-      <c r="F72" s="19" t="s">
+      <c r="F72" s="17" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="73" ht="68" spans="1:6">
-      <c r="A73" s="13">
+      <c r="A73" s="11">
         <v>63</v>
       </c>
-      <c r="B73" s="19" t="s">
+      <c r="B73" s="17" t="s">
         <v>142</v>
       </c>
-      <c r="C73" s="19" t="s">
+      <c r="C73" s="17" t="s">
         <v>138</v>
       </c>
-      <c r="D73" s="19" t="s">
+      <c r="D73" s="17" t="s">
         <v>229</v>
       </c>
-      <c r="E73" s="19" t="s">
+      <c r="E73" s="17" t="s">
         <v>128</v>
       </c>
-      <c r="F73" s="19" t="s">
+      <c r="F73" s="17" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="74" ht="68" spans="1:6">
-      <c r="A74" s="13">
+      <c r="A74" s="11">
         <v>64</v>
       </c>
-      <c r="B74" s="19" t="s">
+      <c r="B74" s="17" t="s">
         <v>242</v>
       </c>
-      <c r="C74" s="19" t="s">
+      <c r="C74" s="17" t="s">
         <v>138</v>
       </c>
-      <c r="D74" s="19" t="s">
+      <c r="D74" s="17" t="s">
         <v>243</v>
       </c>
-      <c r="E74" s="19" t="s">
+      <c r="E74" s="17" t="s">
         <v>244</v>
       </c>
-      <c r="F74" s="19" t="s">
+      <c r="F74" s="17" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="75" ht="68" spans="1:6">
-      <c r="A75" s="13">
+      <c r="A75" s="11">
         <v>65</v>
       </c>
-      <c r="B75" s="19" t="s">
+      <c r="B75" s="17" t="s">
         <v>245</v>
       </c>
-      <c r="C75" s="19" t="s">
+      <c r="C75" s="17" t="s">
         <v>138</v>
       </c>
-      <c r="D75" s="19" t="s">
+      <c r="D75" s="17" t="s">
         <v>246</v>
       </c>
-      <c r="E75" s="19" t="s">
+      <c r="E75" s="17" t="s">
         <v>244</v>
       </c>
-      <c r="F75" s="19" t="s">
+      <c r="F75" s="17" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="76" spans="1:6">
-      <c r="A76" s="18" t="s">
+      <c r="A76" s="16" t="s">
         <v>247</v>
       </c>
-      <c r="B76" s="18"/>
-      <c r="C76" s="18"/>
-      <c r="D76" s="18"/>
-      <c r="E76" s="18"/>
-      <c r="F76" s="18"/>
+      <c r="B76" s="16"/>
+      <c r="C76" s="16"/>
+      <c r="D76" s="16"/>
+      <c r="E76" s="16"/>
+      <c r="F76" s="16"/>
     </row>
     <row r="77" ht="84" spans="1:6">
-      <c r="A77" s="13">
+      <c r="A77" s="11">
         <v>66</v>
       </c>
-      <c r="B77" s="14" t="s">
+      <c r="B77" s="12" t="s">
         <v>224</v>
       </c>
-      <c r="C77" s="14" t="s">
+      <c r="C77" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="D77" s="19" t="s">
+      <c r="D77" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="E77" s="14" t="s">
+      <c r="E77" s="12" t="s">
         <v>226</v>
       </c>
-      <c r="F77" s="14" t="s">
+      <c r="F77" s="12" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="78" ht="68" spans="1:6">
-      <c r="A78" s="13">
+      <c r="A78" s="11">
         <v>67</v>
       </c>
-      <c r="B78" s="14" t="s">
+      <c r="B78" s="12" t="s">
         <v>249</v>
       </c>
-      <c r="C78" s="14" t="s">
+      <c r="C78" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="D78" s="19" t="s">
+      <c r="D78" s="17" t="s">
         <v>229</v>
       </c>
-      <c r="E78" s="14" t="s">
+      <c r="E78" s="12" t="s">
         <v>230</v>
       </c>
-      <c r="F78" s="14" t="s">
+      <c r="F78" s="12" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="79" ht="68" spans="1:6">
-      <c r="A79" s="13">
+      <c r="A79" s="11">
         <v>68</v>
       </c>
-      <c r="B79" s="14" t="s">
+      <c r="B79" s="12" t="s">
         <v>232</v>
       </c>
-      <c r="C79" s="14" t="s">
+      <c r="C79" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="D79" s="19" t="s">
+      <c r="D79" s="17" t="s">
         <v>233</v>
       </c>
-      <c r="E79" s="14" t="s">
+      <c r="E79" s="12" t="s">
         <v>234</v>
       </c>
-      <c r="F79" s="14" t="s">
+      <c r="F79" s="12" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="80" ht="68" spans="1:6">
-      <c r="A80" s="13">
+      <c r="A80" s="11">
         <v>69</v>
       </c>
-      <c r="B80" s="14" t="s">
+      <c r="B80" s="12" t="s">
         <v>236</v>
       </c>
-      <c r="C80" s="14" t="s">
+      <c r="C80" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="D80" s="19" t="s">
+      <c r="D80" s="17" t="s">
         <v>237</v>
       </c>
-      <c r="E80" s="14" t="s">
+      <c r="E80" s="12" t="s">
         <v>250</v>
       </c>
-      <c r="F80" s="14" t="s">
+      <c r="F80" s="12" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="81" ht="68" spans="1:6">
-      <c r="A81" s="13">
+      <c r="A81" s="11">
         <v>70</v>
       </c>
-      <c r="B81" s="19" t="s">
+      <c r="B81" s="17" t="s">
         <v>137</v>
       </c>
-      <c r="C81" s="19" t="s">
+      <c r="C81" s="17" t="s">
         <v>138</v>
       </c>
-      <c r="D81" s="19" t="s">
+      <c r="D81" s="17" t="s">
         <v>239</v>
       </c>
-      <c r="E81" s="19" t="s">
+      <c r="E81" s="17" t="s">
         <v>160</v>
       </c>
-      <c r="F81" s="19" t="s">
+      <c r="F81" s="17" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="82" ht="68" spans="1:6">
-      <c r="A82" s="13">
+      <c r="A82" s="11">
         <v>71</v>
       </c>
-      <c r="B82" s="19" t="s">
+      <c r="B82" s="17" t="s">
         <v>142</v>
       </c>
-      <c r="C82" s="19" t="s">
+      <c r="C82" s="17" t="s">
         <v>138</v>
       </c>
-      <c r="D82" s="19" t="s">
+      <c r="D82" s="17" t="s">
         <v>229</v>
       </c>
-      <c r="E82" s="19" t="s">
+      <c r="E82" s="17" t="s">
         <v>128</v>
       </c>
-      <c r="F82" s="19" t="s">
+      <c r="F82" s="17" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="83" ht="68" spans="1:6">
-      <c r="A83" s="13">
+      <c r="A83" s="11">
         <v>72</v>
       </c>
-      <c r="B83" s="19" t="s">
+      <c r="B83" s="17" t="s">
         <v>242</v>
       </c>
-      <c r="C83" s="19" t="s">
+      <c r="C83" s="17" t="s">
         <v>138</v>
       </c>
-      <c r="D83" s="19" t="s">
+      <c r="D83" s="17" t="s">
         <v>243</v>
       </c>
-      <c r="E83" s="19" t="s">
+      <c r="E83" s="17" t="s">
         <v>244</v>
       </c>
-      <c r="F83" s="19" t="s">
+      <c r="F83" s="17" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="84" ht="68" spans="1:6">
-      <c r="A84" s="13">
+      <c r="A84" s="11">
         <v>73</v>
       </c>
-      <c r="B84" s="19" t="s">
+      <c r="B84" s="17" t="s">
         <v>245</v>
       </c>
-      <c r="C84" s="19" t="s">
+      <c r="C84" s="17" t="s">
         <v>138</v>
       </c>
-      <c r="D84" s="19" t="s">
+      <c r="D84" s="17" t="s">
         <v>246</v>
       </c>
-      <c r="E84" s="19" t="s">
+      <c r="E84" s="17" t="s">
         <v>244</v>
       </c>
-      <c r="F84" s="19" t="s">
+      <c r="F84" s="17" t="s">
         <v>192</v>
       </c>
     </row>
@@ -5731,832 +5725,832 @@
   <dimension ref="A1:F52"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="4.296875" style="6" customWidth="1"/>
-    <col min="2" max="2" width="26.953125" style="8" customWidth="1"/>
-    <col min="3" max="3" width="23.1796875" style="8" customWidth="1"/>
-    <col min="4" max="4" width="25.6484375" style="8" customWidth="1"/>
-    <col min="5" max="5" width="10.15625" style="8" customWidth="1"/>
-    <col min="6" max="6" width="18.8828125" style="8" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="5"/>
+    <col min="1" max="1" width="4.296875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="26.953125" style="6" customWidth="1"/>
+    <col min="3" max="3" width="23.1796875" style="6" customWidth="1"/>
+    <col min="4" max="4" width="25.6484375" style="6" customWidth="1"/>
+    <col min="5" max="5" width="10.15625" style="6" customWidth="1"/>
+    <col min="6" max="6" width="18.8828125" style="6" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="6" customFormat="1" ht="20" customHeight="1" spans="1:6">
-      <c r="A1" s="9" t="s">
+    <row r="1" s="1" customFormat="1" ht="20" customHeight="1" spans="1:6">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="7" t="s">
         <v>251</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="7" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" s="7" customFormat="1" ht="20" customHeight="1" spans="1:6">
-      <c r="A2" s="10" t="s">
+    <row r="2" s="5" customFormat="1" ht="20" customHeight="1" spans="1:6">
+      <c r="A2" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
     </row>
     <row r="3" ht="34" spans="1:5">
-      <c r="A3" s="6">
+      <c r="A3" s="1">
         <v>1</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="6" t="s">
         <v>254</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="6" t="s">
         <v>255</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="6" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="4" ht="84" spans="1:5">
-      <c r="A4" s="6">
+      <c r="A4" s="1">
         <v>2</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="6" t="s">
         <v>257</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="6" t="s">
         <v>258</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="6" t="s">
         <v>255</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="6" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="5" s="8" customFormat="1" ht="51" spans="1:5">
-      <c r="A5" s="6">
+    <row r="5" s="6" customFormat="1" ht="51" spans="1:5">
+      <c r="A5" s="1">
         <v>3</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="6" t="s">
         <v>259</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="6" t="s">
         <v>255</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="6" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="6" s="6" customFormat="1" spans="1:1">
-      <c r="A6" s="6" t="s">
+    <row r="6" s="1" customFormat="1" spans="1:1">
+      <c r="A6" s="1" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="7" ht="34" spans="1:6">
-      <c r="A7" s="6">
+      <c r="A7" s="1">
         <v>3</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="6" t="s">
         <v>261</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="6" t="s">
         <v>262</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="6" t="s">
         <v>256</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="F7" s="1" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="8" ht="51" spans="1:6">
-      <c r="A8" s="6">
+      <c r="A8" s="1">
         <v>4</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="6" t="s">
         <v>264</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="6" t="s">
         <v>265</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="6" t="s">
         <v>266</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="E8" s="6" t="s">
         <v>256</v>
       </c>
-      <c r="F8" s="6"/>
+      <c r="F8" s="1"/>
     </row>
     <row r="9" ht="34" spans="1:6">
-      <c r="A9" s="6">
+      <c r="A9" s="1">
         <v>5</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>267</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>268</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="6" t="s">
         <v>262</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="6" t="s">
         <v>256</v>
       </c>
-      <c r="F9" s="6"/>
+      <c r="F9" s="1"/>
     </row>
     <row r="10" customFormat="1" ht="40" customHeight="1" spans="1:6">
-      <c r="A10" s="6">
+      <c r="A10" s="1">
         <v>6</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="6" t="s">
         <v>270</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="E10" s="6" t="s">
         <v>256</v>
       </c>
-      <c r="F10" s="6"/>
+      <c r="F10" s="1"/>
     </row>
     <row r="11" customFormat="1" ht="39" customHeight="1" spans="1:6">
-      <c r="A11" s="6">
+      <c r="A11" s="1">
         <v>7</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="6" t="s">
         <v>272</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="6" t="s">
         <v>273</v>
       </c>
-      <c r="D11" s="6"/>
-      <c r="E11" s="8" t="s">
+      <c r="D11" s="1"/>
+      <c r="E11" s="6" t="s">
         <v>256</v>
       </c>
-      <c r="F11" s="6"/>
-    </row>
-    <row r="12" s="6" customFormat="1" ht="84" spans="1:5">
-      <c r="A12" s="6">
+      <c r="F11" s="1"/>
+    </row>
+    <row r="12" s="1" customFormat="1" ht="84" spans="1:5">
+      <c r="A12" s="1">
         <v>8</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="6" t="s">
         <v>262</v>
       </c>
-      <c r="E12" s="8" t="s">
+      <c r="E12" s="6" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="13" s="6" customFormat="1" spans="1:1">
-      <c r="A13" s="6" t="s">
+    <row r="13" s="1" customFormat="1" spans="1:1">
+      <c r="A13" s="1" t="s">
         <v>276</v>
       </c>
     </row>
     <row r="14" ht="68" spans="1:5">
-      <c r="A14" s="6">
+      <c r="A14" s="1">
         <v>9</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="6" t="s">
         <v>278</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D14" s="6" t="s">
         <v>279</v>
       </c>
-      <c r="E14" s="8" t="s">
+      <c r="E14" s="6" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="15" ht="68" spans="1:6">
-      <c r="A15" s="6">
+      <c r="A15" s="1">
         <v>10</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="6" t="s">
         <v>280</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D15" s="6" t="s">
         <v>281</v>
       </c>
-      <c r="E15" s="8" t="s">
+      <c r="E15" s="6" t="s">
         <v>256</v>
       </c>
-      <c r="F15" s="8" t="s">
+      <c r="F15" s="6" t="s">
         <v>282</v>
       </c>
     </row>
     <row r="16" ht="68" spans="1:5">
-      <c r="A16" s="6">
+      <c r="A16" s="1">
         <v>11</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="6" t="s">
         <v>283</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="C16" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D16" s="6" t="s">
         <v>281</v>
       </c>
-      <c r="E16" s="8" t="s">
+      <c r="E16" s="6" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="17" s="6" customFormat="1" spans="1:1">
-      <c r="A17" s="6" t="s">
+    <row r="17" s="1" customFormat="1" spans="1:1">
+      <c r="A17" s="1" t="s">
         <v>284</v>
       </c>
     </row>
     <row r="18" ht="84" spans="1:5">
-      <c r="A18" s="6">
+      <c r="A18" s="1">
         <v>12</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="6" t="s">
         <v>285</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="C18" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="D18" s="6" t="s">
         <v>286</v>
       </c>
-      <c r="E18" s="8" t="s">
+      <c r="E18" s="6" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="19" ht="34" spans="1:5">
-      <c r="A19" s="6">
+      <c r="A19" s="1">
         <v>13</v>
       </c>
-      <c r="B19" s="8" t="s">
+      <c r="B19" s="6" t="s">
         <v>287</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="C19" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="D19" s="6" t="s">
         <v>289</v>
       </c>
-      <c r="E19" s="8" t="s">
+      <c r="E19" s="6" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="20" ht="34" spans="1:5">
-      <c r="A20" s="6">
+      <c r="A20" s="1">
         <v>14</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="C20" s="8" t="s">
+      <c r="C20" s="6" t="s">
         <v>291</v>
       </c>
-      <c r="D20" s="8" t="s">
+      <c r="D20" s="6" t="s">
         <v>292</v>
       </c>
-      <c r="E20" s="8" t="s">
+      <c r="E20" s="6" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="21" ht="41" customHeight="1" spans="1:5">
-      <c r="A21" s="6">
+      <c r="A21" s="1">
         <v>15</v>
       </c>
-      <c r="B21" s="6"/>
-      <c r="C21" s="8" t="s">
+      <c r="B21" s="1"/>
+      <c r="C21" s="6" t="s">
         <v>293</v>
       </c>
-      <c r="D21" s="8" t="s">
+      <c r="D21" s="6" t="s">
         <v>294</v>
       </c>
-      <c r="E21" s="8" t="s">
+      <c r="E21" s="6" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="22" ht="34" spans="1:5">
-      <c r="A22" s="6">
+      <c r="A22" s="1">
         <v>16</v>
       </c>
-      <c r="B22" s="6"/>
-      <c r="C22" s="8" t="s">
+      <c r="B22" s="1"/>
+      <c r="C22" s="6" t="s">
         <v>295</v>
       </c>
-      <c r="D22" s="8" t="s">
+      <c r="D22" s="6" t="s">
         <v>296</v>
       </c>
-      <c r="E22" s="8" t="s">
+      <c r="E22" s="6" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="6" t="s">
+      <c r="A23" s="1" t="s">
         <v>297</v>
       </c>
     </row>
     <row r="24" ht="85" customHeight="1" spans="1:5">
-      <c r="A24" s="6">
+      <c r="A24" s="1">
         <v>17</v>
       </c>
-      <c r="B24" s="8" t="s">
+      <c r="B24" s="6" t="s">
         <v>298</v>
       </c>
-      <c r="C24" s="8" t="s">
+      <c r="C24" s="6" t="s">
         <v>299</v>
       </c>
-      <c r="D24" s="8" t="s">
+      <c r="D24" s="6" t="s">
         <v>300</v>
       </c>
-      <c r="E24" s="8" t="s">
+      <c r="E24" s="6" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="25" ht="51" spans="1:5">
-      <c r="A25" s="6">
+      <c r="A25" s="1">
         <v>18</v>
       </c>
-      <c r="B25" s="8" t="s">
+      <c r="B25" s="6" t="s">
         <v>301</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="C25" s="6" t="s">
         <v>302</v>
       </c>
-      <c r="D25" s="8" t="s">
+      <c r="D25" s="6" t="s">
         <v>303</v>
       </c>
-      <c r="E25" s="8" t="s">
+      <c r="E25" s="6" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="26" ht="51" spans="1:5">
-      <c r="A26" s="6">
+      <c r="A26" s="1">
         <v>19</v>
       </c>
-      <c r="B26" s="8" t="s">
+      <c r="B26" s="6" t="s">
         <v>304</v>
       </c>
-      <c r="C26" s="8" t="s">
+      <c r="C26" s="6" t="s">
         <v>302</v>
       </c>
-      <c r="D26" s="8" t="s">
+      <c r="D26" s="6" t="s">
         <v>305</v>
       </c>
-      <c r="E26" s="8" t="s">
+      <c r="E26" s="6" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="27" ht="51" spans="1:5">
-      <c r="A27" s="6">
+      <c r="A27" s="1">
         <v>20</v>
       </c>
-      <c r="B27" s="8" t="s">
+      <c r="B27" s="6" t="s">
         <v>306</v>
       </c>
-      <c r="C27" s="8" t="s">
+      <c r="C27" s="6" t="s">
         <v>307</v>
       </c>
-      <c r="D27" s="8" t="s">
+      <c r="D27" s="6" t="s">
         <v>292</v>
       </c>
-      <c r="E27" s="8" t="s">
+      <c r="E27" s="6" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="28" ht="51" spans="1:5">
-      <c r="A28" s="6">
+      <c r="A28" s="1">
         <v>21</v>
       </c>
-      <c r="B28" s="8" t="s">
+      <c r="B28" s="6" t="s">
         <v>306</v>
       </c>
-      <c r="C28" s="8" t="s">
+      <c r="C28" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="D28" s="8" t="s">
+      <c r="D28" s="6" t="s">
         <v>309</v>
       </c>
-      <c r="E28" s="8" t="s">
+      <c r="E28" s="6" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="29" ht="68" spans="1:5">
-      <c r="A29" s="6">
+      <c r="A29" s="1">
         <v>22</v>
       </c>
-      <c r="B29" s="8" t="s">
+      <c r="B29" s="6" t="s">
         <v>306</v>
       </c>
-      <c r="C29" s="8" t="s">
+      <c r="C29" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="D29" s="8" t="s">
+      <c r="D29" s="6" t="s">
         <v>311</v>
       </c>
-      <c r="E29" s="8" t="s">
+      <c r="E29" s="6" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="30" ht="84" spans="1:6">
-      <c r="A30" s="6">
+      <c r="A30" s="1">
         <v>23</v>
       </c>
-      <c r="B30" s="8" t="s">
+      <c r="B30" s="6" t="s">
         <v>301</v>
       </c>
-      <c r="C30" s="8" t="s">
+      <c r="C30" s="6" t="s">
         <v>312</v>
       </c>
-      <c r="D30" s="8" t="s">
+      <c r="D30" s="6" t="s">
         <v>313</v>
       </c>
-      <c r="E30" s="8" t="s">
+      <c r="E30" s="6" t="s">
         <v>256</v>
       </c>
-      <c r="F30" s="8" t="s">
+      <c r="F30" s="6" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="31" ht="84" spans="1:5">
-      <c r="A31" s="6">
+      <c r="A31" s="1">
         <v>24</v>
       </c>
-      <c r="B31" s="8" t="s">
+      <c r="B31" s="6" t="s">
         <v>315</v>
       </c>
-      <c r="C31" s="8" t="s">
+      <c r="C31" s="6" t="s">
         <v>316</v>
       </c>
-      <c r="D31" s="8" t="s">
+      <c r="D31" s="6" t="s">
         <v>317</v>
       </c>
-      <c r="E31" s="8" t="s">
+      <c r="E31" s="6" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="32" ht="51" spans="1:5">
-      <c r="A32" s="6">
+      <c r="A32" s="1">
         <v>25</v>
       </c>
-      <c r="B32" s="8" t="s">
+      <c r="B32" s="6" t="s">
         <v>315</v>
       </c>
-      <c r="C32" s="8" t="s">
+      <c r="C32" s="6" t="s">
         <v>318</v>
       </c>
-      <c r="D32" s="8" t="s">
+      <c r="D32" s="6" t="s">
         <v>319</v>
       </c>
-      <c r="E32" s="8" t="s">
+      <c r="E32" s="6" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="33" ht="34" spans="1:5">
-      <c r="A33" s="6">
+      <c r="A33" s="1">
         <v>26</v>
       </c>
-      <c r="B33" s="8" t="s">
+      <c r="B33" s="6" t="s">
         <v>320</v>
       </c>
-      <c r="C33" s="8" t="s">
+      <c r="C33" s="6" t="s">
         <v>321</v>
       </c>
-      <c r="D33" s="8" t="s">
+      <c r="D33" s="6" t="s">
         <v>292</v>
       </c>
-      <c r="E33" s="8" t="s">
+      <c r="E33" s="6" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="34" ht="84" spans="1:5">
-      <c r="A34" s="6">
+      <c r="A34" s="1">
         <v>27</v>
       </c>
-      <c r="B34" s="8" t="s">
+      <c r="B34" s="6" t="s">
         <v>320</v>
       </c>
-      <c r="C34" s="11" t="s">
+      <c r="C34" s="9" t="s">
         <v>322</v>
       </c>
-      <c r="D34" s="8" t="s">
+      <c r="D34" s="6" t="s">
         <v>323</v>
       </c>
-      <c r="E34" s="8" t="s">
+      <c r="E34" s="6" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="35" ht="51" spans="1:5">
-      <c r="A35" s="6">
+      <c r="A35" s="1">
         <v>28</v>
       </c>
-      <c r="B35" s="8" t="s">
+      <c r="B35" s="6" t="s">
         <v>320</v>
       </c>
-      <c r="C35" s="8" t="s">
+      <c r="C35" s="6" t="s">
         <v>324</v>
       </c>
-      <c r="D35" s="8" t="s">
+      <c r="D35" s="6" t="s">
         <v>325</v>
       </c>
-      <c r="E35" s="8" t="s">
+      <c r="E35" s="6" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="36" ht="51" spans="1:5">
-      <c r="A36" s="6">
+      <c r="A36" s="1">
         <v>29</v>
       </c>
-      <c r="B36" s="8" t="s">
+      <c r="B36" s="6" t="s">
         <v>320</v>
       </c>
-      <c r="C36" s="8" t="s">
+      <c r="C36" s="6" t="s">
         <v>326</v>
       </c>
-      <c r="D36" s="8" t="s">
+      <c r="D36" s="6" t="s">
         <v>327</v>
       </c>
-      <c r="E36" s="8" t="s">
+      <c r="E36" s="6" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="37" ht="34" spans="1:5">
-      <c r="A37" s="6">
+      <c r="A37" s="1">
         <v>30</v>
       </c>
-      <c r="B37" s="8" t="s">
+      <c r="B37" s="6" t="s">
         <v>320</v>
       </c>
-      <c r="C37" s="8" t="s">
+      <c r="C37" s="6" t="s">
         <v>328</v>
       </c>
-      <c r="D37" s="8" t="s">
+      <c r="D37" s="6" t="s">
         <v>329</v>
       </c>
-      <c r="E37" s="8" t="s">
+      <c r="E37" s="6" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="38" ht="51" spans="1:5">
-      <c r="A38" s="6">
+      <c r="A38" s="1">
         <v>31</v>
       </c>
-      <c r="B38" s="8" t="s">
+      <c r="B38" s="6" t="s">
         <v>320</v>
       </c>
-      <c r="C38" s="8" t="s">
+      <c r="C38" s="6" t="s">
         <v>330</v>
       </c>
-      <c r="D38" s="8" t="s">
+      <c r="D38" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="E38" s="8" t="s">
+      <c r="E38" s="6" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="39" ht="17" spans="1:5">
-      <c r="A39" s="6">
+      <c r="A39" s="1">
         <v>32</v>
       </c>
-      <c r="B39" s="8" t="s">
+      <c r="B39" s="6" t="s">
         <v>315</v>
       </c>
-      <c r="C39" s="8" t="s">
+      <c r="C39" s="6" t="s">
         <v>332</v>
       </c>
-      <c r="D39" s="8" t="s">
+      <c r="D39" s="6" t="s">
         <v>333</v>
       </c>
-      <c r="E39" s="8" t="s">
+      <c r="E39" s="6" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="40" ht="84" spans="1:5">
-      <c r="A40" s="6">
+      <c r="A40" s="1">
         <v>33</v>
       </c>
-      <c r="B40" s="8" t="s">
+      <c r="B40" s="6" t="s">
         <v>334</v>
       </c>
-      <c r="C40" s="8" t="s">
+      <c r="C40" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="D40" s="8" t="s">
+      <c r="D40" s="6" t="s">
         <v>335</v>
       </c>
-      <c r="E40" s="8" t="s">
+      <c r="E40" s="6" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="41" ht="68" spans="1:6">
-      <c r="A41" s="6">
+      <c r="A41" s="1">
         <v>34</v>
       </c>
-      <c r="B41" s="8" t="s">
+      <c r="B41" s="6" t="s">
         <v>315</v>
       </c>
-      <c r="C41" s="8" t="s">
+      <c r="C41" s="6" t="s">
         <v>336</v>
       </c>
-      <c r="D41" s="8" t="s">
+      <c r="D41" s="6" t="s">
         <v>337</v>
       </c>
-      <c r="E41" s="8" t="s">
+      <c r="E41" s="6" t="s">
         <v>256</v>
       </c>
-      <c r="F41" s="8" t="s">
+      <c r="F41" s="6" t="s">
         <v>338</v>
       </c>
     </row>
     <row r="42" ht="84" spans="1:5">
-      <c r="A42" s="6">
+      <c r="A42" s="1">
         <v>35</v>
       </c>
-      <c r="B42" s="8" t="s">
+      <c r="B42" s="6" t="s">
         <v>339</v>
       </c>
-      <c r="C42" s="8" t="s">
+      <c r="C42" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="D42" s="8" t="s">
+      <c r="D42" s="6" t="s">
         <v>335</v>
       </c>
-      <c r="E42" s="8" t="s">
+      <c r="E42" s="6" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="43" spans="1:6">
-      <c r="A43" s="6" t="s">
+      <c r="A43" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="B43" s="6"/>
-      <c r="C43" s="6"/>
-      <c r="D43" s="6"/>
-      <c r="E43" s="6"/>
-      <c r="F43" s="6"/>
+      <c r="B43" s="1"/>
+      <c r="C43" s="1"/>
+      <c r="D43" s="1"/>
+      <c r="E43" s="1"/>
+      <c r="F43" s="1"/>
     </row>
     <row r="44" ht="37" customHeight="1" spans="1:6">
-      <c r="A44" s="6">
+      <c r="A44" s="1">
         <v>36</v>
       </c>
-      <c r="B44" s="8" t="s">
+      <c r="B44" s="6" t="s">
         <v>341</v>
       </c>
-      <c r="C44" s="6" t="s">
+      <c r="C44" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="D44" s="6" t="s">
+      <c r="D44" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="E44" s="8" t="s">
+      <c r="E44" s="6" t="s">
         <v>256</v>
       </c>
-      <c r="F44" s="6" t="s">
+      <c r="F44" s="1" t="s">
         <v>344</v>
       </c>
     </row>
     <row r="45" ht="37" customHeight="1" spans="1:6">
-      <c r="A45" s="6">
+      <c r="A45" s="1">
         <v>37</v>
       </c>
-      <c r="B45" s="8" t="s">
+      <c r="B45" s="6" t="s">
         <v>345</v>
       </c>
-      <c r="C45" s="6"/>
-      <c r="D45" s="6"/>
-      <c r="E45" s="8" t="s">
+      <c r="C45" s="1"/>
+      <c r="D45" s="1"/>
+      <c r="E45" s="6" t="s">
         <v>256</v>
       </c>
-      <c r="F45" s="6"/>
+      <c r="F45" s="1"/>
     </row>
     <row r="46" ht="34" customHeight="1" spans="1:6">
-      <c r="A46" s="6">
+      <c r="A46" s="1">
         <v>38</v>
       </c>
-      <c r="B46" s="8" t="s">
+      <c r="B46" s="6" t="s">
         <v>346</v>
       </c>
-      <c r="C46" s="6"/>
-      <c r="D46" s="6"/>
-      <c r="E46" s="8" t="s">
+      <c r="C46" s="1"/>
+      <c r="D46" s="1"/>
+      <c r="E46" s="6" t="s">
         <v>256</v>
       </c>
-      <c r="F46" s="6"/>
+      <c r="F46" s="1"/>
     </row>
     <row r="47" ht="33" customHeight="1" spans="1:6">
-      <c r="A47" s="6">
+      <c r="A47" s="1">
         <v>39</v>
       </c>
-      <c r="B47" s="8" t="s">
+      <c r="B47" s="6" t="s">
         <v>347</v>
       </c>
-      <c r="C47" s="6"/>
-      <c r="D47" s="6"/>
-      <c r="E47" s="8" t="s">
+      <c r="C47" s="1"/>
+      <c r="D47" s="1"/>
+      <c r="E47" s="6" t="s">
         <v>256</v>
       </c>
-      <c r="F47" s="6"/>
+      <c r="F47" s="1"/>
     </row>
     <row r="48" ht="34" spans="1:6">
-      <c r="A48" s="6">
+      <c r="A48" s="1">
         <v>40</v>
       </c>
-      <c r="B48" s="8" t="s">
+      <c r="B48" s="6" t="s">
         <v>348</v>
       </c>
-      <c r="C48" s="6"/>
-      <c r="D48" s="6"/>
-      <c r="E48" s="8" t="s">
+      <c r="C48" s="1"/>
+      <c r="D48" s="1"/>
+      <c r="E48" s="6" t="s">
         <v>256</v>
       </c>
-      <c r="F48" s="6"/>
+      <c r="F48" s="1"/>
     </row>
     <row r="49" ht="34" spans="1:6">
-      <c r="A49" s="6">
+      <c r="A49" s="1">
         <v>41</v>
       </c>
-      <c r="B49" s="8" t="s">
+      <c r="B49" s="6" t="s">
         <v>349</v>
       </c>
-      <c r="C49" s="6"/>
-      <c r="D49" s="6"/>
-      <c r="E49" s="8" t="s">
+      <c r="C49" s="1"/>
+      <c r="D49" s="1"/>
+      <c r="E49" s="6" t="s">
         <v>256</v>
       </c>
-      <c r="F49" s="6"/>
+      <c r="F49" s="1"/>
     </row>
     <row r="50" ht="34" spans="1:6">
-      <c r="A50" s="6">
+      <c r="A50" s="1">
         <v>42</v>
       </c>
-      <c r="B50" s="8" t="s">
+      <c r="B50" s="6" t="s">
         <v>350</v>
       </c>
-      <c r="C50" s="6"/>
-      <c r="D50" s="6"/>
-      <c r="E50" s="8" t="s">
+      <c r="C50" s="1"/>
+      <c r="D50" s="1"/>
+      <c r="E50" s="6" t="s">
         <v>256</v>
       </c>
-      <c r="F50" s="6"/>
+      <c r="F50" s="1"/>
     </row>
     <row r="51" ht="34" spans="1:6">
-      <c r="A51" s="6">
+      <c r="A51" s="1">
         <v>43</v>
       </c>
-      <c r="B51" s="8" t="s">
+      <c r="B51" s="6" t="s">
         <v>351</v>
       </c>
-      <c r="C51" s="6"/>
-      <c r="D51" s="6"/>
-      <c r="E51" s="8" t="s">
+      <c r="C51" s="1"/>
+      <c r="D51" s="1"/>
+      <c r="E51" s="6" t="s">
         <v>256</v>
       </c>
-      <c r="F51" s="6"/>
+      <c r="F51" s="1"/>
     </row>
     <row r="52" ht="68" spans="1:6">
-      <c r="A52" s="6">
+      <c r="A52" s="1">
         <v>44</v>
       </c>
-      <c r="B52" s="8" t="s">
+      <c r="B52" s="6" t="s">
         <v>352</v>
       </c>
-      <c r="C52" s="8" t="s">
+      <c r="C52" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D52" s="8" t="s">
+      <c r="D52" s="6" t="s">
         <v>353</v>
       </c>
-      <c r="E52" s="8" t="s">
+      <c r="E52" s="6" t="s">
         <v>256</v>
       </c>
-      <c r="F52" s="8" t="s">
+      <c r="F52" s="6" t="s">
         <v>354</v>
       </c>
     </row>
@@ -6586,13 +6580,13 @@
   <dimension ref="A1:I9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="1" width="4.953125" style="5" customWidth="1"/>
-    <col min="2" max="2" width="27.6015625" style="5" customWidth="1"/>
-    <col min="3" max="3" width="16.40625" style="5" customWidth="1"/>
-    <col min="4" max="4" width="25.2578125" style="5" customWidth="1"/>
-    <col min="5" max="5" width="9.2421875" style="5" customWidth="1"/>
-    <col min="6" max="6" width="19.65625" style="5" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="5"/>
+    <col min="1" max="1" width="4.953125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="27.6015625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="16.40625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="25.2578125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="9.2421875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="19.65625" style="2" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" s="4" customFormat="1" ht="17" spans="1:8">
@@ -6619,167 +6613,167 @@
       </c>
     </row>
     <row r="2" ht="70" customHeight="1" spans="1:9">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="2" t="s">
         <v>362</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="2" t="s">
         <v>364</v>
       </c>
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
     </row>
     <row r="3" ht="118" spans="1:9">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="2" t="s">
         <v>368</v>
       </c>
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
     </row>
     <row r="4" ht="34" spans="1:9">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>369</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="2" t="s">
         <v>363</v>
       </c>
       <c r="H4" s="4"/>
       <c r="I4" s="4"/>
     </row>
     <row r="5" ht="34" spans="1:9">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="2" t="s">
         <v>363</v>
       </c>
       <c r="H5" s="4"/>
       <c r="I5" s="4"/>
     </row>
     <row r="6" ht="118" spans="1:9">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="2" t="s">
         <v>378</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="2" t="s">
         <v>379</v>
       </c>
       <c r="H6" s="4"/>
       <c r="I6" s="4"/>
     </row>
     <row r="7" ht="118" spans="1:9">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="F7" s="2" t="s">
         <v>383</v>
       </c>
       <c r="H7" s="4"/>
       <c r="I7" s="4"/>
     </row>
     <row r="8" ht="135" spans="1:9">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="2" t="s">
         <v>384</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="2" t="s">
         <v>385</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="2" t="s">
         <v>368</v>
       </c>
       <c r="H8" s="4"/>
       <c r="I8" s="4"/>
     </row>
     <row r="9" ht="34" spans="1:9">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="2" t="s">
         <v>363</v>
       </c>
       <c r="H9" s="4"/>

--- a/Log/Magic_eraser_test_log.xlsx
+++ b/Log/Magic_eraser_test_log.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23620" windowHeight="9380" firstSheet="2" activeTab="4"/>
+    <workbookView windowWidth="18980" windowHeight="16340" firstSheet="3" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Image_selector_test" sheetId="1" r:id="rId1"/>

--- a/Log/Magic_eraser_test_log.xlsx
+++ b/Log/Magic_eraser_test_log.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18980" windowHeight="16340" firstSheet="3" activeTab="4"/>
+    <workbookView windowWidth="23820" windowHeight="15380" firstSheet="3" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Image_selector_test" sheetId="1" r:id="rId1"/>
@@ -12,6 +12,8 @@
     <sheet name="Home_screen_Remove_background" sheetId="3" r:id="rId3"/>
     <sheet name="Force_update" sheetId="4" r:id="rId4"/>
     <sheet name="Test_thông_luồng" sheetId="5" r:id="rId5"/>
+    <sheet name="Remove_BG_module" sheetId="6" r:id="rId6"/>
+    <sheet name="Sheet2" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="994" uniqueCount="443">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1057" uniqueCount="469">
   <si>
     <t>TC</t>
   </si>
@@ -786,7 +788,13 @@
     <t>chuyển về màn hình "Saved", ảnh mới được lưu trong máy có độ dài cạnh lớn nhất là 3841, vẫn giữ nguyên tỷ lệ</t>
   </si>
   <si>
-    <t>Status</t>
+    <t>IPhone 6s (IOS 15.5)</t>
+  </si>
+  <si>
+    <t>IPhone Xs (IOS 18.4)</t>
+  </si>
+  <si>
+    <t>IPad Air 11-inch(M2) [IOS 17.5]</t>
   </si>
   <si>
     <t>Khả năng truy cập tính năng "Remove background"</t>
@@ -801,7 +809,7 @@
     <t>Hiển thị bảng chọn ảnh (image selector)</t>
   </si>
   <si>
-    <t>Fail</t>
+    <t>PASS</t>
   </si>
   <si>
     <t>Ở màn hình Home, phần giới thiệu chức năng (image carousel) đang hiển thị phông giới thiệu chức năng "Remove Backgound"(Xoá phông)</t>
@@ -834,6 +842,9 @@
     <t>Hệ thống chuyển sang màn hình camera mặc định của IOS</t>
   </si>
   <si>
+    <t>PENDING</t>
+  </si>
+  <si>
     <t>Đã chụp ảnh từ IOS và chuyển về màn hình xác nhận chọn ảnh</t>
   </si>
   <si>
@@ -849,6 +860,9 @@
     <t>Mở app, chuyển sang màn chọn chức năng thao tác với ảnh</t>
   </si>
   <si>
+    <t>FAIL</t>
+  </si>
+  <si>
     <t>Ở màn hình xem ảnh mặc định của IOS</t>
   </si>
   <si>
@@ -861,6 +875,9 @@
     <t>Chọn chức năng "Remove Background"</t>
   </si>
   <si>
+    <t>Hệ thống hiện lên dialog thông báo xử lý (span "Processing" và video hình ảnh đang được xử lý)</t>
+  </si>
+  <si>
     <t>Bước xử lý hình ảnh (fetch với server)</t>
   </si>
   <si>
@@ -933,7 +950,10 @@
     <t>Nhấn vào vùng "Cutout Edit"</t>
   </si>
   <si>
-    <t>Chuyển vào màn "Edit cutout", ở phần Hình ảnh các phần bị xoá được tô màu, có các nút chức năng tương ứng</t>
+    <t>Chuyển vào màn "Edit cutout", ở phần Hình ảnh các phần bị xoá được tô màu đúng với cutout hiển thị bên ngoài, không tồn tại step chỉnh sửa nào, có các nút chức năng tương ứng</t>
+  </si>
+  <si>
+    <t>Lỗi xảy ra khi trước đó đã vào màn cutout edit vẽ chỉnh sửa nhưng sau đó huỷ chỉnh sửa</t>
   </si>
   <si>
     <t>Ở màn "Edit cutout", người dùng đã có các thao tác chỉnh sửa trước đó</t>
@@ -948,7 +968,7 @@
     <t>Ở màn "Edit cutout", người dùng chưa có bất kỳ thao tác chỉnh sửa trước đó</t>
   </si>
   <si>
-    <t>Trở về màn hình "Home - edit"</t>
+    <t>Trở về màn hình "Home - edit", các hình ảnh trên cutout và template hiển thị tương ứng với với cutout trước khi vào chỉnh sửa</t>
   </si>
   <si>
     <t>Ở màn "Edit cutout", trên màn hình đang hiện dialog cảnh báo chưa lưu kết quả chỉnh sửa</t>
@@ -993,70 +1013,37 @@
     <t>Hiện ra bảng tuỳ chỉnh màu (gọi tắt là message tuỳ chỉnh màu)</t>
   </si>
   <si>
-    <t>Ở màn "Home edit", trên màn hình có message tuỳ chỉnh màu</t>
-  </si>
-  <si>
-    <t>nhấn vào vùng ngoài message tuỳ chỉnh màu</t>
-  </si>
-  <si>
-    <t>tùy chỉnh màu trên bảng tròn chọn màu</t>
-  </si>
-  <si>
-    <t>Tone màu trên 2 thanh điều chỉnh độ ‘trong suốt’ và ‘sắc độ’ cũng thay đổi trùng vs màu được chọn trên bảng chọn màu</t>
-  </si>
-  <si>
-    <t>thao tác với thanh điều chỉnh độ trong suốt</t>
-  </si>
-  <si>
-    <t>Thanh điều chỉnh độ trong suốt được cập nhật theo thao tác của người dùng</t>
-  </si>
-  <si>
-    <t>thao tác với thanh điều chỉnh sắc độ</t>
-  </si>
-  <si>
-    <t>Thanh điều chỉnh sắc độ được cập nhật theo thao tác của người dùng</t>
-  </si>
-  <si>
-    <t>nhấn button huỷ tuỳ chỉnh</t>
-  </si>
-  <si>
-    <t>message tuỳ chỉnh màu biến mất, trở về màn "Home edit"</t>
-  </si>
-  <si>
-    <t>nhấn button xác nhận tuỳ chỉnh</t>
-  </si>
-  <si>
-    <t>Chuyển vào màn hình "Edit" cơ bản, nền được chèn bằng phông màu đã tuỳ chỉnh</t>
-  </si>
-  <si>
-    <t>chọn option Tải ảnh lên</t>
-  </si>
-  <si>
-    <t>chuyển sang màn chọn ảnh</t>
-  </si>
-  <si>
-    <t>Ở màn chọn ảnh, chức năng đang sử dụng là"Remove background"</t>
+    <t>Ở màn "Background edit", trên màn hình có message tuỳ chỉnh màu</t>
+  </si>
+  <si>
+    <t>tùy chỉnh màu trên 3 bảng chọn màu:
+a. Grid (chọn ô màu sẵn có)|
+b. Spectrum (chọn màu trên bảng phối hoặc option)
+c. slider (tuỳ chỉnh trên thanh sắc độ RGB hoặc option)</t>
+  </si>
+  <si>
+    <t>Ảnh nền phía sau được thay đổi màu sắc nền đúng theo màu đã chọn (có thể nhìn thấy phía sau bảng mess)</t>
+  </si>
+  <si>
+    <t>chọn option thuộc nhóm group (có nhiều lựa chọn đơn trong nhóm)</t>
+  </si>
+  <si>
+    <t>Hiện lên bảng chọn ảnh có các ảnh thuộc nhóm</t>
+  </si>
+  <si>
+    <t>tương tự như bảng "image selector" nhưng chỉ có các ảnh mà app cung cấp sẵn</t>
+  </si>
+  <si>
+    <t>Ở màn "Home edit", trên màn đang có bảng chọn ảnh</t>
   </si>
   <si>
     <t>Chuyển vào màn hình "Edit" cơ bản, nền được thay bằng ảnh đã chọn, tỷ lệ ảnh được giữ nguyên so với lần chọn size gần nhất</t>
   </si>
   <si>
-    <t>chọn option thuộc nhóm group (có nhiều lựa chọn đơn trong nhóm)</t>
-  </si>
-  <si>
-    <t>Hiện lên bảng chọn ảnh có các ảnh thuộc nhóm</t>
-  </si>
-  <si>
-    <t>tương tự như bảng "image selector" nhưng chỉ có các ảnh mà app cung cấp sẵn</t>
-  </si>
-  <si>
-    <t>Ở màn "Home edit", trên màn đang có bảng chọn ảnh</t>
-  </si>
-  <si>
     <t>Test phi chức năng</t>
   </si>
   <si>
-    <t>Ở màn "Home", Thiết bị: iPhoneX [IOS 15.0]</t>
+    <t>Ở màn "Home", Thiết bị: iPhone 6s [IOS 15.5]</t>
   </si>
   <si>
     <t>1. Chọn button "Remove BG"
@@ -1075,13 +1062,13 @@
     <t>Test tính tương thích: cho từng thiết bị và cỡ màn hình (trọng tâm vào GUI)</t>
   </si>
   <si>
+    <t>HALF_PASS</t>
+  </si>
+  <si>
     <t>Ở màn "Home", Thiết bị: iPhoneXs [IOS 18.5]</t>
   </si>
   <si>
-    <t>Ở màn "Home", Thiết bị: iPhone17 [IOS 26.0]</t>
-  </si>
-  <si>
-    <t>Ở màn "Home", Thiết bị: iPad  Pro 11-inch [IOS 26.0]</t>
+    <t>Ở màn "Home", Thiết bị: IPad Air 11-inch(M2) [IOS 17.5]</t>
   </si>
   <si>
     <t>Ở màn "Home", thiết bị Pixel 3 [Android 12.0]</t>
@@ -1130,9 +1117,6 @@
   </si>
   <si>
     <t>App vào màn hình Home với phiên bản hiện tại</t>
-  </si>
-  <si>
-    <t>PASS</t>
   </si>
   <si>
     <t>fetch failed</t>
@@ -1451,6 +1435,126 @@
   </si>
   <si>
     <t>Mã TC của Connect with us: CWU</t>
+  </si>
+  <si>
+    <t>Test cases: module Processing  (ID: PR)</t>
+  </si>
+  <si>
+    <t>Android</t>
+  </si>
+  <si>
+    <t>IOS</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Items</t>
+  </si>
+  <si>
+    <t>Sub-items</t>
+  </si>
+  <si>
+    <t>Pre-condition</t>
+  </si>
+  <si>
+    <t>steps to Excute</t>
+  </si>
+  <si>
+    <t>Expected output</t>
+  </si>
+  <si>
+    <t>Test Data/ Parameters</t>
+  </si>
+  <si>
+    <t>redmi14C (Android 14)</t>
+  </si>
+  <si>
+    <t>Medium Tablet (Android 9 - SDK 28)</t>
+  </si>
+  <si>
+    <t>Pixcel Fold 
+ (Android 16.0 - SDK 36)</t>
+  </si>
+  <si>
+    <t>ipad air 11-inch (IOS 17.5)</t>
+  </si>
+  <si>
+    <t>iPhone 6s (IOS 15.5)</t>
+  </si>
+  <si>
+    <t>RB_PR_F_01</t>
+  </si>
+  <si>
+    <t>Processing flow</t>
+  </si>
+  <si>
+    <t>Processing functional flow (Chọn và xử lý ảnh (sellect and process))</t>
+  </si>
+  <si>
+    <t>- App mở thành công 
+- Đang ở màn hình Home</t>
+  </si>
+  <si>
+    <t>1. truy cập chức năng Edit background bằng 1 trong các cách sau: 
+1.a. chọn image carousel 
+1.b. chọn button 
+1.c. chọn banner
+2. chọn 1 ảnh bất kỳ trong popup "image selector"
+3. Xác nhận popup Processing hiển thị đúng hình ảnh preview đã chọn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Popup Image Selector hiển thị đúng với mọi cách truy cập (enty poin)
+- Khi chọn ảnh -&gt; hiển thị popup Process GẦN NHƯ ngay lập tức (có thể có độ trễ nhẹ), phần hình ảnh preview hiển thị đúng hình ảnh đã chọn 
+- Không crassh, lag, treo app 
+- Bắt đầu quá trình xử lý ảnh theo logic hệ thống </t>
+  </si>
+  <si>
+    <t>Ảnh HEV, JPEG, PNG &lt; 50MB</t>
+  </si>
+  <si>
+    <t>RB_PR_UI_01</t>
+  </si>
+  <si>
+    <t>Image Aspect Ratio Rendering</t>
+  </si>
+  <si>
+    <t>- App đã mở 
+- Popup "image selector" hoạt động bình thường (đúng) 
+- Đã chuẩn bị bộ ảnh test với nhiều tỷ lệ cạnh khác nhau</t>
+  </si>
+  <si>
+    <t>1. Truy cập chức năng Edit background qua carousel/ button/ banner 
+2. Lần lượt chọn các ảnh theo các khung hình dạng vuông, chữ nhật - ngang, chữ nhật-dọc  
+3. Kiểm tra alignment, crop, padding, spacing, Layout, spinner</t>
+  </si>
+  <si>
+    <t>- Ảnh được render đúng tỷ lệ ảnh gốc 
+- Không bị stretch (kéo giãn), squash (ép chiều), crop sai 
+- Không tràn khỏi container 
+- Layout, padding, spacing khớp với thiết kế 
+-  spinner không che nội dung chính, có hiệu ứng overlay khi xử lý xong
+- UI không nhấp nháy trong quá trình xử lý</t>
+  </si>
+  <si>
+    <t>Bộ test ảnh với tỷ lệ: 4288x2848 (3:2), 1668x2500 (2:3), 1280x1280 (1:1)</t>
+  </si>
+  <si>
+    <t>RB_B_UI_01</t>
+  </si>
+  <si>
+    <t>Background flow</t>
+  </si>
+  <si>
+    <t>Preview Frame</t>
+  </si>
+  <si>
+    <t>- Ảnh được chọn trước đó đã được xử lý xong ở Processing flow
+- Màn hình Background đã được load đầy đủ</t>
+  </si>
+  <si>
+    <t>1. Mở màn hình Background 
+2. Quan sát sát khung preview</t>
   </si>
 </sst>
 </file>
@@ -2214,16 +2318,25 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2245,6 +2358,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -2292,6 +2414,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" quotePrefix="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2829,1292 +2954,1292 @@
   <dimension ref="A1:L61"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="1" width="4" style="11" customWidth="1"/>
-    <col min="2" max="2" width="31.2890625" style="12" customWidth="1"/>
-    <col min="3" max="3" width="21.7109375" style="12" customWidth="1"/>
-    <col min="4" max="5" width="24.4296875" style="12" customWidth="1"/>
-    <col min="6" max="6" width="30.2890625" style="12" customWidth="1"/>
-    <col min="7" max="7" width="20.140625" style="12" customWidth="1"/>
-    <col min="8" max="8" width="9.140625" style="2"/>
-    <col min="9" max="9" width="17.7109375" style="2" customWidth="1"/>
-    <col min="10" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="4" style="17" customWidth="1"/>
+    <col min="2" max="2" width="31.2890625" style="18" customWidth="1"/>
+    <col min="3" max="3" width="21.7109375" style="18" customWidth="1"/>
+    <col min="4" max="5" width="24.4296875" style="18" customWidth="1"/>
+    <col min="6" max="6" width="30.2890625" style="18" customWidth="1"/>
+    <col min="7" max="7" width="20.140625" style="18" customWidth="1"/>
+    <col min="8" max="8" width="9.140625" style="3"/>
+    <col min="9" max="9" width="17.7109375" style="3" customWidth="1"/>
+    <col min="10" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="17.75" spans="1:7">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="23" t="s">
+      <c r="B1" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="23" t="s">
+      <c r="C1" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="23" t="s">
+      <c r="D1" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="23" t="s">
+      <c r="E1" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="23" t="s">
+      <c r="F1" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="25" t="s">
+      <c r="G1" s="31" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" ht="37" customHeight="1" spans="1:12">
-      <c r="A2" s="21">
+      <c r="A2" s="27">
         <v>1</v>
       </c>
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="24" t="s">
+      <c r="C2" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="24" t="s">
+      <c r="D2" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="24" t="s">
+      <c r="E2" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="24" t="s">
+      <c r="F2" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="24"/>
-      <c r="I2" s="6" t="s">
+      <c r="G2" s="30"/>
+      <c r="I2" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="K2" s="6" t="s">
+      <c r="K2" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="L2" s="6"/>
+      <c r="L2" s="9"/>
     </row>
     <row r="3" ht="34" spans="1:12">
-      <c r="A3" s="11">
+      <c r="A3" s="17">
         <v>2</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="E3" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="F3" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="I3" s="6"/>
-      <c r="K3" s="6"/>
-      <c r="L3" s="6"/>
+      <c r="I3" s="9"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
     </row>
     <row r="4" ht="34" spans="1:12">
-      <c r="A4" s="11">
+      <c r="A4" s="17">
         <v>3</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="F4" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="I4" s="6"/>
-      <c r="K4" s="6"/>
-      <c r="L4" s="6"/>
+      <c r="I4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
     </row>
     <row r="5" ht="34" spans="1:12">
-      <c r="A5" s="11">
+      <c r="A5" s="17">
         <v>4</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="E5" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="12" t="s">
+      <c r="F5" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="I5" s="6"/>
-      <c r="K5" s="6"/>
-      <c r="L5" s="6"/>
+      <c r="I5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
     </row>
     <row r="6" ht="34" spans="1:12">
-      <c r="A6" s="11">
+      <c r="A6" s="17">
         <v>5</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="12" t="s">
+      <c r="F6" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="K6" s="6"/>
-      <c r="L6" s="6"/>
+      <c r="K6" s="9"/>
+      <c r="L6" s="9"/>
     </row>
     <row r="7" ht="17" spans="1:6">
-      <c r="A7" s="11">
+      <c r="A7" s="17">
         <v>6</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="12" t="s">
+      <c r="E7" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="F7" s="12" t="s">
+      <c r="F7" s="18" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="8" ht="50" customHeight="1" spans="1:6">
-      <c r="A8" s="11">
+      <c r="A8" s="17">
         <v>7</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="E8" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="12" t="s">
+      <c r="F8" s="18" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="9" ht="34" spans="1:6">
-      <c r="A9" s="11">
+      <c r="A9" s="17">
         <v>8</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="D9" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="12" t="s">
+      <c r="E9" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="F9" s="12" t="s">
+      <c r="F9" s="18" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="10" ht="34" spans="1:6">
-      <c r="A10" s="11">
+      <c r="A10" s="17">
         <v>9</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="E10" s="12" t="s">
+      <c r="E10" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="F10" s="12" t="s">
+      <c r="F10" s="18" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="11" ht="34" spans="1:6">
-      <c r="A11" s="11">
+      <c r="A11" s="17">
         <v>10</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="C11" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="12" t="s">
+      <c r="D11" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="E11" s="12" t="s">
+      <c r="E11" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="F11" s="12" t="s">
+      <c r="F11" s="18" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="12" ht="34" spans="1:6">
-      <c r="A12" s="11">
+      <c r="A12" s="17">
         <v>11</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="D12" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="E12" s="12" t="s">
+      <c r="E12" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="F12" s="12" t="s">
+      <c r="F12" s="18" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="13" ht="34" spans="1:6">
-      <c r="A13" s="11">
+      <c r="A13" s="17">
         <v>12</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="D13" s="12" t="s">
+      <c r="D13" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="E13" s="12" t="s">
+      <c r="E13" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="F13" s="12" t="s">
+      <c r="F13" s="18" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="14" ht="51" spans="1:6">
-      <c r="A14" s="11">
+      <c r="A14" s="17">
         <v>13</v>
       </c>
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="C14" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D14" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="E14" s="12" t="s">
+      <c r="E14" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="F14" s="12" t="s">
+      <c r="F14" s="18" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="15" ht="34" spans="1:6">
-      <c r="A15" s="11">
+      <c r="A15" s="17">
         <v>14</v>
       </c>
-      <c r="B15" s="12" t="s">
+      <c r="B15" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="C15" s="12" t="s">
+      <c r="C15" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="D15" s="12" t="s">
+      <c r="D15" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="E15" s="12" t="s">
+      <c r="E15" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="F15" s="12" t="s">
+      <c r="F15" s="18" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="16" ht="34" spans="1:6">
-      <c r="A16" s="11">
+      <c r="A16" s="17">
         <v>15</v>
       </c>
-      <c r="B16" s="12" t="s">
+      <c r="B16" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="C16" s="12" t="s">
+      <c r="C16" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="D16" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="E16" s="12" t="s">
+      <c r="E16" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="F16" s="12" t="s">
+      <c r="F16" s="18" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="17" ht="34" spans="1:6">
-      <c r="A17" s="11">
+      <c r="A17" s="17">
         <v>16</v>
       </c>
-      <c r="B17" s="12" t="s">
+      <c r="B17" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="C17" s="12" t="s">
+      <c r="C17" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="D17" s="12" t="s">
+      <c r="D17" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="E17" s="12" t="s">
+      <c r="E17" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="F17" s="12" t="s">
+      <c r="F17" s="18" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="18" ht="34" spans="1:6">
-      <c r="A18" s="11">
+      <c r="A18" s="17">
         <v>17</v>
       </c>
-      <c r="B18" s="12" t="s">
+      <c r="B18" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="C18" s="12" t="s">
+      <c r="C18" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="D18" s="12" t="s">
+      <c r="D18" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="E18" s="12" t="s">
+      <c r="E18" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="F18" s="12" t="s">
+      <c r="F18" s="18" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="19" ht="34" spans="1:6">
-      <c r="A19" s="11">
+      <c r="A19" s="17">
         <v>18</v>
       </c>
-      <c r="B19" s="12" t="s">
+      <c r="B19" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="C19" s="12" t="s">
+      <c r="C19" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="D19" s="12" t="s">
+      <c r="D19" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="E19" s="12" t="s">
+      <c r="E19" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="F19" s="12" t="s">
+      <c r="F19" s="18" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="20" ht="51" spans="1:6">
-      <c r="A20" s="11">
+      <c r="A20" s="17">
         <v>19</v>
       </c>
-      <c r="B20" s="12" t="s">
+      <c r="B20" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="C20" s="12" t="s">
+      <c r="C20" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="D20" s="12" t="s">
+      <c r="D20" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="E20" s="12" t="s">
+      <c r="E20" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="F20" s="12" t="s">
+      <c r="F20" s="18" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="21" ht="34" spans="1:6">
-      <c r="A21" s="11">
+      <c r="A21" s="17">
         <v>20</v>
       </c>
-      <c r="B21" s="12" t="s">
+      <c r="B21" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="C21" s="12" t="s">
+      <c r="C21" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="D21" s="12" t="s">
+      <c r="D21" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="E21" s="12" t="s">
+      <c r="E21" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="F21" s="12" t="s">
+      <c r="F21" s="18" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="22" ht="34" spans="1:6">
-      <c r="A22" s="11">
+      <c r="A22" s="17">
         <v>21</v>
       </c>
-      <c r="B22" s="12" t="s">
+      <c r="B22" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="C22" s="12" t="s">
+      <c r="C22" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="D22" s="12" t="s">
+      <c r="D22" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="E22" s="12" t="s">
+      <c r="E22" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="F22" s="12" t="s">
+      <c r="F22" s="18" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="23" ht="34" spans="1:6">
-      <c r="A23" s="11">
+      <c r="A23" s="17">
         <v>22</v>
       </c>
-      <c r="B23" s="12" t="s">
+      <c r="B23" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="C23" s="12" t="s">
+      <c r="C23" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="D23" s="12" t="s">
+      <c r="D23" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="E23" s="12" t="s">
+      <c r="E23" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="F23" s="12" t="s">
+      <c r="F23" s="18" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="24" ht="34" spans="1:6">
-      <c r="A24" s="11">
+      <c r="A24" s="17">
         <v>23</v>
       </c>
-      <c r="B24" s="12" t="s">
+      <c r="B24" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="C24" s="12" t="s">
+      <c r="C24" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="D24" s="12" t="s">
+      <c r="D24" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="E24" s="12" t="s">
+      <c r="E24" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="F24" s="12" t="s">
+      <c r="F24" s="18" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="25" ht="34" spans="1:6">
-      <c r="A25" s="11">
+      <c r="A25" s="17">
         <v>24</v>
       </c>
-      <c r="B25" s="12" t="s">
+      <c r="B25" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="C25" s="12" t="s">
+      <c r="C25" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="D25" s="12" t="s">
+      <c r="D25" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="E25" s="12" t="s">
+      <c r="E25" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="F25" s="12" t="s">
+      <c r="F25" s="18" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="26" ht="34" spans="1:6">
-      <c r="A26" s="11">
+      <c r="A26" s="17">
         <v>25</v>
       </c>
-      <c r="B26" s="12" t="s">
+      <c r="B26" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="C26" s="12" t="s">
+      <c r="C26" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="D26" s="12" t="s">
+      <c r="D26" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="E26" s="12" t="s">
+      <c r="E26" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="F26" s="12" t="s">
+      <c r="F26" s="18" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="27" ht="51" spans="1:6">
-      <c r="A27" s="11">
+      <c r="A27" s="17">
         <v>26</v>
       </c>
-      <c r="B27" s="12" t="s">
+      <c r="B27" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="C27" s="12" t="s">
+      <c r="C27" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="D27" s="12" t="s">
+      <c r="D27" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="E27" s="12" t="s">
+      <c r="E27" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="F27" s="12" t="s">
+      <c r="F27" s="18" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="28" ht="51" spans="1:6">
-      <c r="A28" s="11">
+      <c r="A28" s="17">
         <v>27</v>
       </c>
-      <c r="B28" s="12" t="s">
+      <c r="B28" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="C28" s="12" t="s">
+      <c r="C28" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="D28" s="12" t="s">
+      <c r="D28" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="E28" s="12" t="s">
+      <c r="E28" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="F28" s="12" t="s">
+      <c r="F28" s="18" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="29" ht="51" spans="1:6">
-      <c r="A29" s="11">
+      <c r="A29" s="17">
         <v>28</v>
       </c>
-      <c r="B29" s="12" t="s">
+      <c r="B29" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="C29" s="12" t="s">
+      <c r="C29" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="D29" s="12" t="s">
+      <c r="D29" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="E29" s="12" t="s">
+      <c r="E29" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="F29" s="12" t="s">
+      <c r="F29" s="18" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="30" ht="51" spans="1:6">
-      <c r="A30" s="11">
+      <c r="A30" s="17">
         <v>29</v>
       </c>
-      <c r="B30" s="12" t="s">
+      <c r="B30" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="C30" s="12" t="s">
+      <c r="C30" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="D30" s="12" t="s">
+      <c r="D30" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="E30" s="12" t="s">
+      <c r="E30" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="F30" s="12" t="s">
+      <c r="F30" s="18" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="31" ht="51" spans="1:6">
-      <c r="A31" s="11">
+      <c r="A31" s="17">
         <v>30</v>
       </c>
-      <c r="B31" s="12" t="s">
+      <c r="B31" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="C31" s="12" t="s">
+      <c r="C31" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="D31" s="12" t="s">
+      <c r="D31" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="E31" s="12" t="s">
+      <c r="E31" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="F31" s="12" t="s">
+      <c r="F31" s="18" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="32" ht="51" spans="1:6">
-      <c r="A32" s="11">
+      <c r="A32" s="17">
         <v>31</v>
       </c>
-      <c r="B32" s="12" t="s">
+      <c r="B32" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="C32" s="12" t="s">
+      <c r="C32" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="D32" s="12" t="s">
+      <c r="D32" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="E32" s="12" t="s">
+      <c r="E32" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="F32" s="12" t="s">
+      <c r="F32" s="18" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="33" ht="51" spans="1:6">
-      <c r="A33" s="11">
+      <c r="A33" s="17">
         <v>32</v>
       </c>
-      <c r="B33" s="12" t="s">
+      <c r="B33" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="C33" s="12" t="s">
+      <c r="C33" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="D33" s="12" t="s">
+      <c r="D33" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="E33" s="12" t="s">
+      <c r="E33" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="F33" s="12" t="s">
+      <c r="F33" s="18" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="34" ht="51" spans="1:6">
-      <c r="A34" s="11">
+      <c r="A34" s="17">
         <v>33</v>
       </c>
-      <c r="B34" s="12" t="s">
+      <c r="B34" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="C34" s="12" t="s">
+      <c r="C34" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="D34" s="12" t="s">
+      <c r="D34" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="E34" s="12" t="s">
+      <c r="E34" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="F34" s="12" t="s">
+      <c r="F34" s="18" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="35" ht="34" spans="1:6">
-      <c r="A35" s="11">
+      <c r="A35" s="17">
         <v>34</v>
       </c>
-      <c r="B35" s="12" t="s">
+      <c r="B35" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="C35" s="12" t="s">
+      <c r="C35" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="D35" s="12" t="s">
+      <c r="D35" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="E35" s="12" t="s">
+      <c r="E35" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="F35" s="12" t="s">
+      <c r="F35" s="18" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="36" ht="51" spans="1:7">
-      <c r="A36" s="11">
+      <c r="A36" s="17">
         <v>35</v>
       </c>
-      <c r="B36" s="12" t="s">
+      <c r="B36" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="C36" s="12" t="s">
+      <c r="C36" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="D36" s="12" t="s">
+      <c r="D36" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="E36" s="12" t="s">
+      <c r="E36" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="F36" s="12" t="s">
+      <c r="F36" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="G36" s="11" t="s">
+      <c r="G36" s="17" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="37" ht="101" spans="1:7">
-      <c r="A37" s="11">
+      <c r="A37" s="17">
         <v>36</v>
       </c>
-      <c r="B37" s="12" t="s">
+      <c r="B37" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="C37" s="12" t="s">
+      <c r="C37" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="D37" s="12" t="s">
+      <c r="D37" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="E37" s="12" t="s">
+      <c r="E37" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="F37" s="12" t="s">
+      <c r="F37" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="G37" s="11"/>
+      <c r="G37" s="17"/>
     </row>
     <row r="38" ht="101" spans="1:7">
-      <c r="A38" s="11">
+      <c r="A38" s="17">
         <v>37</v>
       </c>
-      <c r="B38" s="12" t="s">
+      <c r="B38" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="C38" s="12" t="s">
+      <c r="C38" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="D38" s="12" t="s">
+      <c r="D38" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="E38" s="12" t="s">
+      <c r="E38" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="F38" s="12" t="s">
+      <c r="F38" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="G38" s="11"/>
+      <c r="G38" s="17"/>
     </row>
     <row r="39" ht="118" spans="1:7">
-      <c r="A39" s="11">
+      <c r="A39" s="17">
         <v>38</v>
       </c>
-      <c r="B39" s="12" t="s">
+      <c r="B39" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="C39" s="12" t="s">
+      <c r="C39" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="D39" s="12" t="s">
+      <c r="D39" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="E39" s="12" t="s">
+      <c r="E39" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="F39" s="12" t="s">
+      <c r="F39" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="G39" s="11"/>
+      <c r="G39" s="17"/>
     </row>
     <row r="40" ht="51" spans="1:7">
-      <c r="A40" s="11">
+      <c r="A40" s="17">
         <v>39</v>
       </c>
-      <c r="B40" s="12" t="s">
+      <c r="B40" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="C40" s="12" t="s">
+      <c r="C40" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="D40" s="12" t="s">
+      <c r="D40" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="E40" s="12" t="s">
+      <c r="E40" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="F40" s="12" t="s">
+      <c r="F40" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="G40" s="11"/>
+      <c r="G40" s="17"/>
     </row>
     <row r="41" ht="101" spans="1:7">
-      <c r="A41" s="11">
+      <c r="A41" s="17">
         <v>40</v>
       </c>
-      <c r="B41" s="12" t="s">
+      <c r="B41" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="C41" s="12" t="s">
+      <c r="C41" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="D41" s="12" t="s">
+      <c r="D41" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="E41" s="12" t="s">
+      <c r="E41" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="F41" s="12" t="s">
+      <c r="F41" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="G41" s="12" t="s">
+      <c r="G41" s="18" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="42" ht="84" spans="1:7">
-      <c r="A42" s="11">
+      <c r="A42" s="17">
         <v>41</v>
       </c>
-      <c r="B42" s="12" t="s">
+      <c r="B42" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="C42" s="12" t="s">
+      <c r="C42" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="D42" s="12" t="s">
+      <c r="D42" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="E42" s="12" t="s">
+      <c r="E42" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="F42" s="12" t="s">
+      <c r="F42" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="G42" s="12" t="s">
+      <c r="G42" s="18" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="43" ht="84" spans="1:7">
-      <c r="A43" s="11">
+      <c r="A43" s="17">
         <v>42</v>
       </c>
-      <c r="B43" s="12" t="s">
+      <c r="B43" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="C43" s="12" t="s">
+      <c r="C43" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="D43" s="12" t="s">
+      <c r="D43" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="E43" s="12" t="s">
+      <c r="E43" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="F43" s="12" t="s">
+      <c r="F43" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="G43" s="12" t="s">
+      <c r="G43" s="18" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="44" ht="118" spans="1:7">
-      <c r="A44" s="11">
+      <c r="A44" s="17">
         <v>43</v>
       </c>
-      <c r="B44" s="12" t="s">
+      <c r="B44" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="C44" s="12" t="s">
+      <c r="C44" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="D44" s="12" t="s">
+      <c r="D44" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="E44" s="12" t="s">
+      <c r="E44" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="F44" s="12" t="s">
+      <c r="F44" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="G44" s="12" t="s">
+      <c r="G44" s="18" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="45" ht="101" spans="1:7">
-      <c r="A45" s="11">
+      <c r="A45" s="17">
         <v>44</v>
       </c>
-      <c r="B45" s="12" t="s">
+      <c r="B45" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="C45" s="12" t="s">
+      <c r="C45" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="D45" s="12" t="s">
+      <c r="D45" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="E45" s="12" t="s">
+      <c r="E45" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="F45" s="12" t="s">
+      <c r="F45" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="G45" s="12" t="s">
+      <c r="G45" s="18" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="46" ht="118" spans="1:7">
-      <c r="A46" s="11">
+      <c r="A46" s="17">
         <v>45</v>
       </c>
-      <c r="B46" s="12" t="s">
+      <c r="B46" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="C46" s="12" t="s">
+      <c r="C46" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="D46" s="12" t="s">
+      <c r="D46" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="E46" s="12" t="s">
+      <c r="E46" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="F46" s="12" t="s">
+      <c r="F46" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="G46" s="12" t="s">
+      <c r="G46" s="18" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="47" ht="118" spans="1:7">
-      <c r="A47" s="11">
+      <c r="A47" s="17">
         <v>46</v>
       </c>
-      <c r="B47" s="12" t="s">
+      <c r="B47" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="C47" s="12" t="s">
+      <c r="C47" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="D47" s="12" t="s">
+      <c r="D47" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="E47" s="12" t="s">
+      <c r="E47" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="F47" s="12" t="s">
+      <c r="F47" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="G47" s="12" t="s">
+      <c r="G47" s="18" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="48" ht="34" spans="1:7">
-      <c r="A48" s="11">
+      <c r="A48" s="17">
         <v>47</v>
       </c>
-      <c r="B48" s="12" t="s">
+      <c r="B48" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="C48" s="12" t="s">
+      <c r="C48" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="D48" s="12" t="s">
+      <c r="D48" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="E48" s="12" t="s">
+      <c r="E48" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="F48" s="12" t="s">
+      <c r="F48" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="G48" s="12" t="s">
+      <c r="G48" s="18" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="49" ht="34" spans="1:7">
-      <c r="A49" s="11">
+      <c r="A49" s="17">
         <v>48</v>
       </c>
-      <c r="B49" s="12" t="s">
+      <c r="B49" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="C49" s="12" t="s">
+      <c r="C49" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="D49" s="12" t="s">
+      <c r="D49" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="E49" s="12" t="s">
+      <c r="E49" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="F49" s="12" t="s">
+      <c r="F49" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="G49" s="12" t="s">
+      <c r="G49" s="18" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="50" ht="135" spans="1:7">
-      <c r="A50" s="11">
+      <c r="A50" s="17">
         <v>49</v>
       </c>
-      <c r="B50" s="12" t="s">
+      <c r="B50" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="C50" s="12" t="s">
+      <c r="C50" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="D50" s="12" t="s">
+      <c r="D50" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="E50" s="12" t="s">
+      <c r="E50" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="F50" s="12" t="s">
+      <c r="F50" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="G50" s="12" t="s">
+      <c r="G50" s="18" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="51" ht="34" spans="1:7">
-      <c r="A51" s="11">
+      <c r="A51" s="17">
         <v>50</v>
       </c>
-      <c r="B51" s="12" t="s">
+      <c r="B51" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="C51" s="12" t="s">
+      <c r="C51" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="D51" s="12" t="s">
+      <c r="D51" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="E51" s="12" t="s">
+      <c r="E51" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="F51" s="12" t="s">
+      <c r="F51" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="G51" s="12" t="s">
+      <c r="G51" s="18" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="52" ht="68" spans="1:7">
-      <c r="A52" s="11">
+      <c r="A52" s="17">
         <v>51</v>
       </c>
-      <c r="B52" s="12" t="s">
+      <c r="B52" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="C52" s="12" t="s">
+      <c r="C52" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="D52" s="12" t="s">
+      <c r="D52" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="E52" s="12" t="s">
+      <c r="E52" s="18" t="s">
         <v>98</v>
       </c>
-      <c r="F52" s="11" t="s">
+      <c r="F52" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="G52" s="11" t="s">
+      <c r="G52" s="17" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="53" ht="68" spans="1:7">
-      <c r="A53" s="11">
+      <c r="A53" s="17">
         <v>52</v>
       </c>
-      <c r="B53" s="12" t="s">
+      <c r="B53" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="C53" s="12" t="s">
+      <c r="C53" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="D53" s="12" t="s">
+      <c r="D53" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="E53" s="12" t="s">
+      <c r="E53" s="18" t="s">
         <v>98</v>
       </c>
-      <c r="F53" s="11"/>
-      <c r="G53" s="11"/>
+      <c r="F53" s="17"/>
+      <c r="G53" s="17"/>
     </row>
     <row r="54" ht="68" spans="1:7">
-      <c r="A54" s="11">
+      <c r="A54" s="17">
         <v>53</v>
       </c>
-      <c r="B54" s="12" t="s">
+      <c r="B54" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="C54" s="12" t="s">
+      <c r="C54" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="D54" s="12" t="s">
+      <c r="D54" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="E54" s="12" t="s">
+      <c r="E54" s="18" t="s">
         <v>98</v>
       </c>
-      <c r="F54" s="11"/>
-      <c r="G54" s="11"/>
+      <c r="F54" s="17"/>
+      <c r="G54" s="17"/>
     </row>
     <row r="55" ht="68" spans="1:7">
-      <c r="A55" s="11">
+      <c r="A55" s="17">
         <v>54</v>
       </c>
-      <c r="B55" s="12" t="s">
+      <c r="B55" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="C55" s="12" t="s">
+      <c r="C55" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="D55" s="12" t="s">
+      <c r="D55" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="E55" s="12" t="s">
+      <c r="E55" s="18" t="s">
         <v>98</v>
       </c>
-      <c r="F55" s="11"/>
-      <c r="G55" s="11"/>
+      <c r="F55" s="17"/>
+      <c r="G55" s="17"/>
     </row>
     <row r="56" ht="68" spans="1:7">
-      <c r="A56" s="11">
+      <c r="A56" s="17">
         <v>55</v>
       </c>
-      <c r="B56" s="12" t="s">
+      <c r="B56" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="C56" s="12" t="s">
+      <c r="C56" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="D56" s="12" t="s">
+      <c r="D56" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="E56" s="12" t="s">
+      <c r="E56" s="18" t="s">
         <v>98</v>
       </c>
-      <c r="F56" s="11"/>
-      <c r="G56" s="11"/>
+      <c r="F56" s="17"/>
+      <c r="G56" s="17"/>
     </row>
     <row r="57" ht="68" spans="1:7">
-      <c r="A57" s="11">
+      <c r="A57" s="17">
         <v>56</v>
       </c>
-      <c r="B57" s="12" t="s">
+      <c r="B57" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="C57" s="12" t="s">
+      <c r="C57" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="D57" s="12" t="s">
+      <c r="D57" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="E57" s="12" t="s">
+      <c r="E57" s="18" t="s">
         <v>98</v>
       </c>
-      <c r="F57" s="11"/>
-      <c r="G57" s="11"/>
+      <c r="F57" s="17"/>
+      <c r="G57" s="17"/>
     </row>
     <row r="58" ht="68" spans="1:7">
-      <c r="A58" s="11">
+      <c r="A58" s="17">
         <v>57</v>
       </c>
-      <c r="B58" s="12" t="s">
+      <c r="B58" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="C58" s="12" t="s">
+      <c r="C58" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="D58" s="12" t="s">
+      <c r="D58" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="E58" s="12" t="s">
+      <c r="E58" s="18" t="s">
         <v>98</v>
       </c>
-      <c r="F58" s="11"/>
-      <c r="G58" s="11"/>
+      <c r="F58" s="17"/>
+      <c r="G58" s="17"/>
     </row>
     <row r="59" ht="68" spans="1:7">
-      <c r="A59" s="11">
+      <c r="A59" s="17">
         <v>58</v>
       </c>
-      <c r="B59" s="12" t="s">
+      <c r="B59" s="18" t="s">
         <v>106</v>
       </c>
-      <c r="C59" s="12" t="s">
+      <c r="C59" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="D59" s="12" t="s">
+      <c r="D59" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="E59" s="12" t="s">
+      <c r="E59" s="18" t="s">
         <v>98</v>
       </c>
-      <c r="F59" s="11"/>
-      <c r="G59" s="11"/>
+      <c r="F59" s="17"/>
+      <c r="G59" s="17"/>
     </row>
     <row r="60" ht="68" spans="1:7">
-      <c r="A60" s="11">
+      <c r="A60" s="17">
         <v>59</v>
       </c>
-      <c r="B60" s="12" t="s">
+      <c r="B60" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="C60" s="12" t="s">
+      <c r="C60" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="D60" s="12" t="s">
+      <c r="D60" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="E60" s="12" t="s">
+      <c r="E60" s="18" t="s">
         <v>98</v>
       </c>
-      <c r="F60" s="11"/>
-      <c r="G60" s="11"/>
+      <c r="F60" s="17"/>
+      <c r="G60" s="17"/>
     </row>
     <row r="61" ht="68" spans="1:7">
-      <c r="A61" s="11">
+      <c r="A61" s="17">
         <v>60</v>
       </c>
-      <c r="B61" s="12" t="s">
+      <c r="B61" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="C61" s="12" t="s">
+      <c r="C61" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="D61" s="12" t="s">
+      <c r="D61" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="E61" s="12" t="s">
+      <c r="E61" s="18" t="s">
         <v>98</v>
       </c>
-      <c r="F61" s="11"/>
-      <c r="G61" s="11"/>
+      <c r="F61" s="17"/>
+      <c r="G61" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -4135,1566 +4260,1566 @@
   <dimension ref="A1:K84"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="1" width="5.140625" style="11" customWidth="1"/>
-    <col min="2" max="2" width="34.140625" style="12" customWidth="1"/>
-    <col min="3" max="3" width="26.859375" style="12" customWidth="1"/>
-    <col min="4" max="4" width="24.859375" style="12" customWidth="1"/>
-    <col min="5" max="5" width="26.140625" style="12" customWidth="1"/>
-    <col min="6" max="6" width="26.2890625" style="12" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="5.140625" style="17" customWidth="1"/>
+    <col min="2" max="2" width="34.140625" style="18" customWidth="1"/>
+    <col min="3" max="3" width="26.859375" style="18" customWidth="1"/>
+    <col min="4" max="4" width="24.859375" style="18" customWidth="1"/>
+    <col min="5" max="5" width="26.140625" style="18" customWidth="1"/>
+    <col min="6" max="6" width="26.2890625" style="18" customWidth="1"/>
+    <col min="7" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:6">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="10" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" s="10" customFormat="1" ht="20" customHeight="1" spans="1:6">
-      <c r="A2" s="13" t="s">
+    <row r="2" s="16" customFormat="1" ht="20" customHeight="1" spans="1:6">
+      <c r="A2" s="19" t="s">
         <v>109</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="18"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="24"/>
     </row>
     <row r="3" ht="118" customHeight="1" spans="1:11">
-      <c r="A3" s="11">
+      <c r="A3" s="17">
         <v>1</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="D3" s="21" t="s">
         <v>112</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="25" t="s">
         <v>112</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
+      <c r="I3" s="5"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="5"/>
     </row>
     <row r="4" ht="101" customHeight="1" spans="1:11">
-      <c r="A4" s="11">
+      <c r="A4" s="17">
         <v>2</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="D4" s="21" t="s">
         <v>112</v>
       </c>
-      <c r="E4" s="20"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
+      <c r="E4" s="26"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="5"/>
     </row>
     <row r="5" ht="122" customHeight="1" spans="1:11">
-      <c r="A5" s="11">
+      <c r="A5" s="17">
         <v>3</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="18" t="s">
         <v>115</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="21" t="s">
         <v>112</v>
       </c>
-      <c r="E5" s="20"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
+      <c r="E5" s="26"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="5"/>
     </row>
     <row r="6" ht="84" spans="1:5">
-      <c r="A6" s="11">
+      <c r="A6" s="17">
         <v>4</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="18" t="s">
         <v>116</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="D6" s="21" t="s">
         <v>112</v>
       </c>
-      <c r="E6" s="20"/>
+      <c r="E6" s="26"/>
     </row>
     <row r="7" customFormat="1" ht="84" spans="1:6">
-      <c r="A7" s="11">
+      <c r="A7" s="17">
         <v>5</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="18" t="s">
         <v>117</v>
       </c>
-      <c r="D7" s="15" t="s">
+      <c r="D7" s="21" t="s">
         <v>112</v>
       </c>
-      <c r="E7" s="21"/>
-      <c r="F7" s="12"/>
+      <c r="E7" s="27"/>
+      <c r="F7" s="18"/>
     </row>
     <row r="8" customFormat="1" ht="84" spans="1:6">
-      <c r="A8" s="11">
+      <c r="A8" s="17">
         <v>6</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="18" t="s">
         <v>118</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="D8" s="15" t="s">
+      <c r="D8" s="21" t="s">
         <v>119</v>
       </c>
-      <c r="E8" s="19" t="s">
+      <c r="E8" s="25" t="s">
         <v>119</v>
       </c>
-      <c r="F8" s="12"/>
+      <c r="F8" s="18"/>
     </row>
     <row r="9" customFormat="1" ht="84" spans="1:6">
-      <c r="A9" s="11">
+      <c r="A9" s="17">
         <v>7</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="18" t="s">
         <v>118</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="D9" s="15" t="s">
+      <c r="D9" s="21" t="s">
         <v>119</v>
       </c>
-      <c r="E9" s="20"/>
-      <c r="F9" s="12"/>
+      <c r="E9" s="26"/>
+      <c r="F9" s="18"/>
     </row>
     <row r="10" customFormat="1" ht="84" spans="1:6">
-      <c r="A10" s="11">
+      <c r="A10" s="17">
         <v>8</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="18" t="s">
         <v>118</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="18" t="s">
         <v>115</v>
       </c>
-      <c r="D10" s="15" t="s">
+      <c r="D10" s="21" t="s">
         <v>119</v>
       </c>
-      <c r="E10" s="20"/>
-      <c r="F10" s="12"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="18"/>
     </row>
     <row r="11" customFormat="1" ht="84" spans="1:6">
-      <c r="A11" s="11">
+      <c r="A11" s="17">
         <v>9</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="18" t="s">
         <v>118</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="C11" s="18" t="s">
         <v>116</v>
       </c>
-      <c r="D11" s="15" t="s">
+      <c r="D11" s="21" t="s">
         <v>119</v>
       </c>
-      <c r="E11" s="20"/>
-      <c r="F11" s="12"/>
+      <c r="E11" s="26"/>
+      <c r="F11" s="18"/>
     </row>
     <row r="12" customFormat="1" ht="84" spans="1:6">
-      <c r="A12" s="11">
+      <c r="A12" s="17">
         <v>10</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="18" t="s">
         <v>118</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="18" t="s">
         <v>117</v>
       </c>
-      <c r="D12" s="15" t="s">
+      <c r="D12" s="21" t="s">
         <v>119</v>
       </c>
-      <c r="E12" s="21"/>
-      <c r="F12" s="12"/>
+      <c r="E12" s="27"/>
+      <c r="F12" s="18"/>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="16" t="s">
+      <c r="A13" s="22" t="s">
         <v>120</v>
       </c>
-      <c r="B13" s="16"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
+      <c r="B13" s="22"/>
+      <c r="C13" s="22"/>
+      <c r="D13" s="22"/>
+      <c r="E13" s="22"/>
+      <c r="F13" s="22"/>
     </row>
     <row r="14" ht="84" spans="1:6">
-      <c r="A14" s="11">
+      <c r="A14" s="17">
         <v>11</v>
       </c>
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="18" t="s">
         <v>121</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="C14" s="18" t="s">
         <v>122</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D14" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="E14" s="12" t="s">
+      <c r="E14" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="F14" s="12" t="s">
+      <c r="F14" s="18" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="15" ht="68" spans="1:6">
-      <c r="A15" s="11">
+      <c r="A15" s="17">
         <v>12</v>
       </c>
-      <c r="B15" s="12" t="s">
+      <c r="B15" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="C15" s="12" t="s">
+      <c r="C15" s="18" t="s">
         <v>122</v>
       </c>
-      <c r="D15" s="12" t="s">
+      <c r="D15" s="18" t="s">
         <v>127</v>
       </c>
-      <c r="E15" s="12" t="s">
+      <c r="E15" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="F15" s="12" t="s">
+      <c r="F15" s="18" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="16" ht="68" spans="1:6">
-      <c r="A16" s="11">
+      <c r="A16" s="17">
         <v>13</v>
       </c>
-      <c r="B16" s="12" t="s">
+      <c r="B16" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="C16" s="12" t="s">
+      <c r="C16" s="18" t="s">
         <v>122</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="D16" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="E16" s="12" t="s">
+      <c r="E16" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="F16" s="12" t="s">
+      <c r="F16" s="18" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="17" ht="68" spans="1:6">
-      <c r="A17" s="11">
+      <c r="A17" s="17">
         <v>14</v>
       </c>
-      <c r="B17" s="12" t="s">
+      <c r="B17" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="C17" s="12" t="s">
+      <c r="C17" s="18" t="s">
         <v>122</v>
       </c>
-      <c r="D17" s="12" t="s">
+      <c r="D17" s="18" t="s">
         <v>135</v>
       </c>
-      <c r="E17" s="12" t="s">
+      <c r="E17" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="F17" s="12" t="s">
+      <c r="F17" s="18" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="18" ht="90" customHeight="1" spans="1:6">
-      <c r="A18" s="11">
+      <c r="A18" s="17">
         <v>15</v>
       </c>
-      <c r="B18" s="17" t="s">
+      <c r="B18" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="C18" s="17" t="s">
+      <c r="C18" s="23" t="s">
         <v>138</v>
       </c>
-      <c r="D18" s="17" t="s">
+      <c r="D18" s="23" t="s">
         <v>139</v>
       </c>
-      <c r="E18" s="17" t="s">
+      <c r="E18" s="23" t="s">
         <v>140</v>
       </c>
-      <c r="F18" s="17" t="s">
+      <c r="F18" s="23" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="19" ht="66" customHeight="1" spans="1:6">
-      <c r="A19" s="11">
+      <c r="A19" s="17">
         <v>16</v>
       </c>
-      <c r="B19" s="17" t="s">
+      <c r="B19" s="23" t="s">
         <v>142</v>
       </c>
-      <c r="C19" s="17" t="s">
+      <c r="C19" s="23" t="s">
         <v>138</v>
       </c>
-      <c r="D19" s="17" t="s">
+      <c r="D19" s="23" t="s">
         <v>143</v>
       </c>
-      <c r="E19" s="17" t="s">
+      <c r="E19" s="23" t="s">
         <v>128</v>
       </c>
-      <c r="F19" s="17" t="s">
+      <c r="F19" s="23" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="20" ht="79" customHeight="1" spans="1:6">
-      <c r="A20" s="11">
+      <c r="A20" s="17">
         <v>17</v>
       </c>
-      <c r="B20" s="17" t="s">
+      <c r="B20" s="23" t="s">
         <v>145</v>
       </c>
-      <c r="C20" s="17" t="s">
+      <c r="C20" s="23" t="s">
         <v>138</v>
       </c>
-      <c r="D20" s="17" t="s">
+      <c r="D20" s="23" t="s">
         <v>146</v>
       </c>
-      <c r="E20" s="17" t="s">
+      <c r="E20" s="23" t="s">
         <v>147</v>
       </c>
-      <c r="F20" s="17" t="s">
+      <c r="F20" s="23" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="21" ht="80" customHeight="1" spans="1:6">
-      <c r="A21" s="11">
+      <c r="A21" s="17">
         <v>18</v>
       </c>
-      <c r="B21" s="17" t="s">
+      <c r="B21" s="23" t="s">
         <v>149</v>
       </c>
-      <c r="C21" s="17" t="s">
+      <c r="C21" s="23" t="s">
         <v>138</v>
       </c>
-      <c r="D21" s="17" t="s">
+      <c r="D21" s="23" t="s">
         <v>150</v>
       </c>
-      <c r="E21" s="17" t="s">
+      <c r="E21" s="23" t="s">
         <v>132</v>
       </c>
-      <c r="F21" s="17" t="s">
+      <c r="F21" s="23" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="22" ht="17" customHeight="1" spans="1:6">
-      <c r="A22" s="16" t="s">
+      <c r="A22" s="22" t="s">
         <v>152</v>
       </c>
-      <c r="B22" s="16"/>
-      <c r="C22" s="16"/>
-      <c r="D22" s="16"/>
-      <c r="E22" s="16"/>
-      <c r="F22" s="16"/>
+      <c r="B22" s="22"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="22"/>
+      <c r="F22" s="22"/>
     </row>
     <row r="23" ht="84" spans="1:6">
-      <c r="A23" s="11">
+      <c r="A23" s="17">
         <v>19</v>
       </c>
-      <c r="B23" s="12" t="s">
+      <c r="B23" s="18" t="s">
         <v>121</v>
       </c>
-      <c r="C23" s="12" t="s">
+      <c r="C23" s="18" t="s">
         <v>122</v>
       </c>
-      <c r="D23" s="12" t="s">
+      <c r="D23" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="E23" s="12" t="s">
+      <c r="E23" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="F23" s="12" t="s">
+      <c r="F23" s="18" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="24" ht="68" spans="1:6">
-      <c r="A24" s="11">
+      <c r="A24" s="17">
         <v>20</v>
       </c>
-      <c r="B24" s="12" t="s">
+      <c r="B24" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="C24" s="12" t="s">
+      <c r="C24" s="18" t="s">
         <v>122</v>
       </c>
-      <c r="D24" s="12" t="s">
+      <c r="D24" s="18" t="s">
         <v>127</v>
       </c>
-      <c r="E24" s="12" t="s">
+      <c r="E24" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="F24" s="12" t="s">
+      <c r="F24" s="18" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="25" ht="68" spans="1:6">
-      <c r="A25" s="11">
+      <c r="A25" s="17">
         <v>21</v>
       </c>
-      <c r="B25" s="12" t="s">
+      <c r="B25" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="C25" s="12" t="s">
+      <c r="C25" s="18" t="s">
         <v>122</v>
       </c>
-      <c r="D25" s="12" t="s">
+      <c r="D25" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="E25" s="12" t="s">
+      <c r="E25" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="F25" s="12" t="s">
+      <c r="F25" s="18" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="26" ht="68" spans="1:6">
-      <c r="A26" s="11">
+      <c r="A26" s="17">
         <v>22</v>
       </c>
-      <c r="B26" s="12" t="s">
+      <c r="B26" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="C26" s="12" t="s">
+      <c r="C26" s="18" t="s">
         <v>122</v>
       </c>
-      <c r="D26" s="12" t="s">
+      <c r="D26" s="18" t="s">
         <v>135</v>
       </c>
-      <c r="E26" s="12" t="s">
+      <c r="E26" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="F26" s="12" t="s">
+      <c r="F26" s="18" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="27" ht="68" spans="1:6">
-      <c r="A27" s="11">
+      <c r="A27" s="17">
         <v>23</v>
       </c>
-      <c r="B27" s="17" t="s">
+      <c r="B27" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="C27" s="17" t="s">
+      <c r="C27" s="23" t="s">
         <v>138</v>
       </c>
-      <c r="D27" s="17" t="s">
+      <c r="D27" s="23" t="s">
         <v>154</v>
       </c>
-      <c r="E27" s="17" t="s">
+      <c r="E27" s="23" t="s">
         <v>155</v>
       </c>
-      <c r="F27" s="17" t="s">
+      <c r="F27" s="23" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="28" ht="51" spans="1:6">
-      <c r="A28" s="11">
+      <c r="A28" s="17">
         <v>24</v>
       </c>
-      <c r="B28" s="17" t="s">
+      <c r="B28" s="23" t="s">
         <v>142</v>
       </c>
-      <c r="C28" s="17" t="s">
+      <c r="C28" s="23" t="s">
         <v>138</v>
       </c>
-      <c r="D28" s="17" t="s">
+      <c r="D28" s="23" t="s">
         <v>143</v>
       </c>
-      <c r="E28" s="17" t="s">
+      <c r="E28" s="23" t="s">
         <v>128</v>
       </c>
-      <c r="F28" s="17" t="s">
+      <c r="F28" s="23" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="29" ht="68" spans="1:6">
-      <c r="A29" s="11">
+      <c r="A29" s="17">
         <v>25</v>
       </c>
-      <c r="B29" s="17" t="s">
+      <c r="B29" s="23" t="s">
         <v>145</v>
       </c>
-      <c r="C29" s="17" t="s">
+      <c r="C29" s="23" t="s">
         <v>138</v>
       </c>
-      <c r="D29" s="17" t="s">
+      <c r="D29" s="23" t="s">
         <v>146</v>
       </c>
-      <c r="E29" s="17" t="s">
+      <c r="E29" s="23" t="s">
         <v>132</v>
       </c>
-      <c r="F29" s="17" t="s">
+      <c r="F29" s="23" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="30" ht="68" spans="1:6">
-      <c r="A30" s="11">
+      <c r="A30" s="17">
         <v>26</v>
       </c>
-      <c r="B30" s="17" t="s">
+      <c r="B30" s="23" t="s">
         <v>149</v>
       </c>
-      <c r="C30" s="17" t="s">
+      <c r="C30" s="23" t="s">
         <v>138</v>
       </c>
-      <c r="D30" s="17" t="s">
+      <c r="D30" s="23" t="s">
         <v>150</v>
       </c>
-      <c r="E30" s="17" t="s">
+      <c r="E30" s="23" t="s">
         <v>132</v>
       </c>
-      <c r="F30" s="17" t="s">
+      <c r="F30" s="23" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="31" spans="1:6">
-      <c r="A31" s="16" t="s">
+      <c r="A31" s="22" t="s">
         <v>159</v>
       </c>
-      <c r="B31" s="16"/>
-      <c r="C31" s="16"/>
-      <c r="D31" s="16"/>
-      <c r="E31" s="16"/>
-      <c r="F31" s="16"/>
+      <c r="B31" s="22"/>
+      <c r="C31" s="22"/>
+      <c r="D31" s="22"/>
+      <c r="E31" s="22"/>
+      <c r="F31" s="22"/>
     </row>
     <row r="32" ht="68" spans="1:6">
-      <c r="A32" s="11">
+      <c r="A32" s="17">
         <v>27</v>
       </c>
-      <c r="B32" s="17" t="s">
+      <c r="B32" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="C32" s="17" t="s">
+      <c r="C32" s="23" t="s">
         <v>138</v>
       </c>
-      <c r="D32" s="17" t="s">
+      <c r="D32" s="23" t="s">
         <v>154</v>
       </c>
-      <c r="E32" s="17" t="s">
+      <c r="E32" s="23" t="s">
         <v>160</v>
       </c>
-      <c r="F32" s="17" t="s">
+      <c r="F32" s="23" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="33" ht="51" spans="1:6">
-      <c r="A33" s="11">
+      <c r="A33" s="17">
         <v>28</v>
       </c>
-      <c r="B33" s="17" t="s">
+      <c r="B33" s="23" t="s">
         <v>142</v>
       </c>
-      <c r="C33" s="17" t="s">
+      <c r="C33" s="23" t="s">
         <v>138</v>
       </c>
-      <c r="D33" s="17" t="s">
+      <c r="D33" s="23" t="s">
         <v>143</v>
       </c>
-      <c r="E33" s="17" t="s">
+      <c r="E33" s="23" t="s">
         <v>128</v>
       </c>
-      <c r="F33" s="17" t="s">
+      <c r="F33" s="23" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="34" ht="68" spans="1:6">
-      <c r="A34" s="11">
+      <c r="A34" s="17">
         <v>29</v>
       </c>
-      <c r="B34" s="17" t="s">
+      <c r="B34" s="23" t="s">
         <v>145</v>
       </c>
-      <c r="C34" s="17" t="s">
+      <c r="C34" s="23" t="s">
         <v>138</v>
       </c>
-      <c r="D34" s="17" t="s">
+      <c r="D34" s="23" t="s">
         <v>161</v>
       </c>
-      <c r="E34" s="17" t="s">
+      <c r="E34" s="23" t="s">
         <v>132</v>
       </c>
-      <c r="F34" s="17" t="s">
+      <c r="F34" s="23" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="35" ht="68" spans="1:6">
-      <c r="A35" s="11">
+      <c r="A35" s="17">
         <v>30</v>
       </c>
-      <c r="B35" s="17" t="s">
+      <c r="B35" s="23" t="s">
         <v>149</v>
       </c>
-      <c r="C35" s="17" t="s">
+      <c r="C35" s="23" t="s">
         <v>138</v>
       </c>
-      <c r="D35" s="17" t="s">
+      <c r="D35" s="23" t="s">
         <v>162</v>
       </c>
-      <c r="E35" s="17" t="s">
+      <c r="E35" s="23" t="s">
         <v>132</v>
       </c>
-      <c r="F35" s="17" t="s">
+      <c r="F35" s="23" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="36" spans="1:6">
-      <c r="A36" s="16" t="s">
+      <c r="A36" s="22" t="s">
         <v>163</v>
       </c>
-      <c r="B36" s="16"/>
-      <c r="C36" s="16"/>
-      <c r="D36" s="16"/>
-      <c r="E36" s="16"/>
-      <c r="F36" s="16"/>
+      <c r="B36" s="22"/>
+      <c r="C36" s="22"/>
+      <c r="D36" s="22"/>
+      <c r="E36" s="22"/>
+      <c r="F36" s="22"/>
     </row>
     <row r="37" ht="84" spans="1:6">
-      <c r="A37" s="11">
+      <c r="A37" s="17">
         <v>31</v>
       </c>
-      <c r="B37" s="17" t="s">
+      <c r="B37" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="C37" s="17" t="s">
+      <c r="C37" s="23" t="s">
         <v>138</v>
       </c>
-      <c r="D37" s="17" t="s">
+      <c r="D37" s="23" t="s">
         <v>164</v>
       </c>
-      <c r="E37" s="17" t="s">
+      <c r="E37" s="23" t="s">
         <v>165</v>
       </c>
-      <c r="F37" s="17" t="s">
+      <c r="F37" s="23" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="38" ht="68" spans="1:6">
-      <c r="A38" s="11">
+      <c r="A38" s="17">
         <v>32</v>
       </c>
-      <c r="B38" s="17" t="s">
+      <c r="B38" s="23" t="s">
         <v>142</v>
       </c>
-      <c r="C38" s="17" t="s">
+      <c r="C38" s="23" t="s">
         <v>138</v>
       </c>
-      <c r="D38" s="17" t="s">
+      <c r="D38" s="23" t="s">
         <v>166</v>
       </c>
-      <c r="E38" s="17" t="s">
+      <c r="E38" s="23" t="s">
         <v>167</v>
       </c>
-      <c r="F38" s="17" t="s">
+      <c r="F38" s="23" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="39" ht="68" spans="1:6">
-      <c r="A39" s="11">
+      <c r="A39" s="17">
         <v>33</v>
       </c>
-      <c r="B39" s="17" t="s">
+      <c r="B39" s="23" t="s">
         <v>145</v>
       </c>
-      <c r="C39" s="17" t="s">
+      <c r="C39" s="23" t="s">
         <v>138</v>
       </c>
-      <c r="D39" s="17" t="s">
+      <c r="D39" s="23" t="s">
         <v>168</v>
       </c>
-      <c r="E39" s="17" t="s">
+      <c r="E39" s="23" t="s">
         <v>169</v>
       </c>
-      <c r="F39" s="17" t="s">
+      <c r="F39" s="23" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="40" ht="68" spans="1:6">
-      <c r="A40" s="11">
+      <c r="A40" s="17">
         <v>34</v>
       </c>
-      <c r="B40" s="17" t="s">
+      <c r="B40" s="23" t="s">
         <v>149</v>
       </c>
-      <c r="C40" s="17" t="s">
+      <c r="C40" s="23" t="s">
         <v>138</v>
       </c>
-      <c r="D40" s="17" t="s">
+      <c r="D40" s="23" t="s">
         <v>170</v>
       </c>
-      <c r="E40" s="17" t="s">
+      <c r="E40" s="23" t="s">
         <v>169</v>
       </c>
-      <c r="F40" s="17" t="s">
+      <c r="F40" s="23" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="41" spans="1:6">
-      <c r="A41" s="16" t="s">
+      <c r="A41" s="22" t="s">
         <v>171</v>
       </c>
-      <c r="B41" s="16"/>
-      <c r="C41" s="16"/>
-      <c r="D41" s="16"/>
-      <c r="E41" s="16"/>
-      <c r="F41" s="16"/>
+      <c r="B41" s="22"/>
+      <c r="C41" s="22"/>
+      <c r="D41" s="22"/>
+      <c r="E41" s="22"/>
+      <c r="F41" s="22"/>
     </row>
     <row r="42" ht="84" spans="1:6">
-      <c r="A42" s="11">
+      <c r="A42" s="17">
         <v>35</v>
       </c>
-      <c r="B42" s="12" t="s">
+      <c r="B42" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="C42" s="12" t="s">
+      <c r="C42" s="18" t="s">
         <v>173</v>
       </c>
-      <c r="D42" s="17" t="s">
+      <c r="D42" s="23" t="s">
         <v>174</v>
       </c>
-      <c r="E42" s="12" t="s">
+      <c r="E42" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="F42" s="12" t="s">
+      <c r="F42" s="18" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="43" ht="68" spans="1:6">
-      <c r="A43" s="11">
+      <c r="A43" s="17">
         <v>36</v>
       </c>
-      <c r="B43" s="12" t="s">
+      <c r="B43" s="18" t="s">
         <v>176</v>
       </c>
-      <c r="C43" s="12" t="s">
+      <c r="C43" s="18" t="s">
         <v>173</v>
       </c>
-      <c r="D43" s="17" t="s">
+      <c r="D43" s="23" t="s">
         <v>177</v>
       </c>
-      <c r="E43" s="12" t="s">
+      <c r="E43" s="18" t="s">
         <v>178</v>
       </c>
-      <c r="F43" s="12" t="s">
+      <c r="F43" s="18" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="44" ht="68" spans="1:6">
-      <c r="A44" s="11">
+      <c r="A44" s="17">
         <v>37</v>
       </c>
-      <c r="B44" s="12" t="s">
+      <c r="B44" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="C44" s="12" t="s">
+      <c r="C44" s="18" t="s">
         <v>173</v>
       </c>
-      <c r="D44" s="17" t="s">
+      <c r="D44" s="23" t="s">
         <v>180</v>
       </c>
-      <c r="E44" s="12" t="s">
+      <c r="E44" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="F44" s="12" t="s">
+      <c r="F44" s="18" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="45" ht="68" spans="1:6">
-      <c r="A45" s="11">
+      <c r="A45" s="17">
         <v>38</v>
       </c>
-      <c r="B45" s="12" t="s">
+      <c r="B45" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="C45" s="12" t="s">
+      <c r="C45" s="18" t="s">
         <v>173</v>
       </c>
-      <c r="D45" s="17" t="s">
+      <c r="D45" s="23" t="s">
         <v>182</v>
       </c>
-      <c r="E45" s="12" t="s">
+      <c r="E45" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="F45" s="12" t="s">
+      <c r="F45" s="18" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="46" ht="68" spans="1:6">
-      <c r="A46" s="11">
+      <c r="A46" s="17">
         <v>39</v>
       </c>
-      <c r="B46" s="17" t="s">
+      <c r="B46" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="C46" s="17" t="s">
+      <c r="C46" s="23" t="s">
         <v>138</v>
       </c>
-      <c r="D46" s="17" t="s">
+      <c r="D46" s="23" t="s">
         <v>184</v>
       </c>
-      <c r="E46" s="17" t="s">
+      <c r="E46" s="23" t="s">
         <v>160</v>
       </c>
-      <c r="F46" s="17" t="s">
+      <c r="F46" s="23" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="47" ht="118" spans="1:6">
-      <c r="A47" s="11">
+      <c r="A47" s="17">
         <v>40</v>
       </c>
-      <c r="B47" s="17" t="s">
+      <c r="B47" s="23" t="s">
         <v>142</v>
       </c>
-      <c r="C47" s="17" t="s">
+      <c r="C47" s="23" t="s">
         <v>138</v>
       </c>
-      <c r="D47" s="17" t="s">
+      <c r="D47" s="23" t="s">
         <v>186</v>
       </c>
-      <c r="E47" s="17" t="s">
+      <c r="E47" s="23" t="s">
         <v>187</v>
       </c>
-      <c r="F47" s="17" t="s">
+      <c r="F47" s="23" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="48" ht="68" spans="1:6">
-      <c r="A48" s="11">
+      <c r="A48" s="17">
         <v>41</v>
       </c>
-      <c r="B48" s="17" t="s">
+      <c r="B48" s="23" t="s">
         <v>145</v>
       </c>
-      <c r="C48" s="17" t="s">
+      <c r="C48" s="23" t="s">
         <v>138</v>
       </c>
-      <c r="D48" s="17" t="s">
+      <c r="D48" s="23" t="s">
         <v>189</v>
       </c>
-      <c r="E48" s="17" t="s">
+      <c r="E48" s="23" t="s">
         <v>132</v>
       </c>
-      <c r="F48" s="17" t="s">
+      <c r="F48" s="23" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="49" ht="68" spans="1:6">
-      <c r="A49" s="11">
+      <c r="A49" s="17">
         <v>42</v>
       </c>
-      <c r="B49" s="17" t="s">
+      <c r="B49" s="23" t="s">
         <v>149</v>
       </c>
-      <c r="C49" s="17" t="s">
+      <c r="C49" s="23" t="s">
         <v>138</v>
       </c>
-      <c r="D49" s="17" t="s">
+      <c r="D49" s="23" t="s">
         <v>191</v>
       </c>
-      <c r="E49" s="17" t="s">
+      <c r="E49" s="23" t="s">
         <v>132</v>
       </c>
-      <c r="F49" s="17" t="s">
+      <c r="F49" s="23" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="A50" s="16" t="s">
+      <c r="A50" s="22" t="s">
         <v>193</v>
       </c>
-      <c r="B50" s="16"/>
-      <c r="C50" s="16"/>
-      <c r="D50" s="16"/>
-      <c r="E50" s="16"/>
-      <c r="F50" s="16"/>
+      <c r="B50" s="22"/>
+      <c r="C50" s="22"/>
+      <c r="D50" s="22"/>
+      <c r="E50" s="22"/>
+      <c r="F50" s="22"/>
     </row>
     <row r="51" ht="68" spans="1:6">
-      <c r="A51" s="11">
+      <c r="A51" s="17">
         <v>43</v>
       </c>
-      <c r="B51" s="12" t="s">
+      <c r="B51" s="18" t="s">
         <v>194</v>
       </c>
-      <c r="C51" s="12" t="s">
+      <c r="C51" s="18" t="s">
         <v>122</v>
       </c>
-      <c r="D51" s="12" t="s">
+      <c r="D51" s="18" t="s">
         <v>195</v>
       </c>
-      <c r="E51" s="12" t="s">
+      <c r="E51" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="F51" s="12" t="s">
+      <c r="F51" s="18" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="52" ht="68" spans="1:6">
-      <c r="A52" s="11">
+      <c r="A52" s="17">
         <v>44</v>
       </c>
-      <c r="B52" s="12" t="s">
+      <c r="B52" s="18" t="s">
         <v>198</v>
       </c>
-      <c r="C52" s="12" t="s">
+      <c r="C52" s="18" t="s">
         <v>122</v>
       </c>
-      <c r="D52" s="12" t="s">
+      <c r="D52" s="18" t="s">
         <v>199</v>
       </c>
-      <c r="E52" s="12" t="s">
+      <c r="E52" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="F52" s="12" t="s">
+      <c r="F52" s="18" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="53" ht="68" spans="1:6">
-      <c r="A53" s="11">
+      <c r="A53" s="17">
         <v>45</v>
       </c>
-      <c r="B53" s="12" t="s">
+      <c r="B53" s="18" t="s">
         <v>201</v>
       </c>
-      <c r="C53" s="12" t="s">
+      <c r="C53" s="18" t="s">
         <v>122</v>
       </c>
-      <c r="D53" s="12" t="s">
+      <c r="D53" s="18" t="s">
         <v>202</v>
       </c>
-      <c r="E53" s="12" t="s">
+      <c r="E53" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="F53" s="12" t="s">
+      <c r="F53" s="18" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="54" ht="68" spans="1:6">
-      <c r="A54" s="11">
+      <c r="A54" s="17">
         <v>46</v>
       </c>
-      <c r="B54" s="12" t="s">
+      <c r="B54" s="18" t="s">
         <v>204</v>
       </c>
-      <c r="C54" s="17" t="s">
+      <c r="C54" s="23" t="s">
         <v>138</v>
       </c>
-      <c r="D54" s="17" t="s">
+      <c r="D54" s="23" t="s">
         <v>205</v>
       </c>
-      <c r="E54" s="17" t="s">
+      <c r="E54" s="23" t="s">
         <v>160</v>
       </c>
-      <c r="F54" s="17" t="s">
+      <c r="F54" s="23" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="55" ht="68" spans="1:6">
-      <c r="A55" s="11">
+      <c r="A55" s="17">
         <v>47</v>
       </c>
-      <c r="B55" s="12" t="s">
+      <c r="B55" s="18" t="s">
         <v>206</v>
       </c>
-      <c r="C55" s="17" t="s">
+      <c r="C55" s="23" t="s">
         <v>138</v>
       </c>
-      <c r="D55" s="17" t="s">
+      <c r="D55" s="23" t="s">
         <v>207</v>
       </c>
-      <c r="E55" s="17" t="s">
+      <c r="E55" s="23" t="s">
         <v>128</v>
       </c>
-      <c r="F55" s="17" t="s">
+      <c r="F55" s="23" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="56" ht="68" spans="1:6">
-      <c r="A56" s="11">
+      <c r="A56" s="17">
         <v>48</v>
       </c>
-      <c r="B56" s="12" t="s">
+      <c r="B56" s="18" t="s">
         <v>208</v>
       </c>
-      <c r="C56" s="17" t="s">
+      <c r="C56" s="23" t="s">
         <v>138</v>
       </c>
-      <c r="D56" s="17" t="s">
+      <c r="D56" s="23" t="s">
         <v>209</v>
       </c>
-      <c r="E56" s="17" t="s">
+      <c r="E56" s="23" t="s">
         <v>132</v>
       </c>
-      <c r="F56" s="17" t="s">
+      <c r="F56" s="23" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="57" ht="68" spans="1:6">
-      <c r="A57" s="11">
+      <c r="A57" s="17">
         <v>49</v>
       </c>
-      <c r="B57" s="12" t="s">
+      <c r="B57" s="18" t="s">
         <v>210</v>
       </c>
-      <c r="C57" s="17" t="s">
+      <c r="C57" s="23" t="s">
         <v>138</v>
       </c>
-      <c r="D57" s="17" t="s">
+      <c r="D57" s="23" t="s">
         <v>211</v>
       </c>
-      <c r="E57" s="17" t="s">
+      <c r="E57" s="23" t="s">
         <v>132</v>
       </c>
-      <c r="F57" s="17" t="s">
+      <c r="F57" s="23" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="58" spans="1:6">
-      <c r="A58" s="16" t="s">
+      <c r="A58" s="22" t="s">
         <v>212</v>
       </c>
-      <c r="B58" s="16"/>
-      <c r="C58" s="16"/>
-      <c r="D58" s="16"/>
-      <c r="E58" s="16"/>
-      <c r="F58" s="16"/>
+      <c r="B58" s="22"/>
+      <c r="C58" s="22"/>
+      <c r="D58" s="22"/>
+      <c r="E58" s="22"/>
+      <c r="F58" s="22"/>
     </row>
     <row r="59" ht="84" spans="1:6">
-      <c r="A59" s="11">
+      <c r="A59" s="17">
         <v>50</v>
       </c>
-      <c r="B59" s="12" t="s">
+      <c r="B59" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="C59" s="12" t="s">
+      <c r="C59" s="18" t="s">
         <v>173</v>
       </c>
-      <c r="D59" s="17" t="s">
+      <c r="D59" s="23" t="s">
         <v>213</v>
       </c>
-      <c r="E59" s="12" t="s">
+      <c r="E59" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="F59" s="12" t="s">
+      <c r="F59" s="18" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="60" ht="68" spans="1:6">
-      <c r="A60" s="11">
+      <c r="A60" s="17">
         <v>51</v>
       </c>
-      <c r="B60" s="12" t="s">
+      <c r="B60" s="18" t="s">
         <v>176</v>
       </c>
-      <c r="C60" s="12" t="s">
+      <c r="C60" s="18" t="s">
         <v>173</v>
       </c>
-      <c r="D60" s="17" t="s">
+      <c r="D60" s="23" t="s">
         <v>214</v>
       </c>
-      <c r="E60" s="12" t="s">
+      <c r="E60" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="F60" s="12" t="s">
+      <c r="F60" s="18" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="61" ht="68" spans="1:6">
-      <c r="A61" s="11">
+      <c r="A61" s="17">
         <v>52</v>
       </c>
-      <c r="B61" s="12" t="s">
+      <c r="B61" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="C61" s="12" t="s">
+      <c r="C61" s="18" t="s">
         <v>173</v>
       </c>
-      <c r="D61" s="17" t="s">
+      <c r="D61" s="23" t="s">
         <v>215</v>
       </c>
-      <c r="E61" s="12" t="s">
+      <c r="E61" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="F61" s="12" t="s">
+      <c r="F61" s="18" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="62" ht="68" spans="1:6">
-      <c r="A62" s="11">
+      <c r="A62" s="17">
         <v>53</v>
       </c>
-      <c r="B62" s="12" t="s">
+      <c r="B62" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="C62" s="12" t="s">
+      <c r="C62" s="18" t="s">
         <v>173</v>
       </c>
-      <c r="D62" s="17" t="s">
+      <c r="D62" s="23" t="s">
         <v>216</v>
       </c>
-      <c r="E62" s="12" t="s">
+      <c r="E62" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="F62" s="12" t="s">
+      <c r="F62" s="18" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="63" ht="68" spans="1:6">
-      <c r="A63" s="11">
+      <c r="A63" s="17">
         <v>54</v>
       </c>
-      <c r="B63" s="17" t="s">
+      <c r="B63" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="C63" s="17" t="s">
+      <c r="C63" s="23" t="s">
         <v>138</v>
       </c>
-      <c r="D63" s="17" t="s">
+      <c r="D63" s="23" t="s">
         <v>217</v>
       </c>
-      <c r="E63" s="17" t="s">
+      <c r="E63" s="23" t="s">
         <v>218</v>
       </c>
-      <c r="F63" s="17" t="s">
+      <c r="F63" s="23" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="64" ht="84" spans="1:6">
-      <c r="A64" s="11">
+      <c r="A64" s="17">
         <v>55</v>
       </c>
-      <c r="B64" s="17" t="s">
+      <c r="B64" s="23" t="s">
         <v>142</v>
       </c>
-      <c r="C64" s="17" t="s">
+      <c r="C64" s="23" t="s">
         <v>138</v>
       </c>
-      <c r="D64" s="17" t="s">
+      <c r="D64" s="23" t="s">
         <v>214</v>
       </c>
-      <c r="E64" s="17" t="s">
+      <c r="E64" s="23" t="s">
         <v>220</v>
       </c>
-      <c r="F64" s="17" t="s">
+      <c r="F64" s="23" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="65" ht="84" spans="1:6">
-      <c r="A65" s="11">
+      <c r="A65" s="17">
         <v>56</v>
       </c>
-      <c r="B65" s="17" t="s">
+      <c r="B65" s="23" t="s">
         <v>145</v>
       </c>
-      <c r="C65" s="17" t="s">
+      <c r="C65" s="23" t="s">
         <v>138</v>
       </c>
-      <c r="D65" s="17" t="s">
+      <c r="D65" s="23" t="s">
         <v>221</v>
       </c>
-      <c r="E65" s="17" t="s">
+      <c r="E65" s="23" t="s">
         <v>220</v>
       </c>
-      <c r="F65" s="17" t="s">
+      <c r="F65" s="23" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="66" ht="68" spans="1:6">
-      <c r="A66" s="11">
+      <c r="A66" s="17">
         <v>57</v>
       </c>
-      <c r="B66" s="17" t="s">
+      <c r="B66" s="23" t="s">
         <v>149</v>
       </c>
-      <c r="C66" s="17" t="s">
+      <c r="C66" s="23" t="s">
         <v>138</v>
       </c>
-      <c r="D66" s="17" t="s">
+      <c r="D66" s="23" t="s">
         <v>222</v>
       </c>
-      <c r="E66" s="17" t="s">
+      <c r="E66" s="23" t="s">
         <v>132</v>
       </c>
-      <c r="F66" s="17" t="s">
+      <c r="F66" s="23" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="67" spans="1:6">
-      <c r="A67" s="16" t="s">
+      <c r="A67" s="22" t="s">
         <v>223</v>
       </c>
-      <c r="B67" s="16"/>
-      <c r="C67" s="16"/>
-      <c r="D67" s="16"/>
-      <c r="E67" s="16"/>
-      <c r="F67" s="16"/>
+      <c r="B67" s="22"/>
+      <c r="C67" s="22"/>
+      <c r="D67" s="22"/>
+      <c r="E67" s="22"/>
+      <c r="F67" s="22"/>
     </row>
     <row r="68" ht="84" spans="1:6">
-      <c r="A68" s="11">
+      <c r="A68" s="17">
         <v>58</v>
       </c>
-      <c r="B68" s="12" t="s">
+      <c r="B68" s="18" t="s">
         <v>224</v>
       </c>
-      <c r="C68" s="12" t="s">
+      <c r="C68" s="18" t="s">
         <v>173</v>
       </c>
-      <c r="D68" s="17" t="s">
+      <c r="D68" s="23" t="s">
         <v>225</v>
       </c>
-      <c r="E68" s="12" t="s">
+      <c r="E68" s="18" t="s">
         <v>226</v>
       </c>
-      <c r="F68" s="12" t="s">
+      <c r="F68" s="18" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="69" ht="68" spans="1:6">
-      <c r="A69" s="11">
+      <c r="A69" s="17">
         <v>59</v>
       </c>
-      <c r="B69" s="12" t="s">
+      <c r="B69" s="18" t="s">
         <v>228</v>
       </c>
-      <c r="C69" s="12" t="s">
+      <c r="C69" s="18" t="s">
         <v>173</v>
       </c>
-      <c r="D69" s="17" t="s">
+      <c r="D69" s="23" t="s">
         <v>229</v>
       </c>
-      <c r="E69" s="12" t="s">
+      <c r="E69" s="18" t="s">
         <v>230</v>
       </c>
-      <c r="F69" s="12" t="s">
+      <c r="F69" s="18" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="70" ht="68" spans="1:6">
-      <c r="A70" s="11">
+      <c r="A70" s="17">
         <v>60</v>
       </c>
-      <c r="B70" s="12" t="s">
+      <c r="B70" s="18" t="s">
         <v>232</v>
       </c>
-      <c r="C70" s="12" t="s">
+      <c r="C70" s="18" t="s">
         <v>173</v>
       </c>
-      <c r="D70" s="17" t="s">
+      <c r="D70" s="23" t="s">
         <v>233</v>
       </c>
-      <c r="E70" s="12" t="s">
+      <c r="E70" s="18" t="s">
         <v>234</v>
       </c>
-      <c r="F70" s="12" t="s">
+      <c r="F70" s="18" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="71" ht="68" spans="1:6">
-      <c r="A71" s="11">
+      <c r="A71" s="17">
         <v>61</v>
       </c>
-      <c r="B71" s="12" t="s">
+      <c r="B71" s="18" t="s">
         <v>236</v>
       </c>
-      <c r="C71" s="12" t="s">
+      <c r="C71" s="18" t="s">
         <v>173</v>
       </c>
-      <c r="D71" s="17" t="s">
+      <c r="D71" s="23" t="s">
         <v>237</v>
       </c>
-      <c r="E71" s="12" t="s">
+      <c r="E71" s="18" t="s">
         <v>234</v>
       </c>
-      <c r="F71" s="12" t="s">
+      <c r="F71" s="18" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="72" ht="68" spans="1:6">
-      <c r="A72" s="11">
+      <c r="A72" s="17">
         <v>62</v>
       </c>
-      <c r="B72" s="17" t="s">
+      <c r="B72" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="C72" s="17" t="s">
+      <c r="C72" s="23" t="s">
         <v>138</v>
       </c>
-      <c r="D72" s="17" t="s">
+      <c r="D72" s="23" t="s">
         <v>239</v>
       </c>
-      <c r="E72" s="17" t="s">
+      <c r="E72" s="23" t="s">
         <v>240</v>
       </c>
-      <c r="F72" s="17" t="s">
+      <c r="F72" s="23" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="73" ht="68" spans="1:6">
-      <c r="A73" s="11">
+      <c r="A73" s="17">
         <v>63</v>
       </c>
-      <c r="B73" s="17" t="s">
+      <c r="B73" s="23" t="s">
         <v>142</v>
       </c>
-      <c r="C73" s="17" t="s">
+      <c r="C73" s="23" t="s">
         <v>138</v>
       </c>
-      <c r="D73" s="17" t="s">
+      <c r="D73" s="23" t="s">
         <v>229</v>
       </c>
-      <c r="E73" s="17" t="s">
+      <c r="E73" s="23" t="s">
         <v>128</v>
       </c>
-      <c r="F73" s="17" t="s">
+      <c r="F73" s="23" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="74" ht="68" spans="1:6">
-      <c r="A74" s="11">
+      <c r="A74" s="17">
         <v>64</v>
       </c>
-      <c r="B74" s="17" t="s">
+      <c r="B74" s="23" t="s">
         <v>242</v>
       </c>
-      <c r="C74" s="17" t="s">
+      <c r="C74" s="23" t="s">
         <v>138</v>
       </c>
-      <c r="D74" s="17" t="s">
+      <c r="D74" s="23" t="s">
         <v>243</v>
       </c>
-      <c r="E74" s="17" t="s">
+      <c r="E74" s="23" t="s">
         <v>244</v>
       </c>
-      <c r="F74" s="17" t="s">
+      <c r="F74" s="23" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="75" ht="68" spans="1:6">
-      <c r="A75" s="11">
+      <c r="A75" s="17">
         <v>65</v>
       </c>
-      <c r="B75" s="17" t="s">
+      <c r="B75" s="23" t="s">
         <v>245</v>
       </c>
-      <c r="C75" s="17" t="s">
+      <c r="C75" s="23" t="s">
         <v>138</v>
       </c>
-      <c r="D75" s="17" t="s">
+      <c r="D75" s="23" t="s">
         <v>246</v>
       </c>
-      <c r="E75" s="17" t="s">
+      <c r="E75" s="23" t="s">
         <v>244</v>
       </c>
-      <c r="F75" s="17" t="s">
+      <c r="F75" s="23" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="76" spans="1:6">
-      <c r="A76" s="16" t="s">
+      <c r="A76" s="22" t="s">
         <v>247</v>
       </c>
-      <c r="B76" s="16"/>
-      <c r="C76" s="16"/>
-      <c r="D76" s="16"/>
-      <c r="E76" s="16"/>
-      <c r="F76" s="16"/>
+      <c r="B76" s="22"/>
+      <c r="C76" s="22"/>
+      <c r="D76" s="22"/>
+      <c r="E76" s="22"/>
+      <c r="F76" s="22"/>
     </row>
     <row r="77" ht="84" spans="1:6">
-      <c r="A77" s="11">
+      <c r="A77" s="17">
         <v>66</v>
       </c>
-      <c r="B77" s="12" t="s">
+      <c r="B77" s="18" t="s">
         <v>224</v>
       </c>
-      <c r="C77" s="12" t="s">
+      <c r="C77" s="18" t="s">
         <v>173</v>
       </c>
-      <c r="D77" s="17" t="s">
+      <c r="D77" s="23" t="s">
         <v>248</v>
       </c>
-      <c r="E77" s="12" t="s">
+      <c r="E77" s="18" t="s">
         <v>226</v>
       </c>
-      <c r="F77" s="12" t="s">
+      <c r="F77" s="18" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="78" ht="68" spans="1:6">
-      <c r="A78" s="11">
+      <c r="A78" s="17">
         <v>67</v>
       </c>
-      <c r="B78" s="12" t="s">
+      <c r="B78" s="18" t="s">
         <v>249</v>
       </c>
-      <c r="C78" s="12" t="s">
+      <c r="C78" s="18" t="s">
         <v>173</v>
       </c>
-      <c r="D78" s="17" t="s">
+      <c r="D78" s="23" t="s">
         <v>229</v>
       </c>
-      <c r="E78" s="12" t="s">
+      <c r="E78" s="18" t="s">
         <v>230</v>
       </c>
-      <c r="F78" s="12" t="s">
+      <c r="F78" s="18" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="79" ht="68" spans="1:6">
-      <c r="A79" s="11">
+      <c r="A79" s="17">
         <v>68</v>
       </c>
-      <c r="B79" s="12" t="s">
+      <c r="B79" s="18" t="s">
         <v>232</v>
       </c>
-      <c r="C79" s="12" t="s">
+      <c r="C79" s="18" t="s">
         <v>173</v>
       </c>
-      <c r="D79" s="17" t="s">
+      <c r="D79" s="23" t="s">
         <v>233</v>
       </c>
-      <c r="E79" s="12" t="s">
+      <c r="E79" s="18" t="s">
         <v>234</v>
       </c>
-      <c r="F79" s="12" t="s">
+      <c r="F79" s="18" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="80" ht="68" spans="1:6">
-      <c r="A80" s="11">
+      <c r="A80" s="17">
         <v>69</v>
       </c>
-      <c r="B80" s="12" t="s">
+      <c r="B80" s="18" t="s">
         <v>236</v>
       </c>
-      <c r="C80" s="12" t="s">
+      <c r="C80" s="18" t="s">
         <v>173</v>
       </c>
-      <c r="D80" s="17" t="s">
+      <c r="D80" s="23" t="s">
         <v>237</v>
       </c>
-      <c r="E80" s="12" t="s">
+      <c r="E80" s="18" t="s">
         <v>250</v>
       </c>
-      <c r="F80" s="12" t="s">
+      <c r="F80" s="18" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="81" ht="68" spans="1:6">
-      <c r="A81" s="11">
+      <c r="A81" s="17">
         <v>70</v>
       </c>
-      <c r="B81" s="17" t="s">
+      <c r="B81" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="C81" s="17" t="s">
+      <c r="C81" s="23" t="s">
         <v>138</v>
       </c>
-      <c r="D81" s="17" t="s">
+      <c r="D81" s="23" t="s">
         <v>239</v>
       </c>
-      <c r="E81" s="17" t="s">
+      <c r="E81" s="23" t="s">
         <v>160</v>
       </c>
-      <c r="F81" s="17" t="s">
+      <c r="F81" s="23" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="82" ht="68" spans="1:6">
-      <c r="A82" s="11">
+      <c r="A82" s="17">
         <v>71</v>
       </c>
-      <c r="B82" s="17" t="s">
+      <c r="B82" s="23" t="s">
         <v>142</v>
       </c>
-      <c r="C82" s="17" t="s">
+      <c r="C82" s="23" t="s">
         <v>138</v>
       </c>
-      <c r="D82" s="17" t="s">
+      <c r="D82" s="23" t="s">
         <v>229</v>
       </c>
-      <c r="E82" s="17" t="s">
+      <c r="E82" s="23" t="s">
         <v>128</v>
       </c>
-      <c r="F82" s="17" t="s">
+      <c r="F82" s="23" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="83" ht="68" spans="1:6">
-      <c r="A83" s="11">
+      <c r="A83" s="17">
         <v>72</v>
       </c>
-      <c r="B83" s="17" t="s">
+      <c r="B83" s="23" t="s">
         <v>242</v>
       </c>
-      <c r="C83" s="17" t="s">
+      <c r="C83" s="23" t="s">
         <v>138</v>
       </c>
-      <c r="D83" s="17" t="s">
+      <c r="D83" s="23" t="s">
         <v>243</v>
       </c>
-      <c r="E83" s="17" t="s">
+      <c r="E83" s="23" t="s">
         <v>244</v>
       </c>
-      <c r="F83" s="17" t="s">
+      <c r="F83" s="23" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="84" ht="68" spans="1:6">
-      <c r="A84" s="11">
+      <c r="A84" s="17">
         <v>73</v>
       </c>
-      <c r="B84" s="17" t="s">
+      <c r="B84" s="23" t="s">
         <v>245</v>
       </c>
-      <c r="C84" s="17" t="s">
+      <c r="C84" s="23" t="s">
         <v>138</v>
       </c>
-      <c r="D84" s="17" t="s">
+      <c r="D84" s="23" t="s">
         <v>246</v>
       </c>
-      <c r="E84" s="17" t="s">
+      <c r="E84" s="23" t="s">
         <v>244</v>
       </c>
-      <c r="F84" s="17" t="s">
+      <c r="F84" s="23" t="s">
         <v>192</v>
       </c>
     </row>
@@ -5722,852 +5847,896 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F52"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="5"/>
+  <dimension ref="A1:H44"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="4.296875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="26.953125" style="6" customWidth="1"/>
-    <col min="3" max="3" width="23.1796875" style="6" customWidth="1"/>
-    <col min="4" max="4" width="25.6484375" style="6" customWidth="1"/>
-    <col min="5" max="5" width="10.15625" style="6" customWidth="1"/>
-    <col min="6" max="6" width="18.8828125" style="6" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="2"/>
+    <col min="1" max="1" width="4.296875" style="5" customWidth="1"/>
+    <col min="2" max="2" width="26.953125" style="9" customWidth="1"/>
+    <col min="3" max="3" width="23.1796875" style="9" customWidth="1"/>
+    <col min="4" max="4" width="25.6484375" style="9" customWidth="1"/>
+    <col min="5" max="5" width="18.8828125" style="9" customWidth="1"/>
+    <col min="6" max="6" width="8.984375" style="9" customWidth="1"/>
+    <col min="7" max="7" width="9" style="9"/>
+    <col min="8" max="8" width="10.4140625" style="9" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="20" customHeight="1" spans="1:6">
-      <c r="A1" s="7" t="s">
+    <row r="1" s="5" customFormat="1" ht="52" customHeight="1" spans="1:8">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" s="9" t="s">
         <v>251</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="G1" s="9" t="s">
+        <v>252</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="2" s="8" customFormat="1" ht="20" customHeight="1" spans="1:8">
+      <c r="A2" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+    </row>
+    <row r="3" ht="34" spans="1:8">
+      <c r="A3" s="5">
+        <v>1</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="4" ht="84" spans="1:8">
+      <c r="A4" s="5">
+        <v>2</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>259</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="5" s="9" customFormat="1" ht="51" spans="1:8">
+      <c r="A5" s="5">
+        <v>3</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="6" s="5" customFormat="1" spans="1:8">
+      <c r="A6" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
+    </row>
+    <row r="7" ht="34" spans="1:8">
+      <c r="A7" s="5">
+        <v>3</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="8" ht="51" spans="1:8">
+      <c r="A8" s="5">
+        <v>4</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="E8" s="5"/>
+      <c r="F8" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="9" ht="34" spans="1:8">
+      <c r="A9" s="5">
+        <v>5</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="E9" s="5"/>
+      <c r="F9" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="10" customFormat="1" ht="40" customHeight="1" spans="1:8">
+      <c r="A10" s="5">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" s="5" customFormat="1" ht="20" customHeight="1" spans="1:6">
-      <c r="A2" s="8" t="s">
-        <v>252</v>
-      </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-    </row>
-    <row r="3" ht="34" spans="1:5">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>253</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="4" ht="84" spans="1:5">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>257</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>258</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="5" s="6" customFormat="1" ht="51" spans="1:5">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>253</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>259</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" spans="1:1">
-      <c r="A6" s="1" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="7" ht="34" spans="1:6">
-      <c r="A7" s="1">
-        <v>3</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>261</v>
-      </c>
-      <c r="C7" s="6" t="s">
+      <c r="B10" s="9" t="s">
+        <v>272</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="E10" s="5"/>
+      <c r="F10" s="14" t="s">
+        <v>275</v>
+      </c>
+      <c r="G10" s="14" t="s">
+        <v>258</v>
+      </c>
+      <c r="H10" s="14" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="11" customFormat="1" ht="39" customHeight="1" spans="1:8">
+      <c r="A11" s="5">
+        <v>7</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="14" t="s">
+        <v>258</v>
+      </c>
+      <c r="G11" s="14" t="s">
+        <v>258</v>
+      </c>
+      <c r="H11" s="14" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="12" s="5" customFormat="1" ht="84" spans="1:8">
+      <c r="A12" s="5">
+        <v>8</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>280</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="13" s="5" customFormat="1" spans="1:8">
+      <c r="A13" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="9"/>
+    </row>
+    <row r="14" ht="68" spans="1:8">
+      <c r="A14" s="5">
+        <v>9</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>284</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="15" ht="68" spans="1:8">
+      <c r="A15" s="5">
+        <v>10</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>285</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>287</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="16" ht="68" spans="1:8">
+      <c r="A16" s="5">
+        <v>11</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>288</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="17" s="5" customFormat="1" spans="1:8">
+      <c r="A17" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="F17" s="9"/>
+      <c r="G17" s="9"/>
+      <c r="H17" s="9"/>
+    </row>
+    <row r="18" ht="84" spans="1:8">
+      <c r="A18" s="5">
+        <v>12</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>291</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="G18" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="19" ht="34" spans="1:8">
+      <c r="A19" s="5">
+        <v>13</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>292</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>293</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>294</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="G19" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="20" ht="34" spans="1:8">
+      <c r="A20" s="5">
+        <v>14</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="G20" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="21" ht="41" customHeight="1" spans="1:8">
+      <c r="A21" s="5">
+        <v>15</v>
+      </c>
+      <c r="B21" s="5"/>
+      <c r="C21" s="9" t="s">
+        <v>298</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="G21" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="22" ht="34" spans="1:8">
+      <c r="A22" s="5">
+        <v>16</v>
+      </c>
+      <c r="B22" s="5"/>
+      <c r="C22" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="F22" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="G22" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="5" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="24" ht="114" customHeight="1" spans="1:8">
+      <c r="A24" s="5">
+        <v>17</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>303</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>304</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="E24" s="9" t="s">
+        <v>306</v>
+      </c>
+      <c r="F24" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="G24" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="H24" s="9" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="25" ht="51" spans="1:8">
+      <c r="A25" s="5">
+        <v>18</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>308</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>309</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="G25" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="H25" s="9" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="26" ht="84" spans="1:8">
+      <c r="A26" s="5">
+        <v>19</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>310</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>308</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>311</v>
+      </c>
+      <c r="F26" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="G26" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="H26" s="9" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="27" ht="51" spans="1:8">
+      <c r="A27" s="5">
+        <v>20</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>312</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>313</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="F27" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="G27" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="H27" s="9" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="28" ht="51" spans="1:8">
+      <c r="A28" s="5">
+        <v>21</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>312</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>314</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>315</v>
+      </c>
+      <c r="F28" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="G28" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="H28" s="9" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="29" ht="68" spans="1:8">
+      <c r="A29" s="5">
+        <v>22</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>312</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>316</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>317</v>
+      </c>
+      <c r="F29" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="G29" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="H29" s="9" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="30" ht="84" spans="1:8">
+      <c r="A30" s="5">
+        <v>23</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>318</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>319</v>
+      </c>
+      <c r="E30" s="9" t="s">
+        <v>320</v>
+      </c>
+      <c r="F30" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="G30" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="H30" s="9" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="31" ht="84" spans="1:8">
+      <c r="A31" s="5">
+        <v>24</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>321</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>322</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>323</v>
+      </c>
+      <c r="F31" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="G31" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="H31" s="9" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="32" ht="51" spans="1:8">
+      <c r="A32" s="5">
+        <v>25</v>
+      </c>
+      <c r="B32" s="9" t="s">
+        <v>321</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>324</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>325</v>
+      </c>
+      <c r="F32" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="G32" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="H32" s="9" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="33" ht="135" spans="1:8">
+      <c r="A33" s="5">
+        <v>26</v>
+      </c>
+      <c r="B33" s="9" t="s">
+        <v>326</v>
+      </c>
+      <c r="C33" s="12" t="s">
+        <v>327</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="F33" s="15" t="s">
+        <v>258</v>
+      </c>
+      <c r="G33" s="15" t="s">
+        <v>258</v>
+      </c>
+      <c r="H33" s="9" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="34" ht="68" spans="1:8">
+      <c r="A34" s="5">
+        <v>27</v>
+      </c>
+      <c r="B34" s="9" t="s">
+        <v>321</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>329</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>330</v>
+      </c>
+      <c r="E34" s="9" t="s">
+        <v>331</v>
+      </c>
+      <c r="F34" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="G34" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="H34" s="9" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="35" ht="84" spans="1:8">
+      <c r="A35" s="5">
+        <v>28</v>
+      </c>
+      <c r="B35" s="9" t="s">
+        <v>332</v>
+      </c>
+      <c r="C35" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="D7" s="6" t="s">
-        <v>262</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>256</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="8" ht="51" spans="1:6">
-      <c r="A8" s="1">
-        <v>4</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>264</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>265</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>266</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>256</v>
-      </c>
-      <c r="F8" s="1"/>
-    </row>
-    <row r="9" ht="34" spans="1:6">
-      <c r="A9" s="1">
-        <v>5</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>267</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>268</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>262</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>256</v>
-      </c>
-      <c r="F9" s="1"/>
-    </row>
-    <row r="10" customFormat="1" ht="40" customHeight="1" spans="1:6">
-      <c r="A10" s="1">
-        <v>6</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>269</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>270</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>256</v>
-      </c>
-      <c r="F10" s="1"/>
-    </row>
-    <row r="11" customFormat="1" ht="39" customHeight="1" spans="1:6">
-      <c r="A11" s="1">
-        <v>7</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>272</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>273</v>
-      </c>
-      <c r="D11" s="1"/>
-      <c r="E11" s="6" t="s">
-        <v>256</v>
-      </c>
-      <c r="F11" s="1"/>
-    </row>
-    <row r="12" s="1" customFormat="1" ht="84" spans="1:5">
-      <c r="A12" s="1">
-        <v>8</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>262</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="13" s="1" customFormat="1" spans="1:1">
-      <c r="A13" s="1" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="14" ht="68" spans="1:5">
-      <c r="A14" s="1">
+      <c r="D35" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="F35" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="G35" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="H35" s="9" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
+        <v>334</v>
+      </c>
+      <c r="B36" s="5"/>
+      <c r="C36" s="5"/>
+      <c r="D36" s="5"/>
+      <c r="E36" s="5"/>
+    </row>
+    <row r="37" ht="34" spans="1:6">
+      <c r="A37" s="5">
+        <v>29</v>
+      </c>
+      <c r="B37" s="9" t="s">
+        <v>335</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>336</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>337</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>338</v>
+      </c>
+      <c r="F37" s="9" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="38" ht="34" spans="1:5">
+      <c r="A38" s="5">
+        <v>30</v>
+      </c>
+      <c r="B38" s="9" t="s">
+        <v>340</v>
+      </c>
+      <c r="C38" s="5"/>
+      <c r="D38" s="5"/>
+      <c r="E38" s="5"/>
+    </row>
+    <row r="39" ht="34" spans="1:6">
+      <c r="A39" s="5">
+        <v>31</v>
+      </c>
+      <c r="B39" s="9" t="s">
+        <v>341</v>
+      </c>
+      <c r="C39" s="5"/>
+      <c r="D39" s="5"/>
+      <c r="E39" s="5"/>
+      <c r="F39" s="9" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="40" ht="37" customHeight="1" spans="1:5">
+      <c r="A40" s="5">
+        <v>32</v>
+      </c>
+      <c r="B40" s="9" t="s">
+        <v>342</v>
+      </c>
+      <c r="C40" s="5"/>
+      <c r="D40" s="5"/>
+      <c r="E40" s="5"/>
+    </row>
+    <row r="41" ht="37" customHeight="1" spans="1:5">
+      <c r="A41" s="5">
+        <v>33</v>
+      </c>
+      <c r="B41" s="9" t="s">
+        <v>343</v>
+      </c>
+      <c r="C41" s="5"/>
+      <c r="D41" s="5"/>
+      <c r="E41" s="5"/>
+    </row>
+    <row r="42" ht="34" customHeight="1" spans="1:5">
+      <c r="A42" s="5">
+        <v>34</v>
+      </c>
+      <c r="B42" s="9" t="s">
+        <v>344</v>
+      </c>
+      <c r="C42" s="5"/>
+      <c r="D42" s="5"/>
+      <c r="E42" s="5"/>
+    </row>
+    <row r="43" ht="33" customHeight="1" spans="1:5">
+      <c r="A43" s="5">
+        <v>35</v>
+      </c>
+      <c r="B43" s="9" t="s">
+        <v>345</v>
+      </c>
+      <c r="C43" s="5"/>
+      <c r="D43" s="5"/>
+      <c r="E43" s="5"/>
+    </row>
+    <row r="44" ht="68" spans="1:5">
+      <c r="A44" s="5">
+        <v>36</v>
+      </c>
+      <c r="B44" s="9" t="s">
+        <v>346</v>
+      </c>
+      <c r="C44" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>279</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="15" ht="68" spans="1:6">
-      <c r="A15" s="1">
-        <v>10</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>280</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>281</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>256</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="16" ht="68" spans="1:5">
-      <c r="A16" s="1">
-        <v>11</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>283</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>281</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="17" s="1" customFormat="1" spans="1:1">
-      <c r="A17" s="1" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="18" ht="84" spans="1:5">
-      <c r="A18" s="1">
-        <v>12</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>285</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>286</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="19" ht="34" spans="1:5">
-      <c r="A19" s="1">
-        <v>13</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>287</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>288</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>289</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="20" ht="34" spans="1:5">
-      <c r="A20" s="1">
-        <v>14</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>291</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>292</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="21" ht="41" customHeight="1" spans="1:5">
-      <c r="A21" s="1">
-        <v>15</v>
-      </c>
-      <c r="B21" s="1"/>
-      <c r="C21" s="6" t="s">
-        <v>293</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>294</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="22" ht="34" spans="1:5">
-      <c r="A22" s="1">
-        <v>16</v>
-      </c>
-      <c r="B22" s="1"/>
-      <c r="C22" s="6" t="s">
-        <v>295</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>296</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" s="1" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="24" ht="85" customHeight="1" spans="1:5">
-      <c r="A24" s="1">
-        <v>17</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>298</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>299</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>300</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="25" ht="51" spans="1:5">
-      <c r="A25" s="1">
-        <v>18</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>301</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>302</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>303</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="26" ht="51" spans="1:5">
-      <c r="A26" s="1">
-        <v>19</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>304</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>302</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>305</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="27" ht="51" spans="1:5">
-      <c r="A27" s="1">
-        <v>20</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>306</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>307</v>
-      </c>
-      <c r="D27" s="6" t="s">
-        <v>292</v>
-      </c>
-      <c r="E27" s="6" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="28" ht="51" spans="1:5">
-      <c r="A28" s="1">
-        <v>21</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>306</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>308</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>309</v>
-      </c>
-      <c r="E28" s="6" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="29" ht="68" spans="1:5">
-      <c r="A29" s="1">
-        <v>22</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>306</v>
-      </c>
-      <c r="C29" s="6" t="s">
-        <v>310</v>
-      </c>
-      <c r="D29" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="E29" s="6" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="30" ht="84" spans="1:6">
-      <c r="A30" s="1">
-        <v>23</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>301</v>
-      </c>
-      <c r="C30" s="6" t="s">
-        <v>312</v>
-      </c>
-      <c r="D30" s="6" t="s">
-        <v>313</v>
-      </c>
-      <c r="E30" s="6" t="s">
-        <v>256</v>
-      </c>
-      <c r="F30" s="6" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="31" ht="84" spans="1:5">
-      <c r="A31" s="1">
-        <v>24</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>315</v>
-      </c>
-      <c r="C31" s="6" t="s">
-        <v>316</v>
-      </c>
-      <c r="D31" s="6" t="s">
-        <v>317</v>
-      </c>
-      <c r="E31" s="6" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="32" ht="51" spans="1:5">
-      <c r="A32" s="1">
-        <v>25</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>315</v>
-      </c>
-      <c r="C32" s="6" t="s">
-        <v>318</v>
-      </c>
-      <c r="D32" s="6" t="s">
-        <v>319</v>
-      </c>
-      <c r="E32" s="6" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="33" ht="34" spans="1:5">
-      <c r="A33" s="1">
-        <v>26</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>320</v>
-      </c>
-      <c r="C33" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="D33" s="6" t="s">
-        <v>292</v>
-      </c>
-      <c r="E33" s="6" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="34" ht="84" spans="1:5">
-      <c r="A34" s="1">
-        <v>27</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>320</v>
-      </c>
-      <c r="C34" s="9" t="s">
-        <v>322</v>
-      </c>
-      <c r="D34" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="E34" s="6" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="35" ht="51" spans="1:5">
-      <c r="A35" s="1">
-        <v>28</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>320</v>
-      </c>
-      <c r="C35" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="D35" s="6" t="s">
-        <v>325</v>
-      </c>
-      <c r="E35" s="6" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="36" ht="51" spans="1:5">
-      <c r="A36" s="1">
-        <v>29</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>320</v>
-      </c>
-      <c r="C36" s="6" t="s">
-        <v>326</v>
-      </c>
-      <c r="D36" s="6" t="s">
-        <v>327</v>
-      </c>
-      <c r="E36" s="6" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="37" ht="34" spans="1:5">
-      <c r="A37" s="1">
-        <v>30</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>320</v>
-      </c>
-      <c r="C37" s="6" t="s">
-        <v>328</v>
-      </c>
-      <c r="D37" s="6" t="s">
-        <v>329</v>
-      </c>
-      <c r="E37" s="6" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="38" ht="51" spans="1:5">
-      <c r="A38" s="1">
-        <v>31</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>320</v>
-      </c>
-      <c r="C38" s="6" t="s">
-        <v>330</v>
-      </c>
-      <c r="D38" s="6" t="s">
-        <v>331</v>
-      </c>
-      <c r="E38" s="6" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="39" ht="17" spans="1:5">
-      <c r="A39" s="1">
-        <v>32</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>315</v>
-      </c>
-      <c r="C39" s="6" t="s">
-        <v>332</v>
-      </c>
-      <c r="D39" s="6" t="s">
-        <v>333</v>
-      </c>
-      <c r="E39" s="6" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="40" ht="84" spans="1:5">
-      <c r="A40" s="1">
-        <v>33</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>334</v>
-      </c>
-      <c r="C40" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="D40" s="6" t="s">
-        <v>335</v>
-      </c>
-      <c r="E40" s="6" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="41" ht="68" spans="1:6">
-      <c r="A41" s="1">
-        <v>34</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>315</v>
-      </c>
-      <c r="C41" s="6" t="s">
-        <v>336</v>
-      </c>
-      <c r="D41" s="6" t="s">
-        <v>337</v>
-      </c>
-      <c r="E41" s="6" t="s">
-        <v>256</v>
-      </c>
-      <c r="F41" s="6" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="42" ht="84" spans="1:5">
-      <c r="A42" s="1">
-        <v>35</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>339</v>
-      </c>
-      <c r="C42" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="D42" s="6" t="s">
-        <v>335</v>
-      </c>
-      <c r="E42" s="6" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="B43" s="1"/>
-      <c r="C43" s="1"/>
-      <c r="D43" s="1"/>
-      <c r="E43" s="1"/>
-      <c r="F43" s="1"/>
-    </row>
-    <row r="44" ht="37" customHeight="1" spans="1:6">
-      <c r="A44" s="1">
-        <v>36</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>341</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>343</v>
-      </c>
-      <c r="E44" s="6" t="s">
-        <v>256</v>
-      </c>
-      <c r="F44" s="1" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="45" ht="37" customHeight="1" spans="1:6">
-      <c r="A45" s="1">
-        <v>37</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>345</v>
-      </c>
-      <c r="C45" s="1"/>
-      <c r="D45" s="1"/>
-      <c r="E45" s="6" t="s">
-        <v>256</v>
-      </c>
-      <c r="F45" s="1"/>
-    </row>
-    <row r="46" ht="34" customHeight="1" spans="1:6">
-      <c r="A46" s="1">
-        <v>38</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>346</v>
-      </c>
-      <c r="C46" s="1"/>
-      <c r="D46" s="1"/>
-      <c r="E46" s="6" t="s">
-        <v>256</v>
-      </c>
-      <c r="F46" s="1"/>
-    </row>
-    <row r="47" ht="33" customHeight="1" spans="1:6">
-      <c r="A47" s="1">
-        <v>39</v>
-      </c>
-      <c r="B47" s="6" t="s">
+      <c r="D44" s="9" t="s">
         <v>347</v>
       </c>
-      <c r="C47" s="1"/>
-      <c r="D47" s="1"/>
-      <c r="E47" s="6" t="s">
-        <v>256</v>
-      </c>
-      <c r="F47" s="1"/>
-    </row>
-    <row r="48" ht="34" spans="1:6">
-      <c r="A48" s="1">
-        <v>40</v>
-      </c>
-      <c r="B48" s="6" t="s">
+      <c r="E44" s="9" t="s">
         <v>348</v>
-      </c>
-      <c r="C48" s="1"/>
-      <c r="D48" s="1"/>
-      <c r="E48" s="6" t="s">
-        <v>256</v>
-      </c>
-      <c r="F48" s="1"/>
-    </row>
-    <row r="49" ht="34" spans="1:6">
-      <c r="A49" s="1">
-        <v>41</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>349</v>
-      </c>
-      <c r="C49" s="1"/>
-      <c r="D49" s="1"/>
-      <c r="E49" s="6" t="s">
-        <v>256</v>
-      </c>
-      <c r="F49" s="1"/>
-    </row>
-    <row r="50" ht="34" spans="1:6">
-      <c r="A50" s="1">
-        <v>42</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>350</v>
-      </c>
-      <c r="C50" s="1"/>
-      <c r="D50" s="1"/>
-      <c r="E50" s="6" t="s">
-        <v>256</v>
-      </c>
-      <c r="F50" s="1"/>
-    </row>
-    <row r="51" ht="34" spans="1:6">
-      <c r="A51" s="1">
-        <v>43</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>351</v>
-      </c>
-      <c r="C51" s="1"/>
-      <c r="D51" s="1"/>
-      <c r="E51" s="6" t="s">
-        <v>256</v>
-      </c>
-      <c r="F51" s="1"/>
-    </row>
-    <row r="52" ht="68" spans="1:6">
-      <c r="A52" s="1">
-        <v>44</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>352</v>
-      </c>
-      <c r="C52" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D52" s="6" t="s">
-        <v>353</v>
-      </c>
-      <c r="E52" s="6" t="s">
-        <v>256</v>
-      </c>
-      <c r="F52" s="6" t="s">
-        <v>354</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="A17:F17"/>
-    <mergeCell ref="A23:F23"/>
-    <mergeCell ref="A43:F43"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A36:E36"/>
     <mergeCell ref="B20:B22"/>
-    <mergeCell ref="C44:C51"/>
+    <mergeCell ref="C37:C43"/>
     <mergeCell ref="D10:D11"/>
-    <mergeCell ref="D44:D51"/>
-    <mergeCell ref="F7:F12"/>
-    <mergeCell ref="F44:F51"/>
+    <mergeCell ref="D37:D43"/>
+    <mergeCell ref="E7:E12"/>
+    <mergeCell ref="E37:E43"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -6580,204 +6749,204 @@
   <dimension ref="A1:I9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="1" width="4.953125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="27.6015625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="16.40625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="25.2578125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="9.2421875" style="2" customWidth="1"/>
-    <col min="6" max="6" width="19.65625" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="2"/>
+    <col min="1" max="1" width="4.953125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="27.6015625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="16.40625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="25.2578125" style="3" customWidth="1"/>
+    <col min="5" max="5" width="9.2421875" style="3" customWidth="1"/>
+    <col min="6" max="6" width="19.65625" style="3" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" s="4" customFormat="1" ht="17" spans="1:8">
-      <c r="A1" s="3" t="s">
+    <row r="1" s="7" customFormat="1" ht="17" spans="1:8">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="2" ht="70" customHeight="1" spans="1:9">
+      <c r="A2" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>355</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>356</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E2" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>357</v>
       </c>
-      <c r="F1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="4" t="s">
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+    </row>
+    <row r="3" ht="118" spans="1:9">
+      <c r="A3" s="3" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="2" ht="70" customHeight="1" spans="1:9">
-      <c r="A2" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>359</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C3" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="E3" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>361</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="H3" s="7"/>
+      <c r="I3" s="7"/>
+    </row>
+    <row r="4" ht="34" spans="1:9">
+      <c r="A4" s="3" t="s">
         <v>362</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>364</v>
       </c>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-    </row>
-    <row r="3" ht="118" spans="1:9">
-      <c r="A3" s="2" t="s">
+      <c r="D4" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="E4" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
+    </row>
+    <row r="5" ht="34" spans="1:9">
+      <c r="A5" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="B5" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="H5" s="7"/>
+      <c r="I5" s="7"/>
+    </row>
+    <row r="6" ht="118" spans="1:9">
+      <c r="A6" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+    </row>
+    <row r="7" ht="118" spans="1:9">
+      <c r="A7" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+    </row>
+    <row r="8" ht="135" spans="1:9">
+      <c r="A8" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>361</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
-    </row>
-    <row r="4" ht="34" spans="1:9">
-      <c r="A4" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-    </row>
-    <row r="5" ht="34" spans="1:9">
-      <c r="A5" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
-    </row>
-    <row r="6" ht="118" spans="1:9">
-      <c r="A6" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="F6" s="2" t="s">
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+    </row>
+    <row r="9" ht="34" spans="1:9">
+      <c r="A9" s="3" t="s">
         <v>379</v>
       </c>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-    </row>
-    <row r="7" ht="118" spans="1:9">
-      <c r="A7" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>380</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
-    </row>
-    <row r="8" ht="135" spans="1:9">
-      <c r="A8" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
-    </row>
-    <row r="9" ht="34" spans="1:9">
-      <c r="A9" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
+      <c r="C9" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -6794,312 +6963,312 @@
   <dimension ref="A1:I14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="1" width="7.546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="18.75" style="2" customWidth="1"/>
-    <col min="3" max="3" width="26.4296875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="19.78125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="8.84375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="18.359375" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="2"/>
+    <col min="1" max="1" width="7.546875" style="5" customWidth="1"/>
+    <col min="2" max="2" width="18.75" style="3" customWidth="1"/>
+    <col min="3" max="3" width="26.4296875" style="3" customWidth="1"/>
+    <col min="4" max="4" width="19.78125" style="3" customWidth="1"/>
+    <col min="5" max="5" width="8.84375" style="5" customWidth="1"/>
+    <col min="6" max="6" width="18.359375" style="3" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="21" customHeight="1" spans="1:9">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>356</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="F1" s="3" t="s">
+      <c r="C1" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="F1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="I1" s="5"/>
+    </row>
+    <row r="2" ht="159" customHeight="1" spans="1:9">
+      <c r="A2" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+    </row>
+    <row r="3" ht="210" customHeight="1" spans="1:9">
+      <c r="A3" s="5" t="s">
+        <v>386</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>388</v>
       </c>
-      <c r="I1" s="1"/>
-    </row>
-    <row r="2" ht="159" customHeight="1" spans="1:9">
-      <c r="A2" s="1" t="s">
+      <c r="E3" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>389</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
+    </row>
+    <row r="4" ht="226" customHeight="1" spans="1:9">
+      <c r="A4" s="5" t="s">
         <v>390</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="B4" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>391</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D4" s="3" t="s">
         <v>392</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-    </row>
-    <row r="3" ht="210" customHeight="1" spans="1:9">
-      <c r="A3" s="1" t="s">
+      <c r="E4" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>393</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="C3" s="2" t="s">
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+    </row>
+    <row r="5" ht="236" spans="1:9">
+      <c r="A5" s="5" t="s">
         <v>394</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>395</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="F3" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>396</v>
       </c>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-    </row>
-    <row r="4" ht="226" customHeight="1" spans="1:9">
-      <c r="A4" s="1" t="s">
+      <c r="D5" s="3" t="s">
         <v>397</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="C4" s="2" t="s">
+      <c r="E5" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>398</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+    </row>
+    <row r="6" ht="202" spans="1:9">
+      <c r="A6" s="5" t="s">
         <v>399</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="F4" s="2" t="s">
+      <c r="B6" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>400</v>
       </c>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-    </row>
-    <row r="5" ht="236" spans="1:9">
-      <c r="A5" s="1" t="s">
+      <c r="D6" s="3" t="s">
         <v>401</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="E6" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>402</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+    </row>
+    <row r="7" ht="236" spans="1:9">
+      <c r="A7" s="5" t="s">
         <v>403</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="B7" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>404</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="F5" s="2" t="s">
+      <c r="D7" s="3" t="s">
         <v>405</v>
       </c>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-    </row>
-    <row r="6" ht="202" spans="1:9">
-      <c r="A6" s="1" t="s">
+      <c r="E7" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>406</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="C6" s="2" t="s">
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+    </row>
+    <row r="8" ht="152" spans="1:9">
+      <c r="A8" s="5" t="s">
         <v>407</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="B8" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="F6" s="2" t="s">
+      <c r="D8" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-    </row>
-    <row r="7" ht="236" spans="1:9">
-      <c r="A7" s="1" t="s">
+      <c r="E8" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>410</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="C7" s="2" t="s">
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+    </row>
+    <row r="9" ht="185" spans="1:9">
+      <c r="A9" s="5" t="s">
         <v>411</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="B9" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="F7" s="2" t="s">
+      <c r="D9" s="3" t="s">
         <v>413</v>
       </c>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-    </row>
-    <row r="8" ht="152" spans="1:9">
-      <c r="A8" s="1" t="s">
+      <c r="E9" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="F9" s="3" t="s">
         <v>414</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="C8" s="2" t="s">
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+    </row>
+    <row r="10" ht="202" spans="1:9">
+      <c r="A10" s="5" t="s">
         <v>415</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="B10" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>416</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="F8" s="2" t="s">
+      <c r="D10" s="3" t="s">
         <v>417</v>
       </c>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-    </row>
-    <row r="9" ht="185" spans="1:9">
-      <c r="A9" s="1" t="s">
+      <c r="E10" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>418</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="C9" s="2" t="s">
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+    </row>
+    <row r="11" ht="101" spans="1:6">
+      <c r="A11" s="5" t="s">
         <v>419</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="B11" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>420</v>
       </c>
-      <c r="E9" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="F9" s="2" t="s">
+      <c r="D11" s="3" t="s">
         <v>421</v>
       </c>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-    </row>
-    <row r="10" ht="202" spans="1:9">
-      <c r="A10" s="1" t="s">
+      <c r="E11" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>422</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="C10" s="2" t="s">
+    </row>
+    <row r="12" ht="118" spans="1:6">
+      <c r="A12" s="5" t="s">
         <v>423</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="B12" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>424</v>
       </c>
-      <c r="E10" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="F10" s="2" t="s">
+      <c r="D12" s="3" t="s">
         <v>425</v>
       </c>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-    </row>
-    <row r="11" ht="101" spans="1:6">
-      <c r="A11" s="1" t="s">
+      <c r="E12" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>426</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="C11" s="2" t="s">
+    </row>
+    <row r="13" ht="51" spans="1:6">
+      <c r="A13" s="5" t="s">
         <v>427</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="B13" s="3" t="s">
         <v>428</v>
       </c>
-      <c r="E11" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="F11" s="2" t="s">
+      <c r="C13" s="3" t="s">
         <v>429</v>
       </c>
-    </row>
-    <row r="12" ht="118" spans="1:6">
-      <c r="A12" s="1" t="s">
+      <c r="D13" s="3" t="s">
         <v>430</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="C12" s="2" t="s">
+      <c r="E13" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>431</v>
       </c>
-      <c r="D12" s="2" t="s">
+    </row>
+    <row r="14" ht="34" spans="1:6">
+      <c r="A14" s="5" t="s">
         <v>432</v>
       </c>
-      <c r="E12" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="F12" s="2" t="s">
+      <c r="B14" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>433</v>
       </c>
-    </row>
-    <row r="13" ht="51" spans="1:6">
-      <c r="A13" s="1" t="s">
+      <c r="D14" s="3" t="s">
         <v>434</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="E14" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>435</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>437</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="14" ht="34" spans="1:6">
-      <c r="A14" s="1" t="s">
-        <v>439</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>441</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>442</v>
       </c>
     </row>
   </sheetData>
@@ -7109,4 +7278,181 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:M5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="4"/>
+  <cols>
+    <col min="1" max="1" width="6.640625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="21.09375" style="3" customWidth="1"/>
+    <col min="3" max="3" width="18.359375" style="3" customWidth="1"/>
+    <col min="4" max="4" width="20.8359375" style="3" customWidth="1"/>
+    <col min="5" max="5" width="28.8984375" style="3" customWidth="1"/>
+    <col min="6" max="6" width="24.4765625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="27.59375" style="3" customWidth="1"/>
+    <col min="8" max="8" width="10.6796875" style="3" customWidth="1"/>
+    <col min="9" max="9" width="18.6171875" style="3" customWidth="1"/>
+    <col min="10" max="10" width="20.953125" style="3" customWidth="1"/>
+    <col min="11" max="11" width="10.15625" style="3" customWidth="1"/>
+    <col min="12" max="12" width="14.1953125" style="3" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="34" customHeight="1" spans="1:13">
+      <c r="A1" s="4" t="s">
+        <v>436</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="H1" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+    </row>
+    <row r="2" s="2" customFormat="1" ht="43" customHeight="1" spans="1:13">
+      <c r="A2" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="3" ht="202" spans="1:13">
+      <c r="A3" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="D3" s="32" t="s">
+        <v>454</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="F3" s="32" t="s">
+        <v>456</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="H3" s="3"/>
+      <c r="K3" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="4" ht="202" spans="1:7">
+      <c r="A4" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="D4" s="32" t="s">
+        <v>460</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="F4" s="32" t="s">
+        <v>462</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="5" ht="84" spans="1:5">
+      <c r="A5" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="D5" s="32" t="s">
+        <v>467</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>468</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:M1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/Log/Magic_eraser_test_log.xlsx
+++ b/Log/Magic_eraser_test_log.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23820" windowHeight="15380" firstSheet="3" activeTab="5"/>
+    <workbookView windowWidth="20320" windowHeight="16340" firstSheet="3" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Image_selector_test" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1057" uniqueCount="469">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1094" uniqueCount="493">
   <si>
     <t>TC</t>
   </si>
@@ -1546,7 +1546,7 @@
     <t>Background flow</t>
   </si>
   <si>
-    <t>Preview Frame</t>
+    <t>Preview Frame (UI)</t>
   </si>
   <si>
     <t>- Ảnh được chọn trước đó đã được xử lý xong ở Processing flow
@@ -1554,7 +1554,137 @@
   </si>
   <si>
     <t>1. Mở màn hình Background 
-2. Quan sát sát khung preview</t>
+2. Quan sát khung preview cutout: 
++ Bo góc, tỷ lệ ảnh, không méo, không overflow 
++ Kiểm tra nút Cutout nằm đúng vị trí, icon + text đúng style 
+3. Kiểm tra các section title: 
++ font, size, alignment, spacing với các element khác 
+4. Kiểm tra section "Classics": 
++ Kích thước, bo góc, spacing (gap) đều 
++ Ảnh hiển thị đúng, không méo, không overflow 
+5. Cuộn xuống, kiểm tra section "Marketplaces" và section "Social" (các section có tác dụng resize): 
++ kích thước, bo góc, spacing (gap) đều 
++ border thể hiện đúng tỷ lệ hình ảnh sau thay đổi 
+6. Cuộn xuống cuối screen, kiểm rtra section Colors: 
++ kích thước, bo góc, spacing (gap) 
++ Màu nền background và vị trí vật thể 
+7. Kiểm tra section "Background Image": 
++ kích thước, bo góc, spacing (gap) 
++ hiển thị đúng thumnail thiết kế</t>
+  </si>
+  <si>
+    <t>- UI đúng theo thiết kế: font, maù, spacing, alignment. 
+- Preview frame hiển thị đugns, ảnh không méo, không overflow. 
+- Button Cutout đúng style và không bị tràn frame, nằm phía trên và không bị che đi bởi vật thể. 
+- Section titles đúng vị trí, font-size, spacing 
+- Tất cả các thumbnail hiển thị đúng kích thước 
+- Text lable dưới thumnail không bị crop hoặc overflow. 
+- Scroll mượt, không giật, không bị hiển thị rỗng 
+- Layout ổn định và không bị vỡ với các kích thước màn hình</t>
+  </si>
+  <si>
+    <t>RB_B_UI_02</t>
+  </si>
+  <si>
+    <t>Preview popup image selector ở section Background Image</t>
+  </si>
+  <si>
+    <t>- Ảnh được chọn trước đó đã được xử lý xong ở Processing flow 
+- Màn hình Background đã được load đầy đủ</t>
+  </si>
+  <si>
+    <t>1. Mở màn hình Background 
+2. Cuộng xuống cuối trang 
+3. chọn 1 thumnail thuộc nhóm "Background Image" 
+4. kiểm tra Popup "image selector": 
+- heading title hiển thị đúng font, font-size, spacing
+- cuộn lên xuống 
+- kích thước, bo góc, spacing của các image</t>
+  </si>
+  <si>
+    <t>- UI đúng theo thiết kế: font, màu, spacing, alignment
+- heading title đúng font, font-size, spacing so với thiết kế 
+- scroll mượt mà 
+- image đúng kích thước, bo góc, spacing, không bị over flow 
+- Layout ổn định và không bị thay đổi với các kích thước màn hình khác nhau</t>
+  </si>
+  <si>
+    <t>RB_BE_UI_ 01</t>
+  </si>
+  <si>
+    <t>Background-Edit flow</t>
+  </si>
+  <si>
+    <t>Preview popup main function</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Ở màn hình Background 
+- Ảnh đã được load thành công sau khi tách nền </t>
+  </si>
+  <si>
+    <t>1. Chọn 1 option (thumnail) ngẫu nhiên -&gt; Mở màn hình Edit background 
+2. Quan sát popup xuất hiện gồm 3 tabb: Size, Color, Image</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Popup xuất hiện ở cạnh dưới màn hình
+- Layout, spacing, boder-radious, color, của các component đúng theo thiết kế 
+- Các nút cách đều không bị đè lên nhau </t>
+  </si>
+  <si>
+    <t>RB_BE_UI_02</t>
+  </si>
+  <si>
+    <t>Preview popup Size &amp; thumnail</t>
+  </si>
+  <si>
+    <t>- Ở màn Background-Edit 
+- Ảnh đã được load thành công sau khi chọn option</t>
+  </si>
+  <si>
+    <t>1. Chọn button "Size" để mở popup chức năng resize 
+2. Quan sát popup xuất hiện, kiểm tra kích thước hình dạng của border option đặc biệt tỷ lệ 2 cạnh, Logo biểu tượng, text lable, padding, spacing,  size text lable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Hiển thị đầy đủ danh sách template 
+- Mỗi template gồm: 
++ Icon/logo đúng theo nền tảng 
++ Tên template căn giữa, không bị tràn chữ 
++ Preview frame hiển thị đúng tý lệ (chiều dài/chiều rộng) 
+- Danh sách có thể scroll ngang 1 cách mượt mà 
+- buton "V","X" hiển thi đúng vị trí 2 bên góc, đúng size và spacing so với các component khác 
+- Template được chọn thì border sẽ đổi màu sang màu đỏ, các template còn lại có border
+- Text Lable cập nhật khi chọn các template khác nhau, hiển thị đúng font, font-size, nằm ở chính giữa đúng với thiết kế </t>
+  </si>
+  <si>
+    <t>RB_BE_UI_03</t>
+  </si>
+  <si>
+    <t>Preview popup Color &amp; thumnail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Ở màn Background-Edit 
+- Ảnh đã được load thành công sau khi chọn option </t>
+  </si>
+  <si>
+    <t>1. chọn buttonn "Color" để mở popup chức năng color 
+2. Kiểm tra Popup xuất hiện, kiểm tra kích thước, hình dạng của các thumnail 
+3. chọn thumnail custom color 
+4. Kiểm tra các component trong popup custom color: thanh mode màu, grid chọn màu, Bảng màu trong Spectrum, slider và input trong Sliders, Ô màu và các thumnail màu phí dưới</t>
+  </si>
+  <si>
+    <t>- Hiển thị đầy đủ dnah sách template 
+- với 2 thumnail none và custom color hiển thị đúng icon, padding của thiết kế 
+- các thumnail màu đơn sắc hiển thị đầy đủ, đúng kích thước và spacing, khi chọn vào các thumnail đơn sắc thì thumnail được chọn có dấu "V", các thumnail còn lại thì không 
+-  các component trong popup custom color hiển thị đúng padding, spacing, font, font-size so với thiết kế. 
+- ở nhóm Slider, các thanh màu sẽ tự động thay đổi theo màu sắc mà người dùng sẽ đạt được khi kéo thả các thanh slider
+- scroll ngang mượt
+- Không bị vỡ hay thay đổi layout với các kích thước màn hình khác nhau</t>
+  </si>
+  <si>
+    <t>RB_BE_UI_04</t>
+  </si>
+  <si>
+    <t>Preview popup Image &amp; thumnail</t>
   </si>
 </sst>
 </file>
@@ -7283,16 +7413,16 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="4"/>
+  <dimension ref="A1:M10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="1" width="6.640625" style="3" customWidth="1"/>
-    <col min="2" max="2" width="21.09375" style="3" customWidth="1"/>
-    <col min="3" max="3" width="18.359375" style="3" customWidth="1"/>
+    <col min="1" max="1" width="4.6875" style="3" customWidth="1"/>
+    <col min="2" max="2" width="11.578125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="15.359375" style="3" customWidth="1"/>
     <col min="4" max="4" width="20.8359375" style="3" customWidth="1"/>
-    <col min="5" max="5" width="28.8984375" style="3" customWidth="1"/>
-    <col min="6" max="6" width="24.4765625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="27.59375" style="3" customWidth="1"/>
+    <col min="5" max="5" width="39.0625" style="3" customWidth="1"/>
+    <col min="6" max="6" width="31.8984375" style="3" customWidth="1"/>
+    <col min="7" max="7" width="22" style="3" customWidth="1"/>
     <col min="8" max="8" width="10.6796875" style="3" customWidth="1"/>
     <col min="9" max="9" width="18.6171875" style="3" customWidth="1"/>
     <col min="10" max="10" width="20.953125" style="3" customWidth="1"/>
@@ -7362,7 +7492,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="3" ht="202" spans="1:13">
+    <row r="3" ht="168" spans="1:13">
       <c r="A3" s="3" t="s">
         <v>451</v>
       </c>
@@ -7384,7 +7514,6 @@
       <c r="G3" s="3" t="s">
         <v>457</v>
       </c>
-      <c r="H3" s="3"/>
       <c r="K3" s="3" t="s">
         <v>258</v>
       </c>
@@ -7395,7 +7524,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="4" ht="202" spans="1:7">
+    <row r="4" ht="168" spans="1:13">
       <c r="A4" s="3" t="s">
         <v>458</v>
       </c>
@@ -7417,8 +7546,17 @@
       <c r="G4" s="3" t="s">
         <v>463</v>
       </c>
-    </row>
-    <row r="5" ht="84" spans="1:5">
+      <c r="K4" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="5" ht="391" customHeight="1" spans="1:13">
       <c r="A5" s="3" t="s">
         <v>464</v>
       </c>
@@ -7433,6 +7571,124 @@
       </c>
       <c r="E5" s="3" t="s">
         <v>468</v>
+      </c>
+      <c r="F5" s="32" t="s">
+        <v>469</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="K5" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="M5" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" ht="168" spans="1:13">
+      <c r="A6" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="D6" s="32" t="s">
+        <v>472</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="F6" s="32" t="s">
+        <v>474</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="7" ht="118" spans="1:6">
+      <c r="A7" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="D7" s="32" t="s">
+        <v>478</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="F7" s="32" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="8" ht="320" spans="1:6">
+      <c r="A8" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="D8" s="32" t="s">
+        <v>483</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="F8" s="32" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="9" ht="320" spans="1:6">
+      <c r="A9" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="D9" s="32" t="s">
+        <v>488</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>489</v>
+      </c>
+      <c r="F9" s="32" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="10" ht="84" spans="1:4">
+      <c r="A10" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>492</v>
+      </c>
+      <c r="D10" s="32" t="s">
+        <v>488</v>
       </c>
     </row>
   </sheetData>

--- a/Log/Magic_eraser_test_log.xlsx
+++ b/Log/Magic_eraser_test_log.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20320" windowHeight="16340" firstSheet="3" activeTab="5"/>
+    <workbookView windowWidth="25820" windowHeight="16340" firstSheet="3" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Image_selector_test" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1094" uniqueCount="493">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1112" uniqueCount="500">
   <si>
     <t>TC</t>
   </si>
@@ -1554,30 +1554,19 @@
   </si>
   <si>
     <t>1. Mở màn hình Background 
-2. Quan sát khung preview cutout: 
-+ Bo góc, tỷ lệ ảnh, không méo, không overflow 
-+ Kiểm tra nút Cutout nằm đúng vị trí, icon + text đúng style 
-3. Kiểm tra các section title: 
-+ font, size, alignment, spacing với các element khác 
-4. Kiểm tra section "Classics": 
-+ Kích thước, bo góc, spacing (gap) đều 
-+ Ảnh hiển thị đúng, không méo, không overflow 
-5. Cuộn xuống, kiểm tra section "Marketplaces" và section "Social" (các section có tác dụng resize): 
-+ kích thước, bo góc, spacing (gap) đều 
-+ border thể hiện đúng tỷ lệ hình ảnh sau thay đổi 
-6. Cuộn xuống cuối screen, kiểm rtra section Colors: 
-+ kích thước, bo góc, spacing (gap) 
-+ Màu nền background và vị trí vật thể 
-7. Kiểm tra section "Background Image": 
-+ kích thước, bo góc, spacing (gap) 
-+ hiển thị đúng thumnail thiết kế</t>
+2. Quan sát khung preview cutout
+3. Kiểm tra các section title
+4. Kiểm tra section "Classics"
+5. Cuộn xuống, kiểm tra section "Marketplaces" và section "Social" (các section có tác dụng resize)
+6. Cuộn xuống cuối screen, kiểm rtra section Colors
+7. Kiểm tra section "Background Image"</t>
   </si>
   <si>
     <t>- UI đúng theo thiết kế: font, maù, spacing, alignment. 
 - Preview frame hiển thị đugns, ảnh không méo, không overflow. 
 - Button Cutout đúng style và không bị tràn frame, nằm phía trên và không bị che đi bởi vật thể. 
 - Section titles đúng vị trí, font-size, spacing 
-- Tất cả các thumbnail hiển thị đúng kích thước 
+- Tất cả các thumbnail hiển thị đúng kích thước (đối với thumnail thuộc section "Marketplaces" &amp; "Social" thì thể hiện đúng tỷ lệ cạnh mà ảnh sẽ thay đổi sau khi chọn thumnail đó) 
 - Text lable dưới thumnail không bị crop hoặc overflow. 
 - Scroll mượt, không giật, không bị hiển thị rỗng 
 - Layout ổn định và không bị vỡ với các kích thước màn hình</t>
@@ -1597,7 +1586,7 @@
 2. Cuộng xuống cuối trang 
 3. chọn 1 thumnail thuộc nhóm "Background Image" 
 4. kiểm tra Popup "image selector": 
-- heading title hiển thị đúng font, font-size, spacing
+- quan sát heading title
 - cuộn lên xuống 
 - kích thước, bo góc, spacing của các image</t>
   </si>
@@ -1648,7 +1637,7 @@
     <t xml:space="preserve">- Hiển thị đầy đủ danh sách template 
 - Mỗi template gồm: 
 + Icon/logo đúng theo nền tảng 
-+ Tên template căn giữa, không bị tràn chữ 
++ Tên template căn giữa, không bị tràn chữ, nếu tên dài thì trình bày xuống 2 dòng (font-size thống nhất)
 + Preview frame hiển thị đúng tý lệ (chiều dài/chiều rộng) 
 - Danh sách có thể scroll ngang 1 cách mượt mà 
 - buton "V","X" hiển thi đúng vị trí 2 bên góc, đúng size và spacing so với các component khác 
@@ -1672,7 +1661,7 @@
 4. Kiểm tra các component trong popup custom color: thanh mode màu, grid chọn màu, Bảng màu trong Spectrum, slider và input trong Sliders, Ô màu và các thumnail màu phí dưới</t>
   </si>
   <si>
-    <t>- Hiển thị đầy đủ dnah sách template 
+    <t>- Hiển thị đầy đủ danh sách template 
 - với 2 thumnail none và custom color hiển thị đúng icon, padding của thiết kế 
 - các thumnail màu đơn sắc hiển thị đầy đủ, đúng kích thước và spacing, khi chọn vào các thumnail đơn sắc thì thumnail được chọn có dấu "V", các thumnail còn lại thì không 
 -  các component trong popup custom color hiển thị đúng padding, spacing, font, font-size so với thiết kế. 
@@ -1685,6 +1674,67 @@
   </si>
   <si>
     <t>Preview popup Image &amp; thumnail</t>
+  </si>
+  <si>
+    <t>1. Chọn button "Image" để mở popup chức năng chèn ảnh 
+2. Kiểm tra layout và alignment của popup, sau đó kiểm tra riêng các component trong popup: 
+2.a. kiểm tra topic lable bar
+2.b. kiểm tra thumnail bar 
+3. scroll ngang topic bar và thumnail bar 
+4. chọn topic lable và thumnail và kiểm tra hiệu ứng khi chọn của chúng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Hiển thị đầy đủ danh sách topic, thumnail 
+- với 2 thumnail None và upload image hiển thị đúng icon, pading đúng với thiết kế 
+- các thumnail hình ảnh có sẵn hiển thị đầy đủ, đúng size và spacing, giữa các nhóm thumnail thuộc các topic khác nhau  có đường kẻ chia cách chúng 
+- Topic lable hiển thị đúng font, font-size, spacing. 
+- Topic lable được chọn có font-color và underline màu đỏ
+- Thumnail được chọn có boder được tô đỏ.
+- khi chọn 1 topic lable thì scroll đến thumnail đầu tiên của nhóm thumnail thuộc topic đó.
+- scroll ngang mượt, không giật, hay nhảy cóc 
+- Layout ổn định, không bị vỡ hay ép với các kích thước màn hình khác nhau </t>
+  </si>
+  <si>
+    <t>RB_BE_F_01</t>
+  </si>
+  <si>
+    <t>Background editting flow (quá trình chỉnh sửa - edit phông nền)</t>
+  </si>
+  <si>
+    <t>- Ở màn hình Background 
+- Ảnh đã được xử lý tách nền thành công</t>
+  </si>
+  <si>
+    <t>1. Chọn một thumbnail background bất kỳ để áp dụng. 
+2. Di chuyển vị trí vật thể trên ảnh 
+3. Mở công cụ Resize, thao tác thử các lựa chọn resize.
+4. Mở công cụ Color, lần lượt thao tác các chức năng:
++ Chọn màu đơn có sẵn
++ Chọn màu tùy chỉnh (grid, spectrum)
++ Điều chỉnh sắc độ hoặc nhập mã màu (RGB/Hex)
++ Trích xuất màu từ hình ảnh
++ Thêm màu mới và chọn lại màu vừa thêm
+5. Mở công cụ Image, thực hiện các thao tác:
++ Upload ảnh từ thiết bị
++ Chọn template (topic label)
++ Chọn nhiều thumbnail khác nhau
+6. Thực hiện thao tác Undo/Redo hoặc Reset chỉnh sửa.
+7. Nhấn Save để lưu hình ảnh.</t>
+  </si>
+  <si>
+    <t>- Mở màn hình Background-Edit: 
++ button undo và redo bị vô hiệu khi không có thao tác chỉnh sửa nào đã được thực hiện 
++ layer vật thể được tách nền được chọn (bo khung đỏ)
++ popup chức năng chính bao gồm 3 button chức năng lớn: Size, Color, Image
+- Khi vật thể dịch chuyển theo thao tác người dùng, Khi thả ra thì hệ thống ghi nhận 1 thao tác chỉnh sửa 
+- Các pop-up chức năng hiển thị đúng với lựa chọn (Size, Color, Image) 
+- Các chức năng con hoạt động đúng: 
++ Size: kích thước ảnh thay đổi theo lựa chọn, phần text lable cập nhật đúng theo kích thước được chọn 
++ Color: Các template color cho sẵn và template trong suốt hoạt động đúng; Custom color hoặt động đúng, có thể lưu màu mới custom, ảnh được cập nhật màu theo màu đang custom. 
++ Image: topic bar scoll mượt mà, khi 1 topic được chọn thì chuyển sang màu đỏ và thumnail bar được scroll đến thumnail đầu tiên thuộc topic đó; option chọn được viền đỏ và background preview được cập nhật 
+- Undo/redo và reset hoạt động đúng logic 
+- Có thể phóng to, thu nhỏ và xoay vật thể (layer)
+- Ảnh được lưu vào máy đúng với kết quả chỉnh sửa và chuyển sang màn hình saved</t>
   </si>
 </sst>
 </file>
@@ -7413,16 +7463,16 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="4.6875" style="3" customWidth="1"/>
     <col min="2" max="2" width="11.578125" style="3" customWidth="1"/>
     <col min="3" max="3" width="15.359375" style="3" customWidth="1"/>
-    <col min="4" max="4" width="20.8359375" style="3" customWidth="1"/>
-    <col min="5" max="5" width="39.0625" style="3" customWidth="1"/>
-    <col min="6" max="6" width="31.8984375" style="3" customWidth="1"/>
-    <col min="7" max="7" width="22" style="3" customWidth="1"/>
+    <col min="4" max="4" width="19.3984375" style="3" customWidth="1"/>
+    <col min="5" max="5" width="35.15625" style="3" customWidth="1"/>
+    <col min="6" max="6" width="51.296875" style="3" customWidth="1"/>
+    <col min="7" max="7" width="17.96875" style="3" customWidth="1"/>
     <col min="8" max="8" width="10.6796875" style="3" customWidth="1"/>
     <col min="9" max="9" width="18.6171875" style="3" customWidth="1"/>
     <col min="10" max="10" width="20.953125" style="3" customWidth="1"/>
@@ -7492,7 +7542,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="3" ht="168" spans="1:13">
+    <row r="3" ht="152" spans="1:13">
       <c r="A3" s="3" t="s">
         <v>451</v>
       </c>
@@ -7524,7 +7574,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="4" ht="168" spans="1:13">
+    <row r="4" ht="118" spans="1:13">
       <c r="A4" s="3" t="s">
         <v>458</v>
       </c>
@@ -7556,7 +7606,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="5" ht="391" customHeight="1" spans="1:13">
+    <row r="5" ht="193" customHeight="1" spans="1:13">
       <c r="A5" s="3" t="s">
         <v>464</v>
       </c>
@@ -7588,7 +7638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" ht="168" spans="1:13">
+    <row r="6" ht="152" spans="1:13">
       <c r="A6" s="3" t="s">
         <v>470</v>
       </c>
@@ -7617,7 +7667,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="7" ht="118" spans="1:6">
+    <row r="7" ht="84" spans="1:6">
       <c r="A7" s="3" t="s">
         <v>475</v>
       </c>
@@ -7637,7 +7687,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="8" ht="320" spans="1:6">
+    <row r="8" ht="224" customHeight="1" spans="1:13">
       <c r="A8" s="3" t="s">
         <v>481</v>
       </c>
@@ -7656,8 +7706,17 @@
       <c r="F8" s="32" t="s">
         <v>485</v>
       </c>
-    </row>
-    <row r="9" ht="320" spans="1:6">
+      <c r="K8" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="9" ht="219" spans="1:6">
       <c r="A9" s="3" t="s">
         <v>486</v>
       </c>
@@ -7677,7 +7736,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="10" ht="84" spans="1:4">
+    <row r="10" ht="236" spans="1:13">
       <c r="A10" s="3" t="s">
         <v>491</v>
       </c>
@@ -7689,6 +7748,53 @@
       </c>
       <c r="D10" s="32" t="s">
         <v>488</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>493</v>
+      </c>
+      <c r="F10" s="32" t="s">
+        <v>494</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="11" ht="409" customHeight="1" spans="1:13">
+      <c r="A11" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="D11" s="32" t="s">
+        <v>497</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="F11" s="32" t="s">
+        <v>499</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
   </sheetData>

--- a/Log/Magic_eraser_test_log.xlsx
+++ b/Log/Magic_eraser_test_log.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25820" windowHeight="16340" firstSheet="3" activeTab="5"/>
+    <workbookView windowWidth="27320" windowHeight="10920" firstSheet="3" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Image_selector_test" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1112" uniqueCount="500">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1115" uniqueCount="500">
   <si>
     <t>TC</t>
   </si>
@@ -1437,7 +1437,7 @@
     <t>Mã TC của Connect with us: CWU</t>
   </si>
   <si>
-    <t>Test cases: module Processing  (ID: PR)</t>
+    <t>Test cases: module Remove-Background  (ID: RB)</t>
   </si>
   <si>
     <t>Android</t>
@@ -1631,7 +1631,7 @@
   </si>
   <si>
     <t>1. Chọn button "Size" để mở popup chức năng resize 
-2. Quan sát popup xuất hiện, kiểm tra kích thước hình dạng của border option đặc biệt tỷ lệ 2 cạnh, Logo biểu tượng, text lable, padding, spacing,  size text lable</t>
+2. Quan sát popup xuất hiện, kiểm tra UI</t>
   </si>
   <si>
     <t xml:space="preserve">- Hiển thị đầy đủ danh sách template 
@@ -1642,6 +1642,7 @@
 - Danh sách có thể scroll ngang 1 cách mượt mà 
 - buton "V","X" hiển thi đúng vị trí 2 bên góc, đúng size và spacing so với các component khác 
 - Template được chọn thì border sẽ đổi màu sang màu đỏ, các template còn lại có border
+- Template không đè lên và che đi phần preview hình ảnh
 - Text Lable cập nhật khi chọn các template khác nhau, hiển thị đúng font, font-size, nằm ở chính giữa đúng với thiết kế </t>
   </si>
   <si>
@@ -7667,7 +7668,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="7" ht="84" spans="1:6">
+    <row r="7" ht="84" spans="1:13">
       <c r="A7" s="3" t="s">
         <v>475</v>
       </c>
@@ -7686,8 +7687,17 @@
       <c r="F7" s="32" t="s">
         <v>480</v>
       </c>
-    </row>
-    <row r="8" ht="224" customHeight="1" spans="1:13">
+      <c r="K7" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="8" ht="245" customHeight="1" spans="1:13">
       <c r="A8" s="3" t="s">
         <v>481</v>
       </c>

--- a/Log/Magic_eraser_test_log.xlsx
+++ b/Log/Magic_eraser_test_log.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27320" windowHeight="10920" firstSheet="3" activeTab="5"/>
+    <workbookView windowHeight="15700" firstSheet="3" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Image_selector_test" sheetId="1" r:id="rId1"/>
@@ -1214,7 +1214,7 @@
 6. chọn button Less</t>
   </si>
   <si>
-    <t>Chuyển tiếp mượt mà giữa các màn: màn giới thiệu chức năng, màn thăm dò, màn tiếp thị, màn Home. Nhấn nút More sẽ hiển thị toàn bộ các button chức năng, nút Lesss ẩn bớt các chức năng</t>
+    <t>Chuyển tiếp mượt mà giữa các màn: màn "fearture introduction" -&gt; màn thăm dò -&gt; màn "Payment" -&gt; màn "Home". Nhấn nút More sẽ hiển thị toàn bộ các button chức năng, nút Lesss ẩn bớt các chức năng</t>
   </si>
   <si>
     <t>BE</t>
@@ -7177,7 +7177,7 @@
       </c>
       <c r="I1" s="5"/>
     </row>
-    <row r="2" ht="159" customHeight="1" spans="1:9">
+    <row r="2" ht="182" customHeight="1" spans="1:9">
       <c r="A2" s="5" t="s">
         <v>382</v>
       </c>
